--- a/VIENTO/001_SISMO_VIENTO_SALVADOR_R4.67.xlsx
+++ b/VIENTO/001_SISMO_VIENTO_SALVADOR_R4.67.xlsx
@@ -15479,7 +15479,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:K230"/>
+  <dimension ref="B2:K235"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -15641,1188 +15641,1136 @@
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cpi en celdas amarillas: valores editables, confirmar con la NTDV-97. Abertura a barlovento: +0.75 (el 1.45 de la cubierta -Z de la hoja original = 0.70 + 0.75); a sotavento o lateral: Cpe de esa cara.</t>
+          <t xml:space="preserve">NTDV-97, 4.4 Presiones interiores (paredes con aberturas &gt; 30% de su superficie): actuan uniformemente en el interior de paredes y techos, con la ecuacion 4.1 y los factores siguientes.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="34.8" customHeight="1">
+    <row r="24" ht="20.25" customHeight="1">
       <c r="B24" s="72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caso</t>
+          <t xml:space="preserve">Aberturas principalmente en</t>
         </is>
       </c>
-      <c r="C24" s="77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eje 3 abierto respecto al viento</t>
-        </is>
-      </c>
+      <c r="C24" s="27"/>
       <c r="D24" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">Cpi</t>
         </is>
       </c>
-      <c r="E24" s="27" t="inlineStr">
+    </row>
+    <row r="25">
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la cara de barlovento</t>
+        </is>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="74">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la cara de sotavento</t>
+        </is>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="74">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">las caras paralelas al viento</t>
+        </is>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="D27" s="74">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">las 4 caras (uniformes)</t>
+        </is>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="74">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="30" ht="34.8" customHeight="1">
+      <c r="B30" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Caso</t>
+        </is>
+      </c>
+      <c r="C30" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eje 3 abierto respecto al viento</t>
+        </is>
+      </c>
+      <c r="D30" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cpi</t>
+        </is>
+      </c>
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">Pi (kg/m2)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="16" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Viento X</t>
         </is>
       </c>
-      <c r="C25" s="74" t="inlineStr">
+      <c r="C31" s="74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lateral</t>
+          <t xml:space="preserve">Paralela</t>
         </is>
       </c>
-      <c r="D25" s="36">
-        <f>D16</f>
-        <v>-0.7</v>
-      </c>
-      <c r="E25" s="75">
-        <f>$E$9*D25</f>
-        <v>-34.0066119355783</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="16" t="inlineStr">
+      <c r="D31" s="36">
+        <f>D27</f>
+        <v>-0.5</v>
+      </c>
+      <c r="E31" s="75">
+        <f>$E$9*D31</f>
+        <v>-24.2904370968416</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Viento -X</t>
         </is>
       </c>
-      <c r="C26" s="74" t="inlineStr">
+      <c r="C32" s="74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lateral</t>
+          <t xml:space="preserve">Paralela</t>
         </is>
       </c>
-      <c r="D26" s="36">
-        <f>D16</f>
-        <v>-0.7</v>
-      </c>
-      <c r="E26" s="75">
-        <f>$E$9*D26</f>
-        <v>-34.0066119355783</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="16" t="inlineStr">
+      <c r="D32" s="36">
+        <f>D27</f>
+        <v>-0.5</v>
+      </c>
+      <c r="E32" s="75">
+        <f>$E$9*D32</f>
+        <v>-24.2904370968416</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Viento Z</t>
         </is>
       </c>
-      <c r="C27" s="74" t="inlineStr">
+      <c r="C33" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">Sotavento</t>
         </is>
       </c>
-      <c r="D27" s="36">
-        <f>D15</f>
-        <v>-0.5</v>
-      </c>
-      <c r="E27" s="75">
-        <f>$E$9*D27</f>
-        <v>-24.2904370968416</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="16" t="inlineStr">
+      <c r="D33" s="36">
+        <f>D26</f>
+        <v>-0.6</v>
+      </c>
+      <c r="E33" s="75">
+        <f>$E$9*D33</f>
+        <v>-29.1485245162099</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Viento -Z</t>
         </is>
       </c>
-      <c r="C28" s="74" t="inlineStr">
+      <c r="C34" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">Barlovento</t>
         </is>
       </c>
-      <c r="D28" s="36">
+      <c r="D34" s="36">
+        <f>D25</f>
         <v>0.75</v>
       </c>
-      <c r="E28" s="75">
-        <f>$E$9*D28</f>
+      <c r="E34" s="75">
+        <f>$E$9*D34</f>
         <v>36.4356556452624</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="1" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">4. COEFICIENTES Y PRESIONES TOTALES POR SUPERFICIE (Cpe - Cpi)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="34.8" customHeight="1">
-      <c r="B33" s="72" t="inlineStr">
+    <row r="39" ht="34.8" customHeight="1">
+      <c r="B39" s="72" t="inlineStr">
         <is>
           <t xml:space="preserve">Superficie</t>
         </is>
       </c>
-      <c r="C33" s="27"/>
-      <c r="D33" s="77" t="inlineStr">
+      <c r="C39" s="27"/>
+      <c r="D39" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Viento X
 Cneto</t>
         </is>
       </c>
-      <c r="E33" s="77" t="inlineStr">
+      <c r="E39" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Viento X
 P (kg/m2)</t>
         </is>
       </c>
-      <c r="F33" s="77" t="inlineStr">
+      <c r="F39" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Viento -X
 Cneto</t>
         </is>
       </c>
-      <c r="G33" s="77" t="inlineStr">
+      <c r="G39" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Viento -X
 P (kg/m2)</t>
         </is>
       </c>
-      <c r="H33" s="77" t="inlineStr">
+      <c r="H39" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Viento Z
 Cneto</t>
         </is>
       </c>
-      <c r="I33" s="77" t="inlineStr">
+      <c r="I39" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Viento Z
 P (kg/m2)</t>
         </is>
       </c>
-      <c r="J33" s="77" t="inlineStr">
+      <c r="J39" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Viento -Z
 Cneto</t>
         </is>
       </c>
-      <c r="K33" s="77" t="inlineStr">
+      <c r="K39" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Viento -Z
 P (kg/m2)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="16" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Pared de barlovento</t>
         </is>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="74">
-        <f>D14-D25</f>
-        <v>1.5</v>
-      </c>
-      <c r="E34" s="75">
-        <f>$E$9*D34</f>
-        <v>72.8713112905249</v>
-      </c>
-      <c r="F34" s="74">
-        <f>D14-D26</f>
-        <v>1.5</v>
-      </c>
-      <c r="G34" s="75">
-        <f>$E$9*F34</f>
-        <v>72.8713112905249</v>
-      </c>
-      <c r="H34" s="74">
-        <f>D14-D27</f>
+      <c r="C40" s="16"/>
+      <c r="D40" s="74">
+        <f>D14-D31</f>
         <v>1.3</v>
       </c>
-      <c r="I34" s="75">
-        <f>$E$9*H34</f>
+      <c r="E40" s="75">
+        <f>$E$9*D40</f>
         <v>63.1551364517882</v>
       </c>
-      <c r="J34" s="74" t="inlineStr">
+      <c r="F40" s="74">
+        <f>D14-D32</f>
+        <v>1.3</v>
+      </c>
+      <c r="G40" s="75">
+        <f>$E$9*F40</f>
+        <v>63.1551364517882</v>
+      </c>
+      <c r="H40" s="74">
+        <f>D14-D33</f>
+        <v>1.4</v>
+      </c>
+      <c r="I40" s="75">
+        <f>$E$9*H40</f>
+        <v>68.0132238711565</v>
+      </c>
+      <c r="J40" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">abierto</t>
         </is>
       </c>
-      <c r="K34" s="75" t="inlineStr">
+      <c r="K40" s="75" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="16" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Pared de sotavento</t>
         </is>
       </c>
-      <c r="C35" s="16"/>
-      <c r="D35" s="74">
-        <f>D15-D25</f>
-        <v>0.2</v>
-      </c>
-      <c r="E35" s="75">
-        <f>$E$9*D35</f>
-        <v>9.71617483873665</v>
-      </c>
-      <c r="F35" s="74">
-        <f>D15-D26</f>
-        <v>0.2</v>
-      </c>
-      <c r="G35" s="75">
-        <f>$E$9*F35</f>
-        <v>9.71617483873665</v>
-      </c>
-      <c r="H35" s="74" t="inlineStr">
+      <c r="C41" s="16"/>
+      <c r="D41" s="74">
+        <f>D15-D31</f>
+        <v>0.0</v>
+      </c>
+      <c r="E41" s="75">
+        <f>$E$9*D41</f>
+        <v>0.0</v>
+      </c>
+      <c r="F41" s="74">
+        <f>D15-D32</f>
+        <v>0.0</v>
+      </c>
+      <c r="G41" s="75">
+        <f>$E$9*F41</f>
+        <v>0.0</v>
+      </c>
+      <c r="H41" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">abierto</t>
         </is>
       </c>
-      <c r="I35" s="75" t="inlineStr">
+      <c r="I41" s="75" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="J35" s="74">
-        <f>D15-D28</f>
+      <c r="J41" s="74">
+        <f>D15-D34</f>
         <v>-1.25</v>
       </c>
-      <c r="K35" s="75">
-        <f>$E$9*J35</f>
+      <c r="K41" s="75">
+        <f>$E$9*J41</f>
         <v>-60.726092742104</v>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="16" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Paredes laterales</t>
         </is>
       </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="74">
-        <f>D16-D25</f>
-        <v>0.0</v>
-      </c>
-      <c r="E36" s="75">
-        <f>$E$9*D36</f>
-        <v>0.0</v>
-      </c>
-      <c r="F36" s="74">
-        <f>D16-D26</f>
-        <v>0.0</v>
-      </c>
-      <c r="G36" s="75">
-        <f>$E$9*F36</f>
-        <v>0.0</v>
-      </c>
-      <c r="H36" s="74">
-        <f>D16-D27</f>
+      <c r="C42" s="16"/>
+      <c r="D42" s="74">
+        <f>D16-D31</f>
         <v>-0.2</v>
       </c>
-      <c r="I36" s="75">
-        <f>$E$9*H36</f>
+      <c r="E42" s="75">
+        <f>$E$9*D42</f>
         <v>-9.71617483873665</v>
       </c>
-      <c r="J36" s="74">
-        <f>D16-D28</f>
+      <c r="F42" s="74">
+        <f>D16-D32</f>
+        <v>-0.2</v>
+      </c>
+      <c r="G42" s="75">
+        <f>$E$9*F42</f>
+        <v>-9.71617483873665</v>
+      </c>
+      <c r="H42" s="74">
+        <f>D16-D33</f>
+        <v>-0.1</v>
+      </c>
+      <c r="I42" s="75">
+        <f>$E$9*H42</f>
+        <v>-4.85808741936832</v>
+      </c>
+      <c r="J42" s="74">
+        <f>D16-D34</f>
         <v>-1.45</v>
       </c>
-      <c r="K36" s="75">
-        <f>$E$9*J36</f>
+      <c r="K42" s="75">
+        <f>$E$9*J42</f>
         <v>-70.4422675808407</v>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="16" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Techo inclinado (q&lt;30°)</t>
         </is>
       </c>
-      <c r="C37" s="16"/>
-      <c r="D37" s="74">
-        <f>D17-D25</f>
-        <v>0.0</v>
-      </c>
-      <c r="E37" s="75">
-        <f>$E$9*D37</f>
-        <v>0.0</v>
-      </c>
-      <c r="F37" s="74">
-        <f>D17-D26</f>
-        <v>0.0</v>
-      </c>
-      <c r="G37" s="75">
-        <f>$E$9*F37</f>
-        <v>0.0</v>
-      </c>
-      <c r="H37" s="74">
-        <f>D17-D27</f>
+      <c r="C43" s="16"/>
+      <c r="D43" s="74">
+        <f>D17-D31</f>
         <v>-0.2</v>
       </c>
-      <c r="I37" s="75">
-        <f>$E$9*H37</f>
+      <c r="E43" s="75">
+        <f>$E$9*D43</f>
         <v>-9.71617483873665</v>
       </c>
-      <c r="J37" s="74">
-        <f>D17-D28</f>
+      <c r="F43" s="74">
+        <f>D17-D32</f>
+        <v>-0.2</v>
+      </c>
+      <c r="G43" s="75">
+        <f>$E$9*F43</f>
+        <v>-9.71617483873665</v>
+      </c>
+      <c r="H43" s="74">
+        <f>D17-D33</f>
+        <v>-0.1</v>
+      </c>
+      <c r="I43" s="75">
+        <f>$E$9*H43</f>
+        <v>-4.85808741936832</v>
+      </c>
+      <c r="J43" s="74">
+        <f>D17-D34</f>
         <v>-1.45</v>
       </c>
-      <c r="K37" s="75">
-        <f>$E$9*J37</f>
+      <c r="K43" s="75">
+        <f>$E$9*J43</f>
         <v>-70.4422675808407</v>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="1" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">5. PRESIONES DISTRIBUIDAS EN ELEMENTOS ESTRUCTURALES (kg/cm)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
+    <row r="47">
+      <c r="B47" t="inlineStr">
         <is>
           <t xml:space="preserve">Externa = Pe x franja / 100;  Interna = -Pi x franja / 100;  Total = externa + interna. Elementos y franjas ligados a la hoja original. Eje 3 abierto: sin elementos.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="B44" s="81" t="inlineStr">
+    <row r="49" ht="24" customHeight="1">
+      <c r="B49" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">VIENTO EN DIRECCION X:</t>
         </is>
       </c>
-      <c r="C44" s="81"/>
-      <c r="D44" s="81"/>
-      <c r="E44" s="81"/>
-      <c r="F44" s="81"/>
-    </row>
-    <row r="46">
-      <c r="B46" s="78" t="inlineStr">
+      <c r="C49" s="81"/>
+      <c r="D49" s="81"/>
+      <c r="E49" s="81"/>
+      <c r="F49" s="81"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">MURO A EN BARLOVENTO   (Cpe barlovento)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="34.8" customHeight="1">
-      <c r="B47" s="122" t="inlineStr">
+    <row r="52" ht="34.8" customHeight="1">
+      <c r="B52" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="C47" s="77" t="inlineStr">
+      <c r="C52" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="D47" s="77" t="inlineStr">
+      <c r="D52" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd externa (kg/cm)</t>
         </is>
       </c>
-      <c r="E47" s="77" t="inlineStr">
+      <c r="E52" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="F47" s="77" t="inlineStr">
+      <c r="F52" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="123" t="str">
+    <row r="53">
+      <c r="B53" s="123" t="str">
         <f>'VIENTO NTDV-97'!B112</f>
         <v>LA-1</v>
       </c>
-      <c r="C48" s="124">
+      <c r="C53" s="124">
         <f>'VIENTO NTDV-97'!C112</f>
         <v>0.9</v>
       </c>
-      <c r="D48" s="80">
-        <f>$E$14*C48/100</f>
+      <c r="D53" s="80">
+        <f>$E$14*C53/100</f>
         <v>0.349782294194519</v>
       </c>
-      <c r="E48" s="80">
-        <f>-$E$25*C48/100</f>
-        <v>0.306059507420204</v>
-      </c>
-      <c r="F48" s="125">
-        <f>D48+E48</f>
-        <v>0.655841801614724</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="123" t="str">
+      <c r="E53" s="80">
+        <f>-$E$31*C53/100</f>
+        <v>0.218613933871575</v>
+      </c>
+      <c r="F53" s="125">
+        <f>D53+E53</f>
+        <v>0.568396228066094</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="123" t="str">
         <f>'VIENTO NTDV-97'!B113</f>
         <v>LA-2 a 7</v>
       </c>
-      <c r="C49" s="124">
+      <c r="C54" s="124">
         <f>'VIENTO NTDV-97'!C113</f>
         <v>1.2</v>
       </c>
-      <c r="D49" s="80">
-        <f>$E$14*C49/100</f>
+      <c r="D54" s="80">
+        <f>$E$14*C54/100</f>
         <v>0.466376392259359</v>
       </c>
-      <c r="E49" s="80">
-        <f>-$E$25*C49/100</f>
-        <v>0.408079343226939</v>
-      </c>
-      <c r="F49" s="125">
-        <f>D49+E49</f>
-        <v>0.874455735486298</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="123" t="str">
+      <c r="E54" s="80">
+        <f>-$E$31*C54/100</f>
+        <v>0.291485245162099</v>
+      </c>
+      <c r="F54" s="125">
+        <f>D54+E54</f>
+        <v>0.757861637421459</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="123" t="str">
         <f>'VIENTO NTDV-97'!B114</f>
         <v>LA-8 (1-2)</v>
       </c>
-      <c r="C50" s="124">
+      <c r="C55" s="124">
         <f>'VIENTO NTDV-97'!C114</f>
         <v>1.185315</v>
       </c>
-      <c r="D50" s="80">
-        <f>$E$14*C50/100</f>
+      <c r="D55" s="80">
+        <f>$E$14*C55/100</f>
         <v>0.460669111159085</v>
       </c>
-      <c r="E50" s="80">
-        <f>-$E$25*C50/100</f>
-        <v>0.403085472264199</v>
-      </c>
-      <c r="F50" s="125">
-        <f>D50+E50</f>
-        <v>0.863754583423285</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="123" t="str">
+      <c r="E55" s="80">
+        <f>-$E$31*C55/100</f>
+        <v>0.287918194474428</v>
+      </c>
+      <c r="F55" s="125">
+        <f>D55+E55</f>
+        <v>0.748587305633513</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="123" t="str">
         <f>'VIENTO NTDV-97'!B115</f>
         <v>LA-8 (2-3)</v>
       </c>
-      <c r="C51" s="124">
+      <c r="C56" s="124">
         <f>'VIENTO NTDV-97'!C115</f>
         <v>0.97782</v>
       </c>
-      <c r="D51" s="80">
-        <f>$E$14*C51/100</f>
+      <c r="D56" s="80">
+        <f>$E$14*C56/100</f>
         <v>0.380026803232539</v>
       </c>
-      <c r="E51" s="80">
-        <f>-$E$25*C51/100</f>
-        <v>0.332523452828471</v>
-      </c>
-      <c r="F51" s="125">
-        <f>D51+E51</f>
-        <v>0.71255025606101</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="123" t="str">
+      <c r="E56" s="80">
+        <f>-$E$31*C56/100</f>
+        <v>0.237516752020337</v>
+      </c>
+      <c r="F56" s="125">
+        <f>D56+E56</f>
+        <v>0.617543555252876</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="123" t="str">
         <f>'VIENTO NTDV-97'!B116</f>
         <v>VA-1 sup.</v>
       </c>
-      <c r="C52" s="124">
+      <c r="C57" s="124">
         <f>'VIENTO NTDV-97'!C116</f>
         <v>0.585315</v>
       </c>
-      <c r="D52" s="80">
-        <f>$E$14*C52/100</f>
+      <c r="D57" s="80">
+        <f>$E$14*C57/100</f>
         <v>0.227480915029406</v>
       </c>
-      <c r="E52" s="80">
-        <f>-$E$25*C52/100</f>
-        <v>0.19904580065073</v>
-      </c>
-      <c r="F52" s="125">
-        <f>D52+E52</f>
-        <v>0.426526715680136</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="123" t="str">
+      <c r="E57" s="80">
+        <f>-$E$31*C57/100</f>
+        <v>0.142175571893379</v>
+      </c>
+      <c r="F57" s="125">
+        <f>D57+E57</f>
+        <v>0.369656486922784</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="123" t="str">
         <f>'VIENTO NTDV-97'!B117</f>
         <v>VA-2 sup.</v>
       </c>
-      <c r="C53" s="124">
+      <c r="C58" s="124">
         <f>'VIENTO NTDV-97'!C117</f>
         <v>0.37782</v>
       </c>
-      <c r="D53" s="80">
-        <f>$E$14*C53/100</f>
+      <c r="D58" s="80">
+        <f>$E$14*C58/100</f>
         <v>0.146838607102859</v>
       </c>
-      <c r="E53" s="80">
-        <f>-$E$25*C53/100</f>
-        <v>0.128483781215002</v>
-      </c>
-      <c r="F53" s="125">
-        <f>D53+E53</f>
-        <v>0.275322388317861</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="78" t="inlineStr">
+      <c r="E58" s="80">
+        <f>-$E$31*C58/100</f>
+        <v>0.091774129439287</v>
+      </c>
+      <c r="F58" s="125">
+        <f>D58+E58</f>
+        <v>0.238612736542146</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">MURO B EN SOTAVENTO   (Cpe sotavento)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="34.8" customHeight="1">
-      <c r="B56" s="122" t="inlineStr">
+    <row r="61" ht="34.8" customHeight="1">
+      <c r="B61" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="C56" s="77" t="inlineStr">
+      <c r="C61" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="D56" s="77" t="inlineStr">
+      <c r="D61" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd externa (kg/cm)</t>
         </is>
       </c>
-      <c r="E56" s="77" t="inlineStr">
+      <c r="E61" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="F56" s="77" t="inlineStr">
+      <c r="F61" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="123" t="str">
+    <row r="62">
+      <c r="B62" s="123" t="str">
         <f>'VIENTO NTDV-97'!F112</f>
         <v>LB-1</v>
       </c>
-      <c r="C57" s="124">
+      <c r="C62" s="124">
         <f>'VIENTO NTDV-97'!G112</f>
         <v>0.9</v>
       </c>
-      <c r="D57" s="80">
-        <f>$E$15*C57/100</f>
+      <c r="D62" s="80">
+        <f>$E$15*C62/100</f>
         <v>-0.218613933871575</v>
       </c>
-      <c r="E57" s="80">
-        <f>-$E$25*C57/100</f>
-        <v>0.306059507420204</v>
-      </c>
-      <c r="F57" s="125">
-        <f>D57+E57</f>
-        <v>0.0874455735486298</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="123" t="str">
+      <c r="E62" s="80">
+        <f>-$E$31*C62/100</f>
+        <v>0.218613933871575</v>
+      </c>
+      <c r="F62" s="125">
+        <f>D62+E62</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="123" t="str">
         <f>'VIENTO NTDV-97'!F113</f>
         <v>LB-2 a 7</v>
       </c>
-      <c r="C58" s="124">
+      <c r="C63" s="124">
         <f>'VIENTO NTDV-97'!G113</f>
         <v>1.2</v>
       </c>
-      <c r="D58" s="80">
-        <f>$E$15*C58/100</f>
+      <c r="D63" s="80">
+        <f>$E$15*C63/100</f>
         <v>-0.291485245162099</v>
       </c>
-      <c r="E58" s="80">
-        <f>-$E$25*C58/100</f>
-        <v>0.408079343226939</v>
-      </c>
-      <c r="F58" s="125">
-        <f>D58+E58</f>
-        <v>0.11659409806484</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="123" t="str">
+      <c r="E63" s="80">
+        <f>-$E$31*C63/100</f>
+        <v>0.291485245162099</v>
+      </c>
+      <c r="F63" s="125">
+        <f>D63+E63</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="123" t="str">
         <f>'VIENTO NTDV-97'!F114</f>
         <v>LB-8 (1-2)</v>
       </c>
-      <c r="C59" s="124">
+      <c r="C64" s="124">
         <f>'VIENTO NTDV-97'!G114</f>
         <v>1.185315</v>
       </c>
-      <c r="D59" s="80">
-        <f>$E$15*C59/100</f>
+      <c r="D64" s="80">
+        <f>$E$15*C64/100</f>
         <v>-0.287918194474428</v>
       </c>
-      <c r="E59" s="80">
-        <f>-$E$25*C59/100</f>
-        <v>0.403085472264199</v>
-      </c>
-      <c r="F59" s="125">
-        <f>D59+E59</f>
-        <v>0.115167277789771</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="123" t="str">
+      <c r="E64" s="80">
+        <f>-$E$31*C64/100</f>
+        <v>0.287918194474428</v>
+      </c>
+      <c r="F64" s="125">
+        <f>D64+E64</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="123" t="str">
         <f>'VIENTO NTDV-97'!F115</f>
         <v>LB-8 (2-3)</v>
       </c>
-      <c r="C60" s="124">
+      <c r="C65" s="124">
         <f>'VIENTO NTDV-97'!G115</f>
         <v>0.97782</v>
       </c>
-      <c r="D60" s="80">
-        <f>$E$15*C60/100</f>
+      <c r="D65" s="80">
+        <f>$E$15*C65/100</f>
         <v>-0.237516752020337</v>
       </c>
-      <c r="E60" s="80">
-        <f>-$E$25*C60/100</f>
-        <v>0.332523452828471</v>
-      </c>
-      <c r="F60" s="125">
-        <f>D60+E60</f>
-        <v>0.0950067008081347</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="123" t="str">
+      <c r="E65" s="80">
+        <f>-$E$31*C65/100</f>
+        <v>0.237516752020337</v>
+      </c>
+      <c r="F65" s="125">
+        <f>D65+E65</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="123" t="str">
         <f>'VIENTO NTDV-97'!F116</f>
         <v>VB-1 sup.</v>
       </c>
-      <c r="C61" s="124">
+      <c r="C66" s="124">
         <f>'VIENTO NTDV-97'!G116</f>
         <v>0.585315</v>
       </c>
-      <c r="D61" s="80">
-        <f>$E$15*C61/100</f>
+      <c r="D66" s="80">
+        <f>$E$15*C66/100</f>
         <v>-0.142175571893379</v>
       </c>
-      <c r="E61" s="80">
-        <f>-$E$25*C61/100</f>
-        <v>0.19904580065073</v>
-      </c>
-      <c r="F61" s="125">
-        <f>D61+E61</f>
-        <v>0.0568702287573514</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="123" t="str">
+      <c r="E66" s="80">
+        <f>-$E$31*C66/100</f>
+        <v>0.142175571893379</v>
+      </c>
+      <c r="F66" s="125">
+        <f>D66+E66</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="123" t="str">
         <f>'VIENTO NTDV-97'!F117</f>
         <v>VB-2 sup.</v>
       </c>
-      <c r="C62" s="124">
+      <c r="C67" s="124">
         <f>'VIENTO NTDV-97'!G117</f>
         <v>0.37782</v>
       </c>
-      <c r="D62" s="80">
-        <f>$E$15*C62/100</f>
+      <c r="D67" s="80">
+        <f>$E$15*C67/100</f>
         <v>-0.091774129439287</v>
       </c>
-      <c r="E62" s="80">
-        <f>-$E$25*C62/100</f>
-        <v>0.128483781215002</v>
-      </c>
-      <c r="F62" s="125">
-        <f>D62+E62</f>
-        <v>0.0367096517757148</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="78" t="inlineStr">
+      <c r="E67" s="80">
+        <f>-$E$31*C67/100</f>
+        <v>0.091774129439287</v>
+      </c>
+      <c r="F67" s="125">
+        <f>D67+E67</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">MURO 1 LATERAL   (Cpe lateral)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="34.8" customHeight="1">
-      <c r="B65" s="122" t="inlineStr">
+    <row r="70" ht="34.8" customHeight="1">
+      <c r="B70" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="C65" s="77" t="inlineStr">
+      <c r="C70" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="D65" s="77" t="inlineStr">
+      <c r="D70" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd externa (kg/cm)</t>
         </is>
       </c>
-      <c r="E65" s="77" t="inlineStr">
+      <c r="E70" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="F65" s="77" t="inlineStr">
+      <c r="F70" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="123" t="str">
+    <row r="71">
+      <c r="B71" s="123" t="str">
         <f>'VIENTO NTDV-97'!J112</f>
         <v>L1-1</v>
       </c>
-      <c r="C66" s="124">
+      <c r="C71" s="124">
         <f>'VIENTO NTDV-97'!K112</f>
         <v>0.9</v>
       </c>
-      <c r="D66" s="80">
-        <f>$E$16*C66/100</f>
+      <c r="D71" s="80">
+        <f>$E$16*C71/100</f>
         <v>-0.306059507420204</v>
       </c>
-      <c r="E66" s="80">
-        <f>-$E$25*C66/100</f>
-        <v>0.306059507420204</v>
-      </c>
-      <c r="F66" s="125">
-        <f>D66+E66</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="123" t="str">
+      <c r="E71" s="80">
+        <f>-$E$31*C71/100</f>
+        <v>0.218613933871575</v>
+      </c>
+      <c r="F71" s="125">
+        <f>D71+E71</f>
+        <v>-0.0874455735486298</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="123" t="str">
         <f>'VIENTO NTDV-97'!J113</f>
         <v>L1-2</v>
       </c>
-      <c r="C67" s="124">
+      <c r="C72" s="124">
         <f>'VIENTO NTDV-97'!K113</f>
         <v>1.2</v>
       </c>
-      <c r="D67" s="80">
-        <f>$E$16*C67/100</f>
+      <c r="D72" s="80">
+        <f>$E$16*C72/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="E67" s="80">
-        <f>-$E$25*C67/100</f>
-        <v>0.408079343226939</v>
-      </c>
-      <c r="F67" s="125">
-        <f>D67+E67</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="123" t="str">
+      <c r="E72" s="80">
+        <f>-$E$31*C72/100</f>
+        <v>0.291485245162099</v>
+      </c>
+      <c r="F72" s="125">
+        <f>D72+E72</f>
+        <v>-0.11659409806484</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="123" t="str">
         <f>'VIENTO NTDV-97'!J114</f>
         <v>Dintel P.</v>
       </c>
-      <c r="C68" s="124">
+      <c r="C73" s="124">
         <f>'VIENTO NTDV-97'!K114</f>
         <v>0.3</v>
       </c>
-      <c r="D68" s="80">
-        <f>$E$16*C68/100</f>
+      <c r="D73" s="80">
+        <f>$E$16*C73/100</f>
         <v>-0.102019835806735</v>
       </c>
-      <c r="E68" s="80">
-        <f>-$E$25*C68/100</f>
-        <v>0.102019835806735</v>
-      </c>
-      <c r="F68" s="125">
-        <f>D68+E68</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="123" t="str">
+      <c r="E73" s="80">
+        <f>-$E$31*C73/100</f>
+        <v>0.0728713112905249</v>
+      </c>
+      <c r="F73" s="125">
+        <f>D73+E73</f>
+        <v>-0.0291485245162099</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="123" t="str">
         <f>'VIENTO NTDV-97'!J115</f>
         <v>L1-3</v>
       </c>
-      <c r="C69" s="124">
+      <c r="C74" s="124">
         <f>'VIENTO NTDV-97'!K115</f>
         <v>1.2</v>
       </c>
-      <c r="D69" s="80">
-        <f>$E$16*C69/100</f>
+      <c r="D74" s="80">
+        <f>$E$16*C74/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="E69" s="80">
-        <f>-$E$25*C69/100</f>
-        <v>0.408079343226939</v>
-      </c>
-      <c r="F69" s="125">
-        <f>D69+E69</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="123" t="str">
+      <c r="E74" s="80">
+        <f>-$E$31*C74/100</f>
+        <v>0.291485245162099</v>
+      </c>
+      <c r="F74" s="125">
+        <f>D74+E74</f>
+        <v>-0.11659409806484</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="123" t="str">
         <f>'VIENTO NTDV-97'!J116</f>
         <v>L1-3 P.</v>
       </c>
-      <c r="C70" s="124">
+      <c r="C75" s="124">
         <f>'VIENTO NTDV-97'!K116</f>
         <v>0.9</v>
       </c>
-      <c r="D70" s="80">
-        <f>$E$16*C70/100</f>
+      <c r="D75" s="80">
+        <f>$E$16*C75/100</f>
         <v>-0.306059507420204</v>
       </c>
-      <c r="E70" s="80">
-        <f>-$E$25*C70/100</f>
-        <v>0.306059507420204</v>
-      </c>
-      <c r="F70" s="125">
-        <f>D70+E70</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="123" t="str">
+      <c r="E75" s="80">
+        <f>-$E$31*C75/100</f>
+        <v>0.218613933871575</v>
+      </c>
+      <c r="F75" s="125">
+        <f>D75+E75</f>
+        <v>-0.0874455735486298</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="123" t="str">
         <f>'VIENTO NTDV-97'!J117</f>
         <v>L1-4</v>
       </c>
-      <c r="C71" s="124">
+      <c r="C76" s="124">
         <f>'VIENTO NTDV-97'!K117</f>
         <v>1.2</v>
       </c>
-      <c r="D71" s="80">
-        <f>$E$16*C71/100</f>
+      <c r="D76" s="80">
+        <f>$E$16*C76/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="E71" s="80">
-        <f>-$E$25*C71/100</f>
-        <v>0.408079343226939</v>
-      </c>
-      <c r="F71" s="125">
-        <f>D71+E71</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="123" t="str">
+      <c r="E76" s="80">
+        <f>-$E$31*C76/100</f>
+        <v>0.291485245162099</v>
+      </c>
+      <c r="F76" s="125">
+        <f>D76+E76</f>
+        <v>-0.11659409806484</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="123" t="str">
         <f>'VIENTO NTDV-97'!J118</f>
         <v>L1-5</v>
       </c>
-      <c r="C72" s="124">
+      <c r="C77" s="124">
         <f>'VIENTO NTDV-97'!K118</f>
         <v>1.15</v>
       </c>
-      <c r="D72" s="80">
-        <f>$E$16*C72/100</f>
+      <c r="D77" s="80">
+        <f>$E$16*C77/100</f>
         <v>-0.39107603725915</v>
       </c>
-      <c r="E72" s="80">
-        <f>-$E$25*C72/100</f>
-        <v>0.39107603725915</v>
-      </c>
-      <c r="F72" s="125">
-        <f>D72+E72</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="123" t="str">
+      <c r="E77" s="80">
+        <f>-$E$31*C77/100</f>
+        <v>0.279340026613679</v>
+      </c>
+      <c r="F77" s="125">
+        <f>D77+E77</f>
+        <v>-0.111736010645471</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="123" t="str">
         <f>'VIENTO NTDV-97'!J119</f>
         <v>L1-6 lat.</v>
       </c>
-      <c r="C73" s="124">
+      <c r="C78" s="124">
         <f>'VIENTO NTDV-97'!K119</f>
         <v>1.2</v>
       </c>
-      <c r="D73" s="80">
-        <f>$E$16*C73/100</f>
+      <c r="D78" s="80">
+        <f>$E$16*C78/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="E73" s="80">
-        <f>-$E$25*C73/100</f>
-        <v>0.408079343226939</v>
-      </c>
-      <c r="F73" s="125">
-        <f>D73+E73</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="123" t="str">
+      <c r="E78" s="80">
+        <f>-$E$31*C78/100</f>
+        <v>0.291485245162099</v>
+      </c>
+      <c r="F78" s="125">
+        <f>D78+E78</f>
+        <v>-0.11659409806484</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="123" t="str">
         <f>'VIENTO NTDV-97'!J120</f>
         <v>L1-6 cen.</v>
       </c>
-      <c r="C74" s="124">
+      <c r="C79" s="124">
         <f>'VIENTO NTDV-97'!K120</f>
         <v>0.65</v>
       </c>
-      <c r="D74" s="80">
-        <f>$E$16*C74/100</f>
+      <c r="D79" s="80">
+        <f>$E$16*C79/100</f>
         <v>-0.221042977581259</v>
       </c>
-      <c r="E74" s="80">
-        <f>-$E$25*C74/100</f>
-        <v>0.221042977581259</v>
-      </c>
-      <c r="F74" s="125">
-        <f>D74+E74</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="123" t="str">
+      <c r="E79" s="80">
+        <f>-$E$31*C79/100</f>
+        <v>0.157887841129471</v>
+      </c>
+      <c r="F79" s="125">
+        <f>D79+E79</f>
+        <v>-0.0631551364517882</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="123" t="str">
         <f>'VIENTO NTDV-97'!J121</f>
         <v>L1-7</v>
       </c>
-      <c r="C75" s="124">
+      <c r="C80" s="124">
         <f>'VIENTO NTDV-97'!K121</f>
         <v>1.25</v>
       </c>
-      <c r="D75" s="80">
-        <f>$E$16*C75/100</f>
+      <c r="D80" s="80">
+        <f>$E$16*C80/100</f>
         <v>-0.425082649194728</v>
       </c>
-      <c r="E75" s="80">
-        <f>-$E$25*C75/100</f>
-        <v>0.425082649194728</v>
-      </c>
-      <c r="F75" s="125">
-        <f>D75+E75</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="123" t="str">
+      <c r="E80" s="80">
+        <f>-$E$31*C80/100</f>
+        <v>0.30363046371052</v>
+      </c>
+      <c r="F80" s="125">
+        <f>D80+E80</f>
+        <v>-0.121452185484208</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="123" t="str">
         <f>'VIENTO NTDV-97'!J122</f>
         <v>L1-8</v>
       </c>
-      <c r="C76" s="124">
+      <c r="C81" s="124">
         <f>'VIENTO NTDV-97'!K122</f>
         <v>1.315</v>
       </c>
-      <c r="D76" s="80">
-        <f>$E$16*C76/100</f>
+      <c r="D81" s="80">
+        <f>$E$16*C81/100</f>
         <v>-0.447186946952854</v>
       </c>
-      <c r="E76" s="80">
-        <f>-$E$25*C76/100</f>
-        <v>0.447186946952854</v>
-      </c>
-      <c r="F76" s="125">
-        <f>D76+E76</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="123" t="str">
+      <c r="E81" s="80">
+        <f>-$E$31*C81/100</f>
+        <v>0.319419247823467</v>
+      </c>
+      <c r="F81" s="125">
+        <f>D81+E81</f>
+        <v>-0.127767699129387</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="123" t="str">
         <f>'VIENTO NTDV-97'!J123</f>
         <v>VM-1 sup.</v>
       </c>
-      <c r="C77" s="124">
+      <c r="C82" s="124">
         <f>'VIENTO NTDV-97'!K123</f>
         <v>0.715</v>
       </c>
-      <c r="D77" s="80">
-        <f>$E$16*C77/100</f>
+      <c r="D82" s="80">
+        <f>$E$16*C82/100</f>
         <v>-0.243147275339385</v>
       </c>
-      <c r="E77" s="80">
-        <f>-$E$25*C77/100</f>
-        <v>0.243147275339385</v>
-      </c>
-      <c r="F77" s="125">
-        <f>D77+E77</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="78" t="inlineStr">
+      <c r="E82" s="80">
+        <f>-$E$31*C82/100</f>
+        <v>0.173676625242418</v>
+      </c>
+      <c r="F82" s="125">
+        <f>D82+E82</f>
+        <v>-0.069470650096967</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">CUBIERTA — LARGUEROS Y VIGAS DE MARCO   (Cpe techo)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="34.8" customHeight="1">
-      <c r="B80" s="122" t="inlineStr">
+    <row r="85" ht="34.8" customHeight="1">
+      <c r="B85" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="C80" s="77" t="inlineStr">
+      <c r="C85" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="D80" s="77" t="inlineStr">
+      <c r="D85" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd externa (kg/cm)</t>
         </is>
       </c>
-      <c r="E80" s="77" t="inlineStr">
+      <c r="E85" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="F80" s="77" t="inlineStr">
+      <c r="F85" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="123" t="str">
+    <row r="86">
+      <c r="B86" s="123" t="str">
         <f>'VIENTO NTDV-97'!N112</f>
         <v>VM-1</v>
       </c>
-      <c r="C81" s="124">
+      <c r="C86" s="124">
         <f>'VIENTO NTDV-97'!O112</f>
         <v>0.5</v>
       </c>
-      <c r="D81" s="80">
-        <f>$E$17*C81/100</f>
+      <c r="D86" s="80">
+        <f>$E$17*C86/100</f>
         <v>-0.170033059677891</v>
       </c>
-      <c r="E81" s="80">
-        <f>-$E$25*C81/100</f>
-        <v>0.170033059677891</v>
-      </c>
-      <c r="F81" s="125">
-        <f>D81+E81</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="123" t="str">
+      <c r="E86" s="80">
+        <f>-$E$31*C86/100</f>
+        <v>0.121452185484208</v>
+      </c>
+      <c r="F86" s="125">
+        <f>D86+E86</f>
+        <v>-0.0485808741936832</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="123" t="str">
         <f>'VIENTO NTDV-97'!N113</f>
         <v>LT-1</v>
       </c>
-      <c r="C82" s="124">
+      <c r="C87" s="124">
         <f>'VIENTO NTDV-97'!O113</f>
         <v>1.25</v>
       </c>
-      <c r="D82" s="80">
-        <f>$E$17*C82/100</f>
+      <c r="D87" s="80">
+        <f>$E$17*C87/100</f>
         <v>-0.425082649194728</v>
       </c>
-      <c r="E82" s="80">
-        <f>-$E$25*C82/100</f>
-        <v>0.425082649194728</v>
-      </c>
-      <c r="F82" s="125">
-        <f>D82+E82</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="123" t="str">
+      <c r="E87" s="80">
+        <f>-$E$31*C87/100</f>
+        <v>0.30363046371052</v>
+      </c>
+      <c r="F87" s="125">
+        <f>D87+E87</f>
+        <v>-0.121452185484208</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="123" t="str">
         <f>'VIENTO NTDV-97'!N114</f>
         <v>LT-2</v>
       </c>
-      <c r="C83" s="124">
+      <c r="C88" s="124">
         <f>'VIENTO NTDV-97'!O114</f>
-        <v>1.5</v>
-      </c>
-      <c r="D83" s="80">
-        <f>$E$17*C83/100</f>
-        <v>-0.510099179033674</v>
-      </c>
-      <c r="E83" s="80">
-        <f>-$E$25*C83/100</f>
-        <v>0.510099179033674</v>
-      </c>
-      <c r="F83" s="125">
-        <f>D83+E83</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N115</f>
-        <v>LT-3</v>
-      </c>
-      <c r="C84" s="124">
-        <f>'VIENTO NTDV-97'!O115</f>
-        <v>1.5</v>
-      </c>
-      <c r="D84" s="80">
-        <f>$E$17*C84/100</f>
-        <v>-0.510099179033674</v>
-      </c>
-      <c r="E84" s="80">
-        <f>-$E$25*C84/100</f>
-        <v>0.510099179033674</v>
-      </c>
-      <c r="F84" s="125">
-        <f>D84+E84</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N116</f>
-        <v>LT-4</v>
-      </c>
-      <c r="C85" s="124">
-        <f>'VIENTO NTDV-97'!O116</f>
-        <v>1.5</v>
-      </c>
-      <c r="D85" s="80">
-        <f>$E$17*C85/100</f>
-        <v>-0.510099179033674</v>
-      </c>
-      <c r="E85" s="80">
-        <f>-$E$25*C85/100</f>
-        <v>0.510099179033674</v>
-      </c>
-      <c r="F85" s="125">
-        <f>D85+E85</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N117</f>
-        <v>LT-5</v>
-      </c>
-      <c r="C86" s="124">
-        <f>'VIENTO NTDV-97'!O117</f>
-        <v>0.75</v>
-      </c>
-      <c r="D86" s="80">
-        <f>$E$17*C86/100</f>
-        <v>-0.255049589516837</v>
-      </c>
-      <c r="E86" s="80">
-        <f>-$E$25*C86/100</f>
-        <v>0.255049589516837</v>
-      </c>
-      <c r="F86" s="125">
-        <f>D86+E86</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N118</f>
-        <v>LT-6</v>
-      </c>
-      <c r="C87" s="124">
-        <f>'VIENTO NTDV-97'!O118</f>
-        <v>1.5</v>
-      </c>
-      <c r="D87" s="80">
-        <f>$E$17*C87/100</f>
-        <v>-0.510099179033674</v>
-      </c>
-      <c r="E87" s="80">
-        <f>-$E$25*C87/100</f>
-        <v>0.510099179033674</v>
-      </c>
-      <c r="F87" s="125">
-        <f>D87+E87</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N119</f>
-        <v>VM-2</v>
-      </c>
-      <c r="C88" s="124">
-        <f>'VIENTO NTDV-97'!O119</f>
         <v>1.5</v>
       </c>
       <c r="D88" s="80">
@@ -16830,21 +16778,21 @@
         <v>-0.510099179033674</v>
       </c>
       <c r="E88" s="80">
-        <f>-$E$25*C88/100</f>
-        <v>0.510099179033674</v>
+        <f>-$E$31*C88/100</f>
+        <v>0.364356556452624</v>
       </c>
       <c r="F88" s="125">
         <f>D88+E88</f>
-        <v>0.0</v>
+        <v>-0.14574262258105</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N120</f>
-        <v>LT-7</v>
+        <f>'VIENTO NTDV-97'!N115</f>
+        <v>LT-3</v>
       </c>
       <c r="C89" s="124">
-        <f>'VIENTO NTDV-97'!O120</f>
+        <f>'VIENTO NTDV-97'!O115</f>
         <v>1.5</v>
       </c>
       <c r="D89" s="80">
@@ -16852,21 +16800,21 @@
         <v>-0.510099179033674</v>
       </c>
       <c r="E89" s="80">
-        <f>-$E$25*C89/100</f>
-        <v>0.510099179033674</v>
+        <f>-$E$31*C89/100</f>
+        <v>0.364356556452624</v>
       </c>
       <c r="F89" s="125">
         <f>D89+E89</f>
-        <v>0.0</v>
+        <v>-0.14574262258105</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N121</f>
-        <v>LT-8</v>
+        <f>'VIENTO NTDV-97'!N116</f>
+        <v>LT-4</v>
       </c>
       <c r="C90" s="124">
-        <f>'VIENTO NTDV-97'!O121</f>
+        <f>'VIENTO NTDV-97'!O116</f>
         <v>1.5</v>
       </c>
       <c r="D90" s="80">
@@ -16874,894 +16822,894 @@
         <v>-0.510099179033674</v>
       </c>
       <c r="E90" s="80">
-        <f>-$E$25*C90/100</f>
-        <v>0.510099179033674</v>
+        <f>-$E$31*C90/100</f>
+        <v>0.364356556452624</v>
       </c>
       <c r="F90" s="125">
         <f>D90+E90</f>
-        <v>0.0</v>
+        <v>-0.14574262258105</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N117</f>
+        <v>LT-5</v>
+      </c>
+      <c r="C91" s="124">
+        <f>'VIENTO NTDV-97'!O117</f>
+        <v>0.75</v>
+      </c>
+      <c r="D91" s="80">
+        <f>$E$17*C91/100</f>
+        <v>-0.255049589516837</v>
+      </c>
+      <c r="E91" s="80">
+        <f>-$E$31*C91/100</f>
+        <v>0.182178278226312</v>
+      </c>
+      <c r="F91" s="125">
+        <f>D91+E91</f>
+        <v>-0.0728713112905249</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N118</f>
+        <v>LT-6</v>
+      </c>
+      <c r="C92" s="124">
+        <f>'VIENTO NTDV-97'!O118</f>
+        <v>1.5</v>
+      </c>
+      <c r="D92" s="80">
+        <f>$E$17*C92/100</f>
+        <v>-0.510099179033674</v>
+      </c>
+      <c r="E92" s="80">
+        <f>-$E$31*C92/100</f>
+        <v>0.364356556452624</v>
+      </c>
+      <c r="F92" s="125">
+        <f>D92+E92</f>
+        <v>-0.14574262258105</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N119</f>
+        <v>VM-2</v>
+      </c>
+      <c r="C93" s="124">
+        <f>'VIENTO NTDV-97'!O119</f>
+        <v>1.5</v>
+      </c>
+      <c r="D93" s="80">
+        <f>$E$17*C93/100</f>
+        <v>-0.510099179033674</v>
+      </c>
+      <c r="E93" s="80">
+        <f>-$E$31*C93/100</f>
+        <v>0.364356556452624</v>
+      </c>
+      <c r="F93" s="125">
+        <f>D93+E93</f>
+        <v>-0.14574262258105</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N120</f>
+        <v>LT-7</v>
+      </c>
+      <c r="C94" s="124">
+        <f>'VIENTO NTDV-97'!O120</f>
+        <v>1.5</v>
+      </c>
+      <c r="D94" s="80">
+        <f>$E$17*C94/100</f>
+        <v>-0.510099179033674</v>
+      </c>
+      <c r="E94" s="80">
+        <f>-$E$31*C94/100</f>
+        <v>0.364356556452624</v>
+      </c>
+      <c r="F94" s="125">
+        <f>D94+E94</f>
+        <v>-0.14574262258105</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N121</f>
+        <v>LT-8</v>
+      </c>
+      <c r="C95" s="124">
+        <f>'VIENTO NTDV-97'!O121</f>
+        <v>1.5</v>
+      </c>
+      <c r="D95" s="80">
+        <f>$E$17*C95/100</f>
+        <v>-0.510099179033674</v>
+      </c>
+      <c r="E95" s="80">
+        <f>-$E$31*C95/100</f>
+        <v>0.364356556452624</v>
+      </c>
+      <c r="F95" s="125">
+        <f>D95+E95</f>
+        <v>-0.14574262258105</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="123" t="str">
         <f>'VIENTO NTDV-97'!N122</f>
         <v>LT-9</v>
       </c>
-      <c r="C91" s="124">
+      <c r="C96" s="124">
         <f>'VIENTO NTDV-97'!O122</f>
         <v>1.5</v>
       </c>
-      <c r="D91" s="80">
-        <f>$E$17*C91/100</f>
+      <c r="D96" s="80">
+        <f>$E$17*C96/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="E91" s="80">
-        <f>-$E$25*C91/100</f>
-        <v>0.510099179033674</v>
-      </c>
-      <c r="F91" s="125">
-        <f>D91+E91</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="123" t="str">
+      <c r="E96" s="80">
+        <f>-$E$31*C96/100</f>
+        <v>0.364356556452624</v>
+      </c>
+      <c r="F96" s="125">
+        <f>D96+E96</f>
+        <v>-0.14574262258105</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="123" t="str">
         <f>'VIENTO NTDV-97'!N123</f>
         <v>VM-3</v>
       </c>
-      <c r="C92" s="124">
+      <c r="C97" s="124">
         <f>'VIENTO NTDV-97'!O123</f>
         <v>0.75</v>
       </c>
-      <c r="D92" s="80">
-        <f>$E$17*C92/100</f>
+      <c r="D97" s="80">
+        <f>$E$17*C97/100</f>
         <v>-0.255049589516837</v>
       </c>
-      <c r="E92" s="80">
-        <f>-$E$25*C92/100</f>
-        <v>0.255049589516837</v>
-      </c>
-      <c r="F92" s="125">
-        <f>D92+E92</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="95" ht="24" customHeight="1">
-      <c r="B95" s="81" t="inlineStr">
+      <c r="E97" s="80">
+        <f>-$E$31*C97/100</f>
+        <v>0.182178278226312</v>
+      </c>
+      <c r="F97" s="125">
+        <f>D97+E97</f>
+        <v>-0.0728713112905249</v>
+      </c>
+    </row>
+    <row r="100" ht="24" customHeight="1">
+      <c r="B100" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">VIENTO EN DIRECCION -X:</t>
         </is>
       </c>
-      <c r="C95" s="81"/>
-      <c r="D95" s="81"/>
-      <c r="E95" s="81"/>
-      <c r="F95" s="81"/>
-    </row>
-    <row r="97">
-      <c r="B97" s="78" t="inlineStr">
+      <c r="C100" s="81"/>
+      <c r="D100" s="81"/>
+      <c r="E100" s="81"/>
+      <c r="F100" s="81"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">MURO B EN BARLOVENTO   (Cpe barlovento)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="34.8" customHeight="1">
-      <c r="B98" s="122" t="inlineStr">
+    <row r="103" ht="34.8" customHeight="1">
+      <c r="B103" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="C98" s="77" t="inlineStr">
+      <c r="C103" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="D98" s="77" t="inlineStr">
+      <c r="D103" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd externa (kg/cm)</t>
         </is>
       </c>
-      <c r="E98" s="77" t="inlineStr">
+      <c r="E103" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="F98" s="77" t="inlineStr">
+      <c r="F103" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="B99" s="123" t="str">
+    <row r="104">
+      <c r="B104" s="123" t="str">
         <f>'VIENTO NTDV-97'!B142</f>
         <v>LB-1</v>
       </c>
-      <c r="C99" s="124">
+      <c r="C104" s="124">
         <f>'VIENTO NTDV-97'!C142</f>
         <v>0.9</v>
       </c>
-      <c r="D99" s="80">
-        <f>$E$14*C99/100</f>
+      <c r="D104" s="80">
+        <f>$E$14*C104/100</f>
         <v>0.349782294194519</v>
       </c>
-      <c r="E99" s="80">
-        <f>-$E$26*C99/100</f>
-        <v>0.306059507420204</v>
-      </c>
-      <c r="F99" s="125">
-        <f>D99+E99</f>
-        <v>0.655841801614724</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="123" t="str">
+      <c r="E104" s="80">
+        <f>-$E$32*C104/100</f>
+        <v>0.218613933871575</v>
+      </c>
+      <c r="F104" s="125">
+        <f>D104+E104</f>
+        <v>0.568396228066094</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="123" t="str">
         <f>'VIENTO NTDV-97'!B143</f>
         <v>LB-2 a 7</v>
       </c>
-      <c r="C100" s="124">
+      <c r="C105" s="124">
         <f>'VIENTO NTDV-97'!C143</f>
         <v>1.2</v>
       </c>
-      <c r="D100" s="80">
-        <f>$E$14*C100/100</f>
+      <c r="D105" s="80">
+        <f>$E$14*C105/100</f>
         <v>0.466376392259359</v>
       </c>
-      <c r="E100" s="80">
-        <f>-$E$26*C100/100</f>
-        <v>0.408079343226939</v>
-      </c>
-      <c r="F100" s="125">
-        <f>D100+E100</f>
-        <v>0.874455735486298</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="123" t="str">
+      <c r="E105" s="80">
+        <f>-$E$32*C105/100</f>
+        <v>0.291485245162099</v>
+      </c>
+      <c r="F105" s="125">
+        <f>D105+E105</f>
+        <v>0.757861637421459</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="123" t="str">
         <f>'VIENTO NTDV-97'!B144</f>
         <v>LB-8 (1-2)</v>
       </c>
-      <c r="C101" s="124">
+      <c r="C106" s="124">
         <f>'VIENTO NTDV-97'!C144</f>
         <v>1.185315</v>
       </c>
-      <c r="D101" s="80">
-        <f>$E$14*C101/100</f>
+      <c r="D106" s="80">
+        <f>$E$14*C106/100</f>
         <v>0.460669111159085</v>
       </c>
-      <c r="E101" s="80">
-        <f>-$E$26*C101/100</f>
-        <v>0.403085472264199</v>
-      </c>
-      <c r="F101" s="125">
-        <f>D101+E101</f>
-        <v>0.863754583423285</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="123" t="str">
+      <c r="E106" s="80">
+        <f>-$E$32*C106/100</f>
+        <v>0.287918194474428</v>
+      </c>
+      <c r="F106" s="125">
+        <f>D106+E106</f>
+        <v>0.748587305633513</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="123" t="str">
         <f>'VIENTO NTDV-97'!B145</f>
         <v>LB-8 (2-3)</v>
       </c>
-      <c r="C102" s="124">
+      <c r="C107" s="124">
         <f>'VIENTO NTDV-97'!C145</f>
         <v>0.97782</v>
       </c>
-      <c r="D102" s="80">
-        <f>$E$14*C102/100</f>
+      <c r="D107" s="80">
+        <f>$E$14*C107/100</f>
         <v>0.380026803232539</v>
       </c>
-      <c r="E102" s="80">
-        <f>-$E$26*C102/100</f>
-        <v>0.332523452828471</v>
-      </c>
-      <c r="F102" s="125">
-        <f>D102+E102</f>
-        <v>0.71255025606101</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" s="123" t="str">
+      <c r="E107" s="80">
+        <f>-$E$32*C107/100</f>
+        <v>0.237516752020337</v>
+      </c>
+      <c r="F107" s="125">
+        <f>D107+E107</f>
+        <v>0.617543555252876</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="123" t="str">
         <f>'VIENTO NTDV-97'!B146</f>
         <v>VB-1 sup.</v>
       </c>
-      <c r="C103" s="124">
+      <c r="C108" s="124">
         <f>'VIENTO NTDV-97'!C146</f>
         <v>0.585315</v>
       </c>
-      <c r="D103" s="80">
-        <f>$E$14*C103/100</f>
+      <c r="D108" s="80">
+        <f>$E$14*C108/100</f>
         <v>0.227480915029406</v>
       </c>
-      <c r="E103" s="80">
-        <f>-$E$26*C103/100</f>
-        <v>0.19904580065073</v>
-      </c>
-      <c r="F103" s="125">
-        <f>D103+E103</f>
-        <v>0.426526715680136</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" s="123" t="str">
+      <c r="E108" s="80">
+        <f>-$E$32*C108/100</f>
+        <v>0.142175571893379</v>
+      </c>
+      <c r="F108" s="125">
+        <f>D108+E108</f>
+        <v>0.369656486922784</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="123" t="str">
         <f>'VIENTO NTDV-97'!B147</f>
         <v>VB-2 sup.</v>
       </c>
-      <c r="C104" s="124">
+      <c r="C109" s="124">
         <f>'VIENTO NTDV-97'!C147</f>
         <v>0.37782</v>
       </c>
-      <c r="D104" s="80">
-        <f>$E$14*C104/100</f>
+      <c r="D109" s="80">
+        <f>$E$14*C109/100</f>
         <v>0.146838607102859</v>
       </c>
-      <c r="E104" s="80">
-        <f>-$E$26*C104/100</f>
-        <v>0.128483781215002</v>
-      </c>
-      <c r="F104" s="125">
-        <f>D104+E104</f>
-        <v>0.275322388317861</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="B106" s="78" t="inlineStr">
+      <c r="E109" s="80">
+        <f>-$E$32*C109/100</f>
+        <v>0.091774129439287</v>
+      </c>
+      <c r="F109" s="125">
+        <f>D109+E109</f>
+        <v>0.238612736542146</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">MURO A EN SOTAVENTO   (Cpe sotavento)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="34.8" customHeight="1">
-      <c r="B107" s="122" t="inlineStr">
+    <row r="112" ht="34.8" customHeight="1">
+      <c r="B112" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="C107" s="77" t="inlineStr">
+      <c r="C112" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="D107" s="77" t="inlineStr">
+      <c r="D112" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd externa (kg/cm)</t>
         </is>
       </c>
-      <c r="E107" s="77" t="inlineStr">
+      <c r="E112" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="F107" s="77" t="inlineStr">
+      <c r="F112" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="B108" s="123" t="str">
+    <row r="113">
+      <c r="B113" s="123" t="str">
         <f>'VIENTO NTDV-97'!F142</f>
         <v>LA-1</v>
       </c>
-      <c r="C108" s="124">
+      <c r="C113" s="124">
         <f>'VIENTO NTDV-97'!G142</f>
         <v>0.9</v>
       </c>
-      <c r="D108" s="80">
-        <f>$E$15*C108/100</f>
+      <c r="D113" s="80">
+        <f>$E$15*C113/100</f>
         <v>-0.218613933871575</v>
       </c>
-      <c r="E108" s="80">
-        <f>-$E$26*C108/100</f>
-        <v>0.306059507420204</v>
-      </c>
-      <c r="F108" s="125">
-        <f>D108+E108</f>
-        <v>0.0874455735486298</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="B109" s="123" t="str">
+      <c r="E113" s="80">
+        <f>-$E$32*C113/100</f>
+        <v>0.218613933871575</v>
+      </c>
+      <c r="F113" s="125">
+        <f>D113+E113</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="123" t="str">
         <f>'VIENTO NTDV-97'!F143</f>
         <v>LA-2 a 7</v>
       </c>
-      <c r="C109" s="124">
+      <c r="C114" s="124">
         <f>'VIENTO NTDV-97'!G143</f>
         <v>1.2</v>
       </c>
-      <c r="D109" s="80">
-        <f>$E$15*C109/100</f>
+      <c r="D114" s="80">
+        <f>$E$15*C114/100</f>
         <v>-0.291485245162099</v>
       </c>
-      <c r="E109" s="80">
-        <f>-$E$26*C109/100</f>
-        <v>0.408079343226939</v>
-      </c>
-      <c r="F109" s="125">
-        <f>D109+E109</f>
-        <v>0.11659409806484</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="B110" s="123" t="str">
+      <c r="E114" s="80">
+        <f>-$E$32*C114/100</f>
+        <v>0.291485245162099</v>
+      </c>
+      <c r="F114" s="125">
+        <f>D114+E114</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="123" t="str">
         <f>'VIENTO NTDV-97'!F144</f>
         <v>LA-8 (1-2)</v>
       </c>
-      <c r="C110" s="124">
+      <c r="C115" s="124">
         <f>'VIENTO NTDV-97'!G144</f>
         <v>1.185315</v>
       </c>
-      <c r="D110" s="80">
-        <f>$E$15*C110/100</f>
+      <c r="D115" s="80">
+        <f>$E$15*C115/100</f>
         <v>-0.287918194474428</v>
       </c>
-      <c r="E110" s="80">
-        <f>-$E$26*C110/100</f>
-        <v>0.403085472264199</v>
-      </c>
-      <c r="F110" s="125">
-        <f>D110+E110</f>
-        <v>0.115167277789771</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="B111" s="123" t="str">
+      <c r="E115" s="80">
+        <f>-$E$32*C115/100</f>
+        <v>0.287918194474428</v>
+      </c>
+      <c r="F115" s="125">
+        <f>D115+E115</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="123" t="str">
         <f>'VIENTO NTDV-97'!F145</f>
         <v>LA-8 (2-3)</v>
       </c>
-      <c r="C111" s="124">
+      <c r="C116" s="124">
         <f>'VIENTO NTDV-97'!G145</f>
         <v>0.97782</v>
       </c>
-      <c r="D111" s="80">
-        <f>$E$15*C111/100</f>
+      <c r="D116" s="80">
+        <f>$E$15*C116/100</f>
         <v>-0.237516752020337</v>
       </c>
-      <c r="E111" s="80">
-        <f>-$E$26*C111/100</f>
-        <v>0.332523452828471</v>
-      </c>
-      <c r="F111" s="125">
-        <f>D111+E111</f>
-        <v>0.0950067008081347</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="B112" s="123" t="str">
+      <c r="E116" s="80">
+        <f>-$E$32*C116/100</f>
+        <v>0.237516752020337</v>
+      </c>
+      <c r="F116" s="125">
+        <f>D116+E116</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="123" t="str">
         <f>'VIENTO NTDV-97'!F146</f>
         <v>VA-1 sup.</v>
       </c>
-      <c r="C112" s="124">
+      <c r="C117" s="124">
         <f>'VIENTO NTDV-97'!G146</f>
         <v>0.585315</v>
       </c>
-      <c r="D112" s="80">
-        <f>$E$15*C112/100</f>
+      <c r="D117" s="80">
+        <f>$E$15*C117/100</f>
         <v>-0.142175571893379</v>
       </c>
-      <c r="E112" s="80">
-        <f>-$E$26*C112/100</f>
-        <v>0.19904580065073</v>
-      </c>
-      <c r="F112" s="125">
-        <f>D112+E112</f>
-        <v>0.0568702287573514</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="B113" s="123" t="str">
+      <c r="E117" s="80">
+        <f>-$E$32*C117/100</f>
+        <v>0.142175571893379</v>
+      </c>
+      <c r="F117" s="125">
+        <f>D117+E117</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="123" t="str">
         <f>'VIENTO NTDV-97'!F147</f>
         <v>VA-2 sup.</v>
       </c>
-      <c r="C113" s="124">
+      <c r="C118" s="124">
         <f>'VIENTO NTDV-97'!G147</f>
         <v>0.37782</v>
       </c>
-      <c r="D113" s="80">
-        <f>$E$15*C113/100</f>
+      <c r="D118" s="80">
+        <f>$E$15*C118/100</f>
         <v>-0.091774129439287</v>
       </c>
-      <c r="E113" s="80">
-        <f>-$E$26*C113/100</f>
-        <v>0.128483781215002</v>
-      </c>
-      <c r="F113" s="125">
-        <f>D113+E113</f>
-        <v>0.0367096517757148</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="78" t="inlineStr">
+      <c r="E118" s="80">
+        <f>-$E$32*C118/100</f>
+        <v>0.091774129439287</v>
+      </c>
+      <c r="F118" s="125">
+        <f>D118+E118</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">MURO 1 LATERAL   (Cpe lateral)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="34.8" customHeight="1">
-      <c r="B116" s="122" t="inlineStr">
+    <row r="121" ht="34.8" customHeight="1">
+      <c r="B121" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="C116" s="77" t="inlineStr">
+      <c r="C121" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="D116" s="77" t="inlineStr">
+      <c r="D121" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd externa (kg/cm)</t>
         </is>
       </c>
-      <c r="E116" s="77" t="inlineStr">
+      <c r="E121" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="F116" s="77" t="inlineStr">
+      <c r="F121" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="B117" s="123" t="str">
+    <row r="122">
+      <c r="B122" s="123" t="str">
         <f>'VIENTO NTDV-97'!J142</f>
         <v>L1-1</v>
       </c>
-      <c r="C117" s="124">
+      <c r="C122" s="124">
         <f>'VIENTO NTDV-97'!K142</f>
         <v>0.9</v>
       </c>
-      <c r="D117" s="80">
-        <f>$E$16*C117/100</f>
+      <c r="D122" s="80">
+        <f>$E$16*C122/100</f>
         <v>-0.306059507420204</v>
       </c>
-      <c r="E117" s="80">
-        <f>-$E$26*C117/100</f>
-        <v>0.306059507420204</v>
-      </c>
-      <c r="F117" s="125">
-        <f>D117+E117</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" s="123" t="str">
+      <c r="E122" s="80">
+        <f>-$E$32*C122/100</f>
+        <v>0.218613933871575</v>
+      </c>
+      <c r="F122" s="125">
+        <f>D122+E122</f>
+        <v>-0.0874455735486298</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="123" t="str">
         <f>'VIENTO NTDV-97'!J143</f>
         <v>L1-2</v>
       </c>
-      <c r="C118" s="124">
+      <c r="C123" s="124">
         <f>'VIENTO NTDV-97'!K143</f>
         <v>1.2</v>
       </c>
-      <c r="D118" s="80">
-        <f>$E$16*C118/100</f>
+      <c r="D123" s="80">
+        <f>$E$16*C123/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="E118" s="80">
-        <f>-$E$26*C118/100</f>
-        <v>0.408079343226939</v>
-      </c>
-      <c r="F118" s="125">
-        <f>D118+E118</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" s="123" t="str">
+      <c r="E123" s="80">
+        <f>-$E$32*C123/100</f>
+        <v>0.291485245162099</v>
+      </c>
+      <c r="F123" s="125">
+        <f>D123+E123</f>
+        <v>-0.11659409806484</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="123" t="str">
         <f>'VIENTO NTDV-97'!J144</f>
         <v>Dintel P.</v>
       </c>
-      <c r="C119" s="124">
+      <c r="C124" s="124">
         <f>'VIENTO NTDV-97'!K144</f>
         <v>0.3</v>
       </c>
-      <c r="D119" s="80">
-        <f>$E$16*C119/100</f>
+      <c r="D124" s="80">
+        <f>$E$16*C124/100</f>
         <v>-0.102019835806735</v>
       </c>
-      <c r="E119" s="80">
-        <f>-$E$26*C119/100</f>
-        <v>0.102019835806735</v>
-      </c>
-      <c r="F119" s="125">
-        <f>D119+E119</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" s="123" t="str">
+      <c r="E124" s="80">
+        <f>-$E$32*C124/100</f>
+        <v>0.0728713112905249</v>
+      </c>
+      <c r="F124" s="125">
+        <f>D124+E124</f>
+        <v>-0.0291485245162099</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="123" t="str">
         <f>'VIENTO NTDV-97'!J145</f>
         <v>L1-3</v>
       </c>
-      <c r="C120" s="124">
+      <c r="C125" s="124">
         <f>'VIENTO NTDV-97'!K145</f>
         <v>1.2</v>
       </c>
-      <c r="D120" s="80">
-        <f>$E$16*C120/100</f>
+      <c r="D125" s="80">
+        <f>$E$16*C125/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="E120" s="80">
-        <f>-$E$26*C120/100</f>
-        <v>0.408079343226939</v>
-      </c>
-      <c r="F120" s="125">
-        <f>D120+E120</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="B121" s="123" t="str">
+      <c r="E125" s="80">
+        <f>-$E$32*C125/100</f>
+        <v>0.291485245162099</v>
+      </c>
+      <c r="F125" s="125">
+        <f>D125+E125</f>
+        <v>-0.11659409806484</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="123" t="str">
         <f>'VIENTO NTDV-97'!J146</f>
         <v>L1-3 P.</v>
       </c>
-      <c r="C121" s="124">
+      <c r="C126" s="124">
         <f>'VIENTO NTDV-97'!K146</f>
         <v>0.9</v>
       </c>
-      <c r="D121" s="80">
-        <f>$E$16*C121/100</f>
+      <c r="D126" s="80">
+        <f>$E$16*C126/100</f>
         <v>-0.306059507420204</v>
       </c>
-      <c r="E121" s="80">
-        <f>-$E$26*C121/100</f>
-        <v>0.306059507420204</v>
-      </c>
-      <c r="F121" s="125">
-        <f>D121+E121</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="B122" s="123" t="str">
+      <c r="E126" s="80">
+        <f>-$E$32*C126/100</f>
+        <v>0.218613933871575</v>
+      </c>
+      <c r="F126" s="125">
+        <f>D126+E126</f>
+        <v>-0.0874455735486298</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="123" t="str">
         <f>'VIENTO NTDV-97'!J147</f>
         <v>L1-4</v>
       </c>
-      <c r="C122" s="124">
+      <c r="C127" s="124">
         <f>'VIENTO NTDV-97'!K147</f>
         <v>1.2</v>
       </c>
-      <c r="D122" s="80">
-        <f>$E$16*C122/100</f>
+      <c r="D127" s="80">
+        <f>$E$16*C127/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="E122" s="80">
-        <f>-$E$26*C122/100</f>
-        <v>0.408079343226939</v>
-      </c>
-      <c r="F122" s="125">
-        <f>D122+E122</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="B123" s="123" t="str">
+      <c r="E127" s="80">
+        <f>-$E$32*C127/100</f>
+        <v>0.291485245162099</v>
+      </c>
+      <c r="F127" s="125">
+        <f>D127+E127</f>
+        <v>-0.11659409806484</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="123" t="str">
         <f>'VIENTO NTDV-97'!J148</f>
         <v>L1-5</v>
       </c>
-      <c r="C123" s="124">
+      <c r="C128" s="124">
         <f>'VIENTO NTDV-97'!K148</f>
         <v>1.15</v>
       </c>
-      <c r="D123" s="80">
-        <f>$E$16*C123/100</f>
+      <c r="D128" s="80">
+        <f>$E$16*C128/100</f>
         <v>-0.39107603725915</v>
       </c>
-      <c r="E123" s="80">
-        <f>-$E$26*C123/100</f>
-        <v>0.39107603725915</v>
-      </c>
-      <c r="F123" s="125">
-        <f>D123+E123</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" s="123" t="str">
+      <c r="E128" s="80">
+        <f>-$E$32*C128/100</f>
+        <v>0.279340026613679</v>
+      </c>
+      <c r="F128" s="125">
+        <f>D128+E128</f>
+        <v>-0.111736010645471</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="123" t="str">
         <f>'VIENTO NTDV-97'!J149</f>
         <v>L1-6 lat.</v>
       </c>
-      <c r="C124" s="124">
+      <c r="C129" s="124">
         <f>'VIENTO NTDV-97'!K149</f>
         <v>1.2</v>
       </c>
-      <c r="D124" s="80">
-        <f>$E$16*C124/100</f>
+      <c r="D129" s="80">
+        <f>$E$16*C129/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="E124" s="80">
-        <f>-$E$26*C124/100</f>
-        <v>0.408079343226939</v>
-      </c>
-      <c r="F124" s="125">
-        <f>D124+E124</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="B125" s="123" t="str">
+      <c r="E129" s="80">
+        <f>-$E$32*C129/100</f>
+        <v>0.291485245162099</v>
+      </c>
+      <c r="F129" s="125">
+        <f>D129+E129</f>
+        <v>-0.11659409806484</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="123" t="str">
         <f>'VIENTO NTDV-97'!J150</f>
         <v>L1-6 cen.</v>
       </c>
-      <c r="C125" s="124">
+      <c r="C130" s="124">
         <f>'VIENTO NTDV-97'!K150</f>
         <v>0.65</v>
       </c>
-      <c r="D125" s="80">
-        <f>$E$16*C125/100</f>
+      <c r="D130" s="80">
+        <f>$E$16*C130/100</f>
         <v>-0.221042977581259</v>
       </c>
-      <c r="E125" s="80">
-        <f>-$E$26*C125/100</f>
-        <v>0.221042977581259</v>
-      </c>
-      <c r="F125" s="125">
-        <f>D125+E125</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="B126" s="123" t="str">
+      <c r="E130" s="80">
+        <f>-$E$32*C130/100</f>
+        <v>0.157887841129471</v>
+      </c>
+      <c r="F130" s="125">
+        <f>D130+E130</f>
+        <v>-0.0631551364517882</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="123" t="str">
         <f>'VIENTO NTDV-97'!J151</f>
         <v>L1-7</v>
       </c>
-      <c r="C126" s="124">
+      <c r="C131" s="124">
         <f>'VIENTO NTDV-97'!K151</f>
         <v>1.25</v>
       </c>
-      <c r="D126" s="80">
-        <f>$E$16*C126/100</f>
+      <c r="D131" s="80">
+        <f>$E$16*C131/100</f>
         <v>-0.425082649194728</v>
       </c>
-      <c r="E126" s="80">
-        <f>-$E$26*C126/100</f>
-        <v>0.425082649194728</v>
-      </c>
-      <c r="F126" s="125">
-        <f>D126+E126</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" s="123" t="str">
+      <c r="E131" s="80">
+        <f>-$E$32*C131/100</f>
+        <v>0.30363046371052</v>
+      </c>
+      <c r="F131" s="125">
+        <f>D131+E131</f>
+        <v>-0.121452185484208</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="123" t="str">
         <f>'VIENTO NTDV-97'!J152</f>
         <v>L1-8</v>
       </c>
-      <c r="C127" s="124">
+      <c r="C132" s="124">
         <f>'VIENTO NTDV-97'!K152</f>
         <v>1.315</v>
       </c>
-      <c r="D127" s="80">
-        <f>$E$16*C127/100</f>
+      <c r="D132" s="80">
+        <f>$E$16*C132/100</f>
         <v>-0.447186946952854</v>
       </c>
-      <c r="E127" s="80">
-        <f>-$E$26*C127/100</f>
-        <v>0.447186946952854</v>
-      </c>
-      <c r="F127" s="125">
-        <f>D127+E127</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" s="123" t="str">
+      <c r="E132" s="80">
+        <f>-$E$32*C132/100</f>
+        <v>0.319419247823467</v>
+      </c>
+      <c r="F132" s="125">
+        <f>D132+E132</f>
+        <v>-0.127767699129387</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="123" t="str">
         <f>'VIENTO NTDV-97'!J153</f>
         <v>VM-1 sup.</v>
       </c>
-      <c r="C128" s="124">
+      <c r="C133" s="124">
         <f>'VIENTO NTDV-97'!K153</f>
         <v>0.715</v>
       </c>
-      <c r="D128" s="80">
-        <f>$E$16*C128/100</f>
+      <c r="D133" s="80">
+        <f>$E$16*C133/100</f>
         <v>-0.243147275339385</v>
       </c>
-      <c r="E128" s="80">
-        <f>-$E$26*C128/100</f>
-        <v>0.243147275339385</v>
-      </c>
-      <c r="F128" s="125">
-        <f>D128+E128</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="B130" s="78" t="inlineStr">
+      <c r="E133" s="80">
+        <f>-$E$32*C133/100</f>
+        <v>0.173676625242418</v>
+      </c>
+      <c r="F133" s="125">
+        <f>D133+E133</f>
+        <v>-0.069470650096967</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">CUBIERTA — LARGUEROS Y VIGAS DE MARCO   (Cpe techo)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="34.8" customHeight="1">
-      <c r="B131" s="122" t="inlineStr">
+    <row r="136" ht="34.8" customHeight="1">
+      <c r="B136" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="C131" s="77" t="inlineStr">
+      <c r="C136" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="D131" s="77" t="inlineStr">
+      <c r="D136" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd externa (kg/cm)</t>
         </is>
       </c>
-      <c r="E131" s="77" t="inlineStr">
+      <c r="E136" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="F131" s="77" t="inlineStr">
+      <c r="F136" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="B132" s="123" t="str">
+    <row r="137">
+      <c r="B137" s="123" t="str">
         <f>'VIENTO NTDV-97'!N142</f>
         <v>VM-1</v>
       </c>
-      <c r="C132" s="124">
+      <c r="C137" s="124">
         <f>'VIENTO NTDV-97'!O142</f>
         <v>0.5</v>
       </c>
-      <c r="D132" s="80">
-        <f>$E$17*C132/100</f>
+      <c r="D137" s="80">
+        <f>$E$17*C137/100</f>
         <v>-0.170033059677891</v>
       </c>
-      <c r="E132" s="80">
-        <f>-$E$26*C132/100</f>
-        <v>0.170033059677891</v>
-      </c>
-      <c r="F132" s="125">
-        <f>D132+E132</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="B133" s="123" t="str">
+      <c r="E137" s="80">
+        <f>-$E$32*C137/100</f>
+        <v>0.121452185484208</v>
+      </c>
+      <c r="F137" s="125">
+        <f>D137+E137</f>
+        <v>-0.0485808741936832</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="123" t="str">
         <f>'VIENTO NTDV-97'!N143</f>
         <v>LT-1</v>
       </c>
-      <c r="C133" s="124">
+      <c r="C138" s="124">
         <f>'VIENTO NTDV-97'!O143</f>
         <v>1.25</v>
       </c>
-      <c r="D133" s="80">
-        <f>$E$17*C133/100</f>
+      <c r="D138" s="80">
+        <f>$E$17*C138/100</f>
         <v>-0.425082649194728</v>
       </c>
-      <c r="E133" s="80">
-        <f>-$E$26*C133/100</f>
-        <v>0.425082649194728</v>
-      </c>
-      <c r="F133" s="125">
-        <f>D133+E133</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="B134" s="123" t="str">
+      <c r="E138" s="80">
+        <f>-$E$32*C138/100</f>
+        <v>0.30363046371052</v>
+      </c>
+      <c r="F138" s="125">
+        <f>D138+E138</f>
+        <v>-0.121452185484208</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="123" t="str">
         <f>'VIENTO NTDV-97'!N144</f>
         <v>LT-2</v>
       </c>
-      <c r="C134" s="124">
+      <c r="C139" s="124">
         <f>'VIENTO NTDV-97'!O144</f>
-        <v>1.5</v>
-      </c>
-      <c r="D134" s="80">
-        <f>$E$17*C134/100</f>
-        <v>-0.510099179033674</v>
-      </c>
-      <c r="E134" s="80">
-        <f>-$E$26*C134/100</f>
-        <v>0.510099179033674</v>
-      </c>
-      <c r="F134" s="125">
-        <f>D134+E134</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="B135" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N145</f>
-        <v>LT-3</v>
-      </c>
-      <c r="C135" s="124">
-        <f>'VIENTO NTDV-97'!O145</f>
-        <v>1.5</v>
-      </c>
-      <c r="D135" s="80">
-        <f>$E$17*C135/100</f>
-        <v>-0.510099179033674</v>
-      </c>
-      <c r="E135" s="80">
-        <f>-$E$26*C135/100</f>
-        <v>0.510099179033674</v>
-      </c>
-      <c r="F135" s="125">
-        <f>D135+E135</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="B136" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N146</f>
-        <v>LT-4</v>
-      </c>
-      <c r="C136" s="124">
-        <f>'VIENTO NTDV-97'!O146</f>
-        <v>1.5</v>
-      </c>
-      <c r="D136" s="80">
-        <f>$E$17*C136/100</f>
-        <v>-0.510099179033674</v>
-      </c>
-      <c r="E136" s="80">
-        <f>-$E$26*C136/100</f>
-        <v>0.510099179033674</v>
-      </c>
-      <c r="F136" s="125">
-        <f>D136+E136</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="B137" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N147</f>
-        <v>LT-5</v>
-      </c>
-      <c r="C137" s="124">
-        <f>'VIENTO NTDV-97'!O147</f>
-        <v>0.75</v>
-      </c>
-      <c r="D137" s="80">
-        <f>$E$17*C137/100</f>
-        <v>-0.255049589516837</v>
-      </c>
-      <c r="E137" s="80">
-        <f>-$E$26*C137/100</f>
-        <v>0.255049589516837</v>
-      </c>
-      <c r="F137" s="125">
-        <f>D137+E137</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="B138" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N148</f>
-        <v>LT-6</v>
-      </c>
-      <c r="C138" s="124">
-        <f>'VIENTO NTDV-97'!O148</f>
-        <v>1.5</v>
-      </c>
-      <c r="D138" s="80">
-        <f>$E$17*C138/100</f>
-        <v>-0.510099179033674</v>
-      </c>
-      <c r="E138" s="80">
-        <f>-$E$26*C138/100</f>
-        <v>0.510099179033674</v>
-      </c>
-      <c r="F138" s="125">
-        <f>D138+E138</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="B139" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N149</f>
-        <v>VM-2</v>
-      </c>
-      <c r="C139" s="124">
-        <f>'VIENTO NTDV-97'!O149</f>
         <v>1.5</v>
       </c>
       <c r="D139" s="80">
@@ -17769,21 +17717,21 @@
         <v>-0.510099179033674</v>
       </c>
       <c r="E139" s="80">
-        <f>-$E$26*C139/100</f>
-        <v>0.510099179033674</v>
+        <f>-$E$32*C139/100</f>
+        <v>0.364356556452624</v>
       </c>
       <c r="F139" s="125">
         <f>D139+E139</f>
-        <v>0.0</v>
+        <v>-0.14574262258105</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N150</f>
-        <v>LT-7</v>
+        <f>'VIENTO NTDV-97'!N145</f>
+        <v>LT-3</v>
       </c>
       <c r="C140" s="124">
-        <f>'VIENTO NTDV-97'!O150</f>
+        <f>'VIENTO NTDV-97'!O145</f>
         <v>1.5</v>
       </c>
       <c r="D140" s="80">
@@ -17791,21 +17739,21 @@
         <v>-0.510099179033674</v>
       </c>
       <c r="E140" s="80">
-        <f>-$E$26*C140/100</f>
-        <v>0.510099179033674</v>
+        <f>-$E$32*C140/100</f>
+        <v>0.364356556452624</v>
       </c>
       <c r="F140" s="125">
         <f>D140+E140</f>
-        <v>0.0</v>
+        <v>-0.14574262258105</v>
       </c>
     </row>
     <row r="141">
       <c r="B141" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N151</f>
-        <v>LT-8</v>
+        <f>'VIENTO NTDV-97'!N146</f>
+        <v>LT-4</v>
       </c>
       <c r="C141" s="124">
-        <f>'VIENTO NTDV-97'!O151</f>
+        <f>'VIENTO NTDV-97'!O146</f>
         <v>1.5</v>
       </c>
       <c r="D141" s="80">
@@ -17813,728 +17761,728 @@
         <v>-0.510099179033674</v>
       </c>
       <c r="E141" s="80">
-        <f>-$E$26*C141/100</f>
-        <v>0.510099179033674</v>
+        <f>-$E$32*C141/100</f>
+        <v>0.364356556452624</v>
       </c>
       <c r="F141" s="125">
         <f>D141+E141</f>
-        <v>0.0</v>
+        <v>-0.14574262258105</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N147</f>
+        <v>LT-5</v>
+      </c>
+      <c r="C142" s="124">
+        <f>'VIENTO NTDV-97'!O147</f>
+        <v>0.75</v>
+      </c>
+      <c r="D142" s="80">
+        <f>$E$17*C142/100</f>
+        <v>-0.255049589516837</v>
+      </c>
+      <c r="E142" s="80">
+        <f>-$E$32*C142/100</f>
+        <v>0.182178278226312</v>
+      </c>
+      <c r="F142" s="125">
+        <f>D142+E142</f>
+        <v>-0.0728713112905249</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N148</f>
+        <v>LT-6</v>
+      </c>
+      <c r="C143" s="124">
+        <f>'VIENTO NTDV-97'!O148</f>
+        <v>1.5</v>
+      </c>
+      <c r="D143" s="80">
+        <f>$E$17*C143/100</f>
+        <v>-0.510099179033674</v>
+      </c>
+      <c r="E143" s="80">
+        <f>-$E$32*C143/100</f>
+        <v>0.364356556452624</v>
+      </c>
+      <c r="F143" s="125">
+        <f>D143+E143</f>
+        <v>-0.14574262258105</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N149</f>
+        <v>VM-2</v>
+      </c>
+      <c r="C144" s="124">
+        <f>'VIENTO NTDV-97'!O149</f>
+        <v>1.5</v>
+      </c>
+      <c r="D144" s="80">
+        <f>$E$17*C144/100</f>
+        <v>-0.510099179033674</v>
+      </c>
+      <c r="E144" s="80">
+        <f>-$E$32*C144/100</f>
+        <v>0.364356556452624</v>
+      </c>
+      <c r="F144" s="125">
+        <f>D144+E144</f>
+        <v>-0.14574262258105</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N150</f>
+        <v>LT-7</v>
+      </c>
+      <c r="C145" s="124">
+        <f>'VIENTO NTDV-97'!O150</f>
+        <v>1.5</v>
+      </c>
+      <c r="D145" s="80">
+        <f>$E$17*C145/100</f>
+        <v>-0.510099179033674</v>
+      </c>
+      <c r="E145" s="80">
+        <f>-$E$32*C145/100</f>
+        <v>0.364356556452624</v>
+      </c>
+      <c r="F145" s="125">
+        <f>D145+E145</f>
+        <v>-0.14574262258105</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N151</f>
+        <v>LT-8</v>
+      </c>
+      <c r="C146" s="124">
+        <f>'VIENTO NTDV-97'!O151</f>
+        <v>1.5</v>
+      </c>
+      <c r="D146" s="80">
+        <f>$E$17*C146/100</f>
+        <v>-0.510099179033674</v>
+      </c>
+      <c r="E146" s="80">
+        <f>-$E$32*C146/100</f>
+        <v>0.364356556452624</v>
+      </c>
+      <c r="F146" s="125">
+        <f>D146+E146</f>
+        <v>-0.14574262258105</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="123" t="str">
         <f>'VIENTO NTDV-97'!N152</f>
         <v>LT-9</v>
       </c>
-      <c r="C142" s="124">
+      <c r="C147" s="124">
         <f>'VIENTO NTDV-97'!O152</f>
         <v>1.5</v>
       </c>
-      <c r="D142" s="80">
-        <f>$E$17*C142/100</f>
+      <c r="D147" s="80">
+        <f>$E$17*C147/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="E142" s="80">
-        <f>-$E$26*C142/100</f>
-        <v>0.510099179033674</v>
-      </c>
-      <c r="F142" s="125">
-        <f>D142+E142</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="B143" s="123" t="str">
+      <c r="E147" s="80">
+        <f>-$E$32*C147/100</f>
+        <v>0.364356556452624</v>
+      </c>
+      <c r="F147" s="125">
+        <f>D147+E147</f>
+        <v>-0.14574262258105</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="123" t="str">
         <f>'VIENTO NTDV-97'!N153</f>
         <v>VM-3</v>
       </c>
-      <c r="C143" s="124">
+      <c r="C148" s="124">
         <f>'VIENTO NTDV-97'!O153</f>
         <v>0.75</v>
       </c>
-      <c r="D143" s="80">
-        <f>$E$17*C143/100</f>
+      <c r="D148" s="80">
+        <f>$E$17*C148/100</f>
         <v>-0.255049589516837</v>
       </c>
-      <c r="E143" s="80">
-        <f>-$E$26*C143/100</f>
-        <v>0.255049589516837</v>
-      </c>
-      <c r="F143" s="125">
-        <f>D143+E143</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="146" ht="24" customHeight="1">
-      <c r="B146" s="81" t="inlineStr">
+      <c r="E148" s="80">
+        <f>-$E$32*C148/100</f>
+        <v>0.182178278226312</v>
+      </c>
+      <c r="F148" s="125">
+        <f>D148+E148</f>
+        <v>-0.0728713112905249</v>
+      </c>
+    </row>
+    <row r="151" ht="24" customHeight="1">
+      <c r="B151" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">VIENTO EN DIRECCION Z:</t>
         </is>
       </c>
-      <c r="C146" s="81"/>
-      <c r="D146" s="81"/>
-      <c r="E146" s="81"/>
-      <c r="F146" s="81"/>
-    </row>
-    <row r="148">
-      <c r="B148" s="78" t="inlineStr">
+      <c r="C151" s="81"/>
+      <c r="D151" s="81"/>
+      <c r="E151" s="81"/>
+      <c r="F151" s="81"/>
+    </row>
+    <row r="153">
+      <c r="B153" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">MURO 1 EN BARLOVENTO   (Cpe barlovento)</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="34.8" customHeight="1">
-      <c r="B149" s="122" t="inlineStr">
+    <row r="154" ht="34.8" customHeight="1">
+      <c r="B154" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="C149" s="77" t="inlineStr">
+      <c r="C154" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="D149" s="77" t="inlineStr">
+      <c r="D154" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd externa (kg/cm)</t>
         </is>
       </c>
-      <c r="E149" s="77" t="inlineStr">
+      <c r="E154" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="F149" s="77" t="inlineStr">
+      <c r="F154" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="B150" s="123" t="str">
+    <row r="155">
+      <c r="B155" s="123" t="str">
         <f>'VIENTO NTDV-97'!B173</f>
         <v>L1-1</v>
       </c>
-      <c r="C150" s="124">
+      <c r="C155" s="124">
         <f>'VIENTO NTDV-97'!C173</f>
         <v>0.9</v>
       </c>
-      <c r="D150" s="80">
-        <f>$E$14*C150/100</f>
+      <c r="D155" s="80">
+        <f>$E$14*C155/100</f>
         <v>0.349782294194519</v>
       </c>
-      <c r="E150" s="80">
-        <f>-$E$27*C150/100</f>
-        <v>0.218613933871575</v>
-      </c>
-      <c r="F150" s="125">
-        <f>D150+E150</f>
-        <v>0.568396228066094</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="B151" s="123" t="str">
+      <c r="E155" s="80">
+        <f>-$E$33*C155/100</f>
+        <v>0.262336720645889</v>
+      </c>
+      <c r="F155" s="125">
+        <f>D155+E155</f>
+        <v>0.612119014840409</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="123" t="str">
         <f>'VIENTO NTDV-97'!B174</f>
         <v>L1-2</v>
       </c>
-      <c r="C151" s="124">
+      <c r="C156" s="124">
         <f>'VIENTO NTDV-97'!C174</f>
         <v>1.2</v>
       </c>
-      <c r="D151" s="80">
-        <f>$E$14*C151/100</f>
+      <c r="D156" s="80">
+        <f>$E$14*C156/100</f>
         <v>0.466376392259359</v>
       </c>
-      <c r="E151" s="80">
-        <f>-$E$27*C151/100</f>
-        <v>0.291485245162099</v>
-      </c>
-      <c r="F151" s="125">
-        <f>D151+E151</f>
-        <v>0.757861637421459</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="B152" s="123" t="str">
+      <c r="E156" s="80">
+        <f>-$E$33*C156/100</f>
+        <v>0.349782294194519</v>
+      </c>
+      <c r="F156" s="125">
+        <f>D156+E156</f>
+        <v>0.816158686453878</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" s="123" t="str">
         <f>'VIENTO NTDV-97'!B175</f>
         <v>Dintel P.</v>
       </c>
-      <c r="C152" s="124">
+      <c r="C157" s="124">
         <f>'VIENTO NTDV-97'!C175</f>
         <v>0.3</v>
       </c>
-      <c r="D152" s="80">
-        <f>$E$14*C152/100</f>
+      <c r="D157" s="80">
+        <f>$E$14*C157/100</f>
         <v>0.11659409806484</v>
       </c>
-      <c r="E152" s="80">
-        <f>-$E$27*C152/100</f>
-        <v>0.0728713112905249</v>
-      </c>
-      <c r="F152" s="125">
-        <f>D152+E152</f>
-        <v>0.189465409355365</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="B153" s="123" t="str">
+      <c r="E157" s="80">
+        <f>-$E$33*C157/100</f>
+        <v>0.0874455735486298</v>
+      </c>
+      <c r="F157" s="125">
+        <f>D157+E157</f>
+        <v>0.20403967161347</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="123" t="str">
         <f>'VIENTO NTDV-97'!B176</f>
         <v>L1-3</v>
       </c>
-      <c r="C153" s="124">
+      <c r="C158" s="124">
         <f>'VIENTO NTDV-97'!C176</f>
         <v>1.2</v>
       </c>
-      <c r="D153" s="80">
-        <f>$E$14*C153/100</f>
+      <c r="D158" s="80">
+        <f>$E$14*C158/100</f>
         <v>0.466376392259359</v>
       </c>
-      <c r="E153" s="80">
-        <f>-$E$27*C153/100</f>
-        <v>0.291485245162099</v>
-      </c>
-      <c r="F153" s="125">
-        <f>D153+E153</f>
-        <v>0.757861637421459</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="B154" s="123" t="str">
+      <c r="E158" s="80">
+        <f>-$E$33*C158/100</f>
+        <v>0.349782294194519</v>
+      </c>
+      <c r="F158" s="125">
+        <f>D158+E158</f>
+        <v>0.816158686453878</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" s="123" t="str">
         <f>'VIENTO NTDV-97'!B177</f>
         <v>L1-3 P.</v>
       </c>
-      <c r="C154" s="124">
+      <c r="C159" s="124">
         <f>'VIENTO NTDV-97'!C177</f>
         <v>0.9</v>
       </c>
-      <c r="D154" s="80">
-        <f>$E$14*C154/100</f>
+      <c r="D159" s="80">
+        <f>$E$14*C159/100</f>
         <v>0.349782294194519</v>
       </c>
-      <c r="E154" s="80">
-        <f>-$E$27*C154/100</f>
-        <v>0.218613933871575</v>
-      </c>
-      <c r="F154" s="125">
-        <f>D154+E154</f>
-        <v>0.568396228066094</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="B155" s="123" t="str">
+      <c r="E159" s="80">
+        <f>-$E$33*C159/100</f>
+        <v>0.262336720645889</v>
+      </c>
+      <c r="F159" s="125">
+        <f>D159+E159</f>
+        <v>0.612119014840409</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" s="123" t="str">
         <f>'VIENTO NTDV-97'!B178</f>
         <v>L1-4</v>
       </c>
-      <c r="C155" s="124">
+      <c r="C160" s="124">
         <f>'VIENTO NTDV-97'!C178</f>
         <v>1.2</v>
       </c>
-      <c r="D155" s="80">
-        <f>$E$14*C155/100</f>
+      <c r="D160" s="80">
+        <f>$E$14*C160/100</f>
         <v>0.466376392259359</v>
       </c>
-      <c r="E155" s="80">
-        <f>-$E$27*C155/100</f>
-        <v>0.291485245162099</v>
-      </c>
-      <c r="F155" s="125">
-        <f>D155+E155</f>
-        <v>0.757861637421459</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="B156" s="123" t="str">
+      <c r="E160" s="80">
+        <f>-$E$33*C160/100</f>
+        <v>0.349782294194519</v>
+      </c>
+      <c r="F160" s="125">
+        <f>D160+E160</f>
+        <v>0.816158686453878</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="123" t="str">
         <f>'VIENTO NTDV-97'!B179</f>
         <v>L1-5</v>
       </c>
-      <c r="C156" s="124">
+      <c r="C161" s="124">
         <f>'VIENTO NTDV-97'!C179</f>
         <v>1.15</v>
       </c>
-      <c r="D156" s="80">
-        <f>$E$14*C156/100</f>
+      <c r="D161" s="80">
+        <f>$E$14*C161/100</f>
         <v>0.446944042581886</v>
       </c>
-      <c r="E156" s="80">
-        <f>-$E$27*C156/100</f>
-        <v>0.279340026613679</v>
-      </c>
-      <c r="F156" s="125">
-        <f>D156+E156</f>
-        <v>0.726284069195564</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="B157" s="123" t="str">
+      <c r="E161" s="80">
+        <f>-$E$33*C161/100</f>
+        <v>0.335208031936414</v>
+      </c>
+      <c r="F161" s="125">
+        <f>D161+E161</f>
+        <v>0.7821520745183</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="123" t="str">
         <f>'VIENTO NTDV-97'!B180</f>
         <v>L1-6 lat.</v>
       </c>
-      <c r="C157" s="124">
+      <c r="C162" s="124">
         <f>'VIENTO NTDV-97'!C180</f>
         <v>1.2</v>
       </c>
-      <c r="D157" s="80">
-        <f>$E$14*C157/100</f>
+      <c r="D162" s="80">
+        <f>$E$14*C162/100</f>
         <v>0.466376392259359</v>
       </c>
-      <c r="E157" s="80">
-        <f>-$E$27*C157/100</f>
-        <v>0.291485245162099</v>
-      </c>
-      <c r="F157" s="125">
-        <f>D157+E157</f>
-        <v>0.757861637421459</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="B158" s="123" t="str">
+      <c r="E162" s="80">
+        <f>-$E$33*C162/100</f>
+        <v>0.349782294194519</v>
+      </c>
+      <c r="F162" s="125">
+        <f>D162+E162</f>
+        <v>0.816158686453878</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" s="123" t="str">
         <f>'VIENTO NTDV-97'!B181</f>
         <v>L1-6 cen.</v>
       </c>
-      <c r="C158" s="124">
+      <c r="C163" s="124">
         <f>'VIENTO NTDV-97'!C181</f>
         <v>0.65</v>
       </c>
-      <c r="D158" s="80">
-        <f>$E$14*C158/100</f>
+      <c r="D163" s="80">
+        <f>$E$14*C163/100</f>
         <v>0.252620545807153</v>
       </c>
-      <c r="E158" s="80">
-        <f>-$E$27*C158/100</f>
-        <v>0.157887841129471</v>
-      </c>
-      <c r="F158" s="125">
-        <f>D158+E158</f>
-        <v>0.410508386936623</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="B159" s="123" t="str">
+      <c r="E163" s="80">
+        <f>-$E$33*C163/100</f>
+        <v>0.189465409355365</v>
+      </c>
+      <c r="F163" s="125">
+        <f>D163+E163</f>
+        <v>0.442085955162518</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" s="123" t="str">
         <f>'VIENTO NTDV-97'!B182</f>
         <v>L1-7</v>
       </c>
-      <c r="C159" s="124">
+      <c r="C164" s="124">
         <f>'VIENTO NTDV-97'!C182</f>
         <v>1.25</v>
       </c>
-      <c r="D159" s="80">
-        <f>$E$14*C159/100</f>
+      <c r="D164" s="80">
+        <f>$E$14*C164/100</f>
         <v>0.485808741936832</v>
       </c>
-      <c r="E159" s="80">
-        <f>-$E$27*C159/100</f>
-        <v>0.30363046371052</v>
-      </c>
-      <c r="F159" s="125">
-        <f>D159+E159</f>
-        <v>0.789439205647353</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="B160" s="123" t="str">
+      <c r="E164" s="80">
+        <f>-$E$33*C164/100</f>
+        <v>0.364356556452624</v>
+      </c>
+      <c r="F164" s="125">
+        <f>D164+E164</f>
+        <v>0.850165298389457</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="123" t="str">
         <f>'VIENTO NTDV-97'!B183</f>
         <v>L1-8</v>
       </c>
-      <c r="C160" s="124">
+      <c r="C165" s="124">
         <f>'VIENTO NTDV-97'!C183</f>
         <v>1.315</v>
       </c>
-      <c r="D160" s="80">
-        <f>$E$14*C160/100</f>
+      <c r="D165" s="80">
+        <f>$E$14*C165/100</f>
         <v>0.511070796517548</v>
       </c>
-      <c r="E160" s="80">
-        <f>-$E$27*C160/100</f>
-        <v>0.319419247823467</v>
-      </c>
-      <c r="F160" s="125">
-        <f>D160+E160</f>
-        <v>0.830490044341015</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="B161" s="123" t="str">
+      <c r="E165" s="80">
+        <f>-$E$33*C165/100</f>
+        <v>0.383303097388161</v>
+      </c>
+      <c r="F165" s="125">
+        <f>D165+E165</f>
+        <v>0.894373893905708</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" s="123" t="str">
         <f>'VIENTO NTDV-97'!B184</f>
         <v>VM-1 sup.</v>
       </c>
-      <c r="C161" s="124">
+      <c r="C166" s="124">
         <f>'VIENTO NTDV-97'!C184</f>
         <v>0.715</v>
       </c>
-      <c r="D161" s="80">
-        <f>$E$14*C161/100</f>
+      <c r="D166" s="80">
+        <f>$E$14*C166/100</f>
         <v>0.277882600387868</v>
       </c>
-      <c r="E161" s="80">
-        <f>-$E$27*C161/100</f>
-        <v>0.173676625242418</v>
-      </c>
-      <c r="F161" s="125">
-        <f>D161+E161</f>
-        <v>0.451559225630286</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="B163" s="78" t="inlineStr">
+      <c r="E166" s="80">
+        <f>-$E$33*C166/100</f>
+        <v>0.208411950290901</v>
+      </c>
+      <c r="F166" s="125">
+        <f>D166+E166</f>
+        <v>0.486294550678769</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">MUROS LATERALES A/B   (Cpe lateral)</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="34.8" customHeight="1">
-      <c r="B164" s="122" t="inlineStr">
+    <row r="169" ht="34.8" customHeight="1">
+      <c r="B169" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="C164" s="77" t="inlineStr">
+      <c r="C169" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="D164" s="77" t="inlineStr">
+      <c r="D169" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd externa (kg/cm)</t>
         </is>
       </c>
-      <c r="E164" s="77" t="inlineStr">
+      <c r="E169" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="F164" s="77" t="inlineStr">
+      <c r="F169" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="B165" s="123" t="str">
+    <row r="170">
+      <c r="B170" s="123" t="str">
         <f>'VIENTO NTDV-97'!J173</f>
         <v>LA-1</v>
       </c>
-      <c r="C165" s="124">
+      <c r="C170" s="124">
         <f>'VIENTO NTDV-97'!K173</f>
         <v>0.9</v>
       </c>
-      <c r="D165" s="80">
-        <f>$E$16*C165/100</f>
+      <c r="D170" s="80">
+        <f>$E$16*C170/100</f>
         <v>-0.306059507420204</v>
       </c>
-      <c r="E165" s="80">
-        <f>-$E$27*C165/100</f>
-        <v>0.218613933871575</v>
-      </c>
-      <c r="F165" s="125">
-        <f>D165+E165</f>
-        <v>-0.0874455735486298</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="B166" s="123" t="str">
+      <c r="E170" s="80">
+        <f>-$E$33*C170/100</f>
+        <v>0.262336720645889</v>
+      </c>
+      <c r="F170" s="125">
+        <f>D170+E170</f>
+        <v>-0.043722786774315</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" s="123" t="str">
         <f>'VIENTO NTDV-97'!J174</f>
         <v>LA-2 a 7</v>
       </c>
-      <c r="C166" s="124">
+      <c r="C171" s="124">
         <f>'VIENTO NTDV-97'!K174</f>
         <v>1.2</v>
       </c>
-      <c r="D166" s="80">
-        <f>$E$16*C166/100</f>
+      <c r="D171" s="80">
+        <f>$E$16*C171/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="E166" s="80">
-        <f>-$E$27*C166/100</f>
-        <v>0.291485245162099</v>
-      </c>
-      <c r="F166" s="125">
-        <f>D166+E166</f>
-        <v>-0.11659409806484</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="B167" s="123" t="str">
+      <c r="E171" s="80">
+        <f>-$E$33*C171/100</f>
+        <v>0.349782294194519</v>
+      </c>
+      <c r="F171" s="125">
+        <f>D171+E171</f>
+        <v>-0.0582970490324199</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="123" t="str">
         <f>'VIENTO NTDV-97'!J175</f>
         <v>LA-8 (1-2)</v>
       </c>
-      <c r="C167" s="124">
+      <c r="C172" s="124">
         <f>'VIENTO NTDV-97'!K175</f>
         <v>1.185315</v>
       </c>
-      <c r="D167" s="80">
-        <f>$E$16*C167/100</f>
+      <c r="D172" s="80">
+        <f>$E$16*C172/100</f>
         <v>-0.403085472264199</v>
       </c>
-      <c r="E167" s="80">
-        <f>-$E$27*C167/100</f>
-        <v>0.287918194474428</v>
-      </c>
-      <c r="F167" s="125">
-        <f>D167+E167</f>
-        <v>-0.115167277789771</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="B168" s="123" t="str">
+      <c r="E172" s="80">
+        <f>-$E$33*C172/100</f>
+        <v>0.345501833369314</v>
+      </c>
+      <c r="F172" s="125">
+        <f>D172+E172</f>
+        <v>-0.0575836388948856</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" s="123" t="str">
         <f>'VIENTO NTDV-97'!J176</f>
         <v>LA-8 (2-3)</v>
       </c>
-      <c r="C168" s="124">
+      <c r="C173" s="124">
         <f>'VIENTO NTDV-97'!K176</f>
         <v>0.97782</v>
       </c>
-      <c r="D168" s="80">
-        <f>$E$16*C168/100</f>
+      <c r="D173" s="80">
+        <f>$E$16*C173/100</f>
         <v>-0.332523452828471</v>
       </c>
-      <c r="E168" s="80">
-        <f>-$E$27*C168/100</f>
-        <v>0.237516752020337</v>
-      </c>
-      <c r="F168" s="125">
-        <f>D168+E168</f>
-        <v>-0.0950067008081347</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="B169" s="123" t="str">
+      <c r="E173" s="80">
+        <f>-$E$33*C173/100</f>
+        <v>0.285020102424404</v>
+      </c>
+      <c r="F173" s="125">
+        <f>D173+E173</f>
+        <v>-0.0475033504040674</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" s="123" t="str">
         <f>'VIENTO NTDV-97'!J177</f>
         <v>VA-1 sup.</v>
       </c>
-      <c r="C169" s="124">
+      <c r="C174" s="124">
         <f>'VIENTO NTDV-97'!K177</f>
         <v>0.585315</v>
       </c>
-      <c r="D169" s="80">
-        <f>$E$16*C169/100</f>
+      <c r="D174" s="80">
+        <f>$E$16*C174/100</f>
         <v>-0.19904580065073</v>
       </c>
-      <c r="E169" s="80">
-        <f>-$E$27*C169/100</f>
-        <v>0.142175571893379</v>
-      </c>
-      <c r="F169" s="125">
-        <f>D169+E169</f>
-        <v>-0.0568702287573514</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="B170" s="123" t="str">
+      <c r="E174" s="80">
+        <f>-$E$33*C174/100</f>
+        <v>0.170610686272054</v>
+      </c>
+      <c r="F174" s="125">
+        <f>D174+E174</f>
+        <v>-0.0284351143786757</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" s="123" t="str">
         <f>'VIENTO NTDV-97'!J178</f>
         <v>VA-2 sup.</v>
       </c>
-      <c r="C170" s="124">
+      <c r="C175" s="124">
         <f>'VIENTO NTDV-97'!K178</f>
         <v>0.37782</v>
       </c>
-      <c r="D170" s="80">
-        <f>$E$16*C170/100</f>
+      <c r="D175" s="80">
+        <f>$E$16*C175/100</f>
         <v>-0.128483781215002</v>
       </c>
-      <c r="E170" s="80">
-        <f>-$E$27*C170/100</f>
-        <v>0.091774129439287</v>
-      </c>
-      <c r="F170" s="125">
-        <f>D170+E170</f>
-        <v>-0.0367096517757148</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="B172" s="78" t="inlineStr">
+      <c r="E175" s="80">
+        <f>-$E$33*C175/100</f>
+        <v>0.110128955327144</v>
+      </c>
+      <c r="F175" s="125">
+        <f>D175+E175</f>
+        <v>-0.0183548258878574</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">CUBIERTA — LARGUEROS Y VIGAS DE MARCO   (Cpe techo)</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="34.8" customHeight="1">
-      <c r="B173" s="122" t="inlineStr">
+    <row r="178" ht="34.8" customHeight="1">
+      <c r="B178" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="C173" s="77" t="inlineStr">
+      <c r="C178" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="D173" s="77" t="inlineStr">
+      <c r="D178" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd externa (kg/cm)</t>
         </is>
       </c>
-      <c r="E173" s="77" t="inlineStr">
+      <c r="E178" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="F173" s="77" t="inlineStr">
+      <c r="F178" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="B174" s="123" t="str">
+    <row r="179">
+      <c r="B179" s="123" t="str">
         <f>'VIENTO NTDV-97'!N173</f>
         <v>VM-1</v>
       </c>
-      <c r="C174" s="124">
+      <c r="C179" s="124">
         <f>'VIENTO NTDV-97'!O173</f>
         <v>0.5</v>
       </c>
-      <c r="D174" s="80">
-        <f>$E$17*C174/100</f>
+      <c r="D179" s="80">
+        <f>$E$17*C179/100</f>
         <v>-0.170033059677891</v>
       </c>
-      <c r="E174" s="80">
-        <f>-$E$27*C174/100</f>
-        <v>0.121452185484208</v>
-      </c>
-      <c r="F174" s="125">
-        <f>D174+E174</f>
-        <v>-0.0485808741936832</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="B175" s="123" t="str">
+      <c r="E179" s="80">
+        <f>-$E$33*C179/100</f>
+        <v>0.14574262258105</v>
+      </c>
+      <c r="F179" s="125">
+        <f>D179+E179</f>
+        <v>-0.0242904370968416</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" s="123" t="str">
         <f>'VIENTO NTDV-97'!N174</f>
         <v>LT-1</v>
       </c>
-      <c r="C175" s="124">
+      <c r="C180" s="124">
         <f>'VIENTO NTDV-97'!O174</f>
         <v>1.25</v>
       </c>
-      <c r="D175" s="80">
-        <f>$E$17*C175/100</f>
+      <c r="D180" s="80">
+        <f>$E$17*C180/100</f>
         <v>-0.425082649194728</v>
       </c>
-      <c r="E175" s="80">
-        <f>-$E$27*C175/100</f>
-        <v>0.30363046371052</v>
-      </c>
-      <c r="F175" s="125">
-        <f>D175+E175</f>
-        <v>-0.121452185484208</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="B176" s="123" t="str">
+      <c r="E180" s="80">
+        <f>-$E$33*C180/100</f>
+        <v>0.364356556452624</v>
+      </c>
+      <c r="F180" s="125">
+        <f>D180+E180</f>
+        <v>-0.0607260927421041</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" s="123" t="str">
         <f>'VIENTO NTDV-97'!N175</f>
         <v>LT-2</v>
       </c>
-      <c r="C176" s="124">
+      <c r="C181" s="124">
         <f>'VIENTO NTDV-97'!O175</f>
-        <v>1.5</v>
-      </c>
-      <c r="D176" s="80">
-        <f>$E$17*C176/100</f>
-        <v>-0.510099179033674</v>
-      </c>
-      <c r="E176" s="80">
-        <f>-$E$27*C176/100</f>
-        <v>0.364356556452624</v>
-      </c>
-      <c r="F176" s="125">
-        <f>D176+E176</f>
-        <v>-0.14574262258105</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="B177" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N176</f>
-        <v>LT-3</v>
-      </c>
-      <c r="C177" s="124">
-        <f>'VIENTO NTDV-97'!O176</f>
-        <v>1.5</v>
-      </c>
-      <c r="D177" s="80">
-        <f>$E$17*C177/100</f>
-        <v>-0.510099179033674</v>
-      </c>
-      <c r="E177" s="80">
-        <f>-$E$27*C177/100</f>
-        <v>0.364356556452624</v>
-      </c>
-      <c r="F177" s="125">
-        <f>D177+E177</f>
-        <v>-0.14574262258105</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="B178" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N177</f>
-        <v>LT-4</v>
-      </c>
-      <c r="C178" s="124">
-        <f>'VIENTO NTDV-97'!O177</f>
-        <v>1.5</v>
-      </c>
-      <c r="D178" s="80">
-        <f>$E$17*C178/100</f>
-        <v>-0.510099179033674</v>
-      </c>
-      <c r="E178" s="80">
-        <f>-$E$27*C178/100</f>
-        <v>0.364356556452624</v>
-      </c>
-      <c r="F178" s="125">
-        <f>D178+E178</f>
-        <v>-0.14574262258105</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="B179" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N178</f>
-        <v>LT-5</v>
-      </c>
-      <c r="C179" s="124">
-        <f>'VIENTO NTDV-97'!O178</f>
-        <v>0.75</v>
-      </c>
-      <c r="D179" s="80">
-        <f>$E$17*C179/100</f>
-        <v>-0.255049589516837</v>
-      </c>
-      <c r="E179" s="80">
-        <f>-$E$27*C179/100</f>
-        <v>0.182178278226312</v>
-      </c>
-      <c r="F179" s="125">
-        <f>D179+E179</f>
-        <v>-0.0728713112905249</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="B180" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N179</f>
-        <v>LT-6</v>
-      </c>
-      <c r="C180" s="124">
-        <f>'VIENTO NTDV-97'!O179</f>
-        <v>1.5</v>
-      </c>
-      <c r="D180" s="80">
-        <f>$E$17*C180/100</f>
-        <v>-0.510099179033674</v>
-      </c>
-      <c r="E180" s="80">
-        <f>-$E$27*C180/100</f>
-        <v>0.364356556452624</v>
-      </c>
-      <c r="F180" s="125">
-        <f>D180+E180</f>
-        <v>-0.14574262258105</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="B181" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N180</f>
-        <v>VM-2</v>
-      </c>
-      <c r="C181" s="124">
-        <f>'VIENTO NTDV-97'!O180</f>
         <v>1.5</v>
       </c>
       <c r="D181" s="80">
@@ -18542,21 +18490,21 @@
         <v>-0.510099179033674</v>
       </c>
       <c r="E181" s="80">
-        <f>-$E$27*C181/100</f>
-        <v>0.364356556452624</v>
+        <f>-$E$33*C181/100</f>
+        <v>0.437227867743149</v>
       </c>
       <c r="F181" s="125">
         <f>D181+E181</f>
-        <v>-0.14574262258105</v>
+        <v>-0.0728713112905248</v>
       </c>
     </row>
     <row r="182">
       <c r="B182" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N181</f>
-        <v>LT-7</v>
+        <f>'VIENTO NTDV-97'!N176</f>
+        <v>LT-3</v>
       </c>
       <c r="C182" s="124">
-        <f>'VIENTO NTDV-97'!O181</f>
+        <f>'VIENTO NTDV-97'!O176</f>
         <v>1.5</v>
       </c>
       <c r="D182" s="80">
@@ -18564,21 +18512,21 @@
         <v>-0.510099179033674</v>
       </c>
       <c r="E182" s="80">
-        <f>-$E$27*C182/100</f>
-        <v>0.364356556452624</v>
+        <f>-$E$33*C182/100</f>
+        <v>0.437227867743149</v>
       </c>
       <c r="F182" s="125">
         <f>D182+E182</f>
-        <v>-0.14574262258105</v>
+        <v>-0.0728713112905248</v>
       </c>
     </row>
     <row r="183">
       <c r="B183" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N182</f>
-        <v>LT-8</v>
+        <f>'VIENTO NTDV-97'!N177</f>
+        <v>LT-4</v>
       </c>
       <c r="C183" s="124">
-        <f>'VIENTO NTDV-97'!O182</f>
+        <f>'VIENTO NTDV-97'!O177</f>
         <v>1.5</v>
       </c>
       <c r="D183" s="80">
@@ -18586,728 +18534,728 @@
         <v>-0.510099179033674</v>
       </c>
       <c r="E183" s="80">
-        <f>-$E$27*C183/100</f>
-        <v>0.364356556452624</v>
+        <f>-$E$33*C183/100</f>
+        <v>0.437227867743149</v>
       </c>
       <c r="F183" s="125">
         <f>D183+E183</f>
-        <v>-0.14574262258105</v>
+        <v>-0.0728713112905248</v>
       </c>
     </row>
     <row r="184">
       <c r="B184" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N178</f>
+        <v>LT-5</v>
+      </c>
+      <c r="C184" s="124">
+        <f>'VIENTO NTDV-97'!O178</f>
+        <v>0.75</v>
+      </c>
+      <c r="D184" s="80">
+        <f>$E$17*C184/100</f>
+        <v>-0.255049589516837</v>
+      </c>
+      <c r="E184" s="80">
+        <f>-$E$33*C184/100</f>
+        <v>0.218613933871575</v>
+      </c>
+      <c r="F184" s="125">
+        <f>D184+E184</f>
+        <v>-0.0364356556452624</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N179</f>
+        <v>LT-6</v>
+      </c>
+      <c r="C185" s="124">
+        <f>'VIENTO NTDV-97'!O179</f>
+        <v>1.5</v>
+      </c>
+      <c r="D185" s="80">
+        <f>$E$17*C185/100</f>
+        <v>-0.510099179033674</v>
+      </c>
+      <c r="E185" s="80">
+        <f>-$E$33*C185/100</f>
+        <v>0.437227867743149</v>
+      </c>
+      <c r="F185" s="125">
+        <f>D185+E185</f>
+        <v>-0.0728713112905248</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N180</f>
+        <v>VM-2</v>
+      </c>
+      <c r="C186" s="124">
+        <f>'VIENTO NTDV-97'!O180</f>
+        <v>1.5</v>
+      </c>
+      <c r="D186" s="80">
+        <f>$E$17*C186/100</f>
+        <v>-0.510099179033674</v>
+      </c>
+      <c r="E186" s="80">
+        <f>-$E$33*C186/100</f>
+        <v>0.437227867743149</v>
+      </c>
+      <c r="F186" s="125">
+        <f>D186+E186</f>
+        <v>-0.0728713112905248</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N181</f>
+        <v>LT-7</v>
+      </c>
+      <c r="C187" s="124">
+        <f>'VIENTO NTDV-97'!O181</f>
+        <v>1.5</v>
+      </c>
+      <c r="D187" s="80">
+        <f>$E$17*C187/100</f>
+        <v>-0.510099179033674</v>
+      </c>
+      <c r="E187" s="80">
+        <f>-$E$33*C187/100</f>
+        <v>0.437227867743149</v>
+      </c>
+      <c r="F187" s="125">
+        <f>D187+E187</f>
+        <v>-0.0728713112905248</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N182</f>
+        <v>LT-8</v>
+      </c>
+      <c r="C188" s="124">
+        <f>'VIENTO NTDV-97'!O182</f>
+        <v>1.5</v>
+      </c>
+      <c r="D188" s="80">
+        <f>$E$17*C188/100</f>
+        <v>-0.510099179033674</v>
+      </c>
+      <c r="E188" s="80">
+        <f>-$E$33*C188/100</f>
+        <v>0.437227867743149</v>
+      </c>
+      <c r="F188" s="125">
+        <f>D188+E188</f>
+        <v>-0.0728713112905248</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" s="123" t="str">
         <f>'VIENTO NTDV-97'!N183</f>
         <v>LT-9</v>
       </c>
-      <c r="C184" s="124">
+      <c r="C189" s="124">
         <f>'VIENTO NTDV-97'!O183</f>
         <v>1.5</v>
       </c>
-      <c r="D184" s="80">
-        <f>$E$17*C184/100</f>
+      <c r="D189" s="80">
+        <f>$E$17*C189/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="E184" s="80">
-        <f>-$E$27*C184/100</f>
-        <v>0.364356556452624</v>
-      </c>
-      <c r="F184" s="125">
-        <f>D184+E184</f>
-        <v>-0.14574262258105</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="B185" s="123" t="str">
+      <c r="E189" s="80">
+        <f>-$E$33*C189/100</f>
+        <v>0.437227867743149</v>
+      </c>
+      <c r="F189" s="125">
+        <f>D189+E189</f>
+        <v>-0.0728713112905248</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" s="123" t="str">
         <f>'VIENTO NTDV-97'!N184</f>
         <v>VM-3</v>
       </c>
-      <c r="C185" s="124">
+      <c r="C190" s="124">
         <f>'VIENTO NTDV-97'!O184</f>
         <v>0.75</v>
       </c>
-      <c r="D185" s="80">
-        <f>$E$17*C185/100</f>
+      <c r="D190" s="80">
+        <f>$E$17*C190/100</f>
         <v>-0.255049589516837</v>
       </c>
-      <c r="E185" s="80">
-        <f>-$E$27*C185/100</f>
-        <v>0.182178278226312</v>
-      </c>
-      <c r="F185" s="125">
-        <f>D185+E185</f>
-        <v>-0.0728713112905249</v>
-      </c>
-    </row>
-    <row r="188" ht="24" customHeight="1">
-      <c r="B188" s="81" t="inlineStr">
+      <c r="E190" s="80">
+        <f>-$E$33*C190/100</f>
+        <v>0.218613933871575</v>
+      </c>
+      <c r="F190" s="125">
+        <f>D190+E190</f>
+        <v>-0.0364356556452624</v>
+      </c>
+    </row>
+    <row r="193" ht="24" customHeight="1">
+      <c r="B193" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">VIENTO EN DIRECCION -Z:</t>
         </is>
       </c>
-      <c r="C188" s="81"/>
-      <c r="D188" s="81"/>
-      <c r="E188" s="81"/>
-      <c r="F188" s="81"/>
-    </row>
-    <row r="190">
-      <c r="B190" s="78" t="inlineStr">
+      <c r="C193" s="81"/>
+      <c r="D193" s="81"/>
+      <c r="E193" s="81"/>
+      <c r="F193" s="81"/>
+    </row>
+    <row r="195">
+      <c r="B195" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">MURO 1 EN SOTAVENTO   (Cpe sotavento)</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="34.8" customHeight="1">
-      <c r="B191" s="122" t="inlineStr">
+    <row r="196" ht="34.8" customHeight="1">
+      <c r="B196" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="C191" s="77" t="inlineStr">
+      <c r="C196" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="D191" s="77" t="inlineStr">
+      <c r="D196" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd externa (kg/cm)</t>
         </is>
       </c>
-      <c r="E191" s="77" t="inlineStr">
+      <c r="E196" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="F191" s="77" t="inlineStr">
+      <c r="F196" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="B192" s="123" t="str">
+    <row r="197">
+      <c r="B197" s="123" t="str">
         <f>'VIENTO NTDV-97'!F204</f>
         <v>L1-1</v>
       </c>
-      <c r="C192" s="124">
+      <c r="C197" s="124">
         <f>'VIENTO NTDV-97'!G204</f>
         <v>0.9</v>
       </c>
-      <c r="D192" s="80">
-        <f>$E$15*C192/100</f>
+      <c r="D197" s="80">
+        <f>$E$15*C197/100</f>
         <v>-0.218613933871575</v>
       </c>
-      <c r="E192" s="80">
-        <f>-$E$28*C192/100</f>
+      <c r="E197" s="80">
+        <f>-$E$34*C197/100</f>
         <v>-0.327920900807362</v>
       </c>
-      <c r="F192" s="125">
-        <f>D192+E192</f>
+      <c r="F197" s="125">
+        <f>D197+E197</f>
         <v>-0.546534834678937</v>
       </c>
     </row>
-    <row r="193">
-      <c r="B193" s="123" t="str">
+    <row r="198">
+      <c r="B198" s="123" t="str">
         <f>'VIENTO NTDV-97'!F205</f>
         <v>L1-2</v>
       </c>
-      <c r="C193" s="124">
+      <c r="C198" s="124">
         <f>'VIENTO NTDV-97'!G205</f>
         <v>1.2</v>
       </c>
-      <c r="D193" s="80">
-        <f>$E$15*C193/100</f>
+      <c r="D198" s="80">
+        <f>$E$15*C198/100</f>
         <v>-0.291485245162099</v>
       </c>
-      <c r="E193" s="80">
-        <f>-$E$28*C193/100</f>
+      <c r="E198" s="80">
+        <f>-$E$34*C198/100</f>
         <v>-0.437227867743149</v>
       </c>
-      <c r="F193" s="125">
-        <f>D193+E193</f>
+      <c r="F198" s="125">
+        <f>D198+E198</f>
         <v>-0.728713112905249</v>
       </c>
     </row>
-    <row r="194">
-      <c r="B194" s="123" t="str">
+    <row r="199">
+      <c r="B199" s="123" t="str">
         <f>'VIENTO NTDV-97'!F206</f>
         <v>Dintel P.</v>
       </c>
-      <c r="C194" s="124">
+      <c r="C199" s="124">
         <f>'VIENTO NTDV-97'!G206</f>
         <v>0.3</v>
       </c>
-      <c r="D194" s="80">
-        <f>$E$15*C194/100</f>
+      <c r="D199" s="80">
+        <f>$E$15*C199/100</f>
         <v>-0.0728713112905249</v>
       </c>
-      <c r="E194" s="80">
-        <f>-$E$28*C194/100</f>
+      <c r="E199" s="80">
+        <f>-$E$34*C199/100</f>
         <v>-0.109306966935787</v>
       </c>
-      <c r="F194" s="125">
-        <f>D194+E194</f>
+      <c r="F199" s="125">
+        <f>D199+E199</f>
         <v>-0.182178278226312</v>
       </c>
     </row>
-    <row r="195">
-      <c r="B195" s="123" t="str">
+    <row r="200">
+      <c r="B200" s="123" t="str">
         <f>'VIENTO NTDV-97'!F207</f>
         <v>L1-3</v>
       </c>
-      <c r="C195" s="124">
+      <c r="C200" s="124">
         <f>'VIENTO NTDV-97'!G207</f>
         <v>1.2</v>
       </c>
-      <c r="D195" s="80">
-        <f>$E$15*C195/100</f>
+      <c r="D200" s="80">
+        <f>$E$15*C200/100</f>
         <v>-0.291485245162099</v>
       </c>
-      <c r="E195" s="80">
-        <f>-$E$28*C195/100</f>
+      <c r="E200" s="80">
+        <f>-$E$34*C200/100</f>
         <v>-0.437227867743149</v>
       </c>
-      <c r="F195" s="125">
-        <f>D195+E195</f>
+      <c r="F200" s="125">
+        <f>D200+E200</f>
         <v>-0.728713112905249</v>
       </c>
     </row>
-    <row r="196">
-      <c r="B196" s="123" t="str">
+    <row r="201">
+      <c r="B201" s="123" t="str">
         <f>'VIENTO NTDV-97'!F208</f>
         <v>L1-3 P.</v>
       </c>
-      <c r="C196" s="124">
+      <c r="C201" s="124">
         <f>'VIENTO NTDV-97'!G208</f>
         <v>0.9</v>
       </c>
-      <c r="D196" s="80">
-        <f>$E$15*C196/100</f>
+      <c r="D201" s="80">
+        <f>$E$15*C201/100</f>
         <v>-0.218613933871575</v>
       </c>
-      <c r="E196" s="80">
-        <f>-$E$28*C196/100</f>
+      <c r="E201" s="80">
+        <f>-$E$34*C201/100</f>
         <v>-0.327920900807362</v>
       </c>
-      <c r="F196" s="125">
-        <f>D196+E196</f>
+      <c r="F201" s="125">
+        <f>D201+E201</f>
         <v>-0.546534834678937</v>
       </c>
     </row>
-    <row r="197">
-      <c r="B197" s="123" t="str">
+    <row r="202">
+      <c r="B202" s="123" t="str">
         <f>'VIENTO NTDV-97'!F209</f>
         <v>L1-4</v>
       </c>
-      <c r="C197" s="124">
+      <c r="C202" s="124">
         <f>'VIENTO NTDV-97'!G209</f>
         <v>1.2</v>
       </c>
-      <c r="D197" s="80">
-        <f>$E$15*C197/100</f>
+      <c r="D202" s="80">
+        <f>$E$15*C202/100</f>
         <v>-0.291485245162099</v>
       </c>
-      <c r="E197" s="80">
-        <f>-$E$28*C197/100</f>
+      <c r="E202" s="80">
+        <f>-$E$34*C202/100</f>
         <v>-0.437227867743149</v>
       </c>
-      <c r="F197" s="125">
-        <f>D197+E197</f>
+      <c r="F202" s="125">
+        <f>D202+E202</f>
         <v>-0.728713112905249</v>
       </c>
     </row>
-    <row r="198">
-      <c r="B198" s="123" t="str">
+    <row r="203">
+      <c r="B203" s="123" t="str">
         <f>'VIENTO NTDV-97'!F210</f>
         <v>L1-5</v>
       </c>
-      <c r="C198" s="124">
+      <c r="C203" s="124">
         <f>'VIENTO NTDV-97'!G210</f>
         <v>1.15</v>
       </c>
-      <c r="D198" s="80">
-        <f>$E$15*C198/100</f>
+      <c r="D203" s="80">
+        <f>$E$15*C203/100</f>
         <v>-0.279340026613679</v>
       </c>
-      <c r="E198" s="80">
-        <f>-$E$28*C198/100</f>
+      <c r="E203" s="80">
+        <f>-$E$34*C203/100</f>
         <v>-0.419010039920518</v>
       </c>
-      <c r="F198" s="125">
-        <f>D198+E198</f>
+      <c r="F203" s="125">
+        <f>D203+E203</f>
         <v>-0.698350066534196</v>
       </c>
     </row>
-    <row r="199">
-      <c r="B199" s="123" t="str">
+    <row r="204">
+      <c r="B204" s="123" t="str">
         <f>'VIENTO NTDV-97'!F211</f>
         <v>L1-6 lat.</v>
       </c>
-      <c r="C199" s="124">
+      <c r="C204" s="124">
         <f>'VIENTO NTDV-97'!G211</f>
         <v>1.2</v>
       </c>
-      <c r="D199" s="80">
-        <f>$E$15*C199/100</f>
+      <c r="D204" s="80">
+        <f>$E$15*C204/100</f>
         <v>-0.291485245162099</v>
       </c>
-      <c r="E199" s="80">
-        <f>-$E$28*C199/100</f>
+      <c r="E204" s="80">
+        <f>-$E$34*C204/100</f>
         <v>-0.437227867743149</v>
       </c>
-      <c r="F199" s="125">
-        <f>D199+E199</f>
+      <c r="F204" s="125">
+        <f>D204+E204</f>
         <v>-0.728713112905249</v>
       </c>
     </row>
-    <row r="200">
-      <c r="B200" s="123" t="str">
+    <row r="205">
+      <c r="B205" s="123" t="str">
         <f>'VIENTO NTDV-97'!F212</f>
         <v>L1-6 cen.</v>
       </c>
-      <c r="C200" s="124">
+      <c r="C205" s="124">
         <f>'VIENTO NTDV-97'!G212</f>
         <v>0.65</v>
       </c>
-      <c r="D200" s="80">
-        <f>$E$15*C200/100</f>
+      <c r="D205" s="80">
+        <f>$E$15*C205/100</f>
         <v>-0.157887841129471</v>
       </c>
-      <c r="E200" s="80">
-        <f>-$E$28*C200/100</f>
+      <c r="E205" s="80">
+        <f>-$E$34*C205/100</f>
         <v>-0.236831761694206</v>
       </c>
-      <c r="F200" s="125">
-        <f>D200+E200</f>
+      <c r="F205" s="125">
+        <f>D205+E205</f>
         <v>-0.394719602823676</v>
       </c>
     </row>
-    <row r="201">
-      <c r="B201" s="123" t="str">
+    <row r="206">
+      <c r="B206" s="123" t="str">
         <f>'VIENTO NTDV-97'!F213</f>
         <v>L1-7</v>
       </c>
-      <c r="C201" s="124">
+      <c r="C206" s="124">
         <f>'VIENTO NTDV-97'!G213</f>
         <v>1.25</v>
       </c>
-      <c r="D201" s="80">
-        <f>$E$15*C201/100</f>
+      <c r="D206" s="80">
+        <f>$E$15*C206/100</f>
         <v>-0.30363046371052</v>
       </c>
-      <c r="E201" s="80">
-        <f>-$E$28*C201/100</f>
+      <c r="E206" s="80">
+        <f>-$E$34*C206/100</f>
         <v>-0.45544569556578</v>
       </c>
-      <c r="F201" s="125">
-        <f>D201+E201</f>
+      <c r="F206" s="125">
+        <f>D206+E206</f>
         <v>-0.759076159276301</v>
       </c>
     </row>
-    <row r="202">
-      <c r="B202" s="123" t="str">
+    <row r="207">
+      <c r="B207" s="123" t="str">
         <f>'VIENTO NTDV-97'!F214</f>
         <v>L1-8</v>
       </c>
-      <c r="C202" s="124">
+      <c r="C207" s="124">
         <f>'VIENTO NTDV-97'!G214</f>
         <v>1.315</v>
       </c>
-      <c r="D202" s="80">
-        <f>$E$15*C202/100</f>
+      <c r="D207" s="80">
+        <f>$E$15*C207/100</f>
         <v>-0.319419247823467</v>
       </c>
-      <c r="E202" s="80">
-        <f>-$E$28*C202/100</f>
+      <c r="E207" s="80">
+        <f>-$E$34*C207/100</f>
         <v>-0.479128871735201</v>
       </c>
-      <c r="F202" s="125">
-        <f>D202+E202</f>
+      <c r="F207" s="125">
+        <f>D207+E207</f>
         <v>-0.798548119558668</v>
       </c>
     </row>
-    <row r="203">
-      <c r="B203" s="123" t="str">
+    <row r="208">
+      <c r="B208" s="123" t="str">
         <f>'VIENTO NTDV-97'!F215</f>
         <v>VM-1 sup.</v>
       </c>
-      <c r="C203" s="124">
+      <c r="C208" s="124">
         <f>'VIENTO NTDV-97'!G215</f>
         <v>0.715</v>
       </c>
-      <c r="D203" s="80">
-        <f>$E$15*C203/100</f>
+      <c r="D208" s="80">
+        <f>$E$15*C208/100</f>
         <v>-0.173676625242418</v>
       </c>
-      <c r="E203" s="80">
-        <f>-$E$28*C203/100</f>
+      <c r="E208" s="80">
+        <f>-$E$34*C208/100</f>
         <v>-0.260514937863626</v>
       </c>
-      <c r="F203" s="125">
-        <f>D203+E203</f>
+      <c r="F208" s="125">
+        <f>D208+E208</f>
         <v>-0.434191563106044</v>
       </c>
     </row>
-    <row r="205">
-      <c r="B205" s="78" t="inlineStr">
+    <row r="210">
+      <c r="B210" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">MUROS LATERALES A/B   (Cpe lateral)</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="34.8" customHeight="1">
-      <c r="B206" s="122" t="inlineStr">
+    <row r="211" ht="34.8" customHeight="1">
+      <c r="B211" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="C206" s="77" t="inlineStr">
+      <c r="C211" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="D206" s="77" t="inlineStr">
+      <c r="D211" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd externa (kg/cm)</t>
         </is>
       </c>
-      <c r="E206" s="77" t="inlineStr">
+      <c r="E211" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="F206" s="77" t="inlineStr">
+      <c r="F211" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="B207" s="123" t="str">
+    <row r="212">
+      <c r="B212" s="123" t="str">
         <f>'VIENTO NTDV-97'!J204</f>
         <v>LA-1</v>
       </c>
-      <c r="C207" s="124">
+      <c r="C212" s="124">
         <f>'VIENTO NTDV-97'!K204</f>
         <v>0.9</v>
       </c>
-      <c r="D207" s="80">
-        <f>$E$16*C207/100</f>
+      <c r="D212" s="80">
+        <f>$E$16*C212/100</f>
         <v>-0.306059507420204</v>
       </c>
-      <c r="E207" s="80">
-        <f>-$E$28*C207/100</f>
+      <c r="E212" s="80">
+        <f>-$E$34*C212/100</f>
         <v>-0.327920900807362</v>
       </c>
-      <c r="F207" s="125">
-        <f>D207+E207</f>
+      <c r="F212" s="125">
+        <f>D212+E212</f>
         <v>-0.633980408227566</v>
       </c>
     </row>
-    <row r="208">
-      <c r="B208" s="123" t="str">
+    <row r="213">
+      <c r="B213" s="123" t="str">
         <f>'VIENTO NTDV-97'!J205</f>
         <v>LA-2 a 7</v>
       </c>
-      <c r="C208" s="124">
+      <c r="C213" s="124">
         <f>'VIENTO NTDV-97'!K205</f>
         <v>1.2</v>
       </c>
-      <c r="D208" s="80">
-        <f>$E$16*C208/100</f>
+      <c r="D213" s="80">
+        <f>$E$16*C213/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="E208" s="80">
-        <f>-$E$28*C208/100</f>
+      <c r="E213" s="80">
+        <f>-$E$34*C213/100</f>
         <v>-0.437227867743149</v>
       </c>
-      <c r="F208" s="125">
-        <f>D208+E208</f>
+      <c r="F213" s="125">
+        <f>D213+E213</f>
         <v>-0.845307210970088</v>
       </c>
     </row>
-    <row r="209">
-      <c r="B209" s="123" t="str">
+    <row r="214">
+      <c r="B214" s="123" t="str">
         <f>'VIENTO NTDV-97'!J206</f>
         <v>LA-8 (1-2)</v>
       </c>
-      <c r="C209" s="124">
+      <c r="C214" s="124">
         <f>'VIENTO NTDV-97'!K206</f>
         <v>1.185315</v>
       </c>
-      <c r="D209" s="80">
-        <f>$E$16*C209/100</f>
+      <c r="D214" s="80">
+        <f>$E$16*C214/100</f>
         <v>-0.403085472264199</v>
       </c>
-      <c r="E209" s="80">
-        <f>-$E$28*C209/100</f>
+      <c r="E214" s="80">
+        <f>-$E$34*C214/100</f>
         <v>-0.431877291711642</v>
       </c>
-      <c r="F209" s="125">
-        <f>D209+E209</f>
+      <c r="F214" s="125">
+        <f>D214+E214</f>
         <v>-0.834962763975842</v>
       </c>
     </row>
-    <row r="210">
-      <c r="B210" s="123" t="str">
+    <row r="215">
+      <c r="B215" s="123" t="str">
         <f>'VIENTO NTDV-97'!J207</f>
         <v>LA-8 (2-3)</v>
       </c>
-      <c r="C210" s="124">
+      <c r="C215" s="124">
         <f>'VIENTO NTDV-97'!K207</f>
         <v>0.97782</v>
       </c>
-      <c r="D210" s="80">
-        <f>$E$16*C210/100</f>
+      <c r="D215" s="80">
+        <f>$E$16*C215/100</f>
         <v>-0.332523452828471</v>
       </c>
-      <c r="E210" s="80">
-        <f>-$E$28*C210/100</f>
+      <c r="E215" s="80">
+        <f>-$E$34*C215/100</f>
         <v>-0.356275128030505</v>
       </c>
-      <c r="F210" s="125">
-        <f>D210+E210</f>
+      <c r="F215" s="125">
+        <f>D215+E215</f>
         <v>-0.688798580858977</v>
       </c>
     </row>
-    <row r="211">
-      <c r="B211" s="123" t="str">
+    <row r="216">
+      <c r="B216" s="123" t="str">
         <f>'VIENTO NTDV-97'!J208</f>
         <v>VA-1 sup.</v>
       </c>
-      <c r="C211" s="124">
+      <c r="C216" s="124">
         <f>'VIENTO NTDV-97'!K208</f>
         <v>0.585315</v>
       </c>
-      <c r="D211" s="80">
-        <f>$E$16*C211/100</f>
+      <c r="D216" s="80">
+        <f>$E$16*C216/100</f>
         <v>-0.19904580065073</v>
       </c>
-      <c r="E211" s="80">
-        <f>-$E$28*C211/100</f>
+      <c r="E216" s="80">
+        <f>-$E$34*C216/100</f>
         <v>-0.213263357840068</v>
       </c>
-      <c r="F211" s="125">
-        <f>D211+E211</f>
+      <c r="F216" s="125">
+        <f>D216+E216</f>
         <v>-0.412309158490798</v>
       </c>
     </row>
-    <row r="212">
-      <c r="B212" s="123" t="str">
+    <row r="217">
+      <c r="B217" s="123" t="str">
         <f>'VIENTO NTDV-97'!J209</f>
         <v>VA-2 sup.</v>
       </c>
-      <c r="C212" s="124">
+      <c r="C217" s="124">
         <f>'VIENTO NTDV-97'!K209</f>
         <v>0.37782</v>
       </c>
-      <c r="D212" s="80">
-        <f>$E$16*C212/100</f>
+      <c r="D217" s="80">
+        <f>$E$16*C217/100</f>
         <v>-0.128483781215002</v>
       </c>
-      <c r="E212" s="80">
-        <f>-$E$28*C212/100</f>
+      <c r="E217" s="80">
+        <f>-$E$34*C217/100</f>
         <v>-0.137661194158931</v>
       </c>
-      <c r="F212" s="125">
-        <f>D212+E212</f>
+      <c r="F217" s="125">
+        <f>D217+E217</f>
         <v>-0.266144975373932</v>
       </c>
     </row>
-    <row r="214">
-      <c r="B214" s="78" t="inlineStr">
+    <row r="219">
+      <c r="B219" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">CUBIERTA — LARGUEROS Y VIGAS DE MARCO   (Cpe techo)</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="34.8" customHeight="1">
-      <c r="B215" s="122" t="inlineStr">
+    <row r="220" ht="34.8" customHeight="1">
+      <c r="B220" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="C215" s="77" t="inlineStr">
+      <c r="C220" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="D215" s="77" t="inlineStr">
+      <c r="D220" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd externa (kg/cm)</t>
         </is>
       </c>
-      <c r="E215" s="77" t="inlineStr">
+      <c r="E220" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="F215" s="77" t="inlineStr">
+      <c r="F220" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="B216" s="123" t="str">
+    <row r="221">
+      <c r="B221" s="123" t="str">
         <f>'VIENTO NTDV-97'!N204</f>
         <v>VM-1</v>
       </c>
-      <c r="C216" s="124">
+      <c r="C221" s="124">
         <f>'VIENTO NTDV-97'!O204</f>
         <v>0.5</v>
       </c>
-      <c r="D216" s="80">
-        <f>$E$17*C216/100</f>
+      <c r="D221" s="80">
+        <f>$E$17*C221/100</f>
         <v>-0.170033059677891</v>
       </c>
-      <c r="E216" s="80">
-        <f>-$E$28*C216/100</f>
+      <c r="E221" s="80">
+        <f>-$E$34*C221/100</f>
         <v>-0.182178278226312</v>
       </c>
-      <c r="F216" s="125">
-        <f>D216+E216</f>
+      <c r="F221" s="125">
+        <f>D221+E221</f>
         <v>-0.352211337904203</v>
       </c>
     </row>
-    <row r="217">
-      <c r="B217" s="123" t="str">
+    <row r="222">
+      <c r="B222" s="123" t="str">
         <f>'VIENTO NTDV-97'!N205</f>
         <v>LT-1</v>
       </c>
-      <c r="C217" s="124">
+      <c r="C222" s="124">
         <f>'VIENTO NTDV-97'!O205</f>
         <v>1.25</v>
       </c>
-      <c r="D217" s="80">
-        <f>$E$17*C217/100</f>
+      <c r="D222" s="80">
+        <f>$E$17*C222/100</f>
         <v>-0.425082649194728</v>
       </c>
-      <c r="E217" s="80">
-        <f>-$E$28*C217/100</f>
+      <c r="E222" s="80">
+        <f>-$E$34*C222/100</f>
         <v>-0.45544569556578</v>
       </c>
-      <c r="F217" s="125">
-        <f>D217+E217</f>
+      <c r="F222" s="125">
+        <f>D222+E222</f>
         <v>-0.880528344760509</v>
       </c>
     </row>
-    <row r="218">
-      <c r="B218" s="123" t="str">
+    <row r="223">
+      <c r="B223" s="123" t="str">
         <f>'VIENTO NTDV-97'!N206</f>
         <v>LT-2</v>
       </c>
-      <c r="C218" s="124">
+      <c r="C223" s="124">
         <f>'VIENTO NTDV-97'!O206</f>
-        <v>1.5</v>
-      </c>
-      <c r="D218" s="80">
-        <f>$E$17*C218/100</f>
-        <v>-0.510099179033674</v>
-      </c>
-      <c r="E218" s="80">
-        <f>-$E$28*C218/100</f>
-        <v>-0.546534834678937</v>
-      </c>
-      <c r="F218" s="125">
-        <f>D218+E218</f>
-        <v>-1.05663401371261</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="B219" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N207</f>
-        <v>LT-3</v>
-      </c>
-      <c r="C219" s="124">
-        <f>'VIENTO NTDV-97'!O207</f>
-        <v>1.5</v>
-      </c>
-      <c r="D219" s="80">
-        <f>$E$17*C219/100</f>
-        <v>-0.510099179033674</v>
-      </c>
-      <c r="E219" s="80">
-        <f>-$E$28*C219/100</f>
-        <v>-0.546534834678937</v>
-      </c>
-      <c r="F219" s="125">
-        <f>D219+E219</f>
-        <v>-1.05663401371261</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="B220" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N208</f>
-        <v>LT-4</v>
-      </c>
-      <c r="C220" s="124">
-        <f>'VIENTO NTDV-97'!O208</f>
-        <v>1.5</v>
-      </c>
-      <c r="D220" s="80">
-        <f>$E$17*C220/100</f>
-        <v>-0.510099179033674</v>
-      </c>
-      <c r="E220" s="80">
-        <f>-$E$28*C220/100</f>
-        <v>-0.546534834678937</v>
-      </c>
-      <c r="F220" s="125">
-        <f>D220+E220</f>
-        <v>-1.05663401371261</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="B221" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N209</f>
-        <v>LT-5</v>
-      </c>
-      <c r="C221" s="124">
-        <f>'VIENTO NTDV-97'!O209</f>
-        <v>0.75</v>
-      </c>
-      <c r="D221" s="80">
-        <f>$E$17*C221/100</f>
-        <v>-0.255049589516837</v>
-      </c>
-      <c r="E221" s="80">
-        <f>-$E$28*C221/100</f>
-        <v>-0.273267417339468</v>
-      </c>
-      <c r="F221" s="125">
-        <f>D221+E221</f>
-        <v>-0.528317006856305</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="B222" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N210</f>
-        <v>LT-6</v>
-      </c>
-      <c r="C222" s="124">
-        <f>'VIENTO NTDV-97'!O210</f>
-        <v>1.5</v>
-      </c>
-      <c r="D222" s="80">
-        <f>$E$17*C222/100</f>
-        <v>-0.510099179033674</v>
-      </c>
-      <c r="E222" s="80">
-        <f>-$E$28*C222/100</f>
-        <v>-0.546534834678937</v>
-      </c>
-      <c r="F222" s="125">
-        <f>D222+E222</f>
-        <v>-1.05663401371261</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="B223" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N211</f>
-        <v>VM-2</v>
-      </c>
-      <c r="C223" s="124">
-        <f>'VIENTO NTDV-97'!O211</f>
         <v>1.5</v>
       </c>
       <c r="D223" s="80">
@@ -19315,7 +19263,7 @@
         <v>-0.510099179033674</v>
       </c>
       <c r="E223" s="80">
-        <f>-$E$28*C223/100</f>
+        <f>-$E$34*C223/100</f>
         <v>-0.546534834678937</v>
       </c>
       <c r="F223" s="125">
@@ -19325,11 +19273,11 @@
     </row>
     <row r="224">
       <c r="B224" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N212</f>
-        <v>LT-7</v>
+        <f>'VIENTO NTDV-97'!N207</f>
+        <v>LT-3</v>
       </c>
       <c r="C224" s="124">
-        <f>'VIENTO NTDV-97'!O212</f>
+        <f>'VIENTO NTDV-97'!O207</f>
         <v>1.5</v>
       </c>
       <c r="D224" s="80">
@@ -19337,7 +19285,7 @@
         <v>-0.510099179033674</v>
       </c>
       <c r="E224" s="80">
-        <f>-$E$28*C224/100</f>
+        <f>-$E$34*C224/100</f>
         <v>-0.546534834678937</v>
       </c>
       <c r="F224" s="125">
@@ -19347,11 +19295,11 @@
     </row>
     <row r="225">
       <c r="B225" s="123" t="str">
-        <f>'VIENTO NTDV-97'!N213</f>
-        <v>LT-8</v>
+        <f>'VIENTO NTDV-97'!N208</f>
+        <v>LT-4</v>
       </c>
       <c r="C225" s="124">
-        <f>'VIENTO NTDV-97'!O213</f>
+        <f>'VIENTO NTDV-97'!O208</f>
         <v>1.5</v>
       </c>
       <c r="D225" s="80">
@@ -19359,7 +19307,7 @@
         <v>-0.510099179033674</v>
       </c>
       <c r="E225" s="80">
-        <f>-$E$28*C225/100</f>
+        <f>-$E$34*C225/100</f>
         <v>-0.546534834678937</v>
       </c>
       <c r="F225" s="125">
@@ -19369,45 +19317,155 @@
     </row>
     <row r="226">
       <c r="B226" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N209</f>
+        <v>LT-5</v>
+      </c>
+      <c r="C226" s="124">
+        <f>'VIENTO NTDV-97'!O209</f>
+        <v>0.75</v>
+      </c>
+      <c r="D226" s="80">
+        <f>$E$17*C226/100</f>
+        <v>-0.255049589516837</v>
+      </c>
+      <c r="E226" s="80">
+        <f>-$E$34*C226/100</f>
+        <v>-0.273267417339468</v>
+      </c>
+      <c r="F226" s="125">
+        <f>D226+E226</f>
+        <v>-0.528317006856305</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N210</f>
+        <v>LT-6</v>
+      </c>
+      <c r="C227" s="124">
+        <f>'VIENTO NTDV-97'!O210</f>
+        <v>1.5</v>
+      </c>
+      <c r="D227" s="80">
+        <f>$E$17*C227/100</f>
+        <v>-0.510099179033674</v>
+      </c>
+      <c r="E227" s="80">
+        <f>-$E$34*C227/100</f>
+        <v>-0.546534834678937</v>
+      </c>
+      <c r="F227" s="125">
+        <f>D227+E227</f>
+        <v>-1.05663401371261</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N211</f>
+        <v>VM-2</v>
+      </c>
+      <c r="C228" s="124">
+        <f>'VIENTO NTDV-97'!O211</f>
+        <v>1.5</v>
+      </c>
+      <c r="D228" s="80">
+        <f>$E$17*C228/100</f>
+        <v>-0.510099179033674</v>
+      </c>
+      <c r="E228" s="80">
+        <f>-$E$34*C228/100</f>
+        <v>-0.546534834678937</v>
+      </c>
+      <c r="F228" s="125">
+        <f>D228+E228</f>
+        <v>-1.05663401371261</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N212</f>
+        <v>LT-7</v>
+      </c>
+      <c r="C229" s="124">
+        <f>'VIENTO NTDV-97'!O212</f>
+        <v>1.5</v>
+      </c>
+      <c r="D229" s="80">
+        <f>$E$17*C229/100</f>
+        <v>-0.510099179033674</v>
+      </c>
+      <c r="E229" s="80">
+        <f>-$E$34*C229/100</f>
+        <v>-0.546534834678937</v>
+      </c>
+      <c r="F229" s="125">
+        <f>D229+E229</f>
+        <v>-1.05663401371261</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" s="123" t="str">
+        <f>'VIENTO NTDV-97'!N213</f>
+        <v>LT-8</v>
+      </c>
+      <c r="C230" s="124">
+        <f>'VIENTO NTDV-97'!O213</f>
+        <v>1.5</v>
+      </c>
+      <c r="D230" s="80">
+        <f>$E$17*C230/100</f>
+        <v>-0.510099179033674</v>
+      </c>
+      <c r="E230" s="80">
+        <f>-$E$34*C230/100</f>
+        <v>-0.546534834678937</v>
+      </c>
+      <c r="F230" s="125">
+        <f>D230+E230</f>
+        <v>-1.05663401371261</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" s="123" t="str">
         <f>'VIENTO NTDV-97'!N214</f>
         <v>LT-9</v>
       </c>
-      <c r="C226" s="124">
+      <c r="C231" s="124">
         <f>'VIENTO NTDV-97'!O214</f>
         <v>1.5</v>
       </c>
-      <c r="D226" s="80">
-        <f>$E$17*C226/100</f>
+      <c r="D231" s="80">
+        <f>$E$17*C231/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="E226" s="80">
-        <f>-$E$28*C226/100</f>
+      <c r="E231" s="80">
+        <f>-$E$34*C231/100</f>
         <v>-0.546534834678937</v>
       </c>
-      <c r="F226" s="125">
-        <f>D226+E226</f>
+      <c r="F231" s="125">
+        <f>D231+E231</f>
         <v>-1.05663401371261</v>
       </c>
     </row>
-    <row r="227">
-      <c r="B227" s="123" t="str">
+    <row r="232">
+      <c r="B232" s="123" t="str">
         <f>'VIENTO NTDV-97'!N215</f>
         <v>VM-3</v>
       </c>
-      <c r="C227" s="124">
+      <c r="C232" s="124">
         <f>'VIENTO NTDV-97'!O215</f>
         <v>0.75</v>
       </c>
-      <c r="D227" s="80">
-        <f>$E$17*C227/100</f>
+      <c r="D232" s="80">
+        <f>$E$17*C232/100</f>
         <v>-0.255049589516837</v>
       </c>
-      <c r="E227" s="80">
-        <f>-$E$28*C227/100</f>
+      <c r="E232" s="80">
+        <f>-$E$34*C232/100</f>
         <v>-0.273267417339468</v>
       </c>
-      <c r="F227" s="125">
-        <f>D227+E227</f>
+      <c r="F232" s="125">
+        <f>D232+E232</f>
         <v>-0.528317006856305</v>
       </c>
     </row>

--- a/VIENTO/001_SISMO_VIENTO_SALVADOR_R4.67.xlsx
+++ b/VIENTO/001_SISMO_VIENTO_SALVADOR_R4.67.xlsx
@@ -12840,7 +12840,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B2:BC227"/>
+  <dimension ref="B2:BK227"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -12851,6 +12851,7 @@
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="15" max="15" width="12" customWidth="1"/>
     <col min="17" max="17" width="12" customWidth="1"/>
+    <col min="19" max="19" width="16" customWidth="1"/>
     <col min="24" max="24" width="17" customWidth="1"/>
     <col min="26" max="26" width="11.6640625" customWidth="1"/>
     <col min="28" max="28" width="16" customWidth="1"/>
@@ -12858,21 +12859,23 @@
     <col min="32" max="32" width="16" customWidth="1"/>
     <col min="36" max="36" width="12" customWidth="1"/>
     <col min="38" max="38" width="12" customWidth="1"/>
-    <col min="41" max="41" width="17" customWidth="1"/>
-    <col min="43" max="43" width="11.6640625" customWidth="1"/>
-    <col min="45" max="45" width="16" customWidth="1"/>
-    <col min="47" max="47" width="11" customWidth="1"/>
+    <col min="40" max="40" width="16" customWidth="1"/>
+    <col min="45" max="45" width="17" customWidth="1"/>
+    <col min="47" max="47" width="11.6640625" customWidth="1"/>
     <col min="49" max="49" width="16" customWidth="1"/>
-    <col min="53" max="53" width="12" customWidth="1"/>
-    <col min="55" max="55" width="12" customWidth="1"/>
+    <col min="51" max="51" width="11" customWidth="1"/>
+    <col min="53" max="53" width="16" customWidth="1"/>
+    <col min="57" max="57" width="12" customWidth="1"/>
+    <col min="59" max="59" width="12" customWidth="1"/>
+    <col min="61" max="61" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="11" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C4" s="69" t="s">
         <v>161</v>
       </c>
@@ -12880,12 +12883,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>163</v>
       </c>
@@ -12893,17 +12896,17 @@
         <v>164</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" x14ac:dyDescent="0.3">
       <c r="C22" s="12" t="s">
         <v>167</v>
       </c>
@@ -12914,7 +12917,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" x14ac:dyDescent="0.3">
       <c r="C24" s="12" t="s">
         <v>169</v>
       </c>
@@ -12922,7 +12925,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" x14ac:dyDescent="0.3">
       <c r="C26" s="12" t="s">
         <v>170</v>
       </c>
@@ -12934,7 +12937,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" x14ac:dyDescent="0.3">
       <c r="C28" s="17" t="s">
         <v>171</v>
       </c>
@@ -12946,7 +12949,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" x14ac:dyDescent="0.3">
       <c r="C30" s="17" t="s">
         <v>172</v>
       </c>
@@ -12957,12 +12960,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="40" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="42" x14ac:dyDescent="0.3">
       <c r="C42" s="12" t="s">
         <v>174</v>
       </c>
@@ -12970,7 +12973,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="44" x14ac:dyDescent="0.3">
       <c r="C44" s="12" t="s">
         <v>176</v>
       </c>
@@ -12979,10 +12982,10 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="45" x14ac:dyDescent="0.3">
       <c r="C45" s="12"/>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="46" x14ac:dyDescent="0.3">
       <c r="C46" s="12" t="s">
         <v>177</v>
       </c>
@@ -12991,7 +12994,7 @@
         <v>7.0</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="49" x14ac:dyDescent="0.3">
       <c r="C49" s="12" t="s">
         <v>178</v>
       </c>
@@ -13002,7 +13005,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="51" x14ac:dyDescent="0.3">
       <c r="C51" s="12" t="s">
         <v>179</v>
       </c>
@@ -13011,12 +13014,12 @@
         <v>1.01210154570173</v>
       </c>
     </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="61" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="63" x14ac:dyDescent="0.3">
       <c r="D63" s="17" t="s">
         <v>181</v>
       </c>
@@ -13031,12 +13034,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="68" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="70" spans="2:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="72" t="s">
         <v>184</v>
       </c>
@@ -13051,7 +13054,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="71" x14ac:dyDescent="0.3">
       <c r="B71" s="16" t="s">
         <v>188</v>
       </c>
@@ -13074,7 +13077,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="72" x14ac:dyDescent="0.3">
       <c r="B72" s="16" t="s">
         <v>189</v>
       </c>
@@ -13097,7 +13100,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="73" x14ac:dyDescent="0.3">
       <c r="B73" s="16" t="s">
         <v>190</v>
       </c>
@@ -13122,7 +13125,7 @@
         <v>0.431398162839907</v>
       </c>
     </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="74" x14ac:dyDescent="0.3">
       <c r="B74" s="16" t="s">
         <v>191</v>
       </c>
@@ -13139,12 +13142,12 @@
         <v>-0.00340066119355783</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="84" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="86" x14ac:dyDescent="0.3">
       <c r="F86" s="12" t="s">
         <v>193</v>
       </c>
@@ -13156,7 +13159,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="88" x14ac:dyDescent="0.3">
       <c r="F88" s="12" t="s">
         <v>195</v>
       </c>
@@ -13167,7 +13170,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="90" x14ac:dyDescent="0.3">
       <c r="F90" s="12" t="s">
         <v>196</v>
       </c>
@@ -13336,7 +13339,7 @@
         <v>36.4356556452624</v>
       </c>
     </row>
-    <row r="105" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="105" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
         <v>197</v>
       </c>
@@ -13352,7 +13355,7 @@
           <t xml:space="preserve">PRESIONES INTERNAS (Cpi)</t>
         </is>
       </c>
-      <c r="AN106" s="1" t="inlineStr">
+      <c r="AR106" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">PRESION TOTAL (Cpe + Cpi)</t>
         </is>
@@ -13401,15 +13404,15 @@
       <c r="AJ107" s="82"/>
       <c r="AK107" s="82"/>
       <c r="AL107" s="82"/>
-      <c r="AN107" s="81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIENTO EN DIRECCION X — TOTAL (Cpe + Cpi)</t>
-        </is>
-      </c>
+      <c r="AM107" s="82"/>
+      <c r="AN107" s="82"/>
       <c r="AO107" s="82"/>
       <c r="AP107" s="82"/>
-      <c r="AQ107" s="82"/>
-      <c r="AR107" s="82"/>
+      <c r="AR107" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIENTO EN DIRECCION X — TOTAL (Cpe + Cpi)</t>
+        </is>
+      </c>
       <c r="AS107" s="82"/>
       <c r="AT107" s="82"/>
       <c r="AU107" s="82"/>
@@ -13421,6 +13424,14 @@
       <c r="BA107" s="82"/>
       <c r="BB107" s="82"/>
       <c r="BC107" s="82"/>
+      <c r="BD107" s="82"/>
+      <c r="BE107" s="82"/>
+      <c r="BF107" s="82"/>
+      <c r="BG107" s="82"/>
+      <c r="BH107" s="82"/>
+      <c r="BI107" s="82"/>
+      <c r="BJ107" s="82"/>
+      <c r="BK107" s="82"/>
     </row>
     <row r="109" x14ac:dyDescent="0.3">
       <c r="B109" s="78" t="s">
@@ -13432,7 +13443,12 @@
       <c r="J109" s="78" t="s">
         <v>201</v>
       </c>
-      <c r="N109" s="78" t="s">
+      <c r="N109" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EJE 3 ABIERTO (SIN CERRAMIENTO):</t>
+        </is>
+      </c>
+      <c r="R109" s="78" t="s">
         <v>229</v>
       </c>
       <c r="W109" s="78" t="str">
@@ -13449,66 +13465,110 @@
       </c>
       <c r="AI109" s="78" t="str">
         <f>N109</f>
+        <v>EJE 3 ABIERTO (SIN CERRAMIENTO):</v>
+      </c>
+      <c r="AM109" s="78" t="str">
+        <f>R109</f>
         <v>CUBIERTA — LARGUEROS Y VIGAS DE MARCO</v>
       </c>
-      <c r="AN109" s="78" t="str">
+      <c r="AR109" s="78" t="str">
         <f>B109</f>
         <v>MURO A EN BARLOVENTO:</v>
       </c>
-      <c r="AR109" s="78" t="str">
+      <c r="AV109" s="78" t="str">
         <f>F109</f>
         <v>MURO B EN SOTAVENTO:</v>
       </c>
-      <c r="AV109" s="78" t="str">
+      <c r="AZ109" s="78" t="str">
         <f>J109</f>
         <v>MURO 1 LATERAL:</v>
       </c>
-      <c r="AZ109" s="78" t="str">
+      <c r="BD109" s="78" t="str">
         <f>N109</f>
+        <v>EJE 3 ABIERTO (SIN CERRAMIENTO):</v>
+      </c>
+      <c r="BH109" s="78" t="str">
+        <f>R109</f>
         <v>CUBIERTA — LARGUEROS Y VIGAS DE MARCO</v>
       </c>
     </row>
-    <row r="110" spans="2:21" ht="29.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" ht="29.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="111" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B111" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="C111" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="D111" s="77" t="s">
-        <v>204</v>
-      </c>
-      <c r="E111" s="119"/>
-      <c r="F111" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="G111" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="H111" s="77" t="s">
-        <v>204</v>
-      </c>
-      <c r="I111" s="119"/>
-      <c r="J111" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="K111" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="L111" s="77" t="s">
-        <v>204</v>
-      </c>
-      <c r="N111" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="O111" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="P111" s="77" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q111" s="119"/>
+      <c r="B111" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="C111" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="D111" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd (kg/cm)</t>
+        </is>
+      </c>
+      <c r="F111" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="G111" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="H111" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd (kg/cm)</t>
+        </is>
+      </c>
+      <c r="J111" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="K111" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="L111" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd (kg/cm)</t>
+        </is>
+      </c>
+      <c r="N111" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="O111" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="P111" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd (kg/cm)</t>
+        </is>
+      </c>
+      <c r="R111" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="S111" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="T111" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd normal</t>
+        </is>
+      </c>
       <c r="W111" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
@@ -13524,7 +13584,6 @@
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="Z111" s="119"/>
       <c r="AA111" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
@@ -13540,7 +13599,6 @@
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="AD111" s="119"/>
       <c r="AE111" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
@@ -13571,70 +13629,96 @@
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="AL111" s="119"/>
-      <c r="AN111" s="122" t="inlineStr">
+      <c r="AM111" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
+      <c r="AN111" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
       <c r="AO111" s="77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pd interna (kg/cm)</t>
+        </is>
+      </c>
+      <c r="AR111" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="AS111" s="77" t="inlineStr">
+        <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="AP111" s="77" t="inlineStr">
+      <c r="AT111" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
-      <c r="AQ111" s="119"/>
-      <c r="AR111" s="122" t="inlineStr">
+      <c r="AV111" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="AS111" s="77" t="inlineStr">
+      <c r="AW111" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="AT111" s="77" t="inlineStr">
+      <c r="AX111" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
-      <c r="AU111" s="119"/>
-      <c r="AV111" s="122" t="inlineStr">
+      <c r="AZ111" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="AW111" s="77" t="inlineStr">
+      <c r="BA111" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="AX111" s="77" t="inlineStr">
+      <c r="BB111" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
-      <c r="AZ111" s="122" t="inlineStr">
+      <c r="BD111" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="BA111" s="77" t="inlineStr">
+      <c r="BE111" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="BB111" s="77" t="inlineStr">
+      <c r="BF111" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
-      <c r="BC111" s="119"/>
+      <c r="BH111" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="BI111" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="BJ111" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd total (kg/cm)</t>
+        </is>
+      </c>
     </row>
     <row r="112" x14ac:dyDescent="0.3">
       <c r="B112" s="123" t="s">
@@ -13647,7 +13731,6 @@
         <f>$E$71*C112/100</f>
         <v>0.349782294194519</v>
       </c>
-      <c r="E112" s="119"/>
       <c r="F112" s="123" t="s">
         <v>206</v>
       </c>
@@ -13658,7 +13741,6 @@
         <f>$E$72*G112/100</f>
         <v>-0.218613933871575</v>
       </c>
-      <c r="I112" s="119"/>
       <c r="J112" s="123" t="s">
         <v>207</v>
       </c>
@@ -13669,17 +13751,21 @@
         <f>$E$73*K112/100</f>
         <v>-0.306059507420204</v>
       </c>
-      <c r="N112" s="123" t="s">
+      <c r="N112" s="123"/>
+      <c r="O112" s="124"/>
+      <c r="P112" s="125">
+        <v>0</v>
+      </c>
+      <c r="R112" s="123" t="s">
         <v>231</v>
       </c>
-      <c r="O112" s="124">
+      <c r="S112" s="124">
         <v>0.5</v>
       </c>
-      <c r="P112" s="125">
-        <f>$E$74*O112/100</f>
+      <c r="T112" s="125">
+        <f>$E$74*S112/100</f>
         <v>-0.170033059677891</v>
       </c>
-      <c r="Q112" s="119"/>
       <c r="W112" s="123" t="str">
         <f>B112</f>
         <v>LA-1</v>
@@ -13692,7 +13778,6 @@
         <f>-$I$95*C112/100</f>
         <v>0.218613933871575</v>
       </c>
-      <c r="Z112" s="119"/>
       <c r="AA112" s="123" t="str">
         <f>F112</f>
         <v>LB-1</v>
@@ -13705,7 +13790,6 @@
         <f>-$I$95*G112/100</f>
         <v>0.218613933871575</v>
       </c>
-      <c r="AD112" s="119"/>
       <c r="AE112" s="123" t="str">
         <f>J112</f>
         <v>L1-1</v>
@@ -13718,70 +13802,78 @@
         <f>-$I$95*K112/100</f>
         <v>0.218613933871575</v>
       </c>
-      <c r="AI112" s="123" t="str">
-        <f>N112</f>
-        <v>VM-1</v>
-      </c>
-      <c r="AJ112" s="124">
-        <f>O112</f>
-        <v>0.5</v>
-      </c>
+      <c r="AI112" s="123"/>
+      <c r="AJ112" s="124"/>
       <c r="AK112" s="125">
         <f>-$I$95*O112/100</f>
+        <v>0.0</v>
+      </c>
+      <c r="AM112" s="123" t="str">
+        <f>R112</f>
+        <v>VM-1</v>
+      </c>
+      <c r="AN112" s="124">
+        <f>S112</f>
+        <v>0.5</v>
+      </c>
+      <c r="AO112" s="125">
+        <f>-$I$95*S112/100</f>
         <v>0.121452185484208</v>
       </c>
-      <c r="AL112" s="119"/>
-      <c r="AN112" s="123" t="str">
+      <c r="AR112" s="123" t="str">
         <f>B112</f>
         <v>LA-1</v>
       </c>
-      <c r="AO112" s="124">
+      <c r="AS112" s="124">
         <f>C112</f>
         <v>0.9</v>
       </c>
-      <c r="AP112" s="125">
+      <c r="AT112" s="125">
         <f>D112+Y112</f>
         <v>0.568396228066094</v>
       </c>
-      <c r="AQ112" s="119"/>
-      <c r="AR112" s="123" t="str">
+      <c r="AV112" s="123" t="str">
         <f>F112</f>
         <v>LB-1</v>
       </c>
-      <c r="AS112" s="124">
+      <c r="AW112" s="124">
         <f>G112</f>
         <v>0.9</v>
       </c>
-      <c r="AT112" s="125">
+      <c r="AX112" s="125">
         <f>H112+AC112</f>
         <v>0.0</v>
       </c>
-      <c r="AU112" s="119"/>
-      <c r="AV112" s="123" t="str">
+      <c r="AZ112" s="123" t="str">
         <f>J112</f>
         <v>L1-1</v>
       </c>
-      <c r="AW112" s="124">
+      <c r="BA112" s="124">
         <f>K112</f>
         <v>0.9</v>
       </c>
-      <c r="AX112" s="125">
+      <c r="BB112" s="125">
         <f>L112+AG112</f>
         <v>-0.0874455735486298</v>
       </c>
-      <c r="AZ112" s="123" t="str">
-        <f>N112</f>
+      <c r="BD112" s="123"/>
+      <c r="BE112" s="124"/>
+      <c r="BF112" s="125">
+        <f>P112+AK112</f>
+        <v>0.0</v>
+      </c>
+      <c r="BH112" s="123" t="str">
+        <f>R112</f>
         <v>VM-1</v>
       </c>
-      <c r="BA112" s="124">
-        <f>O112</f>
+      <c r="BI112" s="124">
+        <f>S112</f>
         <v>0.5</v>
       </c>
-      <c r="BB112" s="125">
-        <f>P112+AK112</f>
+      <c r="BJ112" s="125">
+        <f>T112+AO112</f>
         <v>-0.0485808741936832</v>
       </c>
-      <c r="BC112" s="119"/>
     </row>
     <row r="113" x14ac:dyDescent="0.3">
       <c r="B113" s="123" t="s">
@@ -13791,10 +13883,9 @@
         <v>1.2</v>
       </c>
       <c r="D113" s="125">
-        <f t="shared" ref="D113:D121" si="2">$E$71*C113/100</f>
+        <f>$E$71*C113/100</f>
         <v>0.466376392259359</v>
       </c>
-      <c r="E113" s="119"/>
       <c r="F113" s="123" t="s">
         <v>209</v>
       </c>
@@ -13802,10 +13893,9 @@
         <v>1.2</v>
       </c>
       <c r="H113" s="125">
-        <f t="shared" ref="H113:H118" si="3">$E$72*G113/100</f>
+        <f>$E$72*G113/100</f>
         <v>-0.291485245162099</v>
       </c>
-      <c r="I113" s="119"/>
       <c r="J113" s="123" t="s">
         <v>210</v>
       </c>
@@ -13816,17 +13906,21 @@
         <f>$E$73*K113/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="N113" s="123" t="s">
+      <c r="N113" s="123"/>
+      <c r="O113" s="124"/>
+      <c r="P113" s="125">
+        <v>0</v>
+      </c>
+      <c r="R113" s="123" t="s">
         <v>234</v>
       </c>
-      <c r="O113" s="124">
+      <c r="S113" s="124">
         <v>1.25</v>
       </c>
-      <c r="P113" s="125">
-        <f t="shared" ref="P113:P114" si="4">$E$74*O113/100</f>
+      <c r="T113" s="125">
+        <f>$E$74*S113/100</f>
         <v>-0.425082649194728</v>
       </c>
-      <c r="Q113" s="119"/>
       <c r="W113" s="123" t="str">
         <f>B113</f>
         <v>LA-2 a 7</v>
@@ -13839,7 +13933,6 @@
         <f>-$I$95*C113/100</f>
         <v>0.291485245162099</v>
       </c>
-      <c r="Z113" s="119"/>
       <c r="AA113" s="123" t="str">
         <f>F113</f>
         <v>LB-2 a 7</v>
@@ -13852,7 +13945,6 @@
         <f>-$I$95*G113/100</f>
         <v>0.291485245162099</v>
       </c>
-      <c r="AD113" s="119"/>
       <c r="AE113" s="123" t="str">
         <f>J113</f>
         <v>L1-2</v>
@@ -13865,70 +13957,78 @@
         <f>-$I$95*K113/100</f>
         <v>0.291485245162099</v>
       </c>
-      <c r="AI113" s="123" t="str">
-        <f>N113</f>
-        <v>LT-1</v>
-      </c>
-      <c r="AJ113" s="124">
-        <f>O113</f>
-        <v>1.25</v>
-      </c>
+      <c r="AI113" s="123"/>
+      <c r="AJ113" s="124"/>
       <c r="AK113" s="125">
         <f>-$I$95*O113/100</f>
+        <v>0.0</v>
+      </c>
+      <c r="AM113" s="123" t="str">
+        <f>R113</f>
+        <v>LT-1</v>
+      </c>
+      <c r="AN113" s="124">
+        <f>S113</f>
+        <v>1.25</v>
+      </c>
+      <c r="AO113" s="125">
+        <f>-$I$95*S113/100</f>
         <v>0.30363046371052</v>
       </c>
-      <c r="AL113" s="119"/>
-      <c r="AN113" s="123" t="str">
+      <c r="AR113" s="123" t="str">
         <f>B113</f>
         <v>LA-2 a 7</v>
       </c>
-      <c r="AO113" s="124">
+      <c r="AS113" s="124">
         <f>C113</f>
         <v>1.2</v>
       </c>
-      <c r="AP113" s="125">
+      <c r="AT113" s="125">
         <f>D113+Y113</f>
         <v>0.757861637421459</v>
       </c>
-      <c r="AQ113" s="119"/>
-      <c r="AR113" s="123" t="str">
+      <c r="AV113" s="123" t="str">
         <f>F113</f>
         <v>LB-2 a 7</v>
       </c>
-      <c r="AS113" s="124">
+      <c r="AW113" s="124">
         <f>G113</f>
         <v>1.2</v>
       </c>
-      <c r="AT113" s="125">
+      <c r="AX113" s="125">
         <f>H113+AC113</f>
         <v>0.0</v>
       </c>
-      <c r="AU113" s="119"/>
-      <c r="AV113" s="123" t="str">
+      <c r="AZ113" s="123" t="str">
         <f>J113</f>
         <v>L1-2</v>
       </c>
-      <c r="AW113" s="124">
+      <c r="BA113" s="124">
         <f>K113</f>
         <v>1.2</v>
       </c>
-      <c r="AX113" s="125">
+      <c r="BB113" s="125">
         <f>L113+AG113</f>
         <v>-0.11659409806484</v>
       </c>
-      <c r="AZ113" s="123" t="str">
-        <f>N113</f>
+      <c r="BD113" s="123"/>
+      <c r="BE113" s="124"/>
+      <c r="BF113" s="125">
+        <f>P113+AK113</f>
+        <v>0.0</v>
+      </c>
+      <c r="BH113" s="123" t="str">
+        <f>R113</f>
         <v>LT-1</v>
       </c>
-      <c r="BA113" s="124">
-        <f>O113</f>
+      <c r="BI113" s="124">
+        <f>S113</f>
         <v>1.25</v>
       </c>
-      <c r="BB113" s="125">
-        <f>P113+AK113</f>
+      <c r="BJ113" s="125">
+        <f>T113+AO113</f>
         <v>-0.121452185484208</v>
       </c>
-      <c r="BC113" s="119"/>
     </row>
     <row r="114" x14ac:dyDescent="0.3">
       <c r="B114" s="123" t="s">
@@ -13938,10 +14038,9 @@
         <v>1.1853149999999999</v>
       </c>
       <c r="D114" s="125">
-        <f t="shared" si="2"/>
+        <f>$E$71*C114/100</f>
         <v>0.460669111159085</v>
       </c>
-      <c r="E114" s="119"/>
       <c r="F114" s="123" t="s">
         <v>212</v>
       </c>
@@ -13949,10 +14048,9 @@
         <v>1.1853149999999999</v>
       </c>
       <c r="H114" s="125">
-        <f t="shared" si="3"/>
+        <f>$E$72*G114/100</f>
         <v>-0.287918194474428</v>
       </c>
-      <c r="I114" s="119"/>
       <c r="J114" s="123" t="s">
         <v>213</v>
       </c>
@@ -13960,20 +14058,24 @@
         <v>0.3</v>
       </c>
       <c r="L114" s="125">
-        <f t="shared" ref="L113:L126" si="5">$E$73*K114/100</f>
+        <f>$E$73*K114/100</f>
         <v>-0.102019835806735</v>
       </c>
-      <c r="N114" s="123" t="s">
+      <c r="N114" s="123"/>
+      <c r="O114" s="124"/>
+      <c r="P114" s="125">
+        <v>0</v>
+      </c>
+      <c r="R114" s="123" t="s">
         <v>237</v>
       </c>
-      <c r="O114" s="124">
+      <c r="S114" s="124">
         <v>1.5</v>
       </c>
-      <c r="P114" s="125">
-        <f t="shared" si="4"/>
+      <c r="T114" s="125">
+        <f>$E$74*S114/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="Q114" s="119"/>
       <c r="W114" s="123" t="str">
         <f>B114</f>
         <v>LA-8 (1-2)</v>
@@ -13986,7 +14088,6 @@
         <f>-$I$95*C114/100</f>
         <v>0.287918194474428</v>
       </c>
-      <c r="Z114" s="119"/>
       <c r="AA114" s="123" t="str">
         <f>F114</f>
         <v>LB-8 (1-2)</v>
@@ -13999,7 +14100,6 @@
         <f>-$I$95*G114/100</f>
         <v>0.287918194474428</v>
       </c>
-      <c r="AD114" s="119"/>
       <c r="AE114" s="123" t="str">
         <f>J114</f>
         <v>Dintel P.</v>
@@ -14012,70 +14112,78 @@
         <f>-$I$95*K114/100</f>
         <v>0.0728713112905249</v>
       </c>
-      <c r="AI114" s="123" t="str">
-        <f>N114</f>
-        <v>LT-2</v>
-      </c>
-      <c r="AJ114" s="124">
-        <f>O114</f>
-        <v>1.5</v>
-      </c>
+      <c r="AI114" s="123"/>
+      <c r="AJ114" s="124"/>
       <c r="AK114" s="125">
         <f>-$I$95*O114/100</f>
+        <v>0.0</v>
+      </c>
+      <c r="AM114" s="123" t="str">
+        <f>R114</f>
+        <v>LT-2</v>
+      </c>
+      <c r="AN114" s="124">
+        <f>S114</f>
+        <v>1.5</v>
+      </c>
+      <c r="AO114" s="125">
+        <f>-$I$95*S114/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AL114" s="119"/>
-      <c r="AN114" s="123" t="str">
+      <c r="AR114" s="123" t="str">
         <f>B114</f>
         <v>LA-8 (1-2)</v>
       </c>
-      <c r="AO114" s="124">
+      <c r="AS114" s="124">
         <f>C114</f>
         <v>1.185315</v>
       </c>
-      <c r="AP114" s="125">
+      <c r="AT114" s="125">
         <f>D114+Y114</f>
         <v>0.748587305633513</v>
       </c>
-      <c r="AQ114" s="119"/>
-      <c r="AR114" s="123" t="str">
+      <c r="AV114" s="123" t="str">
         <f>F114</f>
         <v>LB-8 (1-2)</v>
       </c>
-      <c r="AS114" s="124">
+      <c r="AW114" s="124">
         <f>G114</f>
         <v>1.185315</v>
       </c>
-      <c r="AT114" s="125">
+      <c r="AX114" s="125">
         <f>H114+AC114</f>
         <v>0.0</v>
       </c>
-      <c r="AU114" s="119"/>
-      <c r="AV114" s="123" t="str">
+      <c r="AZ114" s="123" t="str">
         <f>J114</f>
         <v>Dintel P.</v>
       </c>
-      <c r="AW114" s="124">
+      <c r="BA114" s="124">
         <f>K114</f>
         <v>0.3</v>
       </c>
-      <c r="AX114" s="125">
+      <c r="BB114" s="125">
         <f>L114+AG114</f>
         <v>-0.0291485245162099</v>
       </c>
-      <c r="AZ114" s="123" t="str">
-        <f>N114</f>
+      <c r="BD114" s="123"/>
+      <c r="BE114" s="124"/>
+      <c r="BF114" s="125">
+        <f>P114+AK114</f>
+        <v>0.0</v>
+      </c>
+      <c r="BH114" s="123" t="str">
+        <f>R114</f>
         <v>LT-2</v>
       </c>
-      <c r="BA114" s="124">
-        <f>O114</f>
+      <c r="BI114" s="124">
+        <f>S114</f>
         <v>1.5</v>
       </c>
-      <c r="BB114" s="125">
-        <f>P114+AK114</f>
+      <c r="BJ114" s="125">
+        <f>T114+AO114</f>
         <v>-0.14574262258105</v>
       </c>
-      <c r="BC114" s="119"/>
     </row>
     <row r="115" x14ac:dyDescent="0.3">
       <c r="B115" s="123" t="s">
@@ -14085,10 +14193,9 @@
         <v>0.97782000000000002</v>
       </c>
       <c r="D115" s="125">
-        <f t="shared" si="2"/>
+        <f>$E$71*C115/100</f>
         <v>0.380026803232539</v>
       </c>
-      <c r="E115" s="119"/>
       <c r="F115" s="123" t="s">
         <v>215</v>
       </c>
@@ -14096,10 +14203,9 @@
         <v>0.97782000000000002</v>
       </c>
       <c r="H115" s="125">
-        <f t="shared" si="3"/>
+        <f>$E$72*G115/100</f>
         <v>-0.237516752020337</v>
       </c>
-      <c r="I115" s="119"/>
       <c r="J115" s="123" t="s">
         <v>216</v>
       </c>
@@ -14107,20 +14213,24 @@
         <v>1.2</v>
       </c>
       <c r="L115" s="125">
-        <f t="shared" si="5"/>
+        <f>$E$73*K115/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="N115" s="123" t="s">
+      <c r="N115" s="123"/>
+      <c r="O115" s="124"/>
+      <c r="P115" s="125">
+        <v>0</v>
+      </c>
+      <c r="R115" s="123" t="s">
         <v>240</v>
       </c>
-      <c r="O115" s="124">
+      <c r="S115" s="124">
         <v>1.5</v>
       </c>
-      <c r="P115" s="125">
-        <f t="shared" ref="P115:P123" si="6">$E$74*O115/100</f>
+      <c r="T115" s="125">
+        <f>$E$74*S115/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="Q115" s="119"/>
       <c r="W115" s="123" t="str">
         <f>B115</f>
         <v>LA-8 (2-3)</v>
@@ -14133,7 +14243,6 @@
         <f>-$I$95*C115/100</f>
         <v>0.237516752020337</v>
       </c>
-      <c r="Z115" s="119"/>
       <c r="AA115" s="123" t="str">
         <f>F115</f>
         <v>LB-8 (2-3)</v>
@@ -14146,7 +14255,6 @@
         <f>-$I$95*G115/100</f>
         <v>0.237516752020337</v>
       </c>
-      <c r="AD115" s="119"/>
       <c r="AE115" s="123" t="str">
         <f>J115</f>
         <v>L1-3</v>
@@ -14159,70 +14267,78 @@
         <f>-$I$95*K115/100</f>
         <v>0.291485245162099</v>
       </c>
-      <c r="AI115" s="123" t="str">
-        <f>N115</f>
-        <v>LT-3</v>
-      </c>
-      <c r="AJ115" s="124">
-        <f>O115</f>
-        <v>1.5</v>
-      </c>
+      <c r="AI115" s="123"/>
+      <c r="AJ115" s="124"/>
       <c r="AK115" s="125">
         <f>-$I$95*O115/100</f>
+        <v>0.0</v>
+      </c>
+      <c r="AM115" s="123" t="str">
+        <f>R115</f>
+        <v>LT-3</v>
+      </c>
+      <c r="AN115" s="124">
+        <f>S115</f>
+        <v>1.5</v>
+      </c>
+      <c r="AO115" s="125">
+        <f>-$I$95*S115/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AL115" s="119"/>
-      <c r="AN115" s="123" t="str">
+      <c r="AR115" s="123" t="str">
         <f>B115</f>
         <v>LA-8 (2-3)</v>
       </c>
-      <c r="AO115" s="124">
+      <c r="AS115" s="124">
         <f>C115</f>
         <v>0.97782</v>
       </c>
-      <c r="AP115" s="125">
+      <c r="AT115" s="125">
         <f>D115+Y115</f>
         <v>0.617543555252876</v>
       </c>
-      <c r="AQ115" s="119"/>
-      <c r="AR115" s="123" t="str">
+      <c r="AV115" s="123" t="str">
         <f>F115</f>
         <v>LB-8 (2-3)</v>
       </c>
-      <c r="AS115" s="124">
+      <c r="AW115" s="124">
         <f>G115</f>
         <v>0.97782</v>
       </c>
-      <c r="AT115" s="125">
+      <c r="AX115" s="125">
         <f>H115+AC115</f>
         <v>0.0</v>
       </c>
-      <c r="AU115" s="119"/>
-      <c r="AV115" s="123" t="str">
+      <c r="AZ115" s="123" t="str">
         <f>J115</f>
         <v>L1-3</v>
       </c>
-      <c r="AW115" s="124">
+      <c r="BA115" s="124">
         <f>K115</f>
         <v>1.2</v>
       </c>
-      <c r="AX115" s="125">
+      <c r="BB115" s="125">
         <f>L115+AG115</f>
         <v>-0.11659409806484</v>
       </c>
-      <c r="AZ115" s="123" t="str">
-        <f>N115</f>
+      <c r="BD115" s="123"/>
+      <c r="BE115" s="124"/>
+      <c r="BF115" s="125">
+        <f>P115+AK115</f>
+        <v>0.0</v>
+      </c>
+      <c r="BH115" s="123" t="str">
+        <f>R115</f>
         <v>LT-3</v>
       </c>
-      <c r="BA115" s="124">
-        <f>O115</f>
+      <c r="BI115" s="124">
+        <f>S115</f>
         <v>1.5</v>
       </c>
-      <c r="BB115" s="125">
-        <f>P115+AK115</f>
+      <c r="BJ115" s="125">
+        <f>T115+AO115</f>
         <v>-0.14574262258105</v>
       </c>
-      <c r="BC115" s="119"/>
     </row>
     <row r="116" x14ac:dyDescent="0.3">
       <c r="B116" s="123" t="s">
@@ -14232,10 +14348,9 @@
         <v>0.58531500000000003</v>
       </c>
       <c r="D116" s="125">
-        <f t="shared" si="2"/>
+        <f>$E$71*C116/100</f>
         <v>0.227480915029406</v>
       </c>
-      <c r="E116" s="119"/>
       <c r="F116" s="123" t="s">
         <v>218</v>
       </c>
@@ -14243,10 +14358,9 @@
         <v>0.58531500000000003</v>
       </c>
       <c r="H116" s="125">
-        <f t="shared" si="3"/>
+        <f>$E$72*G116/100</f>
         <v>-0.142175571893379</v>
       </c>
-      <c r="I116" s="119"/>
       <c r="J116" s="123" t="s">
         <v>219</v>
       </c>
@@ -14254,17 +14368,22 @@
         <v>0.9</v>
       </c>
       <c r="L116" s="125">
-        <f t="shared" si="5"/>
+        <f>$E$73*K116/100</f>
         <v>-0.306059507420204</v>
       </c>
-      <c r="N116" s="123" t="s">
+      <c r="N116" s="123"/>
+      <c r="O116" s="124"/>
+      <c r="P116" s="125">
+        <v>0</v>
+      </c>
+      <c r="R116" s="123" t="s">
         <v>232</v>
       </c>
-      <c r="O116" s="124">
+      <c r="S116" s="124">
         <v>1.5</v>
       </c>
-      <c r="P116" s="125">
-        <f t="shared" si="6"/>
+      <c r="T116" s="125">
+        <f>$E$74*S116/100</f>
         <v>-0.510099179033674</v>
       </c>
       <c r="W116" s="123" t="str">
@@ -14279,7 +14398,6 @@
         <f>-$I$95*C116/100</f>
         <v>0.142175571893379</v>
       </c>
-      <c r="Z116" s="119"/>
       <c r="AA116" s="123" t="str">
         <f>F116</f>
         <v>VB-1 sup.</v>
@@ -14292,7 +14410,6 @@
         <f>-$I$95*G116/100</f>
         <v>0.142175571893379</v>
       </c>
-      <c r="AD116" s="119"/>
       <c r="AE116" s="123" t="str">
         <f>J116</f>
         <v>L1-3 P.</v>
@@ -14305,66 +14422,76 @@
         <f>-$I$95*K116/100</f>
         <v>0.218613933871575</v>
       </c>
-      <c r="AI116" s="123" t="str">
-        <f>N116</f>
-        <v>LT-4</v>
-      </c>
-      <c r="AJ116" s="124">
-        <f>O116</f>
-        <v>1.5</v>
-      </c>
+      <c r="AI116" s="123"/>
+      <c r="AJ116" s="124"/>
       <c r="AK116" s="125">
         <f>-$I$95*O116/100</f>
+        <v>0.0</v>
+      </c>
+      <c r="AM116" s="123" t="str">
+        <f>R116</f>
+        <v>LT-4</v>
+      </c>
+      <c r="AN116" s="124">
+        <f>S116</f>
+        <v>1.5</v>
+      </c>
+      <c r="AO116" s="125">
+        <f>-$I$95*S116/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AN116" s="123" t="str">
+      <c r="AR116" s="123" t="str">
         <f>B116</f>
         <v>VA-1 sup.</v>
       </c>
-      <c r="AO116" s="124">
+      <c r="AS116" s="124">
         <f>C116</f>
         <v>0.585315</v>
       </c>
-      <c r="AP116" s="125">
+      <c r="AT116" s="125">
         <f>D116+Y116</f>
         <v>0.369656486922784</v>
       </c>
-      <c r="AQ116" s="119"/>
-      <c r="AR116" s="123" t="str">
+      <c r="AV116" s="123" t="str">
         <f>F116</f>
         <v>VB-1 sup.</v>
       </c>
-      <c r="AS116" s="124">
+      <c r="AW116" s="124">
         <f>G116</f>
         <v>0.585315</v>
       </c>
-      <c r="AT116" s="125">
+      <c r="AX116" s="125">
         <f>H116+AC116</f>
         <v>0.0</v>
       </c>
-      <c r="AU116" s="119"/>
-      <c r="AV116" s="123" t="str">
+      <c r="AZ116" s="123" t="str">
         <f>J116</f>
         <v>L1-3 P.</v>
       </c>
-      <c r="AW116" s="124">
+      <c r="BA116" s="124">
         <f>K116</f>
         <v>0.9</v>
       </c>
-      <c r="AX116" s="125">
+      <c r="BB116" s="125">
         <f>L116+AG116</f>
         <v>-0.0874455735486298</v>
       </c>
-      <c r="AZ116" s="123" t="str">
-        <f>N116</f>
+      <c r="BD116" s="123"/>
+      <c r="BE116" s="124"/>
+      <c r="BF116" s="125">
+        <f>P116+AK116</f>
+        <v>0.0</v>
+      </c>
+      <c r="BH116" s="123" t="str">
+        <f>R116</f>
         <v>LT-4</v>
       </c>
-      <c r="BA116" s="124">
-        <f>O116</f>
+      <c r="BI116" s="124">
+        <f>S116</f>
         <v>1.5</v>
       </c>
-      <c r="BB116" s="125">
-        <f>P116+AK116</f>
+      <c r="BJ116" s="125">
+        <f>T116+AO116</f>
         <v>-0.14574262258105</v>
       </c>
     </row>
@@ -14376,10 +14503,9 @@
         <v>0.37781999999999999</v>
       </c>
       <c r="D117" s="125">
-        <f t="shared" si="2"/>
+        <f>$E$71*C117/100</f>
         <v>0.146838607102859</v>
       </c>
-      <c r="E117" s="119"/>
       <c r="F117" s="123" t="s">
         <v>221</v>
       </c>
@@ -14387,10 +14513,9 @@
         <v>0.37781999999999999</v>
       </c>
       <c r="H117" s="125">
-        <f t="shared" si="3"/>
+        <f>$E$72*G117/100</f>
         <v>-0.091774129439287</v>
       </c>
-      <c r="I117" s="119"/>
       <c r="J117" s="123" t="s">
         <v>222</v>
       </c>
@@ -14398,17 +14523,22 @@
         <v>1.2</v>
       </c>
       <c r="L117" s="125">
-        <f t="shared" si="5"/>
+        <f>$E$73*K117/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="N117" s="123" t="s">
+      <c r="N117" s="123"/>
+      <c r="O117" s="124"/>
+      <c r="P117" s="125">
+        <v>0</v>
+      </c>
+      <c r="R117" s="123" t="s">
         <v>235</v>
       </c>
-      <c r="O117" s="124">
+      <c r="S117" s="124">
         <v>0.75</v>
       </c>
-      <c r="P117" s="125">
-        <f t="shared" si="6"/>
+      <c r="T117" s="125">
+        <f>$E$74*S117/100</f>
         <v>-0.255049589516837</v>
       </c>
       <c r="W117" s="123" t="str">
@@ -14423,7 +14553,6 @@
         <f>-$I$95*C117/100</f>
         <v>0.091774129439287</v>
       </c>
-      <c r="Z117" s="119"/>
       <c r="AA117" s="123" t="str">
         <f>F117</f>
         <v>VB-2 sup.</v>
@@ -14436,7 +14565,6 @@
         <f>-$I$95*G117/100</f>
         <v>0.091774129439287</v>
       </c>
-      <c r="AD117" s="119"/>
       <c r="AE117" s="123" t="str">
         <f>J117</f>
         <v>L1-4</v>
@@ -14449,84 +14577,80 @@
         <f>-$I$95*K117/100</f>
         <v>0.291485245162099</v>
       </c>
-      <c r="AI117" s="123" t="str">
-        <f>N117</f>
-        <v>LT-5</v>
-      </c>
-      <c r="AJ117" s="124">
-        <f>O117</f>
-        <v>0.75</v>
-      </c>
+      <c r="AI117" s="123"/>
+      <c r="AJ117" s="124"/>
       <c r="AK117" s="125">
         <f>-$I$95*O117/100</f>
+        <v>0.0</v>
+      </c>
+      <c r="AM117" s="123" t="str">
+        <f>R117</f>
+        <v>LT-5</v>
+      </c>
+      <c r="AN117" s="124">
+        <f>S117</f>
+        <v>0.75</v>
+      </c>
+      <c r="AO117" s="125">
+        <f>-$I$95*S117/100</f>
         <v>0.182178278226312</v>
       </c>
-      <c r="AN117" s="123" t="str">
+      <c r="AR117" s="123" t="str">
         <f>B117</f>
         <v>VA-2 sup.</v>
       </c>
-      <c r="AO117" s="124">
+      <c r="AS117" s="124">
         <f>C117</f>
         <v>0.37782</v>
       </c>
-      <c r="AP117" s="125">
+      <c r="AT117" s="125">
         <f>D117+Y117</f>
         <v>0.238612736542146</v>
       </c>
-      <c r="AQ117" s="119"/>
-      <c r="AR117" s="123" t="str">
+      <c r="AV117" s="123" t="str">
         <f>F117</f>
         <v>VB-2 sup.</v>
       </c>
-      <c r="AS117" s="124">
+      <c r="AW117" s="124">
         <f>G117</f>
         <v>0.37782</v>
       </c>
-      <c r="AT117" s="125">
+      <c r="AX117" s="125">
         <f>H117+AC117</f>
         <v>0.0</v>
       </c>
-      <c r="AU117" s="119"/>
-      <c r="AV117" s="123" t="str">
+      <c r="AZ117" s="123" t="str">
         <f>J117</f>
         <v>L1-4</v>
       </c>
-      <c r="AW117" s="124">
+      <c r="BA117" s="124">
         <f>K117</f>
         <v>1.2</v>
       </c>
-      <c r="AX117" s="125">
+      <c r="BB117" s="125">
         <f>L117+AG117</f>
         <v>-0.11659409806484</v>
       </c>
-      <c r="AZ117" s="123" t="str">
-        <f>N117</f>
+      <c r="BD117" s="123"/>
+      <c r="BE117" s="124"/>
+      <c r="BF117" s="125">
+        <f>P117+AK117</f>
+        <v>0.0</v>
+      </c>
+      <c r="BH117" s="123" t="str">
+        <f>R117</f>
         <v>LT-5</v>
       </c>
-      <c r="BA117" s="124">
-        <f>O117</f>
+      <c r="BI117" s="124">
+        <f>S117</f>
         <v>0.75</v>
       </c>
-      <c r="BB117" s="125">
-        <f>P117+AK117</f>
+      <c r="BJ117" s="125">
+        <f>T117+AO117</f>
         <v>-0.0728713112905249</v>
       </c>
     </row>
     <row r="118" x14ac:dyDescent="0.3">
-      <c r="B118" s="123"/>
-      <c r="C118" s="124"/>
-      <c r="D118" s="125">
-        <f t="shared" si="2"/>
-        <v>0.0</v>
-      </c>
-      <c r="E118" s="119"/>
-      <c r="F118" s="123"/>
-      <c r="G118" s="124"/>
-      <c r="H118" s="125">
-        <f t="shared" si="3"/>
-        <v>0.0</v>
-      </c>
-      <c r="I118" s="119"/>
       <c r="J118" s="123" t="s">
         <v>223</v>
       </c>
@@ -14534,33 +14658,24 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="L118" s="125">
-        <f t="shared" si="5"/>
+        <f>$E$73*K118/100</f>
         <v>-0.39107603725915</v>
       </c>
-      <c r="N118" s="123" t="s">
+      <c r="N118" s="123"/>
+      <c r="O118" s="124"/>
+      <c r="P118" s="125">
+        <v>0</v>
+      </c>
+      <c r="R118" s="123" t="s">
         <v>238</v>
       </c>
-      <c r="O118" s="124">
+      <c r="S118" s="124">
         <v>1.5</v>
       </c>
-      <c r="P118" s="125">
-        <f t="shared" si="6"/>
+      <c r="T118" s="125">
+        <f>$E$74*S118/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="W118" s="123"/>
-      <c r="X118" s="124"/>
-      <c r="Y118" s="125">
-        <f>-$I$95*C118/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z118" s="119"/>
-      <c r="AA118" s="123"/>
-      <c r="AB118" s="124"/>
-      <c r="AC118" s="125">
-        <f>-$I$95*G118/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD118" s="119"/>
       <c r="AE118" s="123" t="str">
         <f>J118</f>
         <v>L1-5</v>
@@ -14573,69 +14688,56 @@
         <f>-$I$95*K118/100</f>
         <v>0.279340026613679</v>
       </c>
-      <c r="AI118" s="123" t="str">
-        <f>N118</f>
-        <v>LT-6</v>
-      </c>
-      <c r="AJ118" s="124">
-        <f>O118</f>
-        <v>1.5</v>
-      </c>
+      <c r="AI118" s="123"/>
+      <c r="AJ118" s="124"/>
       <c r="AK118" s="125">
         <f>-$I$95*O118/100</f>
+        <v>0.0</v>
+      </c>
+      <c r="AM118" s="123" t="str">
+        <f>R118</f>
+        <v>LT-6</v>
+      </c>
+      <c r="AN118" s="124">
+        <f>S118</f>
+        <v>1.5</v>
+      </c>
+      <c r="AO118" s="125">
+        <f>-$I$95*S118/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AN118" s="123"/>
-      <c r="AO118" s="124"/>
-      <c r="AP118" s="125">
-        <f>D118+Y118</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ118" s="119"/>
-      <c r="AR118" s="123"/>
-      <c r="AS118" s="124"/>
-      <c r="AT118" s="125">
-        <f>H118+AC118</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU118" s="119"/>
-      <c r="AV118" s="123" t="str">
+      <c r="AZ118" s="123" t="str">
         <f>J118</f>
         <v>L1-5</v>
       </c>
-      <c r="AW118" s="124">
+      <c r="BA118" s="124">
         <f>K118</f>
         <v>1.15</v>
       </c>
-      <c r="AX118" s="125">
+      <c r="BB118" s="125">
         <f>L118+AG118</f>
         <v>-0.111736010645471</v>
       </c>
-      <c r="AZ118" s="123" t="str">
-        <f>N118</f>
+      <c r="BD118" s="123"/>
+      <c r="BE118" s="124"/>
+      <c r="BF118" s="125">
+        <f>P118+AK118</f>
+        <v>0.0</v>
+      </c>
+      <c r="BH118" s="123" t="str">
+        <f>R118</f>
         <v>LT-6</v>
       </c>
-      <c r="BA118" s="124">
-        <f>O118</f>
+      <c r="BI118" s="124">
+        <f>S118</f>
         <v>1.5</v>
       </c>
-      <c r="BB118" s="125">
-        <f>P118+AK118</f>
+      <c r="BJ118" s="125">
+        <f>T118+AO118</f>
         <v>-0.14574262258105</v>
       </c>
     </row>
     <row r="119" x14ac:dyDescent="0.3">
-      <c r="B119" s="123"/>
-      <c r="C119" s="124"/>
-      <c r="D119" s="125">
-        <f t="shared" si="2"/>
-        <v>0.0</v>
-      </c>
-      <c r="E119" s="119"/>
-      <c r="F119" s="119"/>
-      <c r="G119" s="126"/>
-      <c r="H119" s="119"/>
-      <c r="I119" s="119"/>
       <c r="J119" s="123" t="s">
         <v>224</v>
       </c>
@@ -14646,30 +14748,16 @@
         <f>$E$73*K119/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="N119" s="123" t="s">
+      <c r="R119" s="123" t="s">
         <v>241</v>
       </c>
-      <c r="O119" s="124">
+      <c r="S119" s="124">
         <v>1.5</v>
       </c>
-      <c r="P119" s="125">
-        <f t="shared" si="6"/>
+      <c r="T119" s="125">
+        <f>$E$74*S119/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="W119" s="123"/>
-      <c r="X119" s="124"/>
-      <c r="Y119" s="125">
-        <f>-$I$95*C119/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z119" s="119"/>
-      <c r="AA119" s="119"/>
-      <c r="AB119" s="126"/>
-      <c r="AC119" s="119">
-        <f>-$I$95*G119/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD119" s="119"/>
       <c r="AE119" s="123" t="str">
         <f>J119</f>
         <v>L1-6 lat.</v>
@@ -14682,69 +14770,44 @@
         <f>-$I$95*K119/100</f>
         <v>0.291485245162099</v>
       </c>
-      <c r="AI119" s="123" t="str">
-        <f>N119</f>
+      <c r="AM119" s="123" t="str">
+        <f>R119</f>
         <v>VM-2</v>
       </c>
-      <c r="AJ119" s="124">
-        <f>O119</f>
+      <c r="AN119" s="124">
+        <f>S119</f>
         <v>1.5</v>
       </c>
-      <c r="AK119" s="125">
-        <f>-$I$95*O119/100</f>
+      <c r="AO119" s="125">
+        <f>-$I$95*S119/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AN119" s="123"/>
-      <c r="AO119" s="124"/>
-      <c r="AP119" s="125">
-        <f>D119+Y119</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ119" s="119"/>
-      <c r="AR119" s="119"/>
-      <c r="AS119" s="126"/>
-      <c r="AT119" s="119">
-        <f>H119+AC119</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU119" s="119"/>
-      <c r="AV119" s="123" t="str">
+      <c r="AZ119" s="123" t="str">
         <f>J119</f>
         <v>L1-6 lat.</v>
       </c>
-      <c r="AW119" s="124">
+      <c r="BA119" s="124">
         <f>K119</f>
         <v>1.2</v>
       </c>
-      <c r="AX119" s="125">
+      <c r="BB119" s="125">
         <f>L119+AG119</f>
         <v>-0.11659409806484</v>
       </c>
-      <c r="AZ119" s="123" t="str">
-        <f>N119</f>
+      <c r="BH119" s="123" t="str">
+        <f>R119</f>
         <v>VM-2</v>
       </c>
-      <c r="BA119" s="124">
-        <f>O119</f>
+      <c r="BI119" s="124">
+        <f>S119</f>
         <v>1.5</v>
       </c>
-      <c r="BB119" s="125">
-        <f>P119+AK119</f>
+      <c r="BJ119" s="125">
+        <f>T119+AO119</f>
         <v>-0.14574262258105</v>
       </c>
     </row>
     <row r="120" x14ac:dyDescent="0.3">
-      <c r="B120" s="123"/>
-      <c r="C120" s="124"/>
-      <c r="D120" s="125">
-        <f t="shared" si="2"/>
-        <v>0.0</v>
-      </c>
-      <c r="E120" s="119"/>
-      <c r="F120" s="119"/>
-      <c r="G120" s="119"/>
-      <c r="H120" s="119"/>
-      <c r="I120" s="119"/>
       <c r="J120" s="123" t="s">
         <v>225</v>
       </c>
@@ -14752,33 +14815,19 @@
         <v>0.65</v>
       </c>
       <c r="L120" s="125">
-        <f t="shared" si="5"/>
+        <f>$E$73*K120/100</f>
         <v>-0.221042977581259</v>
       </c>
-      <c r="N120" s="123" t="s">
+      <c r="R120" s="123" t="s">
         <v>233</v>
       </c>
-      <c r="O120" s="124">
+      <c r="S120" s="124">
         <v>1.5</v>
       </c>
-      <c r="P120" s="125">
-        <f t="shared" si="6"/>
+      <c r="T120" s="125">
+        <f>$E$74*S120/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="W120" s="123"/>
-      <c r="X120" s="124"/>
-      <c r="Y120" s="125">
-        <f>-$I$95*C120/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z120" s="119"/>
-      <c r="AA120" s="119"/>
-      <c r="AB120" s="119"/>
-      <c r="AC120" s="119">
-        <f>-$I$95*G120/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD120" s="119"/>
       <c r="AE120" s="123" t="str">
         <f>J120</f>
         <v>L1-6 cen.</v>
@@ -14791,69 +14840,44 @@
         <f>-$I$95*K120/100</f>
         <v>0.157887841129471</v>
       </c>
-      <c r="AI120" s="123" t="str">
-        <f>N120</f>
+      <c r="AM120" s="123" t="str">
+        <f>R120</f>
         <v>LT-7</v>
       </c>
-      <c r="AJ120" s="124">
-        <f>O120</f>
+      <c r="AN120" s="124">
+        <f>S120</f>
         <v>1.5</v>
       </c>
-      <c r="AK120" s="125">
-        <f>-$I$95*O120/100</f>
+      <c r="AO120" s="125">
+        <f>-$I$95*S120/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AN120" s="123"/>
-      <c r="AO120" s="124"/>
-      <c r="AP120" s="125">
-        <f>D120+Y120</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ120" s="119"/>
-      <c r="AR120" s="119"/>
-      <c r="AS120" s="119"/>
-      <c r="AT120" s="119">
-        <f>H120+AC120</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU120" s="119"/>
-      <c r="AV120" s="123" t="str">
+      <c r="AZ120" s="123" t="str">
         <f>J120</f>
         <v>L1-6 cen.</v>
       </c>
-      <c r="AW120" s="124">
+      <c r="BA120" s="124">
         <f>K120</f>
         <v>0.65</v>
       </c>
-      <c r="AX120" s="125">
+      <c r="BB120" s="125">
         <f>L120+AG120</f>
         <v>-0.0631551364517882</v>
       </c>
-      <c r="AZ120" s="123" t="str">
-        <f>N120</f>
+      <c r="BH120" s="123" t="str">
+        <f>R120</f>
         <v>LT-7</v>
       </c>
-      <c r="BA120" s="124">
-        <f>O120</f>
+      <c r="BI120" s="124">
+        <f>S120</f>
         <v>1.5</v>
       </c>
-      <c r="BB120" s="125">
-        <f>P120+AK120</f>
+      <c r="BJ120" s="125">
+        <f>T120+AO120</f>
         <v>-0.14574262258105</v>
       </c>
     </row>
     <row r="121" x14ac:dyDescent="0.3">
-      <c r="B121" s="123"/>
-      <c r="C121" s="124"/>
-      <c r="D121" s="125">
-        <f t="shared" si="2"/>
-        <v>0.0</v>
-      </c>
-      <c r="E121" s="119"/>
-      <c r="F121" s="119"/>
-      <c r="G121" s="119"/>
-      <c r="H121" s="119"/>
-      <c r="I121" s="119"/>
       <c r="J121" s="123" t="s">
         <v>226</v>
       </c>
@@ -14861,33 +14885,19 @@
         <v>1.25</v>
       </c>
       <c r="L121" s="125">
-        <f t="shared" si="5"/>
+        <f>$E$73*K121/100</f>
         <v>-0.425082649194728</v>
       </c>
-      <c r="N121" s="123" t="s">
+      <c r="R121" s="123" t="s">
         <v>236</v>
       </c>
-      <c r="O121" s="124">
+      <c r="S121" s="124">
         <v>1.5</v>
       </c>
-      <c r="P121" s="125">
-        <f t="shared" si="6"/>
+      <c r="T121" s="125">
+        <f>$E$74*S121/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="W121" s="123"/>
-      <c r="X121" s="124"/>
-      <c r="Y121" s="125">
-        <f>-$I$95*C121/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z121" s="119"/>
-      <c r="AA121" s="119"/>
-      <c r="AB121" s="119"/>
-      <c r="AC121" s="119">
-        <f>-$I$95*G121/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD121" s="119"/>
       <c r="AE121" s="123" t="str">
         <f>J121</f>
         <v>L1-7</v>
@@ -14900,66 +14910,44 @@
         <f>-$I$95*K121/100</f>
         <v>0.30363046371052</v>
       </c>
-      <c r="AI121" s="123" t="str">
-        <f>N121</f>
+      <c r="AM121" s="123" t="str">
+        <f>R121</f>
         <v>LT-8</v>
       </c>
-      <c r="AJ121" s="124">
-        <f>O121</f>
+      <c r="AN121" s="124">
+        <f>S121</f>
         <v>1.5</v>
       </c>
-      <c r="AK121" s="125">
-        <f>-$I$95*O121/100</f>
+      <c r="AO121" s="125">
+        <f>-$I$95*S121/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AN121" s="123"/>
-      <c r="AO121" s="124"/>
-      <c r="AP121" s="125">
-        <f>D121+Y121</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ121" s="119"/>
-      <c r="AR121" s="119"/>
-      <c r="AS121" s="119"/>
-      <c r="AT121" s="119">
-        <f>H121+AC121</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU121" s="119"/>
-      <c r="AV121" s="123" t="str">
+      <c r="AZ121" s="123" t="str">
         <f>J121</f>
         <v>L1-7</v>
       </c>
-      <c r="AW121" s="124">
+      <c r="BA121" s="124">
         <f>K121</f>
         <v>1.25</v>
       </c>
-      <c r="AX121" s="125">
+      <c r="BB121" s="125">
         <f>L121+AG121</f>
         <v>-0.121452185484208</v>
       </c>
-      <c r="AZ121" s="123" t="str">
-        <f>N121</f>
+      <c r="BH121" s="123" t="str">
+        <f>R121</f>
         <v>LT-8</v>
       </c>
-      <c r="BA121" s="124">
-        <f>O121</f>
+      <c r="BI121" s="124">
+        <f>S121</f>
         <v>1.5</v>
       </c>
-      <c r="BB121" s="125">
-        <f>P121+AK121</f>
+      <c r="BJ121" s="125">
+        <f>T121+AO121</f>
         <v>-0.14574262258105</v>
       </c>
     </row>
     <row r="122" x14ac:dyDescent="0.3">
-      <c r="B122" s="119"/>
-      <c r="C122" s="119"/>
-      <c r="D122" s="119"/>
-      <c r="E122" s="119"/>
-      <c r="F122" s="119"/>
-      <c r="G122" s="119"/>
-      <c r="H122" s="119"/>
-      <c r="I122" s="119"/>
       <c r="J122" s="123" t="s">
         <v>227</v>
       </c>
@@ -14967,33 +14955,19 @@
         <v>1.3149999999999999</v>
       </c>
       <c r="L122" s="125">
-        <f t="shared" si="5"/>
+        <f>$E$73*K122/100</f>
         <v>-0.447186946952854</v>
       </c>
-      <c r="N122" s="123" t="s">
+      <c r="R122" s="123" t="s">
         <v>239</v>
       </c>
-      <c r="O122" s="124">
+      <c r="S122" s="124">
         <v>1.5</v>
       </c>
-      <c r="P122" s="125">
-        <f>$E$74*O122/100</f>
+      <c r="T122" s="125">
+        <f>$E$74*S122/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="W122" s="119"/>
-      <c r="X122" s="119"/>
-      <c r="Y122" s="119">
-        <f>-$I$95*C122/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z122" s="119"/>
-      <c r="AA122" s="119"/>
-      <c r="AB122" s="119"/>
-      <c r="AC122" s="119">
-        <f>-$I$95*G122/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD122" s="119"/>
       <c r="AE122" s="123" t="str">
         <f>J122</f>
         <v>L1-8</v>
@@ -15006,66 +14980,44 @@
         <f>-$I$95*K122/100</f>
         <v>0.319419247823467</v>
       </c>
-      <c r="AI122" s="123" t="str">
-        <f>N122</f>
+      <c r="AM122" s="123" t="str">
+        <f>R122</f>
         <v>LT-9</v>
       </c>
-      <c r="AJ122" s="124">
-        <f>O122</f>
+      <c r="AN122" s="124">
+        <f>S122</f>
         <v>1.5</v>
       </c>
-      <c r="AK122" s="125">
-        <f>-$I$95*O122/100</f>
+      <c r="AO122" s="125">
+        <f>-$I$95*S122/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AN122" s="119"/>
-      <c r="AO122" s="119"/>
-      <c r="AP122" s="119">
-        <f>D122+Y122</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ122" s="119"/>
-      <c r="AR122" s="119"/>
-      <c r="AS122" s="119"/>
-      <c r="AT122" s="119">
-        <f>H122+AC122</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU122" s="119"/>
-      <c r="AV122" s="123" t="str">
+      <c r="AZ122" s="123" t="str">
         <f>J122</f>
         <v>L1-8</v>
       </c>
-      <c r="AW122" s="124">
+      <c r="BA122" s="124">
         <f>K122</f>
         <v>1.315</v>
       </c>
-      <c r="AX122" s="125">
+      <c r="BB122" s="125">
         <f>L122+AG122</f>
         <v>-0.127767699129387</v>
       </c>
-      <c r="AZ122" s="123" t="str">
-        <f>N122</f>
+      <c r="BH122" s="123" t="str">
+        <f>R122</f>
         <v>LT-9</v>
       </c>
-      <c r="BA122" s="124">
-        <f>O122</f>
+      <c r="BI122" s="124">
+        <f>S122</f>
         <v>1.5</v>
       </c>
-      <c r="BB122" s="125">
-        <f>P122+AK122</f>
+      <c r="BJ122" s="125">
+        <f>T122+AO122</f>
         <v>-0.14574262258105</v>
       </c>
     </row>
     <row r="123" x14ac:dyDescent="0.3">
-      <c r="B123" s="119"/>
-      <c r="C123" s="119"/>
-      <c r="D123" s="119"/>
-      <c r="E123" s="119"/>
-      <c r="F123" s="119"/>
-      <c r="G123" s="119"/>
-      <c r="H123" s="119"/>
-      <c r="I123" s="119"/>
       <c r="J123" s="123" t="s">
         <v>228</v>
       </c>
@@ -15073,33 +15025,19 @@
         <v>0.71499999999999997</v>
       </c>
       <c r="L123" s="125">
-        <f t="shared" si="5"/>
+        <f>$E$73*K123/100</f>
         <v>-0.243147275339385</v>
       </c>
-      <c r="N123" s="123" t="s">
+      <c r="R123" s="123" t="s">
         <v>242</v>
       </c>
-      <c r="O123" s="124">
+      <c r="S123" s="124">
         <v>0.75</v>
       </c>
-      <c r="P123" s="125">
-        <f t="shared" si="6"/>
+      <c r="T123" s="125">
+        <f>$E$74*S123/100</f>
         <v>-0.255049589516837</v>
       </c>
-      <c r="W123" s="119"/>
-      <c r="X123" s="119"/>
-      <c r="Y123" s="119">
-        <f>-$I$95*C123/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z123" s="119"/>
-      <c r="AA123" s="119"/>
-      <c r="AB123" s="119"/>
-      <c r="AC123" s="119">
-        <f>-$I$95*G123/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD123" s="119"/>
       <c r="AE123" s="123" t="str">
         <f>J123</f>
         <v>VM-1 sup.</v>
@@ -15112,139 +15050,48 @@
         <f>-$I$95*K123/100</f>
         <v>0.173676625242418</v>
       </c>
-      <c r="AI123" s="123" t="str">
-        <f>N123</f>
+      <c r="AM123" s="123" t="str">
+        <f>R123</f>
         <v>VM-3</v>
       </c>
-      <c r="AJ123" s="124">
-        <f>O123</f>
+      <c r="AN123" s="124">
+        <f>S123</f>
         <v>0.75</v>
       </c>
-      <c r="AK123" s="125">
-        <f>-$I$95*O123/100</f>
+      <c r="AO123" s="125">
+        <f>-$I$95*S123/100</f>
         <v>0.182178278226312</v>
       </c>
-      <c r="AN123" s="119"/>
-      <c r="AO123" s="119"/>
-      <c r="AP123" s="119">
-        <f>D123+Y123</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ123" s="119"/>
-      <c r="AR123" s="119"/>
-      <c r="AS123" s="119"/>
-      <c r="AT123" s="119">
-        <f>H123+AC123</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU123" s="119"/>
-      <c r="AV123" s="123" t="str">
+      <c r="AZ123" s="123" t="str">
         <f>J123</f>
         <v>VM-1 sup.</v>
       </c>
-      <c r="AW123" s="124">
+      <c r="BA123" s="124">
         <f>K123</f>
         <v>0.715</v>
       </c>
-      <c r="AX123" s="125">
+      <c r="BB123" s="125">
         <f>L123+AG123</f>
         <v>-0.069470650096967</v>
       </c>
-      <c r="AZ123" s="123" t="str">
-        <f>N123</f>
+      <c r="BH123" s="123" t="str">
+        <f>R123</f>
         <v>VM-3</v>
       </c>
-      <c r="BA123" s="124">
-        <f>O123</f>
+      <c r="BI123" s="124">
+        <f>S123</f>
         <v>0.75</v>
       </c>
-      <c r="BB123" s="125">
-        <f>P123+AK123</f>
+      <c r="BJ123" s="125">
+        <f>T123+AO123</f>
         <v>-0.0728713112905249</v>
       </c>
     </row>
-    <row r="124" x14ac:dyDescent="0.3">
-      <c r="J124" s="18"/>
-      <c r="K124" s="79"/>
-      <c r="L124" s="70">
-        <f t="shared" si="5"/>
-        <v>0.0</v>
-      </c>
-      <c r="AE124" s="18"/>
-      <c r="AF124" s="79"/>
-      <c r="AG124" s="70">
-        <f>-$I$95*K124/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV124" s="18"/>
-      <c r="AW124" s="79"/>
-      <c r="AX124" s="70">
-        <f>L124+AG124</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="125" x14ac:dyDescent="0.3">
-      <c r="J125" s="18"/>
-      <c r="K125" s="79"/>
-      <c r="L125" s="70">
-        <f t="shared" si="5"/>
-        <v>0.0</v>
-      </c>
-      <c r="AE125" s="18"/>
-      <c r="AF125" s="79"/>
-      <c r="AG125" s="70">
-        <f>-$I$95*K125/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV125" s="18"/>
-      <c r="AW125" s="79"/>
-      <c r="AX125" s="70">
-        <f>L125+AG125</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="126" x14ac:dyDescent="0.3">
-      <c r="J126" s="18"/>
-      <c r="K126" s="79"/>
-      <c r="L126" s="70">
-        <f t="shared" si="5"/>
-        <v>0.0</v>
-      </c>
-      <c r="AE126" s="18"/>
-      <c r="AF126" s="79"/>
-      <c r="AG126" s="70">
-        <f>-$I$95*K126/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV126" s="18"/>
-      <c r="AW126" s="79"/>
-      <c r="AX126" s="70">
-        <f>L126+AG126</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="131" x14ac:dyDescent="0.3">
-      <c r="J131" s="119"/>
-      <c r="K131" s="119"/>
-      <c r="L131" s="119"/>
-      <c r="AE131" s="119"/>
-      <c r="AF131" s="119"/>
-      <c r="AG131" s="119">
-        <f>-$I$95*K131/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV131" s="119"/>
-      <c r="AW131" s="119"/>
-      <c r="AX131" s="119">
-        <f>L131+AG131</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="135" x14ac:dyDescent="0.3">
-      <c r="I135" s="119"/>
-      <c r="AD135" s="119"/>
-      <c r="AU135" s="119"/>
-    </row>
+    <row r="124" x14ac:dyDescent="0.3"/>
+    <row r="125" x14ac:dyDescent="0.3"/>
+    <row r="126" x14ac:dyDescent="0.3"/>
+    <row r="131" x14ac:dyDescent="0.3"/>
+    <row r="135" x14ac:dyDescent="0.3"/>
     <row r="137" x14ac:dyDescent="0.3">
       <c r="B137" s="81" t="s">
         <v>243</v>
@@ -15288,15 +15135,15 @@
       <c r="AJ137" s="82"/>
       <c r="AK137" s="82"/>
       <c r="AL137" s="82"/>
-      <c r="AN137" s="81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIENTO EN DIRECCION -X — TOTAL (Cpe + Cpi)</t>
-        </is>
-      </c>
+      <c r="AM137" s="82"/>
+      <c r="AN137" s="82"/>
       <c r="AO137" s="82"/>
       <c r="AP137" s="82"/>
-      <c r="AQ137" s="82"/>
-      <c r="AR137" s="82"/>
+      <c r="AR137" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIENTO EN DIRECCION -X — TOTAL (Cpe + Cpi)</t>
+        </is>
+      </c>
       <c r="AS137" s="82"/>
       <c r="AT137" s="82"/>
       <c r="AU137" s="82"/>
@@ -15308,6 +15155,14 @@
       <c r="BA137" s="82"/>
       <c r="BB137" s="82"/>
       <c r="BC137" s="82"/>
+      <c r="BD137" s="82"/>
+      <c r="BE137" s="82"/>
+      <c r="BF137" s="82"/>
+      <c r="BG137" s="82"/>
+      <c r="BH137" s="82"/>
+      <c r="BI137" s="82"/>
+      <c r="BJ137" s="82"/>
+      <c r="BK137" s="82"/>
     </row>
     <row r="139" x14ac:dyDescent="0.3">
       <c r="B139" s="78" t="s">
@@ -15319,7 +15174,12 @@
       <c r="J139" s="78" t="s">
         <v>201</v>
       </c>
-      <c r="N139" s="78" t="s">
+      <c r="N139" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EJE 3 ABIERTO (SIN CERRAMIENTO):</t>
+        </is>
+      </c>
+      <c r="R139" s="78" t="s">
         <v>229</v>
       </c>
       <c r="W139" s="78" t="str">
@@ -15336,65 +15196,109 @@
       </c>
       <c r="AI139" s="78" t="str">
         <f>N139</f>
+        <v>EJE 3 ABIERTO (SIN CERRAMIENTO):</v>
+      </c>
+      <c r="AM139" s="78" t="str">
+        <f>R139</f>
         <v>CUBIERTA — LARGUEROS Y VIGAS DE MARCO</v>
       </c>
-      <c r="AN139" s="78" t="str">
+      <c r="AR139" s="78" t="str">
         <f>B139</f>
         <v>MURO B EN BARLOVENTO:</v>
       </c>
-      <c r="AR139" s="78" t="str">
+      <c r="AV139" s="78" t="str">
         <f>F139</f>
         <v>MURO A EN SOTAVENTO:</v>
       </c>
-      <c r="AV139" s="78" t="str">
+      <c r="AZ139" s="78" t="str">
         <f>J139</f>
         <v>MURO 1 LATERAL:</v>
       </c>
-      <c r="AZ139" s="78" t="str">
+      <c r="BD139" s="78" t="str">
         <f>N139</f>
+        <v>EJE 3 ABIERTO (SIN CERRAMIENTO):</v>
+      </c>
+      <c r="BH139" s="78" t="str">
+        <f>R139</f>
         <v>CUBIERTA — LARGUEROS Y VIGAS DE MARCO</v>
       </c>
     </row>
     <row r="141" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B141" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="C141" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="D141" s="77" t="s">
-        <v>204</v>
-      </c>
-      <c r="E141" s="119"/>
-      <c r="F141" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="G141" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="H141" s="77" t="s">
-        <v>204</v>
-      </c>
-      <c r="I141" s="119"/>
-      <c r="J141" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="K141" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="L141" s="77" t="s">
-        <v>204</v>
-      </c>
-      <c r="N141" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="O141" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="P141" s="77" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q141" s="119"/>
+      <c r="B141" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="C141" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="D141" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd (kg/cm)</t>
+        </is>
+      </c>
+      <c r="F141" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="G141" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="H141" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd (kg/cm)</t>
+        </is>
+      </c>
+      <c r="J141" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="K141" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="L141" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd (kg/cm)</t>
+        </is>
+      </c>
+      <c r="N141" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="O141" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="P141" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd (kg/cm)</t>
+        </is>
+      </c>
+      <c r="R141" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="S141" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="T141" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd normal</t>
+        </is>
+      </c>
       <c r="W141" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
@@ -15410,7 +15314,6 @@
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="Z141" s="119"/>
       <c r="AA141" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
@@ -15426,7 +15329,6 @@
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="AD141" s="119"/>
       <c r="AE141" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
@@ -15457,70 +15359,96 @@
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="AL141" s="119"/>
-      <c r="AN141" s="122" t="inlineStr">
+      <c r="AM141" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
+      <c r="AN141" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
       <c r="AO141" s="77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pd interna (kg/cm)</t>
+        </is>
+      </c>
+      <c r="AR141" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="AS141" s="77" t="inlineStr">
+        <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="AP141" s="77" t="inlineStr">
+      <c r="AT141" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
-      <c r="AQ141" s="119"/>
-      <c r="AR141" s="122" t="inlineStr">
+      <c r="AV141" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="AS141" s="77" t="inlineStr">
+      <c r="AW141" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="AT141" s="77" t="inlineStr">
+      <c r="AX141" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
-      <c r="AU141" s="119"/>
-      <c r="AV141" s="122" t="inlineStr">
+      <c r="AZ141" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="AW141" s="77" t="inlineStr">
+      <c r="BA141" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="AX141" s="77" t="inlineStr">
+      <c r="BB141" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
-      <c r="AZ141" s="122" t="inlineStr">
+      <c r="BD141" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="BA141" s="77" t="inlineStr">
+      <c r="BE141" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="BB141" s="77" t="inlineStr">
+      <c r="BF141" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
-      <c r="BC141" s="119"/>
+      <c r="BH141" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="BI141" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="BJ141" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd total (kg/cm)</t>
+        </is>
+      </c>
     </row>
     <row r="142" x14ac:dyDescent="0.3">
       <c r="B142" s="123" t="s">
@@ -15533,7 +15461,6 @@
         <f>$E$71*C142/100</f>
         <v>0.349782294194519</v>
       </c>
-      <c r="E142" s="119"/>
       <c r="F142" s="123" t="s">
         <v>205</v>
       </c>
@@ -15544,7 +15471,6 @@
         <f>$E$72*G142/100</f>
         <v>-0.218613933871575</v>
       </c>
-      <c r="I142" s="119"/>
       <c r="J142" s="123" t="s">
         <v>207</v>
       </c>
@@ -15555,17 +15481,21 @@
         <f>$E$73*K142/100</f>
         <v>-0.306059507420204</v>
       </c>
-      <c r="N142" s="123" t="s">
+      <c r="N142" s="123"/>
+      <c r="O142" s="124"/>
+      <c r="P142" s="125">
+        <v>0</v>
+      </c>
+      <c r="R142" s="123" t="s">
         <v>231</v>
       </c>
-      <c r="O142" s="124">
+      <c r="S142" s="124">
         <v>0.5</v>
       </c>
-      <c r="P142" s="125">
-        <f>$E$74*O142/100</f>
+      <c r="T142" s="125">
+        <f>$E$74*S142/100</f>
         <v>-0.170033059677891</v>
       </c>
-      <c r="Q142" s="119"/>
       <c r="W142" s="123" t="str">
         <f>B142</f>
         <v>LB-1</v>
@@ -15578,7 +15508,6 @@
         <f>-$I$96*C142/100</f>
         <v>0.218613933871575</v>
       </c>
-      <c r="Z142" s="119"/>
       <c r="AA142" s="123" t="str">
         <f>F142</f>
         <v>LA-1</v>
@@ -15591,7 +15520,6 @@
         <f>-$I$96*G142/100</f>
         <v>0.218613933871575</v>
       </c>
-      <c r="AD142" s="119"/>
       <c r="AE142" s="123" t="str">
         <f>J142</f>
         <v>L1-1</v>
@@ -15604,70 +15532,78 @@
         <f>-$I$96*K142/100</f>
         <v>0.218613933871575</v>
       </c>
-      <c r="AI142" s="123" t="str">
-        <f>N142</f>
-        <v>VM-1</v>
-      </c>
-      <c r="AJ142" s="124">
-        <f>O142</f>
-        <v>0.5</v>
-      </c>
+      <c r="AI142" s="123"/>
+      <c r="AJ142" s="124"/>
       <c r="AK142" s="125">
         <f>-$I$96*O142/100</f>
+        <v>0.0</v>
+      </c>
+      <c r="AM142" s="123" t="str">
+        <f>R142</f>
+        <v>VM-1</v>
+      </c>
+      <c r="AN142" s="124">
+        <f>S142</f>
+        <v>0.5</v>
+      </c>
+      <c r="AO142" s="125">
+        <f>-$I$96*S142/100</f>
         <v>0.121452185484208</v>
       </c>
-      <c r="AL142" s="119"/>
-      <c r="AN142" s="123" t="str">
+      <c r="AR142" s="123" t="str">
         <f>B142</f>
         <v>LB-1</v>
       </c>
-      <c r="AO142" s="124">
+      <c r="AS142" s="124">
         <f>C142</f>
         <v>0.9</v>
       </c>
-      <c r="AP142" s="125">
+      <c r="AT142" s="125">
         <f>D142+Y142</f>
         <v>0.568396228066094</v>
       </c>
-      <c r="AQ142" s="119"/>
-      <c r="AR142" s="123" t="str">
+      <c r="AV142" s="123" t="str">
         <f>F142</f>
         <v>LA-1</v>
       </c>
-      <c r="AS142" s="124">
+      <c r="AW142" s="124">
         <f>G142</f>
         <v>0.9</v>
       </c>
-      <c r="AT142" s="125">
+      <c r="AX142" s="125">
         <f>H142+AC142</f>
         <v>0.0</v>
       </c>
-      <c r="AU142" s="119"/>
-      <c r="AV142" s="123" t="str">
+      <c r="AZ142" s="123" t="str">
         <f>J142</f>
         <v>L1-1</v>
       </c>
-      <c r="AW142" s="124">
+      <c r="BA142" s="124">
         <f>K142</f>
         <v>0.9</v>
       </c>
-      <c r="AX142" s="125">
+      <c r="BB142" s="125">
         <f>L142+AG142</f>
         <v>-0.0874455735486298</v>
       </c>
-      <c r="AZ142" s="123" t="str">
-        <f>N142</f>
+      <c r="BD142" s="123"/>
+      <c r="BE142" s="124"/>
+      <c r="BF142" s="125">
+        <f>P142+AK142</f>
+        <v>0.0</v>
+      </c>
+      <c r="BH142" s="123" t="str">
+        <f>R142</f>
         <v>VM-1</v>
       </c>
-      <c r="BA142" s="124">
-        <f>O142</f>
+      <c r="BI142" s="124">
+        <f>S142</f>
         <v>0.5</v>
       </c>
-      <c r="BB142" s="125">
-        <f>P142+AK142</f>
+      <c r="BJ142" s="125">
+        <f>T142+AO142</f>
         <v>-0.0485808741936832</v>
       </c>
-      <c r="BC142" s="119"/>
     </row>
     <row r="143" x14ac:dyDescent="0.3">
       <c r="B143" s="123" t="s">
@@ -15677,10 +15613,9 @@
         <v>1.2</v>
       </c>
       <c r="D143" s="125">
-        <f t="shared" ref="D143:D148" si="7">$E$71*C143/100</f>
+        <f>$E$71*C143/100</f>
         <v>0.466376392259359</v>
       </c>
-      <c r="E143" s="119"/>
       <c r="F143" s="123" t="s">
         <v>208</v>
       </c>
@@ -15688,10 +15623,9 @@
         <v>1.2</v>
       </c>
       <c r="H143" s="125">
-        <f t="shared" ref="H143:H151" si="8">$E$72*G143/100</f>
+        <f>$E$72*G143/100</f>
         <v>-0.291485245162099</v>
       </c>
-      <c r="I143" s="119"/>
       <c r="J143" s="123" t="s">
         <v>210</v>
       </c>
@@ -15699,20 +15633,24 @@
         <v>1.2</v>
       </c>
       <c r="L143" s="125">
-        <f t="shared" ref="L143:L156" si="9">$E$73*K143/100</f>
+        <f>$E$73*K143/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="N143" s="123" t="s">
+      <c r="N143" s="123"/>
+      <c r="O143" s="124"/>
+      <c r="P143" s="125">
+        <v>0</v>
+      </c>
+      <c r="R143" s="123" t="s">
         <v>234</v>
       </c>
-      <c r="O143" s="124">
+      <c r="S143" s="124">
         <v>1.25</v>
       </c>
-      <c r="P143" s="125">
-        <f t="shared" ref="P143:P144" si="10">$E$74*O143/100</f>
+      <c r="T143" s="125">
+        <f>$E$74*S143/100</f>
         <v>-0.425082649194728</v>
       </c>
-      <c r="Q143" s="119"/>
       <c r="W143" s="123" t="str">
         <f>B143</f>
         <v>LB-2 a 7</v>
@@ -15725,7 +15663,6 @@
         <f>-$I$96*C143/100</f>
         <v>0.291485245162099</v>
       </c>
-      <c r="Z143" s="119"/>
       <c r="AA143" s="123" t="str">
         <f>F143</f>
         <v>LA-2 a 7</v>
@@ -15738,7 +15675,6 @@
         <f>-$I$96*G143/100</f>
         <v>0.291485245162099</v>
       </c>
-      <c r="AD143" s="119"/>
       <c r="AE143" s="123" t="str">
         <f>J143</f>
         <v>L1-2</v>
@@ -15751,70 +15687,78 @@
         <f>-$I$96*K143/100</f>
         <v>0.291485245162099</v>
       </c>
-      <c r="AI143" s="123" t="str">
-        <f>N143</f>
-        <v>LT-1</v>
-      </c>
-      <c r="AJ143" s="124">
-        <f>O143</f>
-        <v>1.25</v>
-      </c>
+      <c r="AI143" s="123"/>
+      <c r="AJ143" s="124"/>
       <c r="AK143" s="125">
         <f>-$I$96*O143/100</f>
+        <v>0.0</v>
+      </c>
+      <c r="AM143" s="123" t="str">
+        <f>R143</f>
+        <v>LT-1</v>
+      </c>
+      <c r="AN143" s="124">
+        <f>S143</f>
+        <v>1.25</v>
+      </c>
+      <c r="AO143" s="125">
+        <f>-$I$96*S143/100</f>
         <v>0.30363046371052</v>
       </c>
-      <c r="AL143" s="119"/>
-      <c r="AN143" s="123" t="str">
+      <c r="AR143" s="123" t="str">
         <f>B143</f>
         <v>LB-2 a 7</v>
       </c>
-      <c r="AO143" s="124">
+      <c r="AS143" s="124">
         <f>C143</f>
         <v>1.2</v>
       </c>
-      <c r="AP143" s="125">
+      <c r="AT143" s="125">
         <f>D143+Y143</f>
         <v>0.757861637421459</v>
       </c>
-      <c r="AQ143" s="119"/>
-      <c r="AR143" s="123" t="str">
+      <c r="AV143" s="123" t="str">
         <f>F143</f>
         <v>LA-2 a 7</v>
       </c>
-      <c r="AS143" s="124">
+      <c r="AW143" s="124">
         <f>G143</f>
         <v>1.2</v>
       </c>
-      <c r="AT143" s="125">
+      <c r="AX143" s="125">
         <f>H143+AC143</f>
         <v>0.0</v>
       </c>
-      <c r="AU143" s="119"/>
-      <c r="AV143" s="123" t="str">
+      <c r="AZ143" s="123" t="str">
         <f>J143</f>
         <v>L1-2</v>
       </c>
-      <c r="AW143" s="124">
+      <c r="BA143" s="124">
         <f>K143</f>
         <v>1.2</v>
       </c>
-      <c r="AX143" s="125">
+      <c r="BB143" s="125">
         <f>L143+AG143</f>
         <v>-0.11659409806484</v>
       </c>
-      <c r="AZ143" s="123" t="str">
-        <f>N143</f>
+      <c r="BD143" s="123"/>
+      <c r="BE143" s="124"/>
+      <c r="BF143" s="125">
+        <f>P143+AK143</f>
+        <v>0.0</v>
+      </c>
+      <c r="BH143" s="123" t="str">
+        <f>R143</f>
         <v>LT-1</v>
       </c>
-      <c r="BA143" s="124">
-        <f>O143</f>
+      <c r="BI143" s="124">
+        <f>S143</f>
         <v>1.25</v>
       </c>
-      <c r="BB143" s="125">
-        <f>P143+AK143</f>
+      <c r="BJ143" s="125">
+        <f>T143+AO143</f>
         <v>-0.121452185484208</v>
       </c>
-      <c r="BC143" s="119"/>
     </row>
     <row r="144" x14ac:dyDescent="0.3">
       <c r="B144" s="123" t="s">
@@ -15824,10 +15768,9 @@
         <v>1.1853149999999999</v>
       </c>
       <c r="D144" s="125">
-        <f t="shared" si="7"/>
+        <f>$E$71*C144/100</f>
         <v>0.460669111159085</v>
       </c>
-      <c r="E144" s="119"/>
       <c r="F144" s="123" t="s">
         <v>211</v>
       </c>
@@ -15835,10 +15778,9 @@
         <v>1.1853149999999999</v>
       </c>
       <c r="H144" s="125">
-        <f t="shared" si="8"/>
+        <f>$E$72*G144/100</f>
         <v>-0.287918194474428</v>
       </c>
-      <c r="I144" s="119"/>
       <c r="J144" s="123" t="s">
         <v>213</v>
       </c>
@@ -15846,20 +15788,24 @@
         <v>0.3</v>
       </c>
       <c r="L144" s="125">
-        <f t="shared" si="9"/>
+        <f>$E$73*K144/100</f>
         <v>-0.102019835806735</v>
       </c>
-      <c r="N144" s="123" t="s">
+      <c r="N144" s="123"/>
+      <c r="O144" s="124"/>
+      <c r="P144" s="125">
+        <v>0</v>
+      </c>
+      <c r="R144" s="123" t="s">
         <v>237</v>
       </c>
-      <c r="O144" s="124">
+      <c r="S144" s="124">
         <v>1.5</v>
       </c>
-      <c r="P144" s="125">
-        <f t="shared" si="10"/>
+      <c r="T144" s="125">
+        <f>$E$74*S144/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="Q144" s="119"/>
       <c r="W144" s="123" t="str">
         <f>B144</f>
         <v>LB-8 (1-2)</v>
@@ -15872,7 +15818,6 @@
         <f>-$I$96*C144/100</f>
         <v>0.287918194474428</v>
       </c>
-      <c r="Z144" s="119"/>
       <c r="AA144" s="123" t="str">
         <f>F144</f>
         <v>LA-8 (1-2)</v>
@@ -15885,7 +15830,6 @@
         <f>-$I$96*G144/100</f>
         <v>0.287918194474428</v>
       </c>
-      <c r="AD144" s="119"/>
       <c r="AE144" s="123" t="str">
         <f>J144</f>
         <v>Dintel P.</v>
@@ -15898,70 +15842,78 @@
         <f>-$I$96*K144/100</f>
         <v>0.0728713112905249</v>
       </c>
-      <c r="AI144" s="123" t="str">
-        <f>N144</f>
-        <v>LT-2</v>
-      </c>
-      <c r="AJ144" s="124">
-        <f>O144</f>
-        <v>1.5</v>
-      </c>
+      <c r="AI144" s="123"/>
+      <c r="AJ144" s="124"/>
       <c r="AK144" s="125">
         <f>-$I$96*O144/100</f>
+        <v>0.0</v>
+      </c>
+      <c r="AM144" s="123" t="str">
+        <f>R144</f>
+        <v>LT-2</v>
+      </c>
+      <c r="AN144" s="124">
+        <f>S144</f>
+        <v>1.5</v>
+      </c>
+      <c r="AO144" s="125">
+        <f>-$I$96*S144/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AL144" s="119"/>
-      <c r="AN144" s="123" t="str">
+      <c r="AR144" s="123" t="str">
         <f>B144</f>
         <v>LB-8 (1-2)</v>
       </c>
-      <c r="AO144" s="124">
+      <c r="AS144" s="124">
         <f>C144</f>
         <v>1.185315</v>
       </c>
-      <c r="AP144" s="125">
+      <c r="AT144" s="125">
         <f>D144+Y144</f>
         <v>0.748587305633513</v>
       </c>
-      <c r="AQ144" s="119"/>
-      <c r="AR144" s="123" t="str">
+      <c r="AV144" s="123" t="str">
         <f>F144</f>
         <v>LA-8 (1-2)</v>
       </c>
-      <c r="AS144" s="124">
+      <c r="AW144" s="124">
         <f>G144</f>
         <v>1.185315</v>
       </c>
-      <c r="AT144" s="125">
+      <c r="AX144" s="125">
         <f>H144+AC144</f>
         <v>0.0</v>
       </c>
-      <c r="AU144" s="119"/>
-      <c r="AV144" s="123" t="str">
+      <c r="AZ144" s="123" t="str">
         <f>J144</f>
         <v>Dintel P.</v>
       </c>
-      <c r="AW144" s="124">
+      <c r="BA144" s="124">
         <f>K144</f>
         <v>0.3</v>
       </c>
-      <c r="AX144" s="125">
+      <c r="BB144" s="125">
         <f>L144+AG144</f>
         <v>-0.0291485245162099</v>
       </c>
-      <c r="AZ144" s="123" t="str">
-        <f>N144</f>
+      <c r="BD144" s="123"/>
+      <c r="BE144" s="124"/>
+      <c r="BF144" s="125">
+        <f>P144+AK144</f>
+        <v>0.0</v>
+      </c>
+      <c r="BH144" s="123" t="str">
+        <f>R144</f>
         <v>LT-2</v>
       </c>
-      <c r="BA144" s="124">
-        <f>O144</f>
+      <c r="BI144" s="124">
+        <f>S144</f>
         <v>1.5</v>
       </c>
-      <c r="BB144" s="125">
-        <f>P144+AK144</f>
+      <c r="BJ144" s="125">
+        <f>T144+AO144</f>
         <v>-0.14574262258105</v>
       </c>
-      <c r="BC144" s="119"/>
     </row>
     <row r="145" x14ac:dyDescent="0.3">
       <c r="B145" s="123" t="s">
@@ -15971,10 +15923,9 @@
         <v>0.97782000000000002</v>
       </c>
       <c r="D145" s="125">
-        <f t="shared" si="7"/>
+        <f>$E$71*C145/100</f>
         <v>0.380026803232539</v>
       </c>
-      <c r="E145" s="119"/>
       <c r="F145" s="123" t="s">
         <v>214</v>
       </c>
@@ -15982,10 +15933,9 @@
         <v>0.97782000000000002</v>
       </c>
       <c r="H145" s="125">
-        <f t="shared" si="8"/>
+        <f>$E$72*G145/100</f>
         <v>-0.237516752020337</v>
       </c>
-      <c r="I145" s="119"/>
       <c r="J145" s="123" t="s">
         <v>216</v>
       </c>
@@ -15993,20 +15943,24 @@
         <v>1.2</v>
       </c>
       <c r="L145" s="125">
-        <f t="shared" si="9"/>
+        <f>$E$73*K145/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="N145" s="123" t="s">
+      <c r="N145" s="123"/>
+      <c r="O145" s="124"/>
+      <c r="P145" s="125">
+        <v>0</v>
+      </c>
+      <c r="R145" s="123" t="s">
         <v>240</v>
       </c>
-      <c r="O145" s="124">
+      <c r="S145" s="124">
         <v>1.5</v>
       </c>
-      <c r="P145" s="125">
-        <f>$E$74*O145/100</f>
+      <c r="T145" s="125">
+        <f>$E$74*S145/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="Q145" s="119"/>
       <c r="W145" s="123" t="str">
         <f>B145</f>
         <v>LB-8 (2-3)</v>
@@ -16019,7 +15973,6 @@
         <f>-$I$96*C145/100</f>
         <v>0.237516752020337</v>
       </c>
-      <c r="Z145" s="119"/>
       <c r="AA145" s="123" t="str">
         <f>F145</f>
         <v>LA-8 (2-3)</v>
@@ -16032,7 +15985,6 @@
         <f>-$I$96*G145/100</f>
         <v>0.237516752020337</v>
       </c>
-      <c r="AD145" s="119"/>
       <c r="AE145" s="123" t="str">
         <f>J145</f>
         <v>L1-3</v>
@@ -16045,70 +15997,78 @@
         <f>-$I$96*K145/100</f>
         <v>0.291485245162099</v>
       </c>
-      <c r="AI145" s="123" t="str">
-        <f>N145</f>
-        <v>LT-3</v>
-      </c>
-      <c r="AJ145" s="124">
-        <f>O145</f>
-        <v>1.5</v>
-      </c>
+      <c r="AI145" s="123"/>
+      <c r="AJ145" s="124"/>
       <c r="AK145" s="125">
         <f>-$I$96*O145/100</f>
+        <v>0.0</v>
+      </c>
+      <c r="AM145" s="123" t="str">
+        <f>R145</f>
+        <v>LT-3</v>
+      </c>
+      <c r="AN145" s="124">
+        <f>S145</f>
+        <v>1.5</v>
+      </c>
+      <c r="AO145" s="125">
+        <f>-$I$96*S145/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AL145" s="119"/>
-      <c r="AN145" s="123" t="str">
+      <c r="AR145" s="123" t="str">
         <f>B145</f>
         <v>LB-8 (2-3)</v>
       </c>
-      <c r="AO145" s="124">
+      <c r="AS145" s="124">
         <f>C145</f>
         <v>0.97782</v>
       </c>
-      <c r="AP145" s="125">
+      <c r="AT145" s="125">
         <f>D145+Y145</f>
         <v>0.617543555252876</v>
       </c>
-      <c r="AQ145" s="119"/>
-      <c r="AR145" s="123" t="str">
+      <c r="AV145" s="123" t="str">
         <f>F145</f>
         <v>LA-8 (2-3)</v>
       </c>
-      <c r="AS145" s="124">
+      <c r="AW145" s="124">
         <f>G145</f>
         <v>0.97782</v>
       </c>
-      <c r="AT145" s="125">
+      <c r="AX145" s="125">
         <f>H145+AC145</f>
         <v>0.0</v>
       </c>
-      <c r="AU145" s="119"/>
-      <c r="AV145" s="123" t="str">
+      <c r="AZ145" s="123" t="str">
         <f>J145</f>
         <v>L1-3</v>
       </c>
-      <c r="AW145" s="124">
+      <c r="BA145" s="124">
         <f>K145</f>
         <v>1.2</v>
       </c>
-      <c r="AX145" s="125">
+      <c r="BB145" s="125">
         <f>L145+AG145</f>
         <v>-0.11659409806484</v>
       </c>
-      <c r="AZ145" s="123" t="str">
-        <f>N145</f>
+      <c r="BD145" s="123"/>
+      <c r="BE145" s="124"/>
+      <c r="BF145" s="125">
+        <f>P145+AK145</f>
+        <v>0.0</v>
+      </c>
+      <c r="BH145" s="123" t="str">
+        <f>R145</f>
         <v>LT-3</v>
       </c>
-      <c r="BA145" s="124">
-        <f>O145</f>
+      <c r="BI145" s="124">
+        <f>S145</f>
         <v>1.5</v>
       </c>
-      <c r="BB145" s="125">
-        <f>P145+AK145</f>
+      <c r="BJ145" s="125">
+        <f>T145+AO145</f>
         <v>-0.14574262258105</v>
       </c>
-      <c r="BC145" s="119"/>
     </row>
     <row r="146" x14ac:dyDescent="0.3">
       <c r="B146" s="123" t="s">
@@ -16118,10 +16078,9 @@
         <v>0.58531500000000003</v>
       </c>
       <c r="D146" s="125">
-        <f t="shared" si="7"/>
+        <f>$E$71*C146/100</f>
         <v>0.227480915029406</v>
       </c>
-      <c r="E146" s="119"/>
       <c r="F146" s="123" t="s">
         <v>217</v>
       </c>
@@ -16129,10 +16088,9 @@
         <v>0.58531500000000003</v>
       </c>
       <c r="H146" s="125">
-        <f t="shared" si="8"/>
+        <f>$E$72*G146/100</f>
         <v>-0.142175571893379</v>
       </c>
-      <c r="I146" s="119"/>
       <c r="J146" s="123" t="s">
         <v>219</v>
       </c>
@@ -16140,17 +16098,22 @@
         <v>0.9</v>
       </c>
       <c r="L146" s="125">
-        <f t="shared" si="9"/>
+        <f>$E$73*K146/100</f>
         <v>-0.306059507420204</v>
       </c>
-      <c r="N146" s="123" t="s">
+      <c r="N146" s="123"/>
+      <c r="O146" s="124"/>
+      <c r="P146" s="125">
+        <v>0</v>
+      </c>
+      <c r="R146" s="123" t="s">
         <v>232</v>
       </c>
-      <c r="O146" s="124">
+      <c r="S146" s="124">
         <v>1.5</v>
       </c>
-      <c r="P146" s="125">
-        <f t="shared" ref="P145:P153" si="11">$E$74*O146/100</f>
+      <c r="T146" s="125">
+        <f>$E$74*S146/100</f>
         <v>-0.510099179033674</v>
       </c>
       <c r="W146" s="123" t="str">
@@ -16165,7 +16128,6 @@
         <f>-$I$96*C146/100</f>
         <v>0.142175571893379</v>
       </c>
-      <c r="Z146" s="119"/>
       <c r="AA146" s="123" t="str">
         <f>F146</f>
         <v>VA-1 sup.</v>
@@ -16178,7 +16140,6 @@
         <f>-$I$96*G146/100</f>
         <v>0.142175571893379</v>
       </c>
-      <c r="AD146" s="119"/>
       <c r="AE146" s="123" t="str">
         <f>J146</f>
         <v>L1-3 P.</v>
@@ -16191,66 +16152,76 @@
         <f>-$I$96*K146/100</f>
         <v>0.218613933871575</v>
       </c>
-      <c r="AI146" s="123" t="str">
-        <f>N146</f>
-        <v>LT-4</v>
-      </c>
-      <c r="AJ146" s="124">
-        <f>O146</f>
-        <v>1.5</v>
-      </c>
+      <c r="AI146" s="123"/>
+      <c r="AJ146" s="124"/>
       <c r="AK146" s="125">
         <f>-$I$96*O146/100</f>
+        <v>0.0</v>
+      </c>
+      <c r="AM146" s="123" t="str">
+        <f>R146</f>
+        <v>LT-4</v>
+      </c>
+      <c r="AN146" s="124">
+        <f>S146</f>
+        <v>1.5</v>
+      </c>
+      <c r="AO146" s="125">
+        <f>-$I$96*S146/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AN146" s="123" t="str">
+      <c r="AR146" s="123" t="str">
         <f>B146</f>
         <v>VB-1 sup.</v>
       </c>
-      <c r="AO146" s="124">
+      <c r="AS146" s="124">
         <f>C146</f>
         <v>0.585315</v>
       </c>
-      <c r="AP146" s="125">
+      <c r="AT146" s="125">
         <f>D146+Y146</f>
         <v>0.369656486922784</v>
       </c>
-      <c r="AQ146" s="119"/>
-      <c r="AR146" s="123" t="str">
+      <c r="AV146" s="123" t="str">
         <f>F146</f>
         <v>VA-1 sup.</v>
       </c>
-      <c r="AS146" s="124">
+      <c r="AW146" s="124">
         <f>G146</f>
         <v>0.585315</v>
       </c>
-      <c r="AT146" s="125">
+      <c r="AX146" s="125">
         <f>H146+AC146</f>
         <v>0.0</v>
       </c>
-      <c r="AU146" s="119"/>
-      <c r="AV146" s="123" t="str">
+      <c r="AZ146" s="123" t="str">
         <f>J146</f>
         <v>L1-3 P.</v>
       </c>
-      <c r="AW146" s="124">
+      <c r="BA146" s="124">
         <f>K146</f>
         <v>0.9</v>
       </c>
-      <c r="AX146" s="125">
+      <c r="BB146" s="125">
         <f>L146+AG146</f>
         <v>-0.0874455735486298</v>
       </c>
-      <c r="AZ146" s="123" t="str">
-        <f>N146</f>
+      <c r="BD146" s="123"/>
+      <c r="BE146" s="124"/>
+      <c r="BF146" s="125">
+        <f>P146+AK146</f>
+        <v>0.0</v>
+      </c>
+      <c r="BH146" s="123" t="str">
+        <f>R146</f>
         <v>LT-4</v>
       </c>
-      <c r="BA146" s="124">
-        <f>O146</f>
+      <c r="BI146" s="124">
+        <f>S146</f>
         <v>1.5</v>
       </c>
-      <c r="BB146" s="125">
-        <f>P146+AK146</f>
+      <c r="BJ146" s="125">
+        <f>T146+AO146</f>
         <v>-0.14574262258105</v>
       </c>
     </row>
@@ -16262,10 +16233,9 @@
         <v>0.37781999999999999</v>
       </c>
       <c r="D147" s="125">
-        <f t="shared" si="7"/>
+        <f>$E$71*C147/100</f>
         <v>0.146838607102859</v>
       </c>
-      <c r="E147" s="119"/>
       <c r="F147" s="123" t="s">
         <v>220</v>
       </c>
@@ -16273,10 +16243,9 @@
         <v>0.37781999999999999</v>
       </c>
       <c r="H147" s="125">
-        <f t="shared" si="8"/>
+        <f>$E$72*G147/100</f>
         <v>-0.091774129439287</v>
       </c>
-      <c r="I147" s="119"/>
       <c r="J147" s="123" t="s">
         <v>222</v>
       </c>
@@ -16284,17 +16253,22 @@
         <v>1.2</v>
       </c>
       <c r="L147" s="125">
-        <f t="shared" si="9"/>
+        <f>$E$73*K147/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="N147" s="123" t="s">
+      <c r="N147" s="123"/>
+      <c r="O147" s="124"/>
+      <c r="P147" s="125">
+        <v>0</v>
+      </c>
+      <c r="R147" s="123" t="s">
         <v>235</v>
       </c>
-      <c r="O147" s="124">
+      <c r="S147" s="124">
         <v>0.75</v>
       </c>
-      <c r="P147" s="125">
-        <f t="shared" si="11"/>
+      <c r="T147" s="125">
+        <f>$E$74*S147/100</f>
         <v>-0.255049589516837</v>
       </c>
       <c r="W147" s="123" t="str">
@@ -16309,7 +16283,6 @@
         <f>-$I$96*C147/100</f>
         <v>0.091774129439287</v>
       </c>
-      <c r="Z147" s="119"/>
       <c r="AA147" s="123" t="str">
         <f>F147</f>
         <v>VA-2 sup.</v>
@@ -16322,7 +16295,6 @@
         <f>-$I$96*G147/100</f>
         <v>0.091774129439287</v>
       </c>
-      <c r="AD147" s="119"/>
       <c r="AE147" s="123" t="str">
         <f>J147</f>
         <v>L1-4</v>
@@ -16335,84 +16307,80 @@
         <f>-$I$96*K147/100</f>
         <v>0.291485245162099</v>
       </c>
-      <c r="AI147" s="123" t="str">
-        <f>N147</f>
-        <v>LT-5</v>
-      </c>
-      <c r="AJ147" s="124">
-        <f>O147</f>
-        <v>0.75</v>
-      </c>
+      <c r="AI147" s="123"/>
+      <c r="AJ147" s="124"/>
       <c r="AK147" s="125">
         <f>-$I$96*O147/100</f>
+        <v>0.0</v>
+      </c>
+      <c r="AM147" s="123" t="str">
+        <f>R147</f>
+        <v>LT-5</v>
+      </c>
+      <c r="AN147" s="124">
+        <f>S147</f>
+        <v>0.75</v>
+      </c>
+      <c r="AO147" s="125">
+        <f>-$I$96*S147/100</f>
         <v>0.182178278226312</v>
       </c>
-      <c r="AN147" s="123" t="str">
+      <c r="AR147" s="123" t="str">
         <f>B147</f>
         <v>VB-2 sup.</v>
       </c>
-      <c r="AO147" s="124">
+      <c r="AS147" s="124">
         <f>C147</f>
         <v>0.37782</v>
       </c>
-      <c r="AP147" s="125">
+      <c r="AT147" s="125">
         <f>D147+Y147</f>
         <v>0.238612736542146</v>
       </c>
-      <c r="AQ147" s="119"/>
-      <c r="AR147" s="123" t="str">
+      <c r="AV147" s="123" t="str">
         <f>F147</f>
         <v>VA-2 sup.</v>
       </c>
-      <c r="AS147" s="124">
+      <c r="AW147" s="124">
         <f>G147</f>
         <v>0.37782</v>
       </c>
-      <c r="AT147" s="125">
+      <c r="AX147" s="125">
         <f>H147+AC147</f>
         <v>0.0</v>
       </c>
-      <c r="AU147" s="119"/>
-      <c r="AV147" s="123" t="str">
+      <c r="AZ147" s="123" t="str">
         <f>J147</f>
         <v>L1-4</v>
       </c>
-      <c r="AW147" s="124">
+      <c r="BA147" s="124">
         <f>K147</f>
         <v>1.2</v>
       </c>
-      <c r="AX147" s="125">
+      <c r="BB147" s="125">
         <f>L147+AG147</f>
         <v>-0.11659409806484</v>
       </c>
-      <c r="AZ147" s="123" t="str">
-        <f>N147</f>
+      <c r="BD147" s="123"/>
+      <c r="BE147" s="124"/>
+      <c r="BF147" s="125">
+        <f>P147+AK147</f>
+        <v>0.0</v>
+      </c>
+      <c r="BH147" s="123" t="str">
+        <f>R147</f>
         <v>LT-5</v>
       </c>
-      <c r="BA147" s="124">
-        <f>O147</f>
+      <c r="BI147" s="124">
+        <f>S147</f>
         <v>0.75</v>
       </c>
-      <c r="BB147" s="125">
-        <f>P147+AK147</f>
+      <c r="BJ147" s="125">
+        <f>T147+AO147</f>
         <v>-0.0728713112905249</v>
       </c>
     </row>
     <row r="148" x14ac:dyDescent="0.3">
-      <c r="B148" s="123"/>
-      <c r="C148" s="124"/>
-      <c r="D148" s="125">
-        <f t="shared" si="7"/>
-        <v>0.0</v>
-      </c>
-      <c r="E148" s="119"/>
-      <c r="F148" s="123"/>
-      <c r="G148" s="124"/>
-      <c r="H148" s="125">
-        <f t="shared" si="8"/>
-        <v>0.0</v>
-      </c>
-      <c r="I148" s="119"/>
       <c r="J148" s="123" t="s">
         <v>223</v>
       </c>
@@ -16420,33 +16388,24 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="L148" s="125">
-        <f t="shared" si="9"/>
+        <f>$E$73*K148/100</f>
         <v>-0.39107603725915</v>
       </c>
-      <c r="N148" s="123" t="s">
+      <c r="N148" s="123"/>
+      <c r="O148" s="124"/>
+      <c r="P148" s="125">
+        <v>0</v>
+      </c>
+      <c r="R148" s="123" t="s">
         <v>238</v>
       </c>
-      <c r="O148" s="124">
+      <c r="S148" s="124">
         <v>1.5</v>
       </c>
-      <c r="P148" s="125">
-        <f t="shared" si="11"/>
+      <c r="T148" s="125">
+        <f>$E$74*S148/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="W148" s="123"/>
-      <c r="X148" s="124"/>
-      <c r="Y148" s="125">
-        <f>-$I$96*C148/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z148" s="119"/>
-      <c r="AA148" s="123"/>
-      <c r="AB148" s="124"/>
-      <c r="AC148" s="125">
-        <f>-$I$96*G148/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD148" s="119"/>
       <c r="AE148" s="123" t="str">
         <f>J148</f>
         <v>L1-5</v>
@@ -16459,69 +16418,56 @@
         <f>-$I$96*K148/100</f>
         <v>0.279340026613679</v>
       </c>
-      <c r="AI148" s="123" t="str">
-        <f>N148</f>
-        <v>LT-6</v>
-      </c>
-      <c r="AJ148" s="124">
-        <f>O148</f>
-        <v>1.5</v>
-      </c>
+      <c r="AI148" s="123"/>
+      <c r="AJ148" s="124"/>
       <c r="AK148" s="125">
         <f>-$I$96*O148/100</f>
+        <v>0.0</v>
+      </c>
+      <c r="AM148" s="123" t="str">
+        <f>R148</f>
+        <v>LT-6</v>
+      </c>
+      <c r="AN148" s="124">
+        <f>S148</f>
+        <v>1.5</v>
+      </c>
+      <c r="AO148" s="125">
+        <f>-$I$96*S148/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AN148" s="123"/>
-      <c r="AO148" s="124"/>
-      <c r="AP148" s="125">
-        <f>D148+Y148</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ148" s="119"/>
-      <c r="AR148" s="123"/>
-      <c r="AS148" s="124"/>
-      <c r="AT148" s="125">
-        <f>H148+AC148</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU148" s="119"/>
-      <c r="AV148" s="123" t="str">
+      <c r="AZ148" s="123" t="str">
         <f>J148</f>
         <v>L1-5</v>
       </c>
-      <c r="AW148" s="124">
+      <c r="BA148" s="124">
         <f>K148</f>
         <v>1.15</v>
       </c>
-      <c r="AX148" s="125">
+      <c r="BB148" s="125">
         <f>L148+AG148</f>
         <v>-0.111736010645471</v>
       </c>
-      <c r="AZ148" s="123" t="str">
-        <f>N148</f>
+      <c r="BD148" s="123"/>
+      <c r="BE148" s="124"/>
+      <c r="BF148" s="125">
+        <f>P148+AK148</f>
+        <v>0.0</v>
+      </c>
+      <c r="BH148" s="123" t="str">
+        <f>R148</f>
         <v>LT-6</v>
       </c>
-      <c r="BA148" s="124">
-        <f>O148</f>
+      <c r="BI148" s="124">
+        <f>S148</f>
         <v>1.5</v>
       </c>
-      <c r="BB148" s="125">
-        <f>P148+AK148</f>
+      <c r="BJ148" s="125">
+        <f>T148+AO148</f>
         <v>-0.14574262258105</v>
       </c>
     </row>
     <row r="149" x14ac:dyDescent="0.3">
-      <c r="B149" s="119"/>
-      <c r="C149" s="119"/>
-      <c r="D149" s="119"/>
-      <c r="E149" s="119"/>
-      <c r="F149" s="123"/>
-      <c r="G149" s="124"/>
-      <c r="H149" s="125">
-        <f t="shared" si="8"/>
-        <v>0.0</v>
-      </c>
-      <c r="I149" s="119"/>
       <c r="J149" s="123" t="s">
         <v>224</v>
       </c>
@@ -16532,30 +16478,16 @@
         <f>$E$73*K149/100</f>
         <v>-0.408079343226939</v>
       </c>
-      <c r="N149" s="123" t="s">
+      <c r="R149" s="123" t="s">
         <v>241</v>
       </c>
-      <c r="O149" s="124">
+      <c r="S149" s="124">
         <v>1.5</v>
       </c>
-      <c r="P149" s="125">
-        <f t="shared" si="11"/>
+      <c r="T149" s="125">
+        <f>$E$74*S149/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="W149" s="119"/>
-      <c r="X149" s="119"/>
-      <c r="Y149" s="119">
-        <f>-$I$96*C149/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z149" s="119"/>
-      <c r="AA149" s="123"/>
-      <c r="AB149" s="124"/>
-      <c r="AC149" s="125">
-        <f>-$I$96*G149/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD149" s="119"/>
       <c r="AE149" s="123" t="str">
         <f>J149</f>
         <v>L1-6 lat.</v>
@@ -16568,69 +16500,44 @@
         <f>-$I$96*K149/100</f>
         <v>0.291485245162099</v>
       </c>
-      <c r="AI149" s="123" t="str">
-        <f>N149</f>
+      <c r="AM149" s="123" t="str">
+        <f>R149</f>
         <v>VM-2</v>
       </c>
-      <c r="AJ149" s="124">
-        <f>O149</f>
+      <c r="AN149" s="124">
+        <f>S149</f>
         <v>1.5</v>
       </c>
-      <c r="AK149" s="125">
-        <f>-$I$96*O149/100</f>
+      <c r="AO149" s="125">
+        <f>-$I$96*S149/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AN149" s="119"/>
-      <c r="AO149" s="119"/>
-      <c r="AP149" s="119">
-        <f>D149+Y149</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ149" s="119"/>
-      <c r="AR149" s="123"/>
-      <c r="AS149" s="124"/>
-      <c r="AT149" s="125">
-        <f>H149+AC149</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU149" s="119"/>
-      <c r="AV149" s="123" t="str">
+      <c r="AZ149" s="123" t="str">
         <f>J149</f>
         <v>L1-6 lat.</v>
       </c>
-      <c r="AW149" s="124">
+      <c r="BA149" s="124">
         <f>K149</f>
         <v>1.2</v>
       </c>
-      <c r="AX149" s="125">
+      <c r="BB149" s="125">
         <f>L149+AG149</f>
         <v>-0.11659409806484</v>
       </c>
-      <c r="AZ149" s="123" t="str">
-        <f>N149</f>
+      <c r="BH149" s="123" t="str">
+        <f>R149</f>
         <v>VM-2</v>
       </c>
-      <c r="BA149" s="124">
-        <f>O149</f>
+      <c r="BI149" s="124">
+        <f>S149</f>
         <v>1.5</v>
       </c>
-      <c r="BB149" s="125">
-        <f>P149+AK149</f>
+      <c r="BJ149" s="125">
+        <f>T149+AO149</f>
         <v>-0.14574262258105</v>
       </c>
     </row>
     <row r="150" x14ac:dyDescent="0.3">
-      <c r="B150" s="119"/>
-      <c r="C150" s="119"/>
-      <c r="D150" s="119"/>
-      <c r="E150" s="119"/>
-      <c r="F150" s="123"/>
-      <c r="G150" s="124"/>
-      <c r="H150" s="125">
-        <f t="shared" si="8"/>
-        <v>0.0</v>
-      </c>
-      <c r="I150" s="119"/>
       <c r="J150" s="123" t="s">
         <v>225</v>
       </c>
@@ -16638,33 +16545,19 @@
         <v>0.65</v>
       </c>
       <c r="L150" s="125">
-        <f t="shared" si="9"/>
+        <f>$E$73*K150/100</f>
         <v>-0.221042977581259</v>
       </c>
-      <c r="N150" s="123" t="s">
+      <c r="R150" s="123" t="s">
         <v>233</v>
       </c>
-      <c r="O150" s="124">
+      <c r="S150" s="124">
         <v>1.5</v>
       </c>
-      <c r="P150" s="125">
-        <f t="shared" si="11"/>
+      <c r="T150" s="125">
+        <f>$E$74*S150/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="W150" s="119"/>
-      <c r="X150" s="119"/>
-      <c r="Y150" s="119">
-        <f>-$I$96*C150/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z150" s="119"/>
-      <c r="AA150" s="123"/>
-      <c r="AB150" s="124"/>
-      <c r="AC150" s="125">
-        <f>-$I$96*G150/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD150" s="119"/>
       <c r="AE150" s="123" t="str">
         <f>J150</f>
         <v>L1-6 cen.</v>
@@ -16677,69 +16570,44 @@
         <f>-$I$96*K150/100</f>
         <v>0.157887841129471</v>
       </c>
-      <c r="AI150" s="123" t="str">
-        <f>N150</f>
+      <c r="AM150" s="123" t="str">
+        <f>R150</f>
         <v>LT-7</v>
       </c>
-      <c r="AJ150" s="124">
-        <f>O150</f>
+      <c r="AN150" s="124">
+        <f>S150</f>
         <v>1.5</v>
       </c>
-      <c r="AK150" s="125">
-        <f>-$I$96*O150/100</f>
+      <c r="AO150" s="125">
+        <f>-$I$96*S150/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AN150" s="119"/>
-      <c r="AO150" s="119"/>
-      <c r="AP150" s="119">
-        <f>D150+Y150</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ150" s="119"/>
-      <c r="AR150" s="123"/>
-      <c r="AS150" s="124"/>
-      <c r="AT150" s="125">
-        <f>H150+AC150</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU150" s="119"/>
-      <c r="AV150" s="123" t="str">
+      <c r="AZ150" s="123" t="str">
         <f>J150</f>
         <v>L1-6 cen.</v>
       </c>
-      <c r="AW150" s="124">
+      <c r="BA150" s="124">
         <f>K150</f>
         <v>0.65</v>
       </c>
-      <c r="AX150" s="125">
+      <c r="BB150" s="125">
         <f>L150+AG150</f>
         <v>-0.0631551364517882</v>
       </c>
-      <c r="AZ150" s="123" t="str">
-        <f>N150</f>
+      <c r="BH150" s="123" t="str">
+        <f>R150</f>
         <v>LT-7</v>
       </c>
-      <c r="BA150" s="124">
-        <f>O150</f>
+      <c r="BI150" s="124">
+        <f>S150</f>
         <v>1.5</v>
       </c>
-      <c r="BB150" s="125">
-        <f>P150+AK150</f>
+      <c r="BJ150" s="125">
+        <f>T150+AO150</f>
         <v>-0.14574262258105</v>
       </c>
     </row>
     <row r="151" x14ac:dyDescent="0.3">
-      <c r="B151" s="119"/>
-      <c r="C151" s="119"/>
-      <c r="D151" s="119"/>
-      <c r="E151" s="119"/>
-      <c r="F151" s="123"/>
-      <c r="G151" s="124"/>
-      <c r="H151" s="125">
-        <f t="shared" si="8"/>
-        <v>0.0</v>
-      </c>
-      <c r="I151" s="119"/>
       <c r="J151" s="123" t="s">
         <v>226</v>
       </c>
@@ -16747,33 +16615,19 @@
         <v>1.25</v>
       </c>
       <c r="L151" s="125">
-        <f t="shared" si="9"/>
+        <f>$E$73*K151/100</f>
         <v>-0.425082649194728</v>
       </c>
-      <c r="N151" s="123" t="s">
+      <c r="R151" s="123" t="s">
         <v>236</v>
       </c>
-      <c r="O151" s="124">
+      <c r="S151" s="124">
         <v>1.5</v>
       </c>
-      <c r="P151" s="125">
-        <f t="shared" si="11"/>
+      <c r="T151" s="125">
+        <f>$E$74*S151/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="W151" s="119"/>
-      <c r="X151" s="119"/>
-      <c r="Y151" s="119">
-        <f>-$I$96*C151/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z151" s="119"/>
-      <c r="AA151" s="123"/>
-      <c r="AB151" s="124"/>
-      <c r="AC151" s="125">
-        <f>-$I$96*G151/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD151" s="119"/>
       <c r="AE151" s="123" t="str">
         <f>J151</f>
         <v>L1-7</v>
@@ -16786,66 +16640,44 @@
         <f>-$I$96*K151/100</f>
         <v>0.30363046371052</v>
       </c>
-      <c r="AI151" s="123" t="str">
-        <f>N151</f>
+      <c r="AM151" s="123" t="str">
+        <f>R151</f>
         <v>LT-8</v>
       </c>
-      <c r="AJ151" s="124">
-        <f>O151</f>
+      <c r="AN151" s="124">
+        <f>S151</f>
         <v>1.5</v>
       </c>
-      <c r="AK151" s="125">
-        <f>-$I$96*O151/100</f>
+      <c r="AO151" s="125">
+        <f>-$I$96*S151/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AN151" s="119"/>
-      <c r="AO151" s="119"/>
-      <c r="AP151" s="119">
-        <f>D151+Y151</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ151" s="119"/>
-      <c r="AR151" s="123"/>
-      <c r="AS151" s="124"/>
-      <c r="AT151" s="125">
-        <f>H151+AC151</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU151" s="119"/>
-      <c r="AV151" s="123" t="str">
+      <c r="AZ151" s="123" t="str">
         <f>J151</f>
         <v>L1-7</v>
       </c>
-      <c r="AW151" s="124">
+      <c r="BA151" s="124">
         <f>K151</f>
         <v>1.25</v>
       </c>
-      <c r="AX151" s="125">
+      <c r="BB151" s="125">
         <f>L151+AG151</f>
         <v>-0.121452185484208</v>
       </c>
-      <c r="AZ151" s="123" t="str">
-        <f>N151</f>
+      <c r="BH151" s="123" t="str">
+        <f>R151</f>
         <v>LT-8</v>
       </c>
-      <c r="BA151" s="124">
-        <f>O151</f>
+      <c r="BI151" s="124">
+        <f>S151</f>
         <v>1.5</v>
       </c>
-      <c r="BB151" s="125">
-        <f>P151+AK151</f>
+      <c r="BJ151" s="125">
+        <f>T151+AO151</f>
         <v>-0.14574262258105</v>
       </c>
     </row>
     <row r="152" x14ac:dyDescent="0.3">
-      <c r="B152" s="119"/>
-      <c r="C152" s="119"/>
-      <c r="D152" s="119"/>
-      <c r="E152" s="119"/>
-      <c r="F152" s="119"/>
-      <c r="G152" s="119"/>
-      <c r="H152" s="119"/>
-      <c r="I152" s="119"/>
       <c r="J152" s="123" t="s">
         <v>227</v>
       </c>
@@ -16853,33 +16685,19 @@
         <v>1.3149999999999999</v>
       </c>
       <c r="L152" s="125">
-        <f t="shared" si="9"/>
+        <f>$E$73*K152/100</f>
         <v>-0.447186946952854</v>
       </c>
-      <c r="N152" s="123" t="s">
+      <c r="R152" s="123" t="s">
         <v>239</v>
       </c>
-      <c r="O152" s="124">
+      <c r="S152" s="124">
         <v>1.5</v>
       </c>
-      <c r="P152" s="125">
-        <f t="shared" si="11"/>
+      <c r="T152" s="125">
+        <f>$E$74*S152/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="W152" s="119"/>
-      <c r="X152" s="119"/>
-      <c r="Y152" s="119">
-        <f>-$I$96*C152/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z152" s="119"/>
-      <c r="AA152" s="119"/>
-      <c r="AB152" s="119"/>
-      <c r="AC152" s="119">
-        <f>-$I$96*G152/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD152" s="119"/>
       <c r="AE152" s="123" t="str">
         <f>J152</f>
         <v>L1-8</v>
@@ -16892,66 +16710,44 @@
         <f>-$I$96*K152/100</f>
         <v>0.319419247823467</v>
       </c>
-      <c r="AI152" s="123" t="str">
-        <f>N152</f>
+      <c r="AM152" s="123" t="str">
+        <f>R152</f>
         <v>LT-9</v>
       </c>
-      <c r="AJ152" s="124">
-        <f>O152</f>
+      <c r="AN152" s="124">
+        <f>S152</f>
         <v>1.5</v>
       </c>
-      <c r="AK152" s="125">
-        <f>-$I$96*O152/100</f>
+      <c r="AO152" s="125">
+        <f>-$I$96*S152/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AN152" s="119"/>
-      <c r="AO152" s="119"/>
-      <c r="AP152" s="119">
-        <f>D152+Y152</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ152" s="119"/>
-      <c r="AR152" s="119"/>
-      <c r="AS152" s="119"/>
-      <c r="AT152" s="119">
-        <f>H152+AC152</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU152" s="119"/>
-      <c r="AV152" s="123" t="str">
+      <c r="AZ152" s="123" t="str">
         <f>J152</f>
         <v>L1-8</v>
       </c>
-      <c r="AW152" s="124">
+      <c r="BA152" s="124">
         <f>K152</f>
         <v>1.315</v>
       </c>
-      <c r="AX152" s="125">
+      <c r="BB152" s="125">
         <f>L152+AG152</f>
         <v>-0.127767699129387</v>
       </c>
-      <c r="AZ152" s="123" t="str">
-        <f>N152</f>
+      <c r="BH152" s="123" t="str">
+        <f>R152</f>
         <v>LT-9</v>
       </c>
-      <c r="BA152" s="124">
-        <f>O152</f>
+      <c r="BI152" s="124">
+        <f>S152</f>
         <v>1.5</v>
       </c>
-      <c r="BB152" s="125">
-        <f>P152+AK152</f>
+      <c r="BJ152" s="125">
+        <f>T152+AO152</f>
         <v>-0.14574262258105</v>
       </c>
     </row>
     <row r="153" x14ac:dyDescent="0.3">
-      <c r="B153" s="119"/>
-      <c r="C153" s="119"/>
-      <c r="D153" s="119"/>
-      <c r="E153" s="119"/>
-      <c r="F153" s="119"/>
-      <c r="G153" s="119"/>
-      <c r="H153" s="119"/>
-      <c r="I153" s="119"/>
       <c r="J153" s="123" t="s">
         <v>228</v>
       </c>
@@ -16959,33 +16755,19 @@
         <v>0.71499999999999997</v>
       </c>
       <c r="L153" s="125">
-        <f t="shared" si="9"/>
+        <f>$E$73*K153/100</f>
         <v>-0.243147275339385</v>
       </c>
-      <c r="N153" s="123" t="s">
+      <c r="R153" s="123" t="s">
         <v>242</v>
       </c>
-      <c r="O153" s="124">
+      <c r="S153" s="124">
         <v>0.75</v>
       </c>
-      <c r="P153" s="125">
-        <f t="shared" si="11"/>
+      <c r="T153" s="125">
+        <f>$E$74*S153/100</f>
         <v>-0.255049589516837</v>
       </c>
-      <c r="W153" s="119"/>
-      <c r="X153" s="119"/>
-      <c r="Y153" s="119">
-        <f>-$I$96*C153/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z153" s="119"/>
-      <c r="AA153" s="119"/>
-      <c r="AB153" s="119"/>
-      <c r="AC153" s="119">
-        <f>-$I$96*G153/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD153" s="119"/>
       <c r="AE153" s="123" t="str">
         <f>J153</f>
         <v>VM-1 sup.</v>
@@ -16998,122 +16780,47 @@
         <f>-$I$96*K153/100</f>
         <v>0.173676625242418</v>
       </c>
-      <c r="AI153" s="123" t="str">
-        <f>N153</f>
+      <c r="AM153" s="123" t="str">
+        <f>R153</f>
         <v>VM-3</v>
       </c>
-      <c r="AJ153" s="124">
-        <f>O153</f>
+      <c r="AN153" s="124">
+        <f>S153</f>
         <v>0.75</v>
       </c>
-      <c r="AK153" s="125">
-        <f>-$I$96*O153/100</f>
+      <c r="AO153" s="125">
+        <f>-$I$96*S153/100</f>
         <v>0.182178278226312</v>
       </c>
-      <c r="AN153" s="119"/>
-      <c r="AO153" s="119"/>
-      <c r="AP153" s="119">
-        <f>D153+Y153</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ153" s="119"/>
-      <c r="AR153" s="119"/>
-      <c r="AS153" s="119"/>
-      <c r="AT153" s="119">
-        <f>H153+AC153</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU153" s="119"/>
-      <c r="AV153" s="123" t="str">
+      <c r="AZ153" s="123" t="str">
         <f>J153</f>
         <v>VM-1 sup.</v>
       </c>
-      <c r="AW153" s="124">
+      <c r="BA153" s="124">
         <f>K153</f>
         <v>0.715</v>
       </c>
-      <c r="AX153" s="125">
+      <c r="BB153" s="125">
         <f>L153+AG153</f>
         <v>-0.069470650096967</v>
       </c>
-      <c r="AZ153" s="123" t="str">
-        <f>N153</f>
+      <c r="BH153" s="123" t="str">
+        <f>R153</f>
         <v>VM-3</v>
       </c>
-      <c r="BA153" s="124">
-        <f>O153</f>
+      <c r="BI153" s="124">
+        <f>S153</f>
         <v>0.75</v>
       </c>
-      <c r="BB153" s="125">
-        <f>P153+AK153</f>
+      <c r="BJ153" s="125">
+        <f>T153+AO153</f>
         <v>-0.0728713112905249</v>
       </c>
     </row>
-    <row r="154" x14ac:dyDescent="0.3">
-      <c r="J154" s="18"/>
-      <c r="K154" s="79"/>
-      <c r="L154" s="70">
-        <f t="shared" si="9"/>
-        <v>0.0</v>
-      </c>
-      <c r="AE154" s="18"/>
-      <c r="AF154" s="79"/>
-      <c r="AG154" s="70">
-        <f>-$I$96*K154/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV154" s="18"/>
-      <c r="AW154" s="79"/>
-      <c r="AX154" s="70">
-        <f>L154+AG154</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="155" x14ac:dyDescent="0.3">
-      <c r="J155" s="18"/>
-      <c r="K155" s="79"/>
-      <c r="L155" s="70">
-        <f t="shared" si="9"/>
-        <v>0.0</v>
-      </c>
-      <c r="AE155" s="18"/>
-      <c r="AF155" s="79"/>
-      <c r="AG155" s="70">
-        <f>-$I$96*K155/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV155" s="18"/>
-      <c r="AW155" s="79"/>
-      <c r="AX155" s="70">
-        <f>L155+AG155</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="156" x14ac:dyDescent="0.3">
-      <c r="J156" s="18"/>
-      <c r="K156" s="79"/>
-      <c r="L156" s="70">
-        <f t="shared" si="9"/>
-        <v>0.0</v>
-      </c>
-      <c r="AE156" s="18"/>
-      <c r="AF156" s="79"/>
-      <c r="AG156" s="70">
-        <f>-$I$96*K156/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV156" s="18"/>
-      <c r="AW156" s="79"/>
-      <c r="AX156" s="70">
-        <f>L156+AG156</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="165" x14ac:dyDescent="0.3">
-      <c r="I165" s="119"/>
-      <c r="AD165" s="119"/>
-      <c r="AU165" s="119"/>
-    </row>
+    <row r="154" x14ac:dyDescent="0.3"/>
+    <row r="155" x14ac:dyDescent="0.3"/>
+    <row r="156" x14ac:dyDescent="0.3"/>
+    <row r="165" x14ac:dyDescent="0.3"/>
     <row r="168" x14ac:dyDescent="0.3">
       <c r="B168" s="81" t="s">
         <v>246</v>
@@ -17157,15 +16864,15 @@
       <c r="AJ168" s="82"/>
       <c r="AK168" s="82"/>
       <c r="AL168" s="82"/>
-      <c r="AN168" s="81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIENTO EN DIRECCION Z — TOTAL (Cpe + Cpi)</t>
-        </is>
-      </c>
+      <c r="AM168" s="82"/>
+      <c r="AN168" s="82"/>
       <c r="AO168" s="82"/>
       <c r="AP168" s="82"/>
-      <c r="AQ168" s="82"/>
-      <c r="AR168" s="82"/>
+      <c r="AR168" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIENTO EN DIRECCION Z — TOTAL (Cpe + Cpi)</t>
+        </is>
+      </c>
       <c r="AS168" s="82"/>
       <c r="AT168" s="82"/>
       <c r="AU168" s="82"/>
@@ -17177,6 +16884,14 @@
       <c r="BA168" s="82"/>
       <c r="BB168" s="82"/>
       <c r="BC168" s="82"/>
+      <c r="BD168" s="82"/>
+      <c r="BE168" s="82"/>
+      <c r="BF168" s="82"/>
+      <c r="BG168" s="82"/>
+      <c r="BH168" s="82"/>
+      <c r="BI168" s="82"/>
+      <c r="BJ168" s="82"/>
+      <c r="BK168" s="82"/>
     </row>
     <row r="170" x14ac:dyDescent="0.3">
       <c r="B170" s="78" t="s">
@@ -17185,10 +16900,17 @@
       <c r="F170" s="78" t="s">
         <v>248</v>
       </c>
-      <c r="J170" s="78" t="s">
-        <v>249</v>
-      </c>
-      <c r="N170" s="78" t="s">
+      <c r="J170" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MURO A LATERAL:</t>
+        </is>
+      </c>
+      <c r="N170" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MURO B LATERAL:</t>
+        </is>
+      </c>
+      <c r="R170" s="78" t="s">
         <v>229</v>
       </c>
       <c r="W170" s="78" t="str">
@@ -17201,67 +16923,112 @@
       </c>
       <c r="AE170" s="78" t="str">
         <f>J170</f>
-        <v>MUROS LATERALES A/B:</v>
+        <v>MURO A LATERAL:</v>
       </c>
       <c r="AI170" s="78" t="str">
         <f>N170</f>
+        <v>MURO B LATERAL:</v>
+      </c>
+      <c r="AM170" s="78" t="str">
+        <f>R170</f>
         <v>CUBIERTA — LARGUEROS Y VIGAS DE MARCO</v>
       </c>
-      <c r="AN170" s="78" t="str">
+      <c r="AR170" s="78" t="str">
         <f>B170</f>
         <v>MURO 1 EN BARLOVENTO:</v>
       </c>
-      <c r="AR170" s="78" t="str">
+      <c r="AV170" s="78" t="str">
         <f>F170</f>
         <v>EJE 3 ABIERTO:</v>
       </c>
-      <c r="AV170" s="78" t="str">
+      <c r="AZ170" s="78" t="str">
         <f>J170</f>
-        <v>MUROS LATERALES A/B:</v>
-      </c>
-      <c r="AZ170" s="78" t="str">
+        <v>MURO A LATERAL:</v>
+      </c>
+      <c r="BD170" s="78" t="str">
         <f>N170</f>
+        <v>MURO B LATERAL:</v>
+      </c>
+      <c r="BH170" s="78" t="str">
+        <f>R170</f>
         <v>CUBIERTA — LARGUEROS Y VIGAS DE MARCO</v>
       </c>
     </row>
     <row r="172" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B172" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="C172" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="D172" s="77" t="s">
-        <v>204</v>
-      </c>
-      <c r="E172" s="119"/>
-      <c r="F172" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="G172" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="H172" s="77" t="s">
-        <v>204</v>
-      </c>
-      <c r="I172" s="119"/>
-      <c r="J172" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="K172" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="L172" s="77" t="s">
-        <v>204</v>
-      </c>
-      <c r="N172" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="O172" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="P172" s="77" t="s">
-        <v>230</v>
+      <c r="B172" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="C172" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="D172" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd (kg/cm)</t>
+        </is>
+      </c>
+      <c r="F172" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="G172" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="H172" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd (kg/cm)</t>
+        </is>
+      </c>
+      <c r="J172" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="K172" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="L172" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd (kg/cm)</t>
+        </is>
+      </c>
+      <c r="N172" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="O172" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="P172" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd (kg/cm)</t>
+        </is>
+      </c>
+      <c r="R172" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="S172" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="T172" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd normal</t>
+        </is>
       </c>
       <c r="W172" s="122" t="inlineStr">
         <is>
@@ -17278,7 +17045,6 @@
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="Z172" s="119"/>
       <c r="AA172" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
@@ -17294,7 +17060,6 @@
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="AD172" s="119"/>
       <c r="AE172" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
@@ -17325,64 +17090,92 @@
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="AN172" s="122" t="inlineStr">
+      <c r="AM172" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
+      <c r="AN172" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
       <c r="AO172" s="77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pd interna (kg/cm)</t>
+        </is>
+      </c>
+      <c r="AR172" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="AS172" s="77" t="inlineStr">
+        <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="AP172" s="77" t="inlineStr">
+      <c r="AT172" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
-      <c r="AQ172" s="119"/>
-      <c r="AR172" s="122" t="inlineStr">
+      <c r="AV172" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="AS172" s="77" t="inlineStr">
+      <c r="AW172" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="AT172" s="77" t="inlineStr">
+      <c r="AX172" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
-      <c r="AU172" s="119"/>
-      <c r="AV172" s="122" t="inlineStr">
+      <c r="AZ172" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="AW172" s="77" t="inlineStr">
+      <c r="BA172" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="AX172" s="77" t="inlineStr">
+      <c r="BB172" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
-      <c r="AZ172" s="122" t="inlineStr">
+      <c r="BD172" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="BA172" s="77" t="inlineStr">
+      <c r="BE172" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="BB172" s="77" t="inlineStr">
+      <c r="BF172" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd total (kg/cm)</t>
+        </is>
+      </c>
+      <c r="BH172" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="BI172" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="BJ172" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
@@ -17399,7 +17192,6 @@
         <f>$E$71*C173/100</f>
         <v>0.349782294194519</v>
       </c>
-      <c r="E173" s="119"/>
       <c r="F173" s="123" t="s">
         <v>250</v>
       </c>
@@ -17407,7 +17199,6 @@
       <c r="H173" s="125">
         <v>0</v>
       </c>
-      <c r="I173" s="119"/>
       <c r="J173" s="123" t="s">
         <v>205</v>
       </c>
@@ -17419,13 +17210,23 @@
         <v>-0.306059507420204</v>
       </c>
       <c r="N173" s="123" t="s">
+        <v>206</v>
+      </c>
+      <c r="O173" s="124">
+        <v>0.9</v>
+      </c>
+      <c r="P173" s="125">
+        <f>$E$73*O173/100</f>
+        <v>-0.306059507420204</v>
+      </c>
+      <c r="R173" s="123" t="s">
         <v>231</v>
       </c>
-      <c r="O173" s="124">
+      <c r="S173" s="124">
         <v>0.5</v>
       </c>
-      <c r="P173" s="125">
-        <f>$E$74*O173/100</f>
+      <c r="T173" s="125">
+        <f>$E$74*S173/100</f>
         <v>-0.170033059677891</v>
       </c>
       <c r="W173" s="123" t="str">
@@ -17440,7 +17241,6 @@
         <f>-$I$97*C173/100</f>
         <v>0.262336720645889</v>
       </c>
-      <c r="Z173" s="119"/>
       <c r="AA173" s="123" t="str">
         <f>F173</f>
         <v>SIN CERRAMIENTO</v>
@@ -17450,7 +17250,6 @@
         <f>-$I$97*G173/100</f>
         <v>0.0</v>
       </c>
-      <c r="AD173" s="119"/>
       <c r="AE173" s="123" t="str">
         <f>J173</f>
         <v>LA-1</v>
@@ -17465,61 +17264,83 @@
       </c>
       <c r="AI173" s="123" t="str">
         <f>N173</f>
-        <v>VM-1</v>
+        <v>LB-1</v>
       </c>
       <c r="AJ173" s="124">
         <f>O173</f>
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="AK173" s="125">
         <f>-$I$97*O173/100</f>
+        <v>0.262336720645889</v>
+      </c>
+      <c r="AM173" s="123" t="str">
+        <f>R173</f>
+        <v>VM-1</v>
+      </c>
+      <c r="AN173" s="124">
+        <f>S173</f>
+        <v>0.5</v>
+      </c>
+      <c r="AO173" s="125">
+        <f>-$I$97*S173/100</f>
         <v>0.14574262258105</v>
       </c>
-      <c r="AN173" s="123" t="str">
+      <c r="AR173" s="123" t="str">
         <f>B173</f>
         <v>L1-1</v>
       </c>
-      <c r="AO173" s="124">
+      <c r="AS173" s="124">
         <f>C173</f>
         <v>0.9</v>
       </c>
-      <c r="AP173" s="125">
+      <c r="AT173" s="125">
         <f>D173+Y173</f>
         <v>0.612119014840409</v>
       </c>
-      <c r="AQ173" s="119"/>
-      <c r="AR173" s="123" t="str">
+      <c r="AV173" s="123" t="str">
         <f>F173</f>
         <v>SIN CERRAMIENTO</v>
       </c>
-      <c r="AS173" s="124"/>
-      <c r="AT173" s="125">
+      <c r="AW173" s="124"/>
+      <c r="AX173" s="125">
         <f>H173+AC173</f>
         <v>0.0</v>
       </c>
-      <c r="AU173" s="119"/>
-      <c r="AV173" s="123" t="str">
+      <c r="AZ173" s="123" t="str">
         <f>J173</f>
         <v>LA-1</v>
       </c>
-      <c r="AW173" s="124">
+      <c r="BA173" s="124">
         <f>K173</f>
         <v>0.9</v>
       </c>
-      <c r="AX173" s="125">
+      <c r="BB173" s="125">
         <f>L173+AG173</f>
         <v>-0.043722786774315</v>
       </c>
-      <c r="AZ173" s="123" t="str">
+      <c r="BD173" s="123" t="str">
         <f>N173</f>
+        <v>LB-1</v>
+      </c>
+      <c r="BE173" s="124">
+        <f>O173</f>
+        <v>0.9</v>
+      </c>
+      <c r="BF173" s="125">
+        <f>P173+AK173</f>
+        <v>-0.043722786774315</v>
+      </c>
+      <c r="BH173" s="123" t="str">
+        <f>R173</f>
         <v>VM-1</v>
       </c>
-      <c r="BA173" s="124">
-        <f>O173</f>
+      <c r="BI173" s="124">
+        <f>S173</f>
         <v>0.5</v>
       </c>
-      <c r="BB173" s="125">
-        <f>P173+AK173</f>
+      <c r="BJ173" s="125">
+        <f>T173+AO173</f>
         <v>-0.0242904370968416</v>
       </c>
     </row>
@@ -17531,17 +17352,14 @@
         <v>1.2</v>
       </c>
       <c r="D174" s="125">
-        <f t="shared" ref="D174:D179" si="12">$E$71*C174/100</f>
+        <f>$E$71*C174/100</f>
         <v>0.466376392259359</v>
       </c>
-      <c r="E174" s="119"/>
       <c r="F174" s="123"/>
       <c r="G174" s="124"/>
       <c r="H174" s="125">
-        <f t="shared" ref="H174:H179" si="13">$E$72*G174/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="I174" s="119"/>
+        <v>0</v>
+      </c>
       <c r="J174" s="123" t="s">
         <v>208</v>
       </c>
@@ -17549,17 +17367,27 @@
         <v>1.2</v>
       </c>
       <c r="L174" s="125">
-        <f t="shared" ref="L174:L190" si="14">$E$73*K174/100</f>
+        <f>$E$73*K174/100</f>
         <v>-0.408079343226939</v>
       </c>
       <c r="N174" s="123" t="s">
+        <v>209</v>
+      </c>
+      <c r="O174" s="124">
+        <v>1.2</v>
+      </c>
+      <c r="P174" s="125">
+        <f>$E$73*O174/100</f>
+        <v>-0.408079343226939</v>
+      </c>
+      <c r="R174" s="123" t="s">
         <v>234</v>
       </c>
-      <c r="O174" s="124">
+      <c r="S174" s="124">
         <v>1.25</v>
       </c>
-      <c r="P174" s="125">
-        <f t="shared" ref="P174:P175" si="15">$E$74*O174/100</f>
+      <c r="T174" s="125">
+        <f>$E$74*S174/100</f>
         <v>-0.425082649194728</v>
       </c>
       <c r="W174" s="123" t="str">
@@ -17574,14 +17402,12 @@
         <f>-$I$97*C174/100</f>
         <v>0.349782294194519</v>
       </c>
-      <c r="Z174" s="119"/>
       <c r="AA174" s="123"/>
       <c r="AB174" s="124"/>
       <c r="AC174" s="125">
         <f>-$I$97*G174/100</f>
         <v>0.0</v>
       </c>
-      <c r="AD174" s="119"/>
       <c r="AE174" s="123" t="str">
         <f>J174</f>
         <v>LA-2 a 7</v>
@@ -17596,58 +17422,80 @@
       </c>
       <c r="AI174" s="123" t="str">
         <f>N174</f>
-        <v>LT-1</v>
+        <v>LB-2 a 7</v>
       </c>
       <c r="AJ174" s="124">
         <f>O174</f>
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK174" s="125">
         <f>-$I$97*O174/100</f>
+        <v>0.349782294194519</v>
+      </c>
+      <c r="AM174" s="123" t="str">
+        <f>R174</f>
+        <v>LT-1</v>
+      </c>
+      <c r="AN174" s="124">
+        <f>S174</f>
+        <v>1.25</v>
+      </c>
+      <c r="AO174" s="125">
+        <f>-$I$97*S174/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="AN174" s="123" t="str">
+      <c r="AR174" s="123" t="str">
         <f>B174</f>
         <v>L1-2</v>
       </c>
-      <c r="AO174" s="124">
+      <c r="AS174" s="124">
         <f>C174</f>
         <v>1.2</v>
       </c>
-      <c r="AP174" s="125">
+      <c r="AT174" s="125">
         <f>D174+Y174</f>
         <v>0.816158686453878</v>
       </c>
-      <c r="AQ174" s="119"/>
-      <c r="AR174" s="123"/>
-      <c r="AS174" s="124"/>
-      <c r="AT174" s="125">
+      <c r="AV174" s="123"/>
+      <c r="AW174" s="124"/>
+      <c r="AX174" s="125">
         <f>H174+AC174</f>
         <v>0.0</v>
       </c>
-      <c r="AU174" s="119"/>
-      <c r="AV174" s="123" t="str">
+      <c r="AZ174" s="123" t="str">
         <f>J174</f>
         <v>LA-2 a 7</v>
       </c>
-      <c r="AW174" s="124">
+      <c r="BA174" s="124">
         <f>K174</f>
         <v>1.2</v>
       </c>
-      <c r="AX174" s="125">
+      <c r="BB174" s="125">
         <f>L174+AG174</f>
         <v>-0.0582970490324199</v>
       </c>
-      <c r="AZ174" s="123" t="str">
+      <c r="BD174" s="123" t="str">
         <f>N174</f>
+        <v>LB-2 a 7</v>
+      </c>
+      <c r="BE174" s="124">
+        <f>O174</f>
+        <v>1.2</v>
+      </c>
+      <c r="BF174" s="125">
+        <f>P174+AK174</f>
+        <v>-0.0582970490324199</v>
+      </c>
+      <c r="BH174" s="123" t="str">
+        <f>R174</f>
         <v>LT-1</v>
       </c>
-      <c r="BA174" s="124">
-        <f>O174</f>
+      <c r="BI174" s="124">
+        <f>S174</f>
         <v>1.25</v>
       </c>
-      <c r="BB174" s="125">
-        <f>P174+AK174</f>
+      <c r="BJ174" s="125">
+        <f>T174+AO174</f>
         <v>-0.0607260927421041</v>
       </c>
     </row>
@@ -17659,17 +17507,14 @@
         <v>0.3</v>
       </c>
       <c r="D175" s="125">
-        <f t="shared" si="12"/>
+        <f>$E$71*C175/100</f>
         <v>0.11659409806484</v>
       </c>
-      <c r="E175" s="119"/>
       <c r="F175" s="123"/>
       <c r="G175" s="124"/>
       <c r="H175" s="125">
-        <f t="shared" si="13"/>
-        <v>0.0</v>
-      </c>
-      <c r="I175" s="119"/>
+        <v>0</v>
+      </c>
       <c r="J175" s="123" t="s">
         <v>211</v>
       </c>
@@ -17681,13 +17526,23 @@
         <v>-0.403085472264199</v>
       </c>
       <c r="N175" s="123" t="s">
+        <v>212</v>
+      </c>
+      <c r="O175" s="124">
+        <v>1.1853149999999999</v>
+      </c>
+      <c r="P175" s="125">
+        <f>$E$73*O175/100</f>
+        <v>-0.403085472264199</v>
+      </c>
+      <c r="R175" s="123" t="s">
         <v>237</v>
       </c>
-      <c r="O175" s="124">
+      <c r="S175" s="124">
         <v>1.5</v>
       </c>
-      <c r="P175" s="125">
-        <f t="shared" si="15"/>
+      <c r="T175" s="125">
+        <f>$E$74*S175/100</f>
         <v>-0.510099179033674</v>
       </c>
       <c r="W175" s="123" t="str">
@@ -17702,14 +17557,12 @@
         <f>-$I$97*C175/100</f>
         <v>0.0874455735486298</v>
       </c>
-      <c r="Z175" s="119"/>
       <c r="AA175" s="123"/>
       <c r="AB175" s="124"/>
       <c r="AC175" s="125">
         <f>-$I$97*G175/100</f>
         <v>0.0</v>
       </c>
-      <c r="AD175" s="119"/>
       <c r="AE175" s="123" t="str">
         <f>J175</f>
         <v>LA-8 (1-2)</v>
@@ -17724,58 +17577,80 @@
       </c>
       <c r="AI175" s="123" t="str">
         <f>N175</f>
-        <v>LT-2</v>
+        <v>LB-8 (1-2)</v>
       </c>
       <c r="AJ175" s="124">
         <f>O175</f>
-        <v>1.5</v>
+        <v>1.185315</v>
       </c>
       <c r="AK175" s="125">
         <f>-$I$97*O175/100</f>
+        <v>0.345501833369314</v>
+      </c>
+      <c r="AM175" s="123" t="str">
+        <f>R175</f>
+        <v>LT-2</v>
+      </c>
+      <c r="AN175" s="124">
+        <f>S175</f>
+        <v>1.5</v>
+      </c>
+      <c r="AO175" s="125">
+        <f>-$I$97*S175/100</f>
         <v>0.437227867743149</v>
       </c>
-      <c r="AN175" s="123" t="str">
+      <c r="AR175" s="123" t="str">
         <f>B175</f>
         <v>Dintel P.</v>
       </c>
-      <c r="AO175" s="124">
+      <c r="AS175" s="124">
         <f>C175</f>
         <v>0.3</v>
       </c>
-      <c r="AP175" s="125">
+      <c r="AT175" s="125">
         <f>D175+Y175</f>
         <v>0.20403967161347</v>
       </c>
-      <c r="AQ175" s="119"/>
-      <c r="AR175" s="123"/>
-      <c r="AS175" s="124"/>
-      <c r="AT175" s="125">
+      <c r="AV175" s="123"/>
+      <c r="AW175" s="124"/>
+      <c r="AX175" s="125">
         <f>H175+AC175</f>
         <v>0.0</v>
       </c>
-      <c r="AU175" s="119"/>
-      <c r="AV175" s="123" t="str">
+      <c r="AZ175" s="123" t="str">
         <f>J175</f>
         <v>LA-8 (1-2)</v>
       </c>
-      <c r="AW175" s="124">
+      <c r="BA175" s="124">
         <f>K175</f>
         <v>1.185315</v>
       </c>
-      <c r="AX175" s="125">
+      <c r="BB175" s="125">
         <f>L175+AG175</f>
         <v>-0.0575836388948856</v>
       </c>
-      <c r="AZ175" s="123" t="str">
+      <c r="BD175" s="123" t="str">
         <f>N175</f>
+        <v>LB-8 (1-2)</v>
+      </c>
+      <c r="BE175" s="124">
+        <f>O175</f>
+        <v>1.185315</v>
+      </c>
+      <c r="BF175" s="125">
+        <f>P175+AK175</f>
+        <v>-0.0575836388948856</v>
+      </c>
+      <c r="BH175" s="123" t="str">
+        <f>R175</f>
         <v>LT-2</v>
       </c>
-      <c r="BA175" s="124">
-        <f>O175</f>
+      <c r="BI175" s="124">
+        <f>S175</f>
         <v>1.5</v>
       </c>
-      <c r="BB175" s="125">
-        <f>P175+AK175</f>
+      <c r="BJ175" s="125">
+        <f>T175+AO175</f>
         <v>-0.0728713112905248</v>
       </c>
     </row>
@@ -17790,14 +17665,11 @@
         <f>$E$71*C176/100</f>
         <v>0.466376392259359</v>
       </c>
-      <c r="E176" s="119"/>
       <c r="F176" s="123"/>
       <c r="G176" s="124"/>
       <c r="H176" s="125">
-        <f t="shared" si="13"/>
-        <v>0.0</v>
-      </c>
-      <c r="I176" s="119"/>
+        <v>0</v>
+      </c>
       <c r="J176" s="123" t="s">
         <v>214</v>
       </c>
@@ -17805,17 +17677,27 @@
         <v>0.97782000000000002</v>
       </c>
       <c r="L176" s="125">
-        <f t="shared" si="14"/>
+        <f>$E$73*K176/100</f>
         <v>-0.332523452828471</v>
       </c>
       <c r="N176" s="123" t="s">
+        <v>215</v>
+      </c>
+      <c r="O176" s="124">
+        <v>0.97782000000000002</v>
+      </c>
+      <c r="P176" s="125">
+        <f>$E$73*O176/100</f>
+        <v>-0.332523452828471</v>
+      </c>
+      <c r="R176" s="123" t="s">
         <v>240</v>
       </c>
-      <c r="O176" s="124">
+      <c r="S176" s="124">
         <v>1.5</v>
       </c>
-      <c r="P176" s="125">
-        <f t="shared" ref="P176:P184" si="16">$E$74*O176/100</f>
+      <c r="T176" s="125">
+        <f>$E$74*S176/100</f>
         <v>-0.510099179033674</v>
       </c>
       <c r="W176" s="123" t="str">
@@ -17830,14 +17712,12 @@
         <f>-$I$97*C176/100</f>
         <v>0.349782294194519</v>
       </c>
-      <c r="Z176" s="119"/>
       <c r="AA176" s="123"/>
       <c r="AB176" s="124"/>
       <c r="AC176" s="125">
         <f>-$I$97*G176/100</f>
         <v>0.0</v>
       </c>
-      <c r="AD176" s="119"/>
       <c r="AE176" s="123" t="str">
         <f>J176</f>
         <v>LA-8 (2-3)</v>
@@ -17852,58 +17732,80 @@
       </c>
       <c r="AI176" s="123" t="str">
         <f>N176</f>
-        <v>LT-3</v>
+        <v>LB-8 (2-3)</v>
       </c>
       <c r="AJ176" s="124">
         <f>O176</f>
-        <v>1.5</v>
+        <v>0.97782</v>
       </c>
       <c r="AK176" s="125">
         <f>-$I$97*O176/100</f>
+        <v>0.285020102424404</v>
+      </c>
+      <c r="AM176" s="123" t="str">
+        <f>R176</f>
+        <v>LT-3</v>
+      </c>
+      <c r="AN176" s="124">
+        <f>S176</f>
+        <v>1.5</v>
+      </c>
+      <c r="AO176" s="125">
+        <f>-$I$97*S176/100</f>
         <v>0.437227867743149</v>
       </c>
-      <c r="AN176" s="123" t="str">
+      <c r="AR176" s="123" t="str">
         <f>B176</f>
         <v>L1-3</v>
       </c>
-      <c r="AO176" s="124">
+      <c r="AS176" s="124">
         <f>C176</f>
         <v>1.2</v>
       </c>
-      <c r="AP176" s="125">
+      <c r="AT176" s="125">
         <f>D176+Y176</f>
         <v>0.816158686453878</v>
       </c>
-      <c r="AQ176" s="119"/>
-      <c r="AR176" s="123"/>
-      <c r="AS176" s="124"/>
-      <c r="AT176" s="125">
+      <c r="AV176" s="123"/>
+      <c r="AW176" s="124"/>
+      <c r="AX176" s="125">
         <f>H176+AC176</f>
         <v>0.0</v>
       </c>
-      <c r="AU176" s="119"/>
-      <c r="AV176" s="123" t="str">
+      <c r="AZ176" s="123" t="str">
         <f>J176</f>
         <v>LA-8 (2-3)</v>
       </c>
-      <c r="AW176" s="124">
+      <c r="BA176" s="124">
         <f>K176</f>
         <v>0.97782</v>
       </c>
-      <c r="AX176" s="125">
+      <c r="BB176" s="125">
         <f>L176+AG176</f>
         <v>-0.0475033504040674</v>
       </c>
-      <c r="AZ176" s="123" t="str">
+      <c r="BD176" s="123" t="str">
         <f>N176</f>
+        <v>LB-8 (2-3)</v>
+      </c>
+      <c r="BE176" s="124">
+        <f>O176</f>
+        <v>0.97782</v>
+      </c>
+      <c r="BF176" s="125">
+        <f>P176+AK176</f>
+        <v>-0.0475033504040674</v>
+      </c>
+      <c r="BH176" s="123" t="str">
+        <f>R176</f>
         <v>LT-3</v>
       </c>
-      <c r="BA176" s="124">
-        <f>O176</f>
+      <c r="BI176" s="124">
+        <f>S176</f>
         <v>1.5</v>
       </c>
-      <c r="BB176" s="125">
-        <f>P176+AK176</f>
+      <c r="BJ176" s="125">
+        <f>T176+AO176</f>
         <v>-0.0728713112905248</v>
       </c>
     </row>
@@ -17915,17 +17817,14 @@
         <v>0.9</v>
       </c>
       <c r="D177" s="125">
-        <f t="shared" si="12"/>
+        <f>$E$71*C177/100</f>
         <v>0.349782294194519</v>
       </c>
-      <c r="E177" s="119"/>
       <c r="F177" s="123"/>
       <c r="G177" s="124"/>
       <c r="H177" s="125">
-        <f t="shared" si="13"/>
-        <v>0.0</v>
-      </c>
-      <c r="I177" s="119"/>
+        <v>0</v>
+      </c>
       <c r="J177" s="123" t="s">
         <v>217</v>
       </c>
@@ -17933,17 +17832,27 @@
         <v>0.58531500000000003</v>
       </c>
       <c r="L177" s="125">
-        <f t="shared" si="14"/>
+        <f>$E$73*K177/100</f>
         <v>-0.19904580065073</v>
       </c>
       <c r="N177" s="123" t="s">
+        <v>218</v>
+      </c>
+      <c r="O177" s="124">
+        <v>0.58531500000000003</v>
+      </c>
+      <c r="P177" s="125">
+        <f>$E$73*O177/100</f>
+        <v>-0.19904580065073</v>
+      </c>
+      <c r="R177" s="123" t="s">
         <v>232</v>
       </c>
-      <c r="O177" s="124">
+      <c r="S177" s="124">
         <v>1.5</v>
       </c>
-      <c r="P177" s="125">
-        <f>$E$74*O177/100</f>
+      <c r="T177" s="125">
+        <f>$E$74*S177/100</f>
         <v>-0.510099179033674</v>
       </c>
       <c r="W177" s="123" t="str">
@@ -17958,14 +17867,12 @@
         <f>-$I$97*C177/100</f>
         <v>0.262336720645889</v>
       </c>
-      <c r="Z177" s="119"/>
       <c r="AA177" s="123"/>
       <c r="AB177" s="124"/>
       <c r="AC177" s="125">
         <f>-$I$97*G177/100</f>
         <v>0.0</v>
       </c>
-      <c r="AD177" s="119"/>
       <c r="AE177" s="123" t="str">
         <f>J177</f>
         <v>VA-1 sup.</v>
@@ -17980,58 +17887,80 @@
       </c>
       <c r="AI177" s="123" t="str">
         <f>N177</f>
-        <v>LT-4</v>
+        <v>VB-1 sup.</v>
       </c>
       <c r="AJ177" s="124">
         <f>O177</f>
-        <v>1.5</v>
+        <v>0.585315</v>
       </c>
       <c r="AK177" s="125">
         <f>-$I$97*O177/100</f>
+        <v>0.170610686272054</v>
+      </c>
+      <c r="AM177" s="123" t="str">
+        <f>R177</f>
+        <v>LT-4</v>
+      </c>
+      <c r="AN177" s="124">
+        <f>S177</f>
+        <v>1.5</v>
+      </c>
+      <c r="AO177" s="125">
+        <f>-$I$97*S177/100</f>
         <v>0.437227867743149</v>
       </c>
-      <c r="AN177" s="123" t="str">
+      <c r="AR177" s="123" t="str">
         <f>B177</f>
         <v>L1-3 P.</v>
       </c>
-      <c r="AO177" s="124">
+      <c r="AS177" s="124">
         <f>C177</f>
         <v>0.9</v>
       </c>
-      <c r="AP177" s="125">
+      <c r="AT177" s="125">
         <f>D177+Y177</f>
         <v>0.612119014840409</v>
       </c>
-      <c r="AQ177" s="119"/>
-      <c r="AR177" s="123"/>
-      <c r="AS177" s="124"/>
-      <c r="AT177" s="125">
+      <c r="AV177" s="123"/>
+      <c r="AW177" s="124"/>
+      <c r="AX177" s="125">
         <f>H177+AC177</f>
         <v>0.0</v>
       </c>
-      <c r="AU177" s="119"/>
-      <c r="AV177" s="123" t="str">
+      <c r="AZ177" s="123" t="str">
         <f>J177</f>
         <v>VA-1 sup.</v>
       </c>
-      <c r="AW177" s="124">
+      <c r="BA177" s="124">
         <f>K177</f>
         <v>0.585315</v>
       </c>
-      <c r="AX177" s="125">
+      <c r="BB177" s="125">
         <f>L177+AG177</f>
         <v>-0.0284351143786757</v>
       </c>
-      <c r="AZ177" s="123" t="str">
+      <c r="BD177" s="123" t="str">
         <f>N177</f>
+        <v>VB-1 sup.</v>
+      </c>
+      <c r="BE177" s="124">
+        <f>O177</f>
+        <v>0.585315</v>
+      </c>
+      <c r="BF177" s="125">
+        <f>P177+AK177</f>
+        <v>-0.0284351143786757</v>
+      </c>
+      <c r="BH177" s="123" t="str">
+        <f>R177</f>
         <v>LT-4</v>
       </c>
-      <c r="BA177" s="124">
-        <f>O177</f>
+      <c r="BI177" s="124">
+        <f>S177</f>
         <v>1.5</v>
       </c>
-      <c r="BB177" s="125">
-        <f>P177+AK177</f>
+      <c r="BJ177" s="125">
+        <f>T177+AO177</f>
         <v>-0.0728713112905248</v>
       </c>
     </row>
@@ -18043,17 +17972,14 @@
         <v>1.2</v>
       </c>
       <c r="D178" s="125">
-        <f t="shared" si="12"/>
+        <f>$E$71*C178/100</f>
         <v>0.466376392259359</v>
       </c>
-      <c r="E178" s="119"/>
       <c r="F178" s="123"/>
       <c r="G178" s="124"/>
       <c r="H178" s="125">
-        <f t="shared" si="13"/>
-        <v>0.0</v>
-      </c>
-      <c r="I178" s="119"/>
+        <v>0</v>
+      </c>
       <c r="J178" s="123" t="s">
         <v>220</v>
       </c>
@@ -18061,17 +17987,27 @@
         <v>0.37781999999999999</v>
       </c>
       <c r="L178" s="125">
-        <f t="shared" si="14"/>
+        <f>$E$73*K178/100</f>
         <v>-0.128483781215002</v>
       </c>
       <c r="N178" s="123" t="s">
+        <v>221</v>
+      </c>
+      <c r="O178" s="124">
+        <v>0.37781999999999999</v>
+      </c>
+      <c r="P178" s="125">
+        <f>$E$73*O178/100</f>
+        <v>-0.128483781215002</v>
+      </c>
+      <c r="R178" s="123" t="s">
         <v>235</v>
       </c>
-      <c r="O178" s="124">
+      <c r="S178" s="124">
         <v>0.75</v>
       </c>
-      <c r="P178" s="125">
-        <f t="shared" si="16"/>
+      <c r="T178" s="125">
+        <f>$E$74*S178/100</f>
         <v>-0.255049589516837</v>
       </c>
       <c r="W178" s="123" t="str">
@@ -18086,14 +18022,12 @@
         <f>-$I$97*C178/100</f>
         <v>0.349782294194519</v>
       </c>
-      <c r="Z178" s="119"/>
       <c r="AA178" s="123"/>
       <c r="AB178" s="124"/>
       <c r="AC178" s="125">
         <f>-$I$97*G178/100</f>
         <v>0.0</v>
       </c>
-      <c r="AD178" s="119"/>
       <c r="AE178" s="123" t="str">
         <f>J178</f>
         <v>VA-2 sup.</v>
@@ -18108,58 +18042,80 @@
       </c>
       <c r="AI178" s="123" t="str">
         <f>N178</f>
-        <v>LT-5</v>
+        <v>VB-2 sup.</v>
       </c>
       <c r="AJ178" s="124">
         <f>O178</f>
-        <v>0.75</v>
+        <v>0.37782</v>
       </c>
       <c r="AK178" s="125">
         <f>-$I$97*O178/100</f>
+        <v>0.110128955327144</v>
+      </c>
+      <c r="AM178" s="123" t="str">
+        <f>R178</f>
+        <v>LT-5</v>
+      </c>
+      <c r="AN178" s="124">
+        <f>S178</f>
+        <v>0.75</v>
+      </c>
+      <c r="AO178" s="125">
+        <f>-$I$97*S178/100</f>
         <v>0.218613933871575</v>
       </c>
-      <c r="AN178" s="123" t="str">
+      <c r="AR178" s="123" t="str">
         <f>B178</f>
         <v>L1-4</v>
       </c>
-      <c r="AO178" s="124">
+      <c r="AS178" s="124">
         <f>C178</f>
         <v>1.2</v>
       </c>
-      <c r="AP178" s="125">
+      <c r="AT178" s="125">
         <f>D178+Y178</f>
         <v>0.816158686453878</v>
       </c>
-      <c r="AQ178" s="119"/>
-      <c r="AR178" s="123"/>
-      <c r="AS178" s="124"/>
-      <c r="AT178" s="125">
+      <c r="AV178" s="123"/>
+      <c r="AW178" s="124"/>
+      <c r="AX178" s="125">
         <f>H178+AC178</f>
         <v>0.0</v>
       </c>
-      <c r="AU178" s="119"/>
-      <c r="AV178" s="123" t="str">
+      <c r="AZ178" s="123" t="str">
         <f>J178</f>
         <v>VA-2 sup.</v>
       </c>
-      <c r="AW178" s="124">
+      <c r="BA178" s="124">
         <f>K178</f>
         <v>0.37782</v>
       </c>
-      <c r="AX178" s="125">
+      <c r="BB178" s="125">
         <f>L178+AG178</f>
         <v>-0.0183548258878574</v>
       </c>
-      <c r="AZ178" s="123" t="str">
+      <c r="BD178" s="123" t="str">
         <f>N178</f>
+        <v>VB-2 sup.</v>
+      </c>
+      <c r="BE178" s="124">
+        <f>O178</f>
+        <v>0.37782</v>
+      </c>
+      <c r="BF178" s="125">
+        <f>P178+AK178</f>
+        <v>-0.0183548258878574</v>
+      </c>
+      <c r="BH178" s="123" t="str">
+        <f>R178</f>
         <v>LT-5</v>
       </c>
-      <c r="BA178" s="124">
-        <f>O178</f>
+      <c r="BI178" s="124">
+        <f>S178</f>
         <v>0.75</v>
       </c>
-      <c r="BB178" s="125">
-        <f>P178+AK178</f>
+      <c r="BJ178" s="125">
+        <f>T178+AO178</f>
         <v>-0.0364356556452624</v>
       </c>
     </row>
@@ -18171,31 +18127,22 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="D179" s="125">
-        <f t="shared" si="12"/>
+        <f>$E$71*C179/100</f>
         <v>0.446944042581886</v>
       </c>
-      <c r="E179" s="119"/>
       <c r="F179" s="123"/>
       <c r="G179" s="124"/>
       <c r="H179" s="125">
-        <f t="shared" si="13"/>
-        <v>0.0</v>
-      </c>
-      <c r="I179" s="119"/>
-      <c r="J179" s="123"/>
-      <c r="K179" s="124"/>
-      <c r="L179" s="125">
-        <f t="shared" si="14"/>
-        <v>0.0</v>
-      </c>
-      <c r="N179" s="123" t="s">
+        <v>0</v>
+      </c>
+      <c r="R179" s="123" t="s">
         <v>238</v>
       </c>
-      <c r="O179" s="124">
+      <c r="S179" s="124">
         <v>1.5</v>
       </c>
-      <c r="P179" s="125">
-        <f t="shared" si="16"/>
+      <c r="T179" s="125">
+        <f>$E$74*S179/100</f>
         <v>-0.510099179033674</v>
       </c>
       <c r="W179" s="123" t="str">
@@ -18210,68 +18157,52 @@
         <f>-$I$97*C179/100</f>
         <v>0.335208031936414</v>
       </c>
-      <c r="Z179" s="119"/>
       <c r="AA179" s="123"/>
       <c r="AB179" s="124"/>
       <c r="AC179" s="125">
         <f>-$I$97*G179/100</f>
         <v>0.0</v>
       </c>
-      <c r="AD179" s="119"/>
-      <c r="AE179" s="123"/>
-      <c r="AF179" s="124"/>
-      <c r="AG179" s="125">
-        <f>-$I$97*K179/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AI179" s="123" t="str">
-        <f>N179</f>
+      <c r="AM179" s="123" t="str">
+        <f>R179</f>
         <v>LT-6</v>
       </c>
-      <c r="AJ179" s="124">
-        <f>O179</f>
+      <c r="AN179" s="124">
+        <f>S179</f>
         <v>1.5</v>
       </c>
-      <c r="AK179" s="125">
-        <f>-$I$97*O179/100</f>
+      <c r="AO179" s="125">
+        <f>-$I$97*S179/100</f>
         <v>0.437227867743149</v>
       </c>
-      <c r="AN179" s="123" t="str">
+      <c r="AR179" s="123" t="str">
         <f>B179</f>
         <v>L1-5</v>
       </c>
-      <c r="AO179" s="124">
+      <c r="AS179" s="124">
         <f>C179</f>
         <v>1.15</v>
       </c>
-      <c r="AP179" s="125">
+      <c r="AT179" s="125">
         <f>D179+Y179</f>
         <v>0.7821520745183</v>
       </c>
-      <c r="AQ179" s="119"/>
-      <c r="AR179" s="123"/>
-      <c r="AS179" s="124"/>
-      <c r="AT179" s="125">
-        <f>H179+AC179</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU179" s="119"/>
       <c r="AV179" s="123"/>
       <c r="AW179" s="124"/>
       <c r="AX179" s="125">
-        <f>L179+AG179</f>
+        <f>H179+AC179</f>
         <v>0.0</v>
       </c>
-      <c r="AZ179" s="123" t="str">
-        <f>N179</f>
+      <c r="BH179" s="123" t="str">
+        <f>R179</f>
         <v>LT-6</v>
       </c>
-      <c r="BA179" s="124">
-        <f>O179</f>
+      <c r="BI179" s="124">
+        <f>S179</f>
         <v>1.5</v>
       </c>
-      <c r="BB179" s="125">
-        <f>P179+AK179</f>
+      <c r="BJ179" s="125">
+        <f>T179+AO179</f>
         <v>-0.0728713112905248</v>
       </c>
     </row>
@@ -18286,22 +18217,14 @@
         <f>$E$71*C180/100</f>
         <v>0.466376392259359</v>
       </c>
-      <c r="E180" s="119"/>
-      <c r="F180" s="119"/>
-      <c r="G180" s="119"/>
-      <c r="H180" s="119"/>
-      <c r="I180" s="119"/>
-      <c r="J180" s="123"/>
-      <c r="K180" s="123"/>
-      <c r="L180" s="125"/>
-      <c r="N180" s="123" t="s">
+      <c r="R180" s="123" t="s">
         <v>241</v>
       </c>
-      <c r="O180" s="124">
+      <c r="S180" s="124">
         <v>1.5</v>
       </c>
-      <c r="P180" s="125">
-        <f t="shared" si="16"/>
+      <c r="T180" s="125">
+        <f>$E$74*S180/100</f>
         <v>-0.510099179033674</v>
       </c>
       <c r="W180" s="123" t="str">
@@ -18316,68 +18239,40 @@
         <f>-$I$97*C180/100</f>
         <v>0.349782294194519</v>
       </c>
-      <c r="Z180" s="119"/>
-      <c r="AA180" s="119"/>
-      <c r="AB180" s="119"/>
-      <c r="AC180" s="119">
-        <f>-$I$97*G180/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD180" s="119"/>
-      <c r="AE180" s="123"/>
-      <c r="AF180" s="123"/>
-      <c r="AG180" s="125">
-        <f>-$I$97*K180/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AI180" s="123" t="str">
-        <f>N180</f>
+      <c r="AM180" s="123" t="str">
+        <f>R180</f>
         <v>VM-2</v>
       </c>
-      <c r="AJ180" s="124">
-        <f>O180</f>
+      <c r="AN180" s="124">
+        <f>S180</f>
         <v>1.5</v>
       </c>
-      <c r="AK180" s="125">
-        <f>-$I$97*O180/100</f>
+      <c r="AO180" s="125">
+        <f>-$I$97*S180/100</f>
         <v>0.437227867743149</v>
       </c>
-      <c r="AN180" s="123" t="str">
+      <c r="AR180" s="123" t="str">
         <f>B180</f>
         <v>L1-6 lat.</v>
       </c>
-      <c r="AO180" s="124">
+      <c r="AS180" s="124">
         <f>C180</f>
         <v>1.2</v>
       </c>
-      <c r="AP180" s="125">
+      <c r="AT180" s="125">
         <f>D180+Y180</f>
         <v>0.816158686453878</v>
       </c>
-      <c r="AQ180" s="119"/>
-      <c r="AR180" s="119"/>
-      <c r="AS180" s="119"/>
-      <c r="AT180" s="119">
-        <f>H180+AC180</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU180" s="119"/>
-      <c r="AV180" s="123"/>
-      <c r="AW180" s="123"/>
-      <c r="AX180" s="125">
-        <f>L180+AG180</f>
-        <v>0.0</v>
-      </c>
-      <c r="AZ180" s="123" t="str">
-        <f>N180</f>
+      <c r="BH180" s="123" t="str">
+        <f>R180</f>
         <v>VM-2</v>
       </c>
-      <c r="BA180" s="124">
-        <f>O180</f>
+      <c r="BI180" s="124">
+        <f>S180</f>
         <v>1.5</v>
       </c>
-      <c r="BB180" s="125">
-        <f>P180+AK180</f>
+      <c r="BJ180" s="125">
+        <f>T180+AO180</f>
         <v>-0.0728713112905248</v>
       </c>
     </row>
@@ -18392,25 +18287,14 @@
         <f>$E$71*C181/100</f>
         <v>0.252620545807153</v>
       </c>
-      <c r="E181" s="119"/>
-      <c r="F181" s="119"/>
-      <c r="G181" s="119"/>
-      <c r="H181" s="119"/>
-      <c r="I181" s="119"/>
-      <c r="J181" s="123"/>
-      <c r="K181" s="124"/>
-      <c r="L181" s="125">
-        <f t="shared" si="14"/>
-        <v>0.0</v>
-      </c>
-      <c r="N181" s="123" t="s">
+      <c r="R181" s="123" t="s">
         <v>233</v>
       </c>
-      <c r="O181" s="124">
+      <c r="S181" s="124">
         <v>1.5</v>
       </c>
-      <c r="P181" s="125">
-        <f t="shared" si="16"/>
+      <c r="T181" s="125">
+        <f>$E$74*S181/100</f>
         <v>-0.510099179033674</v>
       </c>
       <c r="W181" s="123" t="str">
@@ -18425,68 +18309,40 @@
         <f>-$I$97*C181/100</f>
         <v>0.189465409355365</v>
       </c>
-      <c r="Z181" s="119"/>
-      <c r="AA181" s="119"/>
-      <c r="AB181" s="119"/>
-      <c r="AC181" s="119">
-        <f>-$I$97*G181/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD181" s="119"/>
-      <c r="AE181" s="123"/>
-      <c r="AF181" s="124"/>
-      <c r="AG181" s="125">
-        <f>-$I$97*K181/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AI181" s="123" t="str">
-        <f>N181</f>
+      <c r="AM181" s="123" t="str">
+        <f>R181</f>
         <v>LT-7</v>
       </c>
-      <c r="AJ181" s="124">
-        <f>O181</f>
+      <c r="AN181" s="124">
+        <f>S181</f>
         <v>1.5</v>
       </c>
-      <c r="AK181" s="125">
-        <f>-$I$97*O181/100</f>
+      <c r="AO181" s="125">
+        <f>-$I$97*S181/100</f>
         <v>0.437227867743149</v>
       </c>
-      <c r="AN181" s="123" t="str">
+      <c r="AR181" s="123" t="str">
         <f>B181</f>
         <v>L1-6 cen.</v>
       </c>
-      <c r="AO181" s="124">
+      <c r="AS181" s="124">
         <f>C181</f>
         <v>0.65</v>
       </c>
-      <c r="AP181" s="125">
+      <c r="AT181" s="125">
         <f>D181+Y181</f>
         <v>0.442085955162518</v>
       </c>
-      <c r="AQ181" s="119"/>
-      <c r="AR181" s="119"/>
-      <c r="AS181" s="119"/>
-      <c r="AT181" s="119">
-        <f>H181+AC181</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU181" s="119"/>
-      <c r="AV181" s="123"/>
-      <c r="AW181" s="124"/>
-      <c r="AX181" s="125">
-        <f>L181+AG181</f>
-        <v>0.0</v>
-      </c>
-      <c r="AZ181" s="123" t="str">
-        <f>N181</f>
+      <c r="BH181" s="123" t="str">
+        <f>R181</f>
         <v>LT-7</v>
       </c>
-      <c r="BA181" s="124">
-        <f>O181</f>
+      <c r="BI181" s="124">
+        <f>S181</f>
         <v>1.5</v>
       </c>
-      <c r="BB181" s="125">
-        <f>P181+AK181</f>
+      <c r="BJ181" s="125">
+        <f>T181+AO181</f>
         <v>-0.0728713112905248</v>
       </c>
     </row>
@@ -18501,25 +18357,14 @@
         <f>$E$71*C182/100</f>
         <v>0.485808741936832</v>
       </c>
-      <c r="E182" s="119"/>
-      <c r="F182" s="119"/>
-      <c r="G182" s="119"/>
-      <c r="H182" s="119"/>
-      <c r="I182" s="119"/>
-      <c r="J182" s="123"/>
-      <c r="K182" s="124"/>
-      <c r="L182" s="125">
-        <f t="shared" si="14"/>
-        <v>0.0</v>
-      </c>
-      <c r="N182" s="123" t="s">
+      <c r="R182" s="123" t="s">
         <v>236</v>
       </c>
-      <c r="O182" s="124">
+      <c r="S182" s="124">
         <v>1.5</v>
       </c>
-      <c r="P182" s="125">
-        <f t="shared" si="16"/>
+      <c r="T182" s="125">
+        <f>$E$74*S182/100</f>
         <v>-0.510099179033674</v>
       </c>
       <c r="W182" s="123" t="str">
@@ -18534,68 +18379,40 @@
         <f>-$I$97*C182/100</f>
         <v>0.364356556452624</v>
       </c>
-      <c r="Z182" s="119"/>
-      <c r="AA182" s="119"/>
-      <c r="AB182" s="119"/>
-      <c r="AC182" s="119">
-        <f>-$I$97*G182/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD182" s="119"/>
-      <c r="AE182" s="123"/>
-      <c r="AF182" s="124"/>
-      <c r="AG182" s="125">
-        <f>-$I$97*K182/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AI182" s="123" t="str">
-        <f>N182</f>
+      <c r="AM182" s="123" t="str">
+        <f>R182</f>
         <v>LT-8</v>
       </c>
-      <c r="AJ182" s="124">
-        <f>O182</f>
+      <c r="AN182" s="124">
+        <f>S182</f>
         <v>1.5</v>
       </c>
-      <c r="AK182" s="125">
-        <f>-$I$97*O182/100</f>
+      <c r="AO182" s="125">
+        <f>-$I$97*S182/100</f>
         <v>0.437227867743149</v>
       </c>
-      <c r="AN182" s="123" t="str">
+      <c r="AR182" s="123" t="str">
         <f>B182</f>
         <v>L1-7</v>
       </c>
-      <c r="AO182" s="124">
+      <c r="AS182" s="124">
         <f>C182</f>
         <v>1.25</v>
       </c>
-      <c r="AP182" s="125">
+      <c r="AT182" s="125">
         <f>D182+Y182</f>
         <v>0.850165298389457</v>
       </c>
-      <c r="AQ182" s="119"/>
-      <c r="AR182" s="119"/>
-      <c r="AS182" s="119"/>
-      <c r="AT182" s="119">
-        <f>H182+AC182</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU182" s="119"/>
-      <c r="AV182" s="123"/>
-      <c r="AW182" s="124"/>
-      <c r="AX182" s="125">
-        <f>L182+AG182</f>
-        <v>0.0</v>
-      </c>
-      <c r="AZ182" s="123" t="str">
-        <f>N182</f>
+      <c r="BH182" s="123" t="str">
+        <f>R182</f>
         <v>LT-8</v>
       </c>
-      <c r="BA182" s="124">
-        <f>O182</f>
+      <c r="BI182" s="124">
+        <f>S182</f>
         <v>1.5</v>
       </c>
-      <c r="BB182" s="125">
-        <f>P182+AK182</f>
+      <c r="BJ182" s="125">
+        <f>T182+AO182</f>
         <v>-0.0728713112905248</v>
       </c>
     </row>
@@ -18610,25 +18427,14 @@
         <f>$E$71*C183/100</f>
         <v>0.511070796517548</v>
       </c>
-      <c r="E183" s="119"/>
-      <c r="F183" s="119"/>
-      <c r="G183" s="119"/>
-      <c r="H183" s="119"/>
-      <c r="I183" s="119"/>
-      <c r="J183" s="123"/>
-      <c r="K183" s="124"/>
-      <c r="L183" s="125">
-        <f t="shared" si="14"/>
-        <v>0.0</v>
-      </c>
-      <c r="N183" s="123" t="s">
+      <c r="R183" s="123" t="s">
         <v>239</v>
       </c>
-      <c r="O183" s="124">
+      <c r="S183" s="124">
         <v>1.5</v>
       </c>
-      <c r="P183" s="125">
-        <f t="shared" si="16"/>
+      <c r="T183" s="125">
+        <f>$E$74*S183/100</f>
         <v>-0.510099179033674</v>
       </c>
       <c r="W183" s="123" t="str">
@@ -18643,68 +18449,40 @@
         <f>-$I$97*C183/100</f>
         <v>0.383303097388161</v>
       </c>
-      <c r="Z183" s="119"/>
-      <c r="AA183" s="119"/>
-      <c r="AB183" s="119"/>
-      <c r="AC183" s="119">
-        <f>-$I$97*G183/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD183" s="119"/>
-      <c r="AE183" s="123"/>
-      <c r="AF183" s="124"/>
-      <c r="AG183" s="125">
-        <f>-$I$97*K183/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AI183" s="123" t="str">
-        <f>N183</f>
+      <c r="AM183" s="123" t="str">
+        <f>R183</f>
         <v>LT-9</v>
       </c>
-      <c r="AJ183" s="124">
-        <f>O183</f>
+      <c r="AN183" s="124">
+        <f>S183</f>
         <v>1.5</v>
       </c>
-      <c r="AK183" s="125">
-        <f>-$I$97*O183/100</f>
+      <c r="AO183" s="125">
+        <f>-$I$97*S183/100</f>
         <v>0.437227867743149</v>
       </c>
-      <c r="AN183" s="123" t="str">
+      <c r="AR183" s="123" t="str">
         <f>B183</f>
         <v>L1-8</v>
       </c>
-      <c r="AO183" s="124">
+      <c r="AS183" s="124">
         <f>C183</f>
         <v>1.315</v>
       </c>
-      <c r="AP183" s="125">
+      <c r="AT183" s="125">
         <f>D183+Y183</f>
         <v>0.894373893905708</v>
       </c>
-      <c r="AQ183" s="119"/>
-      <c r="AR183" s="119"/>
-      <c r="AS183" s="119"/>
-      <c r="AT183" s="119">
-        <f>H183+AC183</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU183" s="119"/>
-      <c r="AV183" s="123"/>
-      <c r="AW183" s="124"/>
-      <c r="AX183" s="125">
-        <f>L183+AG183</f>
-        <v>0.0</v>
-      </c>
-      <c r="AZ183" s="123" t="str">
-        <f>N183</f>
+      <c r="BH183" s="123" t="str">
+        <f>R183</f>
         <v>LT-9</v>
       </c>
-      <c r="BA183" s="124">
-        <f>O183</f>
+      <c r="BI183" s="124">
+        <f>S183</f>
         <v>1.5</v>
       </c>
-      <c r="BB183" s="125">
-        <f>P183+AK183</f>
+      <c r="BJ183" s="125">
+        <f>T183+AO183</f>
         <v>-0.0728713112905248</v>
       </c>
     </row>
@@ -18719,25 +18497,14 @@
         <f>$E$71*C184/100</f>
         <v>0.277882600387868</v>
       </c>
-      <c r="E184" s="119"/>
-      <c r="F184" s="119"/>
-      <c r="G184" s="119"/>
-      <c r="H184" s="119"/>
-      <c r="I184" s="119"/>
-      <c r="J184" s="123"/>
-      <c r="K184" s="124"/>
-      <c r="L184" s="125">
-        <f t="shared" si="14"/>
-        <v>0.0</v>
-      </c>
-      <c r="N184" s="123" t="s">
+      <c r="R184" s="123" t="s">
         <v>242</v>
       </c>
-      <c r="O184" s="124">
+      <c r="S184" s="124">
         <v>0.75</v>
       </c>
-      <c r="P184" s="125">
-        <f t="shared" si="16"/>
+      <c r="T184" s="125">
+        <f>$E$74*S184/100</f>
         <v>-0.255049589516837</v>
       </c>
       <c r="W184" s="123" t="str">
@@ -18752,202 +18519,50 @@
         <f>-$I$97*C184/100</f>
         <v>0.208411950290901</v>
       </c>
-      <c r="Z184" s="119"/>
-      <c r="AA184" s="119"/>
-      <c r="AB184" s="119"/>
-      <c r="AC184" s="119">
-        <f>-$I$97*G184/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AD184" s="119"/>
-      <c r="AE184" s="123"/>
-      <c r="AF184" s="124"/>
-      <c r="AG184" s="125">
-        <f>-$I$97*K184/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AI184" s="123" t="str">
-        <f>N184</f>
+      <c r="AM184" s="123" t="str">
+        <f>R184</f>
         <v>VM-3</v>
       </c>
-      <c r="AJ184" s="124">
-        <f>O184</f>
+      <c r="AN184" s="124">
+        <f>S184</f>
         <v>0.75</v>
       </c>
-      <c r="AK184" s="125">
-        <f>-$I$97*O184/100</f>
+      <c r="AO184" s="125">
+        <f>-$I$97*S184/100</f>
         <v>0.218613933871575</v>
       </c>
-      <c r="AN184" s="123" t="str">
+      <c r="AR184" s="123" t="str">
         <f>B184</f>
         <v>VM-1 sup.</v>
       </c>
-      <c r="AO184" s="124">
+      <c r="AS184" s="124">
         <f>C184</f>
         <v>0.715</v>
       </c>
-      <c r="AP184" s="125">
+      <c r="AT184" s="125">
         <f>D184+Y184</f>
         <v>0.486294550678769</v>
       </c>
-      <c r="AQ184" s="119"/>
-      <c r="AR184" s="119"/>
-      <c r="AS184" s="119"/>
-      <c r="AT184" s="119">
-        <f>H184+AC184</f>
-        <v>0.0</v>
-      </c>
-      <c r="AU184" s="119"/>
-      <c r="AV184" s="123"/>
-      <c r="AW184" s="124"/>
-      <c r="AX184" s="125">
-        <f>L184+AG184</f>
-        <v>0.0</v>
-      </c>
-      <c r="AZ184" s="123" t="str">
-        <f>N184</f>
+      <c r="BH184" s="123" t="str">
+        <f>R184</f>
         <v>VM-3</v>
       </c>
-      <c r="BA184" s="124">
-        <f>O184</f>
+      <c r="BI184" s="124">
+        <f>S184</f>
         <v>0.75</v>
       </c>
-      <c r="BB184" s="125">
-        <f>P184+AK184</f>
+      <c r="BJ184" s="125">
+        <f>T184+AO184</f>
         <v>-0.0364356556452624</v>
       </c>
     </row>
-    <row r="185" x14ac:dyDescent="0.3">
-      <c r="J185" s="18"/>
-      <c r="K185" s="79"/>
-      <c r="L185" s="70">
-        <f t="shared" si="14"/>
-        <v>0.0</v>
-      </c>
-      <c r="AE185" s="18"/>
-      <c r="AF185" s="79"/>
-      <c r="AG185" s="70">
-        <f>-$I$97*K185/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV185" s="18"/>
-      <c r="AW185" s="79"/>
-      <c r="AX185" s="70">
-        <f>L185+AG185</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="186" x14ac:dyDescent="0.3">
-      <c r="J186" s="18"/>
-      <c r="K186" s="79"/>
-      <c r="L186" s="70">
-        <f t="shared" si="14"/>
-        <v>0.0</v>
-      </c>
-      <c r="AE186" s="18"/>
-      <c r="AF186" s="79"/>
-      <c r="AG186" s="70">
-        <f>-$I$97*K186/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV186" s="18"/>
-      <c r="AW186" s="79"/>
-      <c r="AX186" s="70">
-        <f>L186+AG186</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="187" x14ac:dyDescent="0.3">
-      <c r="J187" s="18"/>
-      <c r="K187" s="79"/>
-      <c r="L187" s="70">
-        <f t="shared" si="14"/>
-        <v>0.0</v>
-      </c>
-      <c r="AE187" s="18"/>
-      <c r="AF187" s="79"/>
-      <c r="AG187" s="70">
-        <f>-$I$97*K187/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV187" s="18"/>
-      <c r="AW187" s="79"/>
-      <c r="AX187" s="70">
-        <f>L187+AG187</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="188" x14ac:dyDescent="0.3">
-      <c r="J188" s="18"/>
-      <c r="K188" s="79"/>
-      <c r="L188" s="70">
-        <f t="shared" si="14"/>
-        <v>0.0</v>
-      </c>
-      <c r="AE188" s="18"/>
-      <c r="AF188" s="79"/>
-      <c r="AG188" s="70">
-        <f>-$I$97*K188/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV188" s="18"/>
-      <c r="AW188" s="79"/>
-      <c r="AX188" s="70">
-        <f>L188+AG188</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="189" x14ac:dyDescent="0.3">
-      <c r="J189" s="18"/>
-      <c r="K189" s="79"/>
-      <c r="L189" s="70">
-        <f t="shared" si="14"/>
-        <v>0.0</v>
-      </c>
-      <c r="AE189" s="18"/>
-      <c r="AF189" s="79"/>
-      <c r="AG189" s="70">
-        <f>-$I$97*K189/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV189" s="18"/>
-      <c r="AW189" s="79"/>
-      <c r="AX189" s="70">
-        <f>L189+AG189</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="190" x14ac:dyDescent="0.3">
-      <c r="F190" s="78"/>
-      <c r="J190" s="18"/>
-      <c r="K190" s="79"/>
-      <c r="L190" s="70">
-        <f t="shared" si="14"/>
-        <v>0.0</v>
-      </c>
-      <c r="AA190" s="78"/>
-      <c r="AE190" s="18"/>
-      <c r="AF190" s="79"/>
-      <c r="AG190" s="70">
-        <f>-$I$97*K190/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AR190" s="78"/>
-      <c r="AV190" s="18"/>
-      <c r="AW190" s="79"/>
-      <c r="AX190" s="70">
-        <f>L190+AG190</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="196" x14ac:dyDescent="0.3">
-      <c r="E196" s="119"/>
-      <c r="I196" s="119"/>
-      <c r="Z196" s="119"/>
-      <c r="AD196" s="119"/>
-      <c r="AQ196" s="119"/>
-      <c r="AU196" s="119"/>
-    </row>
+    <row r="185" x14ac:dyDescent="0.3"/>
+    <row r="186" x14ac:dyDescent="0.3"/>
+    <row r="187" x14ac:dyDescent="0.3"/>
+    <row r="188" x14ac:dyDescent="0.3"/>
+    <row r="189" x14ac:dyDescent="0.3"/>
+    <row r="190" x14ac:dyDescent="0.3"/>
+    <row r="196" x14ac:dyDescent="0.3"/>
     <row r="199" x14ac:dyDescent="0.3">
       <c r="B199" s="81" t="s">
         <v>251</v>
@@ -18991,15 +18606,15 @@
       <c r="AJ199" s="82"/>
       <c r="AK199" s="82"/>
       <c r="AL199" s="82"/>
-      <c r="AN199" s="81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIENTO EN DIRECCION -Z — TOTAL (Cpe + Cpi)</t>
-        </is>
-      </c>
+      <c r="AM199" s="82"/>
+      <c r="AN199" s="82"/>
       <c r="AO199" s="82"/>
       <c r="AP199" s="82"/>
-      <c r="AQ199" s="82"/>
-      <c r="AR199" s="82"/>
+      <c r="AR199" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIENTO EN DIRECCION -Z — TOTAL (Cpe + Cpi)</t>
+        </is>
+      </c>
       <c r="AS199" s="82"/>
       <c r="AT199" s="82"/>
       <c r="AU199" s="82"/>
@@ -19011,6 +18626,14 @@
       <c r="BA199" s="82"/>
       <c r="BB199" s="82"/>
       <c r="BC199" s="82"/>
+      <c r="BD199" s="82"/>
+      <c r="BE199" s="82"/>
+      <c r="BF199" s="82"/>
+      <c r="BG199" s="82"/>
+      <c r="BH199" s="82"/>
+      <c r="BI199" s="82"/>
+      <c r="BJ199" s="82"/>
+      <c r="BK199" s="82"/>
     </row>
     <row r="201" x14ac:dyDescent="0.3">
       <c r="B201" s="78" t="s">
@@ -19019,10 +18642,17 @@
       <c r="F201" s="78" t="s">
         <v>252</v>
       </c>
-      <c r="J201" s="78" t="s">
-        <v>249</v>
-      </c>
-      <c r="N201" s="78" t="s">
+      <c r="J201" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MURO A LATERAL:</t>
+        </is>
+      </c>
+      <c r="N201" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MURO B LATERAL:</t>
+        </is>
+      </c>
+      <c r="R201" s="78" t="s">
         <v>229</v>
       </c>
       <c r="W201" s="78" t="str">
@@ -19035,69 +18665,113 @@
       </c>
       <c r="AE201" s="78" t="str">
         <f>J201</f>
-        <v>MUROS LATERALES A/B:</v>
+        <v>MURO A LATERAL:</v>
       </c>
       <c r="AI201" s="78" t="str">
         <f>N201</f>
+        <v>MURO B LATERAL:</v>
+      </c>
+      <c r="AM201" s="78" t="str">
+        <f>R201</f>
         <v>CUBIERTA — LARGUEROS Y VIGAS DE MARCO</v>
       </c>
-      <c r="AN201" s="78" t="str">
+      <c r="AR201" s="78" t="str">
         <f>B201</f>
         <v>EJE 3 ABIERTO:</v>
       </c>
-      <c r="AR201" s="78" t="str">
+      <c r="AV201" s="78" t="str">
         <f>F201</f>
         <v>MURO 1 EN SOTAVENTO:</v>
       </c>
-      <c r="AV201" s="78" t="str">
+      <c r="AZ201" s="78" t="str">
         <f>J201</f>
-        <v>MUROS LATERALES A/B:</v>
-      </c>
-      <c r="AZ201" s="78" t="str">
+        <v>MURO A LATERAL:</v>
+      </c>
+      <c r="BD201" s="78" t="str">
         <f>N201</f>
+        <v>MURO B LATERAL:</v>
+      </c>
+      <c r="BH201" s="78" t="str">
+        <f>R201</f>
         <v>CUBIERTA — LARGUEROS Y VIGAS DE MARCO</v>
       </c>
     </row>
     <row r="203" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B203" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="C203" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="D203" s="77" t="s">
-        <v>204</v>
-      </c>
-      <c r="E203" s="119"/>
-      <c r="F203" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="G203" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="H203" s="77" t="s">
-        <v>204</v>
-      </c>
-      <c r="I203" s="119"/>
-      <c r="J203" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="K203" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="L203" s="77" t="s">
-        <v>204</v>
-      </c>
-      <c r="N203" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="O203" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="P203" s="77" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q203" s="119"/>
+      <c r="B203" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="C203" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="D203" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd (kg/cm)</t>
+        </is>
+      </c>
+      <c r="F203" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="G203" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="H203" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd (kg/cm)</t>
+        </is>
+      </c>
+      <c r="J203" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="K203" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="L203" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd (kg/cm)</t>
+        </is>
+      </c>
+      <c r="N203" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="O203" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="P203" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd (kg/cm)</t>
+        </is>
+      </c>
+      <c r="R203" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="S203" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="T203" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd normal</t>
+        </is>
+      </c>
       <c r="W203" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
@@ -19113,7 +18787,6 @@
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="Z203" s="119"/>
       <c r="AA203" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
@@ -19129,7 +18802,6 @@
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="AD203" s="119"/>
       <c r="AE203" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
@@ -19160,70 +18832,96 @@
           <t xml:space="preserve">Pd interna (kg/cm)</t>
         </is>
       </c>
-      <c r="AL203" s="119"/>
-      <c r="AN203" s="122" t="inlineStr">
+      <c r="AM203" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
+      <c r="AN203" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
       <c r="AO203" s="77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pd interna (kg/cm)</t>
+        </is>
+      </c>
+      <c r="AR203" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="AS203" s="77" t="inlineStr">
+        <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="AP203" s="77" t="inlineStr">
+      <c r="AT203" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
-      <c r="AQ203" s="119"/>
-      <c r="AR203" s="122" t="inlineStr">
+      <c r="AV203" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="AS203" s="77" t="inlineStr">
+      <c r="AW203" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="AT203" s="77" t="inlineStr">
+      <c r="AX203" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
-      <c r="AU203" s="119"/>
-      <c r="AV203" s="122" t="inlineStr">
+      <c r="AZ203" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="AW203" s="77" t="inlineStr">
+      <c r="BA203" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="AX203" s="77" t="inlineStr">
+      <c r="BB203" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
-      <c r="AZ203" s="122" t="inlineStr">
+      <c r="BD203" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">Elemento</t>
         </is>
       </c>
-      <c r="BA203" s="77" t="inlineStr">
+      <c r="BE203" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Franja trib. (m)</t>
         </is>
       </c>
-      <c r="BB203" s="77" t="inlineStr">
+      <c r="BF203" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Pd total (kg/cm)</t>
         </is>
       </c>
-      <c r="BC203" s="119"/>
+      <c r="BH203" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elemento</t>
+        </is>
+      </c>
+      <c r="BI203" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Franja trib. (m)</t>
+        </is>
+      </c>
+      <c r="BJ203" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pd total (kg/cm)</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B204" s="123" t="s">
@@ -19233,7 +18931,6 @@
       <c r="D204" s="125">
         <v>0</v>
       </c>
-      <c r="E204" s="119"/>
       <c r="F204" s="123" t="s">
         <v>207</v>
       </c>
@@ -19244,7 +18941,6 @@
         <f>$E$72*G204/100</f>
         <v>-0.218613933871575</v>
       </c>
-      <c r="I204" s="119"/>
       <c r="J204" s="123" t="s">
         <v>205</v>
       </c>
@@ -19256,16 +18952,25 @@
         <v>-0.306059507420204</v>
       </c>
       <c r="N204" s="123" t="s">
+        <v>206</v>
+      </c>
+      <c r="O204" s="124">
+        <v>0.9</v>
+      </c>
+      <c r="P204" s="125">
+        <f>$E$73*O204/100</f>
+        <v>-0.306059507420204</v>
+      </c>
+      <c r="R204" s="123" t="s">
         <v>231</v>
       </c>
-      <c r="O204" s="124">
+      <c r="S204" s="124">
         <v>0.5</v>
       </c>
-      <c r="P204" s="125">
-        <f>$E$74*O204/100</f>
+      <c r="T204" s="125">
+        <f>$E$74*S204/100</f>
         <v>-0.170033059677891</v>
       </c>
-      <c r="Q204" s="119"/>
       <c r="W204" s="123" t="str">
         <f>B204</f>
         <v>SIN CERRAMIENTO</v>
@@ -19275,7 +18980,6 @@
         <f>-$I$98*C204/100</f>
         <v>0.0</v>
       </c>
-      <c r="Z204" s="119"/>
       <c r="AA204" s="123" t="str">
         <f>F204</f>
         <v>L1-1</v>
@@ -19288,7 +18992,6 @@
         <f>-$I$98*G204/100</f>
         <v>-0.327920900807362</v>
       </c>
-      <c r="AD204" s="119"/>
       <c r="AE204" s="123" t="str">
         <f>J204</f>
         <v>LA-1</v>
@@ -19303,74 +19006,92 @@
       </c>
       <c r="AI204" s="123" t="str">
         <f>N204</f>
-        <v>VM-1</v>
+        <v>LB-1</v>
       </c>
       <c r="AJ204" s="124">
         <f>O204</f>
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="AK204" s="125">
         <f>-$I$98*O204/100</f>
+        <v>-0.327920900807362</v>
+      </c>
+      <c r="AM204" s="123" t="str">
+        <f>R204</f>
+        <v>VM-1</v>
+      </c>
+      <c r="AN204" s="124">
+        <f>S204</f>
+        <v>0.5</v>
+      </c>
+      <c r="AO204" s="125">
+        <f>-$I$98*S204/100</f>
         <v>-0.182178278226312</v>
       </c>
-      <c r="AL204" s="119"/>
-      <c r="AN204" s="123" t="str">
+      <c r="AR204" s="123" t="str">
         <f>B204</f>
         <v>SIN CERRAMIENTO</v>
       </c>
-      <c r="AO204" s="124"/>
-      <c r="AP204" s="125">
+      <c r="AS204" s="124"/>
+      <c r="AT204" s="125">
         <f>D204+Y204</f>
         <v>0.0</v>
       </c>
-      <c r="AQ204" s="119"/>
-      <c r="AR204" s="123" t="str">
+      <c r="AV204" s="123" t="str">
         <f>F204</f>
         <v>L1-1</v>
       </c>
-      <c r="AS204" s="124">
+      <c r="AW204" s="124">
         <f>G204</f>
         <v>0.9</v>
       </c>
-      <c r="AT204" s="125">
+      <c r="AX204" s="125">
         <f>H204+AC204</f>
         <v>-0.546534834678937</v>
       </c>
-      <c r="AU204" s="119"/>
-      <c r="AV204" s="123" t="str">
+      <c r="AZ204" s="123" t="str">
         <f>J204</f>
         <v>LA-1</v>
       </c>
-      <c r="AW204" s="124">
+      <c r="BA204" s="124">
         <f>K204</f>
         <v>0.9</v>
       </c>
-      <c r="AX204" s="125">
+      <c r="BB204" s="125">
         <f>L204+AG204</f>
         <v>-0.633980408227566</v>
       </c>
-      <c r="AZ204" s="123" t="str">
+      <c r="BD204" s="123" t="str">
         <f>N204</f>
+        <v>LB-1</v>
+      </c>
+      <c r="BE204" s="124">
+        <f>O204</f>
+        <v>0.9</v>
+      </c>
+      <c r="BF204" s="125">
+        <f>P204+AK204</f>
+        <v>-0.633980408227566</v>
+      </c>
+      <c r="BH204" s="123" t="str">
+        <f>R204</f>
         <v>VM-1</v>
       </c>
-      <c r="BA204" s="124">
-        <f>O204</f>
+      <c r="BI204" s="124">
+        <f>S204</f>
         <v>0.5</v>
       </c>
-      <c r="BB204" s="125">
-        <f>P204+AK204</f>
+      <c r="BJ204" s="125">
+        <f>T204+AO204</f>
         <v>-0.352211337904203</v>
       </c>
-      <c r="BC204" s="119"/>
     </row>
     <row r="205" x14ac:dyDescent="0.3">
       <c r="B205" s="123"/>
       <c r="C205" s="124"/>
       <c r="D205" s="125">
-        <f t="shared" ref="D205:D210" si="17">$E$71*C205/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="E205" s="119"/>
+        <v>0</v>
+      </c>
       <c r="F205" s="123" t="s">
         <v>210</v>
       </c>
@@ -19378,10 +19099,9 @@
         <v>1.2</v>
       </c>
       <c r="H205" s="125">
-        <f t="shared" ref="H205:H210" si="18">$E$72*G205/100</f>
+        <f>$E$72*G205/100</f>
         <v>-0.291485245162099</v>
       </c>
-      <c r="I205" s="119"/>
       <c r="J205" s="123" t="s">
         <v>208</v>
       </c>
@@ -19389,27 +19109,35 @@
         <v>1.2</v>
       </c>
       <c r="L205" s="125">
-        <f t="shared" ref="L205:L221" si="19">$E$73*K205/100</f>
+        <f>$E$73*K205/100</f>
         <v>-0.408079343226939</v>
       </c>
       <c r="N205" s="123" t="s">
+        <v>209</v>
+      </c>
+      <c r="O205" s="124">
+        <v>1.2</v>
+      </c>
+      <c r="P205" s="125">
+        <f>$E$73*O205/100</f>
+        <v>-0.408079343226939</v>
+      </c>
+      <c r="R205" s="123" t="s">
         <v>234</v>
       </c>
-      <c r="O205" s="124">
+      <c r="S205" s="124">
         <v>1.25</v>
       </c>
-      <c r="P205" s="125">
-        <f t="shared" ref="P205:P206" si="20">$E$74*O205/100</f>
+      <c r="T205" s="125">
+        <f>$E$74*S205/100</f>
         <v>-0.425082649194728</v>
       </c>
-      <c r="Q205" s="119"/>
       <c r="W205" s="123"/>
       <c r="X205" s="124"/>
       <c r="Y205" s="125">
         <f>-$I$98*C205/100</f>
         <v>0.0</v>
       </c>
-      <c r="Z205" s="119"/>
       <c r="AA205" s="123" t="str">
         <f>F205</f>
         <v>L1-2</v>
@@ -19422,7 +19150,6 @@
         <f>-$I$98*G205/100</f>
         <v>-0.437227867743149</v>
       </c>
-      <c r="AD205" s="119"/>
       <c r="AE205" s="123" t="str">
         <f>J205</f>
         <v>LA-2 a 7</v>
@@ -19437,71 +19164,89 @@
       </c>
       <c r="AI205" s="123" t="str">
         <f>N205</f>
-        <v>LT-1</v>
+        <v>LB-2 a 7</v>
       </c>
       <c r="AJ205" s="124">
         <f>O205</f>
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK205" s="125">
         <f>-$I$98*O205/100</f>
+        <v>-0.437227867743149</v>
+      </c>
+      <c r="AM205" s="123" t="str">
+        <f>R205</f>
+        <v>LT-1</v>
+      </c>
+      <c r="AN205" s="124">
+        <f>S205</f>
+        <v>1.25</v>
+      </c>
+      <c r="AO205" s="125">
+        <f>-$I$98*S205/100</f>
         <v>-0.45544569556578</v>
       </c>
-      <c r="AL205" s="119"/>
-      <c r="AN205" s="123"/>
-      <c r="AO205" s="124"/>
-      <c r="AP205" s="125">
+      <c r="AR205" s="123"/>
+      <c r="AS205" s="124"/>
+      <c r="AT205" s="125">
         <f>D205+Y205</f>
         <v>0.0</v>
       </c>
-      <c r="AQ205" s="119"/>
-      <c r="AR205" s="123" t="str">
+      <c r="AV205" s="123" t="str">
         <f>F205</f>
         <v>L1-2</v>
       </c>
-      <c r="AS205" s="124">
+      <c r="AW205" s="124">
         <f>G205</f>
         <v>1.2</v>
       </c>
-      <c r="AT205" s="125">
+      <c r="AX205" s="125">
         <f>H205+AC205</f>
         <v>-0.728713112905249</v>
       </c>
-      <c r="AU205" s="119"/>
-      <c r="AV205" s="123" t="str">
+      <c r="AZ205" s="123" t="str">
         <f>J205</f>
         <v>LA-2 a 7</v>
       </c>
-      <c r="AW205" s="124">
+      <c r="BA205" s="124">
         <f>K205</f>
         <v>1.2</v>
       </c>
-      <c r="AX205" s="125">
+      <c r="BB205" s="125">
         <f>L205+AG205</f>
         <v>-0.845307210970088</v>
       </c>
-      <c r="AZ205" s="123" t="str">
+      <c r="BD205" s="123" t="str">
         <f>N205</f>
+        <v>LB-2 a 7</v>
+      </c>
+      <c r="BE205" s="124">
+        <f>O205</f>
+        <v>1.2</v>
+      </c>
+      <c r="BF205" s="125">
+        <f>P205+AK205</f>
+        <v>-0.845307210970088</v>
+      </c>
+      <c r="BH205" s="123" t="str">
+        <f>R205</f>
         <v>LT-1</v>
       </c>
-      <c r="BA205" s="124">
-        <f>O205</f>
+      <c r="BI205" s="124">
+        <f>S205</f>
         <v>1.25</v>
       </c>
-      <c r="BB205" s="125">
-        <f>P205+AK205</f>
+      <c r="BJ205" s="125">
+        <f>T205+AO205</f>
         <v>-0.880528344760509</v>
       </c>
-      <c r="BC205" s="119"/>
     </row>
     <row r="206" x14ac:dyDescent="0.3">
       <c r="B206" s="123"/>
       <c r="C206" s="124"/>
       <c r="D206" s="125">
-        <f t="shared" si="17"/>
-        <v>0.0</v>
-      </c>
-      <c r="E206" s="119"/>
+        <v>0</v>
+      </c>
       <c r="F206" s="123" t="s">
         <v>213</v>
       </c>
@@ -19509,10 +19254,9 @@
         <v>0.3</v>
       </c>
       <c r="H206" s="125">
-        <f t="shared" si="18"/>
+        <f>$E$72*G206/100</f>
         <v>-0.0728713112905249</v>
       </c>
-      <c r="I206" s="119"/>
       <c r="J206" s="123" t="s">
         <v>211</v>
       </c>
@@ -19520,27 +19264,35 @@
         <v>1.1853149999999999</v>
       </c>
       <c r="L206" s="125">
-        <f t="shared" si="19"/>
+        <f>$E$73*K206/100</f>
         <v>-0.403085472264199</v>
       </c>
       <c r="N206" s="123" t="s">
+        <v>212</v>
+      </c>
+      <c r="O206" s="124">
+        <v>1.1853149999999999</v>
+      </c>
+      <c r="P206" s="125">
+        <f>$E$73*O206/100</f>
+        <v>-0.403085472264199</v>
+      </c>
+      <c r="R206" s="123" t="s">
         <v>237</v>
       </c>
-      <c r="O206" s="124">
+      <c r="S206" s="124">
         <v>1.5</v>
       </c>
-      <c r="P206" s="125">
-        <f t="shared" si="20"/>
+      <c r="T206" s="125">
+        <f>$E$74*S206/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="Q206" s="119"/>
       <c r="W206" s="123"/>
       <c r="X206" s="124"/>
       <c r="Y206" s="125">
         <f>-$I$98*C206/100</f>
         <v>0.0</v>
       </c>
-      <c r="Z206" s="119"/>
       <c r="AA206" s="123" t="str">
         <f>F206</f>
         <v>Dintel P.</v>
@@ -19553,7 +19305,6 @@
         <f>-$I$98*G206/100</f>
         <v>-0.109306966935787</v>
       </c>
-      <c r="AD206" s="119"/>
       <c r="AE206" s="123" t="str">
         <f>J206</f>
         <v>LA-8 (1-2)</v>
@@ -19568,71 +19319,89 @@
       </c>
       <c r="AI206" s="123" t="str">
         <f>N206</f>
-        <v>LT-2</v>
+        <v>LB-8 (1-2)</v>
       </c>
       <c r="AJ206" s="124">
         <f>O206</f>
-        <v>1.5</v>
+        <v>1.185315</v>
       </c>
       <c r="AK206" s="125">
         <f>-$I$98*O206/100</f>
+        <v>-0.431877291711642</v>
+      </c>
+      <c r="AM206" s="123" t="str">
+        <f>R206</f>
+        <v>LT-2</v>
+      </c>
+      <c r="AN206" s="124">
+        <f>S206</f>
+        <v>1.5</v>
+      </c>
+      <c r="AO206" s="125">
+        <f>-$I$98*S206/100</f>
         <v>-0.546534834678937</v>
       </c>
-      <c r="AL206" s="119"/>
-      <c r="AN206" s="123"/>
-      <c r="AO206" s="124"/>
-      <c r="AP206" s="125">
+      <c r="AR206" s="123"/>
+      <c r="AS206" s="124"/>
+      <c r="AT206" s="125">
         <f>D206+Y206</f>
         <v>0.0</v>
       </c>
-      <c r="AQ206" s="119"/>
-      <c r="AR206" s="123" t="str">
+      <c r="AV206" s="123" t="str">
         <f>F206</f>
         <v>Dintel P.</v>
       </c>
-      <c r="AS206" s="124">
+      <c r="AW206" s="124">
         <f>G206</f>
         <v>0.3</v>
       </c>
-      <c r="AT206" s="125">
+      <c r="AX206" s="125">
         <f>H206+AC206</f>
         <v>-0.182178278226312</v>
       </c>
-      <c r="AU206" s="119"/>
-      <c r="AV206" s="123" t="str">
+      <c r="AZ206" s="123" t="str">
         <f>J206</f>
         <v>LA-8 (1-2)</v>
       </c>
-      <c r="AW206" s="124">
+      <c r="BA206" s="124">
         <f>K206</f>
         <v>1.185315</v>
       </c>
-      <c r="AX206" s="125">
+      <c r="BB206" s="125">
         <f>L206+AG206</f>
         <v>-0.834962763975842</v>
       </c>
-      <c r="AZ206" s="123" t="str">
+      <c r="BD206" s="123" t="str">
         <f>N206</f>
+        <v>LB-8 (1-2)</v>
+      </c>
+      <c r="BE206" s="124">
+        <f>O206</f>
+        <v>1.185315</v>
+      </c>
+      <c r="BF206" s="125">
+        <f>P206+AK206</f>
+        <v>-0.834962763975842</v>
+      </c>
+      <c r="BH206" s="123" t="str">
+        <f>R206</f>
         <v>LT-2</v>
       </c>
-      <c r="BA206" s="124">
-        <f>O206</f>
+      <c r="BI206" s="124">
+        <f>S206</f>
         <v>1.5</v>
       </c>
-      <c r="BB206" s="125">
-        <f>P206+AK206</f>
+      <c r="BJ206" s="125">
+        <f>T206+AO206</f>
         <v>-1.05663401371261</v>
       </c>
-      <c r="BC206" s="119"/>
     </row>
     <row r="207" x14ac:dyDescent="0.3">
       <c r="B207" s="123"/>
       <c r="C207" s="124"/>
       <c r="D207" s="125">
-        <f t="shared" si="17"/>
-        <v>0.0</v>
-      </c>
-      <c r="E207" s="119"/>
+        <v>0</v>
+      </c>
       <c r="F207" s="123" t="s">
         <v>216</v>
       </c>
@@ -19640,10 +19409,9 @@
         <v>1.2</v>
       </c>
       <c r="H207" s="125">
-        <f t="shared" si="18"/>
+        <f>$E$72*G207/100</f>
         <v>-0.291485245162099</v>
       </c>
-      <c r="I207" s="119"/>
       <c r="J207" s="123" t="s">
         <v>214</v>
       </c>
@@ -19651,27 +19419,35 @@
         <v>0.97782000000000002</v>
       </c>
       <c r="L207" s="125">
-        <f t="shared" si="19"/>
+        <f>$E$73*K207/100</f>
         <v>-0.332523452828471</v>
       </c>
       <c r="N207" s="123" t="s">
+        <v>215</v>
+      </c>
+      <c r="O207" s="124">
+        <v>0.97782000000000002</v>
+      </c>
+      <c r="P207" s="125">
+        <f>$E$73*O207/100</f>
+        <v>-0.332523452828471</v>
+      </c>
+      <c r="R207" s="123" t="s">
         <v>240</v>
       </c>
-      <c r="O207" s="124">
+      <c r="S207" s="124">
         <v>1.5</v>
       </c>
-      <c r="P207" s="125">
-        <f t="shared" ref="P207:P215" si="21">$E$74*O207/100</f>
+      <c r="T207" s="125">
+        <f>$E$74*S207/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="Q207" s="119"/>
       <c r="W207" s="123"/>
       <c r="X207" s="124"/>
       <c r="Y207" s="125">
         <f>-$I$98*C207/100</f>
         <v>0.0</v>
       </c>
-      <c r="Z207" s="119"/>
       <c r="AA207" s="123" t="str">
         <f>F207</f>
         <v>L1-3</v>
@@ -19684,7 +19460,6 @@
         <f>-$I$98*G207/100</f>
         <v>-0.437227867743149</v>
       </c>
-      <c r="AD207" s="119"/>
       <c r="AE207" s="123" t="str">
         <f>J207</f>
         <v>LA-8 (2-3)</v>
@@ -19699,71 +19474,89 @@
       </c>
       <c r="AI207" s="123" t="str">
         <f>N207</f>
-        <v>LT-3</v>
+        <v>LB-8 (2-3)</v>
       </c>
       <c r="AJ207" s="124">
         <f>O207</f>
-        <v>1.5</v>
+        <v>0.97782</v>
       </c>
       <c r="AK207" s="125">
         <f>-$I$98*O207/100</f>
+        <v>-0.356275128030505</v>
+      </c>
+      <c r="AM207" s="123" t="str">
+        <f>R207</f>
+        <v>LT-3</v>
+      </c>
+      <c r="AN207" s="124">
+        <f>S207</f>
+        <v>1.5</v>
+      </c>
+      <c r="AO207" s="125">
+        <f>-$I$98*S207/100</f>
         <v>-0.546534834678937</v>
       </c>
-      <c r="AL207" s="119"/>
-      <c r="AN207" s="123"/>
-      <c r="AO207" s="124"/>
-      <c r="AP207" s="125">
+      <c r="AR207" s="123"/>
+      <c r="AS207" s="124"/>
+      <c r="AT207" s="125">
         <f>D207+Y207</f>
         <v>0.0</v>
       </c>
-      <c r="AQ207" s="119"/>
-      <c r="AR207" s="123" t="str">
+      <c r="AV207" s="123" t="str">
         <f>F207</f>
         <v>L1-3</v>
       </c>
-      <c r="AS207" s="124">
+      <c r="AW207" s="124">
         <f>G207</f>
         <v>1.2</v>
       </c>
-      <c r="AT207" s="125">
+      <c r="AX207" s="125">
         <f>H207+AC207</f>
         <v>-0.728713112905249</v>
       </c>
-      <c r="AU207" s="119"/>
-      <c r="AV207" s="123" t="str">
+      <c r="AZ207" s="123" t="str">
         <f>J207</f>
         <v>LA-8 (2-3)</v>
       </c>
-      <c r="AW207" s="124">
+      <c r="BA207" s="124">
         <f>K207</f>
         <v>0.97782</v>
       </c>
-      <c r="AX207" s="125">
+      <c r="BB207" s="125">
         <f>L207+AG207</f>
         <v>-0.688798580858977</v>
       </c>
-      <c r="AZ207" s="123" t="str">
+      <c r="BD207" s="123" t="str">
         <f>N207</f>
+        <v>LB-8 (2-3)</v>
+      </c>
+      <c r="BE207" s="124">
+        <f>O207</f>
+        <v>0.97782</v>
+      </c>
+      <c r="BF207" s="125">
+        <f>P207+AK207</f>
+        <v>-0.688798580858977</v>
+      </c>
+      <c r="BH207" s="123" t="str">
+        <f>R207</f>
         <v>LT-3</v>
       </c>
-      <c r="BA207" s="124">
-        <f>O207</f>
+      <c r="BI207" s="124">
+        <f>S207</f>
         <v>1.5</v>
       </c>
-      <c r="BB207" s="125">
-        <f>P207+AK207</f>
+      <c r="BJ207" s="125">
+        <f>T207+AO207</f>
         <v>-1.05663401371261</v>
       </c>
-      <c r="BC207" s="119"/>
     </row>
     <row r="208" x14ac:dyDescent="0.3">
       <c r="B208" s="123"/>
       <c r="C208" s="124"/>
       <c r="D208" s="125">
-        <f t="shared" si="17"/>
-        <v>0.0</v>
-      </c>
-      <c r="E208" s="119"/>
+        <v>0</v>
+      </c>
       <c r="F208" s="123" t="s">
         <v>219</v>
       </c>
@@ -19771,10 +19564,9 @@
         <v>0.9</v>
       </c>
       <c r="H208" s="125">
-        <f t="shared" si="18"/>
+        <f>$E$72*G208/100</f>
         <v>-0.218613933871575</v>
       </c>
-      <c r="I208" s="119"/>
       <c r="J208" s="123" t="s">
         <v>217</v>
       </c>
@@ -19782,17 +19574,27 @@
         <v>0.58531500000000003</v>
       </c>
       <c r="L208" s="125">
-        <f t="shared" si="19"/>
+        <f>$E$73*K208/100</f>
         <v>-0.19904580065073</v>
       </c>
       <c r="N208" s="123" t="s">
+        <v>218</v>
+      </c>
+      <c r="O208" s="124">
+        <v>0.58531500000000003</v>
+      </c>
+      <c r="P208" s="125">
+        <f>$E$73*O208/100</f>
+        <v>-0.19904580065073</v>
+      </c>
+      <c r="R208" s="123" t="s">
         <v>232</v>
       </c>
-      <c r="O208" s="124">
+      <c r="S208" s="124">
         <v>1.5</v>
       </c>
-      <c r="P208" s="125">
-        <f t="shared" si="21"/>
+      <c r="T208" s="125">
+        <f>$E$74*S208/100</f>
         <v>-0.510099179033674</v>
       </c>
       <c r="W208" s="123"/>
@@ -19801,7 +19603,6 @@
         <f>-$I$98*C208/100</f>
         <v>0.0</v>
       </c>
-      <c r="Z208" s="119"/>
       <c r="AA208" s="123" t="str">
         <f>F208</f>
         <v>L1-3 P.</v>
@@ -19814,7 +19615,6 @@
         <f>-$I$98*G208/100</f>
         <v>-0.327920900807362</v>
       </c>
-      <c r="AD208" s="119"/>
       <c r="AE208" s="123" t="str">
         <f>J208</f>
         <v>VA-1 sup.</v>
@@ -19829,58 +19629,80 @@
       </c>
       <c r="AI208" s="123" t="str">
         <f>N208</f>
-        <v>LT-4</v>
+        <v>VB-1 sup.</v>
       </c>
       <c r="AJ208" s="124">
         <f>O208</f>
-        <v>1.5</v>
+        <v>0.585315</v>
       </c>
       <c r="AK208" s="125">
         <f>-$I$98*O208/100</f>
+        <v>-0.213263357840068</v>
+      </c>
+      <c r="AM208" s="123" t="str">
+        <f>R208</f>
+        <v>LT-4</v>
+      </c>
+      <c r="AN208" s="124">
+        <f>S208</f>
+        <v>1.5</v>
+      </c>
+      <c r="AO208" s="125">
+        <f>-$I$98*S208/100</f>
         <v>-0.546534834678937</v>
       </c>
-      <c r="AN208" s="123"/>
-      <c r="AO208" s="124"/>
-      <c r="AP208" s="125">
+      <c r="AR208" s="123"/>
+      <c r="AS208" s="124"/>
+      <c r="AT208" s="125">
         <f>D208+Y208</f>
         <v>0.0</v>
       </c>
-      <c r="AQ208" s="119"/>
-      <c r="AR208" s="123" t="str">
+      <c r="AV208" s="123" t="str">
         <f>F208</f>
         <v>L1-3 P.</v>
       </c>
-      <c r="AS208" s="124">
+      <c r="AW208" s="124">
         <f>G208</f>
         <v>0.9</v>
       </c>
-      <c r="AT208" s="125">
+      <c r="AX208" s="125">
         <f>H208+AC208</f>
         <v>-0.546534834678937</v>
       </c>
-      <c r="AU208" s="119"/>
-      <c r="AV208" s="123" t="str">
+      <c r="AZ208" s="123" t="str">
         <f>J208</f>
         <v>VA-1 sup.</v>
       </c>
-      <c r="AW208" s="124">
+      <c r="BA208" s="124">
         <f>K208</f>
         <v>0.585315</v>
       </c>
-      <c r="AX208" s="125">
+      <c r="BB208" s="125">
         <f>L208+AG208</f>
         <v>-0.412309158490798</v>
       </c>
-      <c r="AZ208" s="123" t="str">
+      <c r="BD208" s="123" t="str">
         <f>N208</f>
+        <v>VB-1 sup.</v>
+      </c>
+      <c r="BE208" s="124">
+        <f>O208</f>
+        <v>0.585315</v>
+      </c>
+      <c r="BF208" s="125">
+        <f>P208+AK208</f>
+        <v>-0.412309158490798</v>
+      </c>
+      <c r="BH208" s="123" t="str">
+        <f>R208</f>
         <v>LT-4</v>
       </c>
-      <c r="BA208" s="124">
-        <f>O208</f>
+      <c r="BI208" s="124">
+        <f>S208</f>
         <v>1.5</v>
       </c>
-      <c r="BB208" s="125">
-        <f>P208+AK208</f>
+      <c r="BJ208" s="125">
+        <f>T208+AO208</f>
         <v>-1.05663401371261</v>
       </c>
     </row>
@@ -19888,10 +19710,8 @@
       <c r="B209" s="123"/>
       <c r="C209" s="124"/>
       <c r="D209" s="125">
-        <f t="shared" si="17"/>
-        <v>0.0</v>
-      </c>
-      <c r="E209" s="119"/>
+        <v>0</v>
+      </c>
       <c r="F209" s="123" t="s">
         <v>222</v>
       </c>
@@ -19902,7 +19722,6 @@
         <f>$E$72*G209/100</f>
         <v>-0.291485245162099</v>
       </c>
-      <c r="I209" s="119"/>
       <c r="J209" s="123" t="s">
         <v>220</v>
       </c>
@@ -19910,17 +19729,27 @@
         <v>0.37781999999999999</v>
       </c>
       <c r="L209" s="125">
-        <f t="shared" si="19"/>
+        <f>$E$73*K209/100</f>
         <v>-0.128483781215002</v>
       </c>
       <c r="N209" s="123" t="s">
+        <v>221</v>
+      </c>
+      <c r="O209" s="124">
+        <v>0.37781999999999999</v>
+      </c>
+      <c r="P209" s="125">
+        <f>$E$73*O209/100</f>
+        <v>-0.128483781215002</v>
+      </c>
+      <c r="R209" s="123" t="s">
         <v>235</v>
       </c>
-      <c r="O209" s="124">
+      <c r="S209" s="124">
         <v>0.75</v>
       </c>
-      <c r="P209" s="125">
-        <f t="shared" si="21"/>
+      <c r="T209" s="125">
+        <f>$E$74*S209/100</f>
         <v>-0.255049589516837</v>
       </c>
       <c r="W209" s="123"/>
@@ -19929,7 +19758,6 @@
         <f>-$I$98*C209/100</f>
         <v>0.0</v>
       </c>
-      <c r="Z209" s="119"/>
       <c r="AA209" s="123" t="str">
         <f>F209</f>
         <v>L1-4</v>
@@ -19942,7 +19770,6 @@
         <f>-$I$98*G209/100</f>
         <v>-0.437227867743149</v>
       </c>
-      <c r="AD209" s="119"/>
       <c r="AE209" s="123" t="str">
         <f>J209</f>
         <v>VA-2 sup.</v>
@@ -19957,58 +19784,80 @@
       </c>
       <c r="AI209" s="123" t="str">
         <f>N209</f>
-        <v>LT-5</v>
+        <v>VB-2 sup.</v>
       </c>
       <c r="AJ209" s="124">
         <f>O209</f>
-        <v>0.75</v>
+        <v>0.37782</v>
       </c>
       <c r="AK209" s="125">
         <f>-$I$98*O209/100</f>
+        <v>-0.137661194158931</v>
+      </c>
+      <c r="AM209" s="123" t="str">
+        <f>R209</f>
+        <v>LT-5</v>
+      </c>
+      <c r="AN209" s="124">
+        <f>S209</f>
+        <v>0.75</v>
+      </c>
+      <c r="AO209" s="125">
+        <f>-$I$98*S209/100</f>
         <v>-0.273267417339468</v>
       </c>
-      <c r="AN209" s="123"/>
-      <c r="AO209" s="124"/>
-      <c r="AP209" s="125">
+      <c r="AR209" s="123"/>
+      <c r="AS209" s="124"/>
+      <c r="AT209" s="125">
         <f>D209+Y209</f>
         <v>0.0</v>
       </c>
-      <c r="AQ209" s="119"/>
-      <c r="AR209" s="123" t="str">
+      <c r="AV209" s="123" t="str">
         <f>F209</f>
         <v>L1-4</v>
       </c>
-      <c r="AS209" s="124">
+      <c r="AW209" s="124">
         <f>G209</f>
         <v>1.2</v>
       </c>
-      <c r="AT209" s="125">
+      <c r="AX209" s="125">
         <f>H209+AC209</f>
         <v>-0.728713112905249</v>
       </c>
-      <c r="AU209" s="119"/>
-      <c r="AV209" s="123" t="str">
+      <c r="AZ209" s="123" t="str">
         <f>J209</f>
         <v>VA-2 sup.</v>
       </c>
-      <c r="AW209" s="124">
+      <c r="BA209" s="124">
         <f>K209</f>
         <v>0.37782</v>
       </c>
-      <c r="AX209" s="125">
+      <c r="BB209" s="125">
         <f>L209+AG209</f>
         <v>-0.266144975373932</v>
       </c>
-      <c r="AZ209" s="123" t="str">
+      <c r="BD209" s="123" t="str">
         <f>N209</f>
+        <v>VB-2 sup.</v>
+      </c>
+      <c r="BE209" s="124">
+        <f>O209</f>
+        <v>0.37782</v>
+      </c>
+      <c r="BF209" s="125">
+        <f>P209+AK209</f>
+        <v>-0.266144975373932</v>
+      </c>
+      <c r="BH209" s="123" t="str">
+        <f>R209</f>
         <v>LT-5</v>
       </c>
-      <c r="BA209" s="124">
-        <f>O209</f>
+      <c r="BI209" s="124">
+        <f>S209</f>
         <v>0.75</v>
       </c>
-      <c r="BB209" s="125">
-        <f>P209+AK209</f>
+      <c r="BJ209" s="125">
+        <f>T209+AO209</f>
         <v>-0.528317006856305</v>
       </c>
     </row>
@@ -20016,10 +19865,8 @@
       <c r="B210" s="123"/>
       <c r="C210" s="124"/>
       <c r="D210" s="125">
-        <f t="shared" si="17"/>
-        <v>0.0</v>
-      </c>
-      <c r="E210" s="119"/>
+        <v>0</v>
+      </c>
       <c r="F210" s="123" t="s">
         <v>223</v>
       </c>
@@ -20027,24 +19874,17 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="H210" s="125">
-        <f t="shared" si="18"/>
+        <f>$E$72*G210/100</f>
         <v>-0.279340026613679</v>
       </c>
-      <c r="I210" s="119"/>
-      <c r="J210" s="123"/>
-      <c r="K210" s="124"/>
-      <c r="L210" s="125">
-        <f t="shared" si="19"/>
-        <v>0.0</v>
-      </c>
-      <c r="N210" s="123" t="s">
+      <c r="R210" s="123" t="s">
         <v>238</v>
       </c>
-      <c r="O210" s="124">
+      <c r="S210" s="124">
         <v>1.5</v>
       </c>
-      <c r="P210" s="125">
-        <f>$E$74*O210/100</f>
+      <c r="T210" s="125">
+        <f>$E$74*S210/100</f>
         <v>-0.510099179033674</v>
       </c>
       <c r="W210" s="123"/>
@@ -20053,7 +19893,6 @@
         <f>-$I$98*C210/100</f>
         <v>0.0</v>
       </c>
-      <c r="Z210" s="119"/>
       <c r="AA210" s="123" t="str">
         <f>F210</f>
         <v>L1-5</v>
@@ -20066,69 +19905,50 @@
         <f>-$I$98*G210/100</f>
         <v>-0.419010039920518</v>
       </c>
-      <c r="AD210" s="119"/>
-      <c r="AE210" s="123"/>
-      <c r="AF210" s="124"/>
-      <c r="AG210" s="125">
-        <f>-$I$98*K210/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AI210" s="123" t="str">
-        <f>N210</f>
+      <c r="AM210" s="123" t="str">
+        <f>R210</f>
         <v>LT-6</v>
       </c>
-      <c r="AJ210" s="124">
-        <f>O210</f>
+      <c r="AN210" s="124">
+        <f>S210</f>
         <v>1.5</v>
       </c>
-      <c r="AK210" s="125">
-        <f>-$I$98*O210/100</f>
+      <c r="AO210" s="125">
+        <f>-$I$98*S210/100</f>
         <v>-0.546534834678937</v>
       </c>
-      <c r="AN210" s="123"/>
-      <c r="AO210" s="124"/>
-      <c r="AP210" s="125">
+      <c r="AR210" s="123"/>
+      <c r="AS210" s="124"/>
+      <c r="AT210" s="125">
         <f>D210+Y210</f>
         <v>0.0</v>
       </c>
-      <c r="AQ210" s="119"/>
-      <c r="AR210" s="123" t="str">
+      <c r="AV210" s="123" t="str">
         <f>F210</f>
         <v>L1-5</v>
       </c>
-      <c r="AS210" s="124">
+      <c r="AW210" s="124">
         <f>G210</f>
         <v>1.15</v>
       </c>
-      <c r="AT210" s="125">
+      <c r="AX210" s="125">
         <f>H210+AC210</f>
         <v>-0.698350066534196</v>
       </c>
-      <c r="AU210" s="119"/>
-      <c r="AV210" s="123"/>
-      <c r="AW210" s="124"/>
-      <c r="AX210" s="125">
-        <f>L210+AG210</f>
-        <v>0.0</v>
-      </c>
-      <c r="AZ210" s="123" t="str">
-        <f>N210</f>
+      <c r="BH210" s="123" t="str">
+        <f>R210</f>
         <v>LT-6</v>
       </c>
-      <c r="BA210" s="124">
-        <f>O210</f>
+      <c r="BI210" s="124">
+        <f>S210</f>
         <v>1.5</v>
       </c>
-      <c r="BB210" s="125">
-        <f>P210+AK210</f>
+      <c r="BJ210" s="125">
+        <f>T210+AO210</f>
         <v>-1.05663401371261</v>
       </c>
     </row>
     <row r="211" x14ac:dyDescent="0.3">
-      <c r="B211" s="119"/>
-      <c r="C211" s="119"/>
-      <c r="D211" s="119"/>
-      <c r="E211" s="119"/>
       <c r="F211" s="123" t="s">
         <v>224</v>
       </c>
@@ -20139,27 +19959,16 @@
         <f>$E$72*G211/100</f>
         <v>-0.291485245162099</v>
       </c>
-      <c r="I211" s="119"/>
-      <c r="J211" s="123"/>
-      <c r="K211" s="123"/>
-      <c r="L211" s="125"/>
-      <c r="N211" s="123" t="s">
+      <c r="R211" s="123" t="s">
         <v>241</v>
       </c>
-      <c r="O211" s="124">
+      <c r="S211" s="124">
         <v>1.5</v>
       </c>
-      <c r="P211" s="125">
-        <f t="shared" si="21"/>
+      <c r="T211" s="125">
+        <f>$E$74*S211/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="W211" s="119"/>
-      <c r="X211" s="119"/>
-      <c r="Y211" s="119">
-        <f>-$I$98*C211/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z211" s="119"/>
       <c r="AA211" s="123" t="str">
         <f>F211</f>
         <v>L1-6 lat.</v>
@@ -20172,69 +19981,44 @@
         <f>-$I$98*G211/100</f>
         <v>-0.437227867743149</v>
       </c>
-      <c r="AD211" s="119"/>
-      <c r="AE211" s="123"/>
-      <c r="AF211" s="123"/>
-      <c r="AG211" s="125">
-        <f>-$I$98*K211/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AI211" s="123" t="str">
-        <f>N211</f>
+      <c r="AM211" s="123" t="str">
+        <f>R211</f>
         <v>VM-2</v>
       </c>
-      <c r="AJ211" s="124">
-        <f>O211</f>
+      <c r="AN211" s="124">
+        <f>S211</f>
         <v>1.5</v>
       </c>
-      <c r="AK211" s="125">
-        <f>-$I$98*O211/100</f>
+      <c r="AO211" s="125">
+        <f>-$I$98*S211/100</f>
         <v>-0.546534834678937</v>
       </c>
-      <c r="AN211" s="119"/>
-      <c r="AO211" s="119"/>
-      <c r="AP211" s="119">
-        <f>D211+Y211</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ211" s="119"/>
-      <c r="AR211" s="123" t="str">
+      <c r="AV211" s="123" t="str">
         <f>F211</f>
         <v>L1-6 lat.</v>
       </c>
-      <c r="AS211" s="124">
+      <c r="AW211" s="124">
         <f>G211</f>
         <v>1.2</v>
       </c>
-      <c r="AT211" s="125">
+      <c r="AX211" s="125">
         <f>H211+AC211</f>
         <v>-0.728713112905249</v>
       </c>
-      <c r="AU211" s="119"/>
-      <c r="AV211" s="123"/>
-      <c r="AW211" s="123"/>
-      <c r="AX211" s="125">
-        <f>L211+AG211</f>
-        <v>0.0</v>
-      </c>
-      <c r="AZ211" s="123" t="str">
-        <f>N211</f>
+      <c r="BH211" s="123" t="str">
+        <f>R211</f>
         <v>VM-2</v>
       </c>
-      <c r="BA211" s="124">
-        <f>O211</f>
+      <c r="BI211" s="124">
+        <f>S211</f>
         <v>1.5</v>
       </c>
-      <c r="BB211" s="125">
-        <f>P211+AK211</f>
+      <c r="BJ211" s="125">
+        <f>T211+AO211</f>
         <v>-1.05663401371261</v>
       </c>
     </row>
     <row r="212" x14ac:dyDescent="0.3">
-      <c r="B212" s="119"/>
-      <c r="C212" s="119"/>
-      <c r="D212" s="119"/>
-      <c r="E212" s="119"/>
       <c r="F212" s="123" t="s">
         <v>225</v>
       </c>
@@ -20245,30 +20029,16 @@
         <f>$E$72*G212/100</f>
         <v>-0.157887841129471</v>
       </c>
-      <c r="I212" s="119"/>
-      <c r="J212" s="123"/>
-      <c r="K212" s="124"/>
-      <c r="L212" s="125">
-        <f t="shared" si="19"/>
-        <v>0.0</v>
-      </c>
-      <c r="N212" s="123" t="s">
+      <c r="R212" s="123" t="s">
         <v>233</v>
       </c>
-      <c r="O212" s="124">
+      <c r="S212" s="124">
         <v>1.5</v>
       </c>
-      <c r="P212" s="125">
-        <f t="shared" si="21"/>
+      <c r="T212" s="125">
+        <f>$E$74*S212/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="W212" s="119"/>
-      <c r="X212" s="119"/>
-      <c r="Y212" s="119">
-        <f>-$I$98*C212/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z212" s="119"/>
       <c r="AA212" s="123" t="str">
         <f>F212</f>
         <v>L1-6 cen.</v>
@@ -20281,69 +20051,44 @@
         <f>-$I$98*G212/100</f>
         <v>-0.236831761694206</v>
       </c>
-      <c r="AD212" s="119"/>
-      <c r="AE212" s="123"/>
-      <c r="AF212" s="124"/>
-      <c r="AG212" s="125">
-        <f>-$I$98*K212/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AI212" s="123" t="str">
-        <f>N212</f>
+      <c r="AM212" s="123" t="str">
+        <f>R212</f>
         <v>LT-7</v>
       </c>
-      <c r="AJ212" s="124">
-        <f>O212</f>
+      <c r="AN212" s="124">
+        <f>S212</f>
         <v>1.5</v>
       </c>
-      <c r="AK212" s="125">
-        <f>-$I$98*O212/100</f>
+      <c r="AO212" s="125">
+        <f>-$I$98*S212/100</f>
         <v>-0.546534834678937</v>
       </c>
-      <c r="AN212" s="119"/>
-      <c r="AO212" s="119"/>
-      <c r="AP212" s="119">
-        <f>D212+Y212</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ212" s="119"/>
-      <c r="AR212" s="123" t="str">
+      <c r="AV212" s="123" t="str">
         <f>F212</f>
         <v>L1-6 cen.</v>
       </c>
-      <c r="AS212" s="124">
+      <c r="AW212" s="124">
         <f>G212</f>
         <v>0.65</v>
       </c>
-      <c r="AT212" s="125">
+      <c r="AX212" s="125">
         <f>H212+AC212</f>
         <v>-0.394719602823676</v>
       </c>
-      <c r="AU212" s="119"/>
-      <c r="AV212" s="123"/>
-      <c r="AW212" s="124"/>
-      <c r="AX212" s="125">
-        <f>L212+AG212</f>
-        <v>0.0</v>
-      </c>
-      <c r="AZ212" s="123" t="str">
-        <f>N212</f>
+      <c r="BH212" s="123" t="str">
+        <f>R212</f>
         <v>LT-7</v>
       </c>
-      <c r="BA212" s="124">
-        <f>O212</f>
+      <c r="BI212" s="124">
+        <f>S212</f>
         <v>1.5</v>
       </c>
-      <c r="BB212" s="125">
-        <f>P212+AK212</f>
+      <c r="BJ212" s="125">
+        <f>T212+AO212</f>
         <v>-1.05663401371261</v>
       </c>
     </row>
     <row r="213" x14ac:dyDescent="0.3">
-      <c r="B213" s="119"/>
-      <c r="C213" s="119"/>
-      <c r="D213" s="119"/>
-      <c r="E213" s="119"/>
       <c r="F213" s="123" t="s">
         <v>226</v>
       </c>
@@ -20354,30 +20099,16 @@
         <f>$E$72*G213/100</f>
         <v>-0.30363046371052</v>
       </c>
-      <c r="I213" s="119"/>
-      <c r="J213" s="123"/>
-      <c r="K213" s="124"/>
-      <c r="L213" s="125">
-        <f t="shared" si="19"/>
-        <v>0.0</v>
-      </c>
-      <c r="N213" s="123" t="s">
+      <c r="R213" s="123" t="s">
         <v>236</v>
       </c>
-      <c r="O213" s="124">
+      <c r="S213" s="124">
         <v>1.5</v>
       </c>
-      <c r="P213" s="125">
-        <f t="shared" si="21"/>
+      <c r="T213" s="125">
+        <f>$E$74*S213/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="W213" s="119"/>
-      <c r="X213" s="119"/>
-      <c r="Y213" s="119">
-        <f>-$I$98*C213/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z213" s="119"/>
       <c r="AA213" s="123" t="str">
         <f>F213</f>
         <v>L1-7</v>
@@ -20390,69 +20121,44 @@
         <f>-$I$98*G213/100</f>
         <v>-0.45544569556578</v>
       </c>
-      <c r="AD213" s="119"/>
-      <c r="AE213" s="123"/>
-      <c r="AF213" s="124"/>
-      <c r="AG213" s="125">
-        <f>-$I$98*K213/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AI213" s="123" t="str">
-        <f>N213</f>
+      <c r="AM213" s="123" t="str">
+        <f>R213</f>
         <v>LT-8</v>
       </c>
-      <c r="AJ213" s="124">
-        <f>O213</f>
+      <c r="AN213" s="124">
+        <f>S213</f>
         <v>1.5</v>
       </c>
-      <c r="AK213" s="125">
-        <f>-$I$98*O213/100</f>
+      <c r="AO213" s="125">
+        <f>-$I$98*S213/100</f>
         <v>-0.546534834678937</v>
       </c>
-      <c r="AN213" s="119"/>
-      <c r="AO213" s="119"/>
-      <c r="AP213" s="119">
-        <f>D213+Y213</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ213" s="119"/>
-      <c r="AR213" s="123" t="str">
+      <c r="AV213" s="123" t="str">
         <f>F213</f>
         <v>L1-7</v>
       </c>
-      <c r="AS213" s="124">
+      <c r="AW213" s="124">
         <f>G213</f>
         <v>1.25</v>
       </c>
-      <c r="AT213" s="125">
+      <c r="AX213" s="125">
         <f>H213+AC213</f>
         <v>-0.759076159276301</v>
       </c>
-      <c r="AU213" s="119"/>
-      <c r="AV213" s="123"/>
-      <c r="AW213" s="124"/>
-      <c r="AX213" s="125">
-        <f>L213+AG213</f>
-        <v>0.0</v>
-      </c>
-      <c r="AZ213" s="123" t="str">
-        <f>N213</f>
+      <c r="BH213" s="123" t="str">
+        <f>R213</f>
         <v>LT-8</v>
       </c>
-      <c r="BA213" s="124">
-        <f>O213</f>
+      <c r="BI213" s="124">
+        <f>S213</f>
         <v>1.5</v>
       </c>
-      <c r="BB213" s="125">
-        <f>P213+AK213</f>
+      <c r="BJ213" s="125">
+        <f>T213+AO213</f>
         <v>-1.05663401371261</v>
       </c>
     </row>
     <row r="214" x14ac:dyDescent="0.3">
-      <c r="B214" s="119"/>
-      <c r="C214" s="119"/>
-      <c r="D214" s="119"/>
-      <c r="E214" s="119"/>
       <c r="F214" s="123" t="s">
         <v>227</v>
       </c>
@@ -20463,30 +20169,16 @@
         <f>$E$72*G214/100</f>
         <v>-0.319419247823467</v>
       </c>
-      <c r="I214" s="119"/>
-      <c r="J214" s="123"/>
-      <c r="K214" s="124"/>
-      <c r="L214" s="125">
-        <f t="shared" si="19"/>
-        <v>0.0</v>
-      </c>
-      <c r="N214" s="123" t="s">
+      <c r="R214" s="123" t="s">
         <v>239</v>
       </c>
-      <c r="O214" s="124">
+      <c r="S214" s="124">
         <v>1.5</v>
       </c>
-      <c r="P214" s="125">
-        <f t="shared" si="21"/>
+      <c r="T214" s="125">
+        <f>$E$74*S214/100</f>
         <v>-0.510099179033674</v>
       </c>
-      <c r="W214" s="119"/>
-      <c r="X214" s="119"/>
-      <c r="Y214" s="119">
-        <f>-$I$98*C214/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z214" s="119"/>
       <c r="AA214" s="123" t="str">
         <f>F214</f>
         <v>L1-8</v>
@@ -20499,69 +20191,44 @@
         <f>-$I$98*G214/100</f>
         <v>-0.479128871735201</v>
       </c>
-      <c r="AD214" s="119"/>
-      <c r="AE214" s="123"/>
-      <c r="AF214" s="124"/>
-      <c r="AG214" s="125">
-        <f>-$I$98*K214/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AI214" s="123" t="str">
-        <f>N214</f>
+      <c r="AM214" s="123" t="str">
+        <f>R214</f>
         <v>LT-9</v>
       </c>
-      <c r="AJ214" s="124">
-        <f>O214</f>
+      <c r="AN214" s="124">
+        <f>S214</f>
         <v>1.5</v>
       </c>
-      <c r="AK214" s="125">
-        <f>-$I$98*O214/100</f>
+      <c r="AO214" s="125">
+        <f>-$I$98*S214/100</f>
         <v>-0.546534834678937</v>
       </c>
-      <c r="AN214" s="119"/>
-      <c r="AO214" s="119"/>
-      <c r="AP214" s="119">
-        <f>D214+Y214</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ214" s="119"/>
-      <c r="AR214" s="123" t="str">
+      <c r="AV214" s="123" t="str">
         <f>F214</f>
         <v>L1-8</v>
       </c>
-      <c r="AS214" s="124">
+      <c r="AW214" s="124">
         <f>G214</f>
         <v>1.315</v>
       </c>
-      <c r="AT214" s="125">
+      <c r="AX214" s="125">
         <f>H214+AC214</f>
         <v>-0.798548119558668</v>
       </c>
-      <c r="AU214" s="119"/>
-      <c r="AV214" s="123"/>
-      <c r="AW214" s="124"/>
-      <c r="AX214" s="125">
-        <f>L214+AG214</f>
-        <v>0.0</v>
-      </c>
-      <c r="AZ214" s="123" t="str">
-        <f>N214</f>
+      <c r="BH214" s="123" t="str">
+        <f>R214</f>
         <v>LT-9</v>
       </c>
-      <c r="BA214" s="124">
-        <f>O214</f>
+      <c r="BI214" s="124">
+        <f>S214</f>
         <v>1.5</v>
       </c>
-      <c r="BB214" s="125">
-        <f>P214+AK214</f>
+      <c r="BJ214" s="125">
+        <f>T214+AO214</f>
         <v>-1.05663401371261</v>
       </c>
     </row>
     <row r="215" x14ac:dyDescent="0.3">
-      <c r="B215" s="119"/>
-      <c r="C215" s="119"/>
-      <c r="D215" s="119"/>
-      <c r="E215" s="119"/>
       <c r="F215" s="123" t="s">
         <v>228</v>
       </c>
@@ -20572,30 +20239,16 @@
         <f>$E$72*G215/100</f>
         <v>-0.173676625242418</v>
       </c>
-      <c r="I215" s="119"/>
-      <c r="J215" s="123"/>
-      <c r="K215" s="124"/>
-      <c r="L215" s="125">
-        <f t="shared" si="19"/>
-        <v>0.0</v>
-      </c>
-      <c r="N215" s="123" t="s">
+      <c r="R215" s="123" t="s">
         <v>242</v>
       </c>
-      <c r="O215" s="124">
+      <c r="S215" s="124">
         <v>0.75</v>
       </c>
-      <c r="P215" s="125">
-        <f t="shared" si="21"/>
+      <c r="T215" s="125">
+        <f>$E$74*S215/100</f>
         <v>-0.255049589516837</v>
       </c>
-      <c r="W215" s="119"/>
-      <c r="X215" s="119"/>
-      <c r="Y215" s="119">
-        <f>-$I$98*C215/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="Z215" s="119"/>
       <c r="AA215" s="123" t="str">
         <f>F215</f>
         <v>VM-1 sup.</v>
@@ -20608,203 +20261,50 @@
         <f>-$I$98*G215/100</f>
         <v>-0.260514937863626</v>
       </c>
-      <c r="AD215" s="119"/>
-      <c r="AE215" s="123"/>
-      <c r="AF215" s="124"/>
-      <c r="AG215" s="125">
-        <f>-$I$98*K215/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AI215" s="123" t="str">
-        <f>N215</f>
+      <c r="AM215" s="123" t="str">
+        <f>R215</f>
         <v>VM-3</v>
       </c>
-      <c r="AJ215" s="124">
-        <f>O215</f>
+      <c r="AN215" s="124">
+        <f>S215</f>
         <v>0.75</v>
       </c>
-      <c r="AK215" s="125">
-        <f>-$I$98*O215/100</f>
+      <c r="AO215" s="125">
+        <f>-$I$98*S215/100</f>
         <v>-0.273267417339468</v>
       </c>
-      <c r="AN215" s="119"/>
-      <c r="AO215" s="119"/>
-      <c r="AP215" s="119">
-        <f>D215+Y215</f>
-        <v>0.0</v>
-      </c>
-      <c r="AQ215" s="119"/>
-      <c r="AR215" s="123" t="str">
+      <c r="AV215" s="123" t="str">
         <f>F215</f>
         <v>VM-1 sup.</v>
       </c>
-      <c r="AS215" s="124">
+      <c r="AW215" s="124">
         <f>G215</f>
         <v>0.715</v>
       </c>
-      <c r="AT215" s="125">
+      <c r="AX215" s="125">
         <f>H215+AC215</f>
         <v>-0.434191563106044</v>
       </c>
-      <c r="AU215" s="119"/>
-      <c r="AV215" s="123"/>
-      <c r="AW215" s="124"/>
-      <c r="AX215" s="125">
-        <f>L215+AG215</f>
-        <v>0.0</v>
-      </c>
-      <c r="AZ215" s="123" t="str">
-        <f>N215</f>
+      <c r="BH215" s="123" t="str">
+        <f>R215</f>
         <v>VM-3</v>
       </c>
-      <c r="BA215" s="124">
-        <f>O215</f>
+      <c r="BI215" s="124">
+        <f>S215</f>
         <v>0.75</v>
       </c>
-      <c r="BB215" s="125">
-        <f>P215+AK215</f>
+      <c r="BJ215" s="125">
+        <f>T215+AO215</f>
         <v>-0.528317006856305</v>
       </c>
     </row>
-    <row r="216" x14ac:dyDescent="0.3">
-      <c r="J216" s="18"/>
-      <c r="K216" s="79"/>
-      <c r="L216" s="70">
-        <f t="shared" si="19"/>
-        <v>0.0</v>
-      </c>
-      <c r="N216" s="123"/>
-      <c r="O216" s="124"/>
-      <c r="P216" s="125"/>
-      <c r="AE216" s="18"/>
-      <c r="AF216" s="79"/>
-      <c r="AG216" s="70">
-        <f>-$I$98*K216/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AI216" s="123"/>
-      <c r="AJ216" s="124"/>
-      <c r="AK216" s="125">
-        <f>-$I$98*O216/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV216" s="18"/>
-      <c r="AW216" s="79"/>
-      <c r="AX216" s="70">
-        <f>L216+AG216</f>
-        <v>0.0</v>
-      </c>
-      <c r="AZ216" s="123"/>
-      <c r="BA216" s="124"/>
-      <c r="BB216" s="125">
-        <f>P216+AK216</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="217" x14ac:dyDescent="0.3">
-      <c r="J217" s="18"/>
-      <c r="K217" s="79"/>
-      <c r="L217" s="70">
-        <f t="shared" si="19"/>
-        <v>0.0</v>
-      </c>
-      <c r="AE217" s="18"/>
-      <c r="AF217" s="79"/>
-      <c r="AG217" s="70">
-        <f>-$I$98*K217/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV217" s="18"/>
-      <c r="AW217" s="79"/>
-      <c r="AX217" s="70">
-        <f>L217+AG217</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="218" x14ac:dyDescent="0.3">
-      <c r="J218" s="18"/>
-      <c r="K218" s="79"/>
-      <c r="L218" s="70">
-        <f t="shared" si="19"/>
-        <v>0.0</v>
-      </c>
-      <c r="AE218" s="18"/>
-      <c r="AF218" s="79"/>
-      <c r="AG218" s="70">
-        <f>-$I$98*K218/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV218" s="18"/>
-      <c r="AW218" s="79"/>
-      <c r="AX218" s="70">
-        <f>L218+AG218</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="219" x14ac:dyDescent="0.3">
-      <c r="J219" s="18"/>
-      <c r="K219" s="79"/>
-      <c r="L219" s="70">
-        <f t="shared" si="19"/>
-        <v>0.0</v>
-      </c>
-      <c r="AE219" s="18"/>
-      <c r="AF219" s="79"/>
-      <c r="AG219" s="70">
-        <f>-$I$98*K219/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV219" s="18"/>
-      <c r="AW219" s="79"/>
-      <c r="AX219" s="70">
-        <f>L219+AG219</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="220" x14ac:dyDescent="0.3">
-      <c r="J220" s="18"/>
-      <c r="K220" s="79"/>
-      <c r="L220" s="70">
-        <f t="shared" si="19"/>
-        <v>0.0</v>
-      </c>
-      <c r="AE220" s="18"/>
-      <c r="AF220" s="79"/>
-      <c r="AG220" s="70">
-        <f>-$I$98*K220/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AV220" s="18"/>
-      <c r="AW220" s="79"/>
-      <c r="AX220" s="70">
-        <f>L220+AG220</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="221" x14ac:dyDescent="0.3">
-      <c r="F221" s="78"/>
-      <c r="J221" s="18"/>
-      <c r="K221" s="79"/>
-      <c r="L221" s="70">
-        <f t="shared" si="19"/>
-        <v>0.0</v>
-      </c>
-      <c r="AA221" s="78"/>
-      <c r="AE221" s="18"/>
-      <c r="AF221" s="79"/>
-      <c r="AG221" s="70">
-        <f>-$I$98*K221/100</f>
-        <v>0.0</v>
-      </c>
-      <c r="AR221" s="78"/>
-      <c r="AV221" s="18"/>
-      <c r="AW221" s="79"/>
-      <c r="AX221" s="70">
-        <f>L221+AG221</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="227" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="216" x14ac:dyDescent="0.3"/>
+    <row r="217" x14ac:dyDescent="0.3"/>
+    <row r="218" x14ac:dyDescent="0.3"/>
+    <row r="219" x14ac:dyDescent="0.3"/>
+    <row r="220" x14ac:dyDescent="0.3"/>
+    <row r="221" x14ac:dyDescent="0.3"/>
+    <row r="227" x14ac:dyDescent="0.3">
       <c r="I227" s="119"/>
     </row>
   </sheetData>
